--- a/nacte/nacte_data.xlsx
+++ b/nacte/nacte_data.xlsx
@@ -481,7 +481,9 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Holders of Certificate in Arts with Education or Certificate of Teachers</t>
+          <t>Holders of Certificate in Arts with Education or Certificate of Teachers
+AU
+Education Grade III A</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -516,13 +518,37 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Ordinary Diploma in Business Information</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
+          <t>Ordinary Diploma in Business Information Technology</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with
+AU
+at least four (4) passes in non-religious subjects including Basic
+AU
+Mathematics and English Language OR National Vocational Award
+AU
+(NVA) Level III or Trade Test Grade I with a Certificate of Secondary
+AU
+Education Examination (CSEE)
+AU
+Holders of Basic Technician Certificate (NTA Level 4) in Business
+AU
+Information Technology, Information Technology, Computer
+AU
+Sciences/Engineering OR Advanced Certificate of Secondary Education
+AU
+Examination (ACSEE) with at least one Principal pass and one
+AU
+Subsidiary in Principal subjects.</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 / 2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -552,13 +578,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Ordinary Diploma in Computing and Information</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
+          <t>Ordinary Diploma in Computing and Information Technology</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with
+AU
+at least four (4) passes in Non-religious subjects including passes in
+AU
+Basic Mathematics and English Language.
+AU
+Holders of Basic Technician Certificate (NTA Level 4) in Computing and
+AU
+Information Technology OR Advanced Certificate of Secondary
+AU
+Education (ACSEE) with at least one Principal pass and one Subsidiary in
+AU
+Principal subjects.</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 / 2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -591,10 +635,28 @@
           <t>Ordinary Diploma in Counselling and Psychology</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with
+AU
+At Least four (4) Passes in non-religious subjects or National Vocational
+AU
+Award (NVA) Level III with At Least two Passes in Certificate of
+AU
+Secondary Education Examination (CSEE).
+AU
+Holders of NTA 4 in Counseling Psychology and related fields or form VI
+AU
+with at least one Principal and a subsidiary pass excluding religious
+AU
+subjects.</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 / 2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -627,10 +689,28 @@
           <t>Ordinary Diploma in Office Administration</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with
+AU
+at least four (4) passes in non-religious subjects including English
+AU
+Language.
+AU
+Holders of Basic Technician Certificate (NTA Level 4) in Office
+AU
+Administration, Secretarial Studies OR Advanced Certificate of
+AU
+Secondary Education Examinations (ACSEE) with at least one Principal
+AU
+pass and one Subsidiary in Principal subjects.</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 / 2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -663,10 +743,24 @@
           <t>Ordinary Diploma in Science with Education</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with
+AU
+Minimum of Division III with at least two (2) passes in Science Subjects
+AU
+(Physics, Chemistry, Biology, Mathematics and Geography)
+AU
+CATHOLIC UNIVERSITY COLLEGE OF MBEYA (TCU/M.10/1.1) - FBO
+AU
+Mbeya City Council - Mbeya</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2 / Program Duration (Yrs)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -701,7 +795,13 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Holders of Basic Technician Certificate (NTA Level 4) in Accountancy,</t>
+          <t>Holders of Basic Technician Certificate (NTA Level 4) in Accountancy,
+AU
+Finance and Banking OR Advanced Certificate of Secondary Education
+AU
+Examination (ACSEE) with at least one Principal pass and one
+AU
+Subsidiary in Principal subjects.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -739,7 +839,19 @@
           <t>Diploma in Business Administration</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Basic Technician Certificate (NTA Level 4) in Business
+AU
+Administration, Finance and Banking, Marketing OR Advanced Certificate
+AU
+of Secondary Education Examination (ACSEE) with at least one Principal
+AU
+pass and one Subsidiary in Principal subjects.</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>2</t>
@@ -775,7 +887,19 @@
           <t>Diploma in Community Development</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Basic Technician Certificate (NTA Level 4 ) in Community
+AU
+Development, Social Work, Gender, Youth Work OR Advanced Certificate
+AU
+of Secondary Education Examination (ACSEE) with at least one Principal
+AU
+pass and one Subsidiary in Principal subjects.</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>2</t>
@@ -811,7 +935,19 @@
           <t>Diploma in Entrepreneurship Development</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Basic Technician Certificate (NTA Level 4) in
+AU
+Entrepreneurship Development OR Advanced Certificate of Secondary
+AU
+Education Examination (ACSEE) with at least one Principal pass and one
+AU
+Subsidiary in Principal subjects.</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>2</t>
@@ -847,7 +983,21 @@
           <t>Diploma in Human Resources Management</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Basic Technician certificate (NTA Level 4) in Human
+AU
+Resource, Local Government Administration, Social work, Community
+AU
+Development, Business Management OR Advanced Certificate of
+AU
+Secondary Education Examination (ACSEE) with at least one Principal pass
+AU
+and one Subsidiary in Principal subjects.</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2</t>
@@ -880,10 +1030,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Diploma in Information Communication Technology</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
+          <t>Diploma in Information Communication Technology Diploma in Law</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Basic Technician Certificate (NTA Level 4) in Computing and
+AU
+Information Technology OR Advanced Certificate of Secondary Education
+AU
+(ACSEE) with at least one Principal pass and one Subsidiary in Principal
+AU
+subjects</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2</t>
@@ -951,7 +1113,19 @@
           <t>Diploma in Library Studies, Records Management with Ict</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Basic Technician Certificate (NTA Level 4) in Records
+AU
+Management, Medical Records, Library and information studies OR
+AU
+Advanced Certificate of Secondary Education Examination (ACSEE) with
+AU
+at least one Principal pass and one Subsidiary in Principal subjects</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>2</t>
@@ -987,7 +1161,21 @@
           <t>Diploma in Marketing Management</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Basic Technician Certificate (NTA Level 4) in Marketing, Public
+AU
+Relation, Business Administration, Accounting and Finance,
+AU
+Economics OR Advanced Certificate of Secondary Education Examination
+AU
+(ACSEE) with at least one Principal pass and one
+AU
+Subsidiary in Principal subjects.</t>
+        </is>
+      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2</t>
@@ -1023,7 +1211,25 @@
           <t>Diploma in Procurement and Supply Chain Management</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Basic Technician Certificate (NTA Level 4) in Procurement and
+AU
+Supply, Logistics, Clearing and Forwarding, Purchasing and Inventory OR
+AU
+Advanced Certificate of Secondary Education Examination (ACSEE) with
+AU
+at least one Principal pass and one
+AU
+Subsidiary in Principal subjects.
+AU
+CATHOLIC UNIVERSITY OF HEALTH AND ALLIED SCIENCES (CUHAS) (CU) - FBO
+AU
+Nyamagana Municipal Council - Mwanza</t>
+        </is>
+      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>2</t>
@@ -1059,7 +1265,21 @@
           <t>Diploma in Diagnostic Radiography</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate in Diagnostic Radiology with passes in science
+AU
+subjects including passes in Biology, Chemistry and Physics in
+AU
+Certificate of Secondary Education Examination (CSEE)
+AU
+DAR ES SALAAM UNIVERSITY COLLEGE OF EDUCATION (DUCE) (U/SAT/42) - Government
+AU
+Temeke Municipal Council - Dar es Salaam</t>
+        </is>
+      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>2</t>
@@ -1095,10 +1315,32 @@
           <t>Ordinary Diploma in Educational Laboratory Science Technology</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with
+AU
+at least four (4) passes in Non-religious subjects including two passes in
+AU
+Physics, chemistry, biology, Geography and Mathematics
+AU
+Holders of Basic Technician Certificate in Educational laboratory and
+AU
+Technology OR Advanced Certificate of Secondary Education (ACSEE)
+AU
+with one principal pass and subsidiary pass in Physics, chemistry,
+AU
+Biology, Agriculture, and Geography
+AU
+HUBERT KAIRUKI MEMORIAL UNIVERSITY (HK) - Private
+AU
+Kinondoni Municipal Council - Dar es Salaam</t>
+        </is>
+      </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 / 2</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1131,10 +1373,28 @@
           <t>Ordinary Diploma in Social Work</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with
+AU
+at Least four (4) Passes in non-religious Subjects
+AU
+Holders of Basic Technician Certificate (NTA Level 4) in Social Work,
+AU
+Development Planning and Community Development, Gender,
+AU
+Community Health OR Advanced Certificate of Secondary Examination
+AU
+(ACSEE) with at least one Principal Pass and one Subsidiary in Principal
+AU
+subjects</t>
+        </is>
+      </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 / 2</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1167,7 +1427,17 @@
           <t>Diploma in Law</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate in Law OR Holders of Advanced Certificate of
+AU
+Secondary Education Examination (CSEE) with one Principal Pass and
+AU
+One Subsidiary in Principal subjects</t>
+        </is>
+      </c>
       <c r="F21" t="inlineStr">
         <is>
           <t>2</t>
@@ -1203,7 +1473,21 @@
           <t>Diploma in Psychology and Counseling</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with at
+AU
+least four (4) passes in non-religious subjects and Technician Certificate
+AU
+in Psychology and Counselling OR Advanced Certificate of Secondary
+AU
+Education Examination (ACSEE) with one Principal pass and one subsidiary
+AU
+in Principal subjects</t>
+        </is>
+      </c>
       <c r="F22" t="inlineStr">
         <is>
           <t>2</t>
@@ -1239,10 +1523,30 @@
           <t>Ordinary Diploma in Accountancy</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with
+AU
+at least four (4) passes in non-religious subjects OR National
+AU
+Vocational Award (NVA III) with a Certificate of Secondary Education
+AU
+Examination(CSEE)
+AU
+Holders of Basic Technician Certificate (NTA level 4) in Accounts,
+AU
+Banking and Finance OR Advanced Certificate in Secondary Education
+AU
+Examination (ACSEE) with at least one Principal pass and one
+AU
+Subsidiary in Principal subjects</t>
+        </is>
+      </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 / 2</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1275,10 +1579,30 @@
           <t>Ordinary Diploma in Business Administration</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with
+AU
+at least four (4) passes in non-religious subjects OR National
+AU
+Vocational Award (NVA III) with two passes in Certificate of Secondary
+AU
+Education Examination(CSEE)
+AU
+Holders of Basic Technician Certificate (NTA level 4) in Business and
+AU
+Business Administration OR Advanced Certificate in Secondary Education
+AU
+Examination (ACSEE) with at least one Principal pass and one Subsidiary
+AU
+in Principal subjects</t>
+        </is>
+      </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 / 2</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1311,10 +1635,30 @@
           <t>Ordinary Diploma in Business Administration and Tourism Management</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with
+AU
+at least four (4) passes in non-religious subjects OR National
+AU
+Vocational Award (NVA III) with a Certificate of Secondary Education
+AU
+Examination(CSEE)
+AU
+Holders of Basic Technician Certificate (NTA level 4) in Business
+AU
+Administration and Tourism Management OR Advanced Certificate in
+AU
+Secondary Education Examination (ACSEE) with at least one Principal
+AU
+pass and one Subsidiary in Principal subjects</t>
+        </is>
+      </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 / 2</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1347,10 +1691,34 @@
           <t>Ordinary Diploma in Community Development</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with
+AU
+at least four (4) passes in non-religious subjects OR National
+AU
+Vocational Award (NVA III) with a Certificate of Secondary Education
+AU
+Examination(CSEE)
+AU
+Holders of Basic Technician Certificate (NTA level 4) in Community
+AU
+Development,Business Administration,Social Protection,Social
+AU
+Work,Development Planning,Community Health,Local Goverment
+AU
+Administration,Youth Work OR Advanced Certificate in Secondary
+AU
+Education Examination (ACSEE) with at least one Principal pass and one
+AU
+Subsidiary in Principal subjects</t>
+        </is>
+      </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 / 2</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1383,10 +1751,28 @@
           <t>Ordinary Diploma in Computer Science</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with
+AU
+at least four (4) passes in non-religious subjects OR National
+AU
+Vocational Award (NVA) III/Trade Test II with a Certificate of
+AU
+Secondary Education Examination (CSEE).
+AU
+Holders of Basic Technician Certificate (NTA Level 4) in Computer
+AU
+Engineering OR Advanced Certificate Education Examination (ACSEE)
+AU
+with one Principal pass and one Subsidiary.</t>
+        </is>
+      </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 / 2</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1421,12 +1807,26 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Holders of Certificate of Secondary Education Examination (CSEE) with</t>
+          <t>Holders of Certificate of Secondary Education Examination (CSEE) with
+AU
+at least four (4) passes in non-religious subjects OR National
+AU
+Vocational Award (NVA III) with a Certificate of Secondary Education
+AU
+Examination (CSEE)
+AU
+Holders of Basic Technician Certificate (NTA level 4) in Education with
+AU
+Religious Studies, Theology OR Advanced Certificate in Secondary
+AU
+Education Examination (ACSEE) with one Principal pass and one
+AU
+Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 / 2</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1459,10 +1859,32 @@
           <t>Ordinary Diploma in Information and Communication Technology</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holder of Certificate of Secondary Education Examination (CSEE) with at
+AU
+least four (4) passes in non religious subjects OR National
+AU
+Vocational Award (NVA) III/Trade Test II with a Certificate of
+AU
+Secondary Education Examination (CSEE).
+AU
+Holders of Basic Technician Certificate (NTA Level 4) in Computer
+AU
+Science, Computing Information Communication Technology, Business
+AU
+Information Technology OR Holder of Advanced Certificate of
+AU
+Secondary Education Examination (ACSEE) with one Principal pass and
+AU
+one Subsidiary pass in Principal subjects.</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 / 2</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1495,10 +1917,28 @@
           <t>Ordinary Diploma in Law</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with
+AU
+at least four (4) passes in non-religious subjects OR National
+AU
+Vocational Award (NVA III) with a Certificate of Secondary Education
+AU
+Examination(CSEE)
+AU
+Holders of Basic Technician Certificate (NTA level 4) in Law OR
+AU
+Advanced Certificate in Secondary Education Examination (ACSEE) with
+AU
+at least one Principal pass and one Subsidiary pass in Principal subjects</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 / 2</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1531,10 +1971,30 @@
           <t>Ordinary Diploma in Library and Information Studies</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with
+AU
+at least four (4) passes in non-religious subjects OR National
+AU
+Vocational Award (NVA III) with a Certificate of Secondary Education
+AU
+Examination(CSEE)
+AU
+Holders of Basic Technician Certificate (NTA Level 4) in Library and
+AU
+Information Studies OR Advanced Certificate in Secondary Education
+AU
+Examination (ACSEE) with at least One Principal Pass and one
+AU
+Subsidiary in Principal subjects</t>
+        </is>
+      </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 / 2</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1567,10 +2027,32 @@
           <t>Ordinary Diploma in Procurement and Supply Chain Management</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with
+AU
+at least four (4) passes in non-religious subjects OR National
+AU
+Vocational Award (NVAIII) with a Certificate of Secondary Education
+AU
+Examination(CSEE)
+AU
+Holders of Basic Technician Certificate (NTA level 4) in Procurement
+AU
+and Supply, Business Administration,logistics,Clearing and Forwarding,
+AU
+Accounts banking, Purchasing and Inventory OR Advanced Certificate in
+AU
+Secondary Education Examination (ACSEE) with one Principal pass and
+AU
+one Subsidiary in Principal subjects</t>
+        </is>
+      </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 / 2</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1603,10 +2085,26 @@
           <t>Ordinary Diploma in Psychology and Counselling</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with
+AU
+at least four (4) passes in non-religious subjects
+AU
+Holders of Basic Technician Certificate (NTA level 4) in Counselling
+AU
+Psychology, Education OR Advanced Certificate in Secondary Education
+AU
+Examination (ACSEE) with at least one Principal pass and one Subsidiary
+AU
+in Principal subjects.</t>
+        </is>
+      </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 / 2</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1639,10 +2137,32 @@
           <t>Ordinary Diploma in Records, Archives and Information Management</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with
+AU
+at least four (4) passes in non-religious subjects OR National
+AU
+Vocational Award (NVA III) with a Certificate of Secondary Education
+AU
+Examination (CSEE)
+AU
+Holders of Basic Technician Certificate (NTA level 4) in Records
+AU
+Management, Medical Records, Health in Information Science, Library
+AU
+and Information Science OR Advanced Certificate in Secondary
+AU
+Education Examination (ACSEE) with one Principal pass and one
+AU
+Subsidiary in Principal subjects</t>
+        </is>
+      </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 / 2</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1677,7 +2197,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Holders of Certificate in Business Administration, Accountancy,</t>
+          <t>Holders of Certificate in Business Administration, Accountancy,
+AU
+Economics, Banking and Finance, Marketing, Human Resource,
+AU
+Procurement and Supplies, Law and Tax, Local Government
+AU
+Administration OR Advanced Certificate of Secondary Education
+AU
+Examination (ACSEE) with at least one Principal pass and one
+AU
+Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1715,7 +2245,19 @@
           <t>Diploma in Computer Science</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate in Information Technology, Computer Science
+AU
+Information Technology, Business Information Technology OR Holder of
+AU
+Advanced Certificate of Secondary Education Examination (ACSEE) with
+AU
+one Principal pass and Subsidiary pass in principal subjects</t>
+        </is>
+      </c>
       <c r="F36" t="inlineStr">
         <is>
           <t>2</t>
@@ -1751,7 +2293,17 @@
           <t>Diploma in Guidance and Counseling</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate in Guidance and Counseling OR Holders of Advanced
+AU
+Certificate of Secondary Education Examination ( ACSEE) with at least
+AU
+one Principal Pass and one Subsidiary in Principal subjects</t>
+        </is>
+      </c>
       <c r="F37" t="inlineStr">
         <is>
           <t>2</t>
@@ -1787,7 +2339,19 @@
           <t>Diploma in Human Resource Management</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate in Business Administration, Accountancy, Human
+AU
+Resource, Supplies and Procurement OR Advanced Certificate of
+AU
+Secondary Education Examination (ACSEE) with One Principal Pass and
+AU
+one Subsidiary in Principal subjects</t>
+        </is>
+      </c>
       <c r="F38" t="inlineStr">
         <is>
           <t>2</t>
@@ -1823,7 +2387,19 @@
           <t>Diploma in in Conflict Resolution and Peace Studies</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate in Conflict Resolution and Peace Studies,
+AU
+Counselling Psychology OR Advanced Certificate of Secondary
+AU
+Education Examination (ACSEE) with one Principal Pass and One
+AU
+Subsidiary in Principal Subjects</t>
+        </is>
+      </c>
       <c r="F39" t="inlineStr">
         <is>
           <t>2</t>
@@ -1859,7 +2435,19 @@
           <t>Diploma in Law</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate in Law, Criminal Investigation, police science,
+AU
+Criminal Investigation, Police Science, OR Advanced Certificate of
+AU
+Secondary Education Examination (ACSEE) with one Principal Pass and
+AU
+one Subsidiary in Principal subjects</t>
+        </is>
+      </c>
       <c r="F40" t="inlineStr">
         <is>
           <t>2</t>
@@ -1897,7 +2485,15 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Holders of Certificate in Business Administration, Accountancy, Human</t>
+          <t>Holders of Certificate in Business Administration, Accountancy, Human
+AU
+Resource Management, Marketing Management, Marketing &amp; Public
+AU
+Relation OR Advanced Certificate of Secondary Education Examination
+AU
+(ACSEE) with at least one Principal Pass and one Subsidiary in Principal
+AU
+subjects</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1935,7 +2531,23 @@
           <t>Diploma in Public Administration</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate in Public Administration, Local Government
+AU
+Administration, Business Administration, Human Resource management,
+AU
+Secretarial services, Community Development,
+AU
+Community Health and Public Relation OR Advanced Certificate of
+AU
+Secondary Education Examination (ACSEE) with at least one Principal
+AU
+Pass and one Subsidiary in Principal subjects</t>
+        </is>
+      </c>
       <c r="F42" t="inlineStr">
         <is>
           <t>2</t>
@@ -1971,7 +2583,19 @@
           <t>Diploma in Social Work</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate in Social Work, Community Health, theology,
+AU
+Community Development, sociology, Social Protection OR Advanced
+AU
+Certificate of Secondary Education Examination (ACSEE) with at least one
+AU
+Principal Pass and one Subsidiary pass in Principal Subjects</t>
+        </is>
+      </c>
       <c r="F43" t="inlineStr">
         <is>
           <t>2</t>
@@ -2007,7 +2631,21 @@
           <t>Diploma in Supplies and Procurement Management</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate in Procurement and Supply, Business
+AU
+Administration, Logistics, Perchance and Inventory/ clearing and
+AU
+forwarding OR Advanced Certificate of Secondary Education Examination
+AU
+(ACSEE) with at least one Principal Pass and one
+AU
+Subsidiary in Principal subjects</t>
+        </is>
+      </c>
       <c r="F44" t="inlineStr">
         <is>
           <t>2</t>
@@ -2043,7 +2681,19 @@
           <t>Ordinary Diploma in Clinical Medicine</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with
+AU
+four (4) passes in non-religious subjects including Chemistry, Biology and
+AU
+Physics/Engineering Sciences. A pass in Basic Mathematics and English
+AU
+Language is an added advantage.</t>
+        </is>
+      </c>
       <c r="F45" t="inlineStr">
         <is>
           <t>3</t>
@@ -2079,7 +2729,17 @@
           <t>Ordinary Diploma in Environmental Health Sciences</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with At
+AU
+Least four (4) Passes in non-religious Subjects including
+AU
+Biology Chemistry and Physics/Engineering Sciences.</t>
+        </is>
+      </c>
       <c r="F46" t="inlineStr">
         <is>
           <t>3</t>
@@ -2115,7 +2775,19 @@
           <t>Ordinary Diploma in Medical Laboratory Sciences</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with At
+AU
+Least four (4) Passes in non-religious Subjects including Chemistry,
+AU
+Biology, Physics/Engineering sciences/Basic Mathematics and English
+AU
+Language.</t>
+        </is>
+      </c>
       <c r="F47" t="inlineStr">
         <is>
           <t>3</t>
@@ -2151,10 +2823,26 @@
           <t>Ordinary Diploma in Pharmaceutical Sciences</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with At
+AU
+Least four (4) Passes in non-religious Subjects including Chemistry and
+AU
+Biology. A Pass in Basic Mathematics and English
+AU
+Language Is An Added Advantage.
+AU
+KILIMANJARO CHRISTIAN MEDICAL UNIVERSITY COLLEGE (KCMU) (KC) - FBO
+AU
+Moshi Municipal Council - Kilimanjaro</t>
+        </is>
+      </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 / Program Duration (Yrs)</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2187,7 +2875,19 @@
           <t>Diploma in Occupational Therapy</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with at
+AU
+least four (4) passes in non religious Subjects including C pass in Biology
+AU
+and any two subjects in Chemistry, Mathematics,
+AU
+Geography, Economics, Physics/Physical Sciences.</t>
+        </is>
+      </c>
       <c r="F49" t="inlineStr">
         <is>
           <t>3</t>
@@ -2223,10 +2923,26 @@
           <t>Ordinary Diploma in Medical Laboratory Sciences</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with At
+AU
+Least four (4) Passes in non-religious Subjects including Chemistry,
+AU
+Biology, Physics/Engineering sciences/Basic Mathematics and English
+AU
+Language.
+AU
+MARIAN UNIVERSITY COLLEGE (MAR) - FBO
+AU
+Bagamoyo District Council - Pwani</t>
+        </is>
+      </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 / Program Duration (Yrs)</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2259,10 +2975,26 @@
           <t>Ordinary Diploma in Pharmaceutical Sciences</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with At
+AU
+Least four (4) Passes in non-religious Subjects including
+AU
+Chemistry and Biology. A Pass in Basic Mathematics and English
+AU
+Language Is An Added Advantage.
+AU
+MBEYA UNIVERSITY OF SCIENCE AND TECHNOLOGY (REG/EOS/003) - Government
+AU
+Mbeya City Council - Mbeya</t>
+        </is>
+      </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 / Program Duration (Yrs)</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2295,7 +3027,17 @@
           <t>Diploma in Architecture</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with
+AU
+Four (4) Passes in non-religious Subjects, three of which must be
+AU
+Mathematics, Physics, Chemistry/Geography</t>
+        </is>
+      </c>
       <c r="F52" t="inlineStr">
         <is>
           <t>3</t>
@@ -2331,7 +3073,17 @@
           <t>Diploma in Bio Medical Equipment Engineering</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with at
+AU
+least Four (4) Passes in non-religious Subjects including
+AU
+Physics,Chemistry and Basic Mathematics.</t>
+        </is>
+      </c>
       <c r="F53" t="inlineStr">
         <is>
           <t>3</t>
@@ -2367,7 +3119,15 @@
           <t>Diploma in Business Administration</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with at
+AU
+least four (4) passes in non-religious subjects</t>
+        </is>
+      </c>
       <c r="F54" t="inlineStr">
         <is>
           <t>3</t>
@@ -2403,7 +3163,17 @@
           <t>Diploma in Civil Engineering</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with at
+AU
+least Four (4) passes in non-religious subjects including
+AU
+Physics, Chemistry and Basic Mathematics.</t>
+        </is>
+      </c>
       <c r="F55" t="inlineStr">
         <is>
           <t>3</t>
@@ -2439,7 +3209,17 @@
           <t>Diploma in Computer Engineering</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with at
+AU
+least Four (4) passes in non-religious subjects including
+AU
+Physics, Chemistry and Basic Mathematics subjects.</t>
+        </is>
+      </c>
       <c r="F56" t="inlineStr">
         <is>
           <t>3</t>
@@ -2475,7 +3255,15 @@
           <t>Diploma in Computer Science</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with
+AU
+Four (4) passes in non-religious subjects.</t>
+        </is>
+      </c>
       <c r="F57" t="inlineStr">
         <is>
           <t>3</t>
@@ -2511,7 +3299,17 @@
           <t>Diploma in Electric and Electronics Engineering</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with at
+AU
+least Four (4) passes in non- religious subjects including a pass in Basic
+AU
+Mathematics and Physics/Engineering Sciences and Chemistry</t>
+        </is>
+      </c>
       <c r="F58" t="inlineStr">
         <is>
           <t>3</t>
@@ -2547,7 +3345,17 @@
           <t>Diploma in Electrical Engineering</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with at
+AU
+least Four (4) passes in non- religious subjects including a pass in Basic
+AU
+Mathematics and Physics/Engineering Sciences</t>
+        </is>
+      </c>
       <c r="F59" t="inlineStr">
         <is>
           <t>3</t>
@@ -2583,7 +3391,17 @@
           <t>Diploma in Electronics and Telecomunication Engineering</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with at
+AU
+least Four (4) passes in non-religious subjects including passes in Physics,
+AU
+Chemistry and Basic Mathematics.</t>
+        </is>
+      </c>
       <c r="F60" t="inlineStr">
         <is>
           <t>3</t>
@@ -2619,7 +3437,39 @@
           <t>Diploma in Food Science and Technology</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Certificate of Secondary Education Examination (CSEE) with at least four
+AU
+passes in non-religious subjects three of which must be in Mathematics,
+AU
+Physics/Chemistry or Biology. OR Certificate of
+AU
+Secondary Education Examination (CSEE) from Technical Secondary
+AU
+School with a pass in at least four passes in non-religious subjects
+AU
+three of which must be in Mathematics, Engineering
+AU
+Science/Chemistry and Biology and one of the following subjects:
+AU
+Architectural Drafting/Building, Construction, Electrical Engineering,
+AU
+Science/Electrical Drafting or Workshop Technology/Mechanical
+AU
+Drafting. OR Certificate of Secondary Education Examination (CSEE) with
+AU
+at least four passes in non-religious subjects two of which must be in the
+AU
+following subjects Mathematics, Physics, Chemistry or
+AU
+Biology with Trade Test Grade 1 or National Vocational Award (NVA)
+AU
+Level III issued by VETA.</t>
+        </is>
+      </c>
       <c r="F61" t="inlineStr">
         <is>
           <t>3</t>
@@ -2655,7 +3505,17 @@
           <t>Diploma in High Way Engineering</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with at
+AU
+least Four (4) Passes in non-religious Subjects including
+AU
+Physics, Chemistry and Basic Mathematics.</t>
+        </is>
+      </c>
       <c r="F62" t="inlineStr">
         <is>
           <t>3</t>
@@ -2691,7 +3551,17 @@
           <t>Diploma in Information and Communication Technology</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holder of Certificate of Secondary Education with at least Four (4) passes
+AU
+in non-religious subject including Basic Mathematics and
+AU
+English Language.</t>
+        </is>
+      </c>
       <c r="F63" t="inlineStr">
         <is>
           <t>3</t>
@@ -2727,7 +3597,17 @@
           <t>Diploma in Laboratory Sciences Technology</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with at
+AU
+least Four (4) passes in non-religious subjects including
+AU
+Physics, Chemistry and Basic Mathematics.</t>
+        </is>
+      </c>
       <c r="F64" t="inlineStr">
         <is>
           <t>3</t>
@@ -2763,7 +3643,17 @@
           <t>Diploma in Mechanical Engineering</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with at
+AU
+least Four (4) passes in non-religious subjects including
+AU
+Physics, Chemistry and Basic Mathematics.</t>
+        </is>
+      </c>
       <c r="F65" t="inlineStr">
         <is>
           <t>3</t>
@@ -2799,7 +3689,17 @@
           <t>Diploma in Mechatronics Engineering</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with at
+AU
+least Four (4) passes in non-religious subjects including
+AU
+Physics, Chemistry and Basic Mathematics.</t>
+        </is>
+      </c>
       <c r="F66" t="inlineStr">
         <is>
           <t>3</t>
@@ -2832,10 +3732,20 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Diploma in Mining Engineering</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr"/>
+          <t>Diploma in Mining Engineering MOSHI UNIVERSITY COLLEGE OF COOPERATIVE AND BUSINESS STUDIES (MOCU) (MC) - Government Moshi Municipal Council - Kilimanjaro</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with at
+AU
+least Four (4) passes in non-religious subjects including
+AU
+Physics, Chemistry and Basic Mathematics.</t>
+        </is>
+      </c>
       <c r="F67" t="inlineStr">
         <is>
           <t>3</t>
@@ -2871,7 +3781,17 @@
           <t>Diploma in Business Information and Communication Technology</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate in Business and Information Technology OR
+AU
+Advanced Certificate of Secondary Education Examination (ACSEE) with
+AU
+at least one principal pass and one subsidiary in Principal subjects</t>
+        </is>
+      </c>
       <c r="F68" t="inlineStr">
         <is>
           <t>2</t>
@@ -2907,7 +3827,17 @@
           <t>Diploma in Co-operative Management and Accounting</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate in Cooperative Management and Accounting OR
+AU
+Advanced Certificate of Secondary Education Examination (ACSEE) with
+AU
+at least one principal pass and one subsidiary in Principal subjects</t>
+        </is>
+      </c>
       <c r="F69" t="inlineStr">
         <is>
           <t>2</t>
@@ -2943,7 +3873,17 @@
           <t>Diploma in Enterprise Management</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate in Enterprise Management OR Advanced Certificate
+AU
+of Secondary Education Examination (ACSEE) with at least one principal
+AU
+pass and one subsidiary Principal subjects</t>
+        </is>
+      </c>
       <c r="F70" t="inlineStr">
         <is>
           <t>2</t>
@@ -2979,7 +3919,17 @@
           <t>Diploma in Human Resource Management</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate in Human Resource Management OR Advanced
+AU
+Certificate of Secondary Education Examination (ACSEE) with at least one
+AU
+principal pass and one subsidiary in Principal subjects</t>
+        </is>
+      </c>
       <c r="F71" t="inlineStr">
         <is>
           <t>2</t>
@@ -3015,7 +3965,17 @@
           <t>Diploma in Library and Archival Studies</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate in Library and Archival Studies OR Advanced
+AU
+Certificate of Secondary Education Examination (ACSEE) with at least one
+AU
+principal pass and one subsidiary Principal subjects</t>
+        </is>
+      </c>
       <c r="F72" t="inlineStr">
         <is>
           <t>2</t>
@@ -3048,10 +4008,20 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Diploma in Microfinance Management</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr"/>
+          <t>Diploma in Microfinance Management MUHIMBILI UNIVERSITY OF HEALTH AND ALLIED SCIENCES (MH) - Government Kinondoni Municipal Council - Dar es Salaam</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate in Accounting, Banking and Finance OR Advanced
+AU
+Certificate of Secondary Education Examination (ACSEE) with at least one
+AU
+principal pass and one subsidiary Principal subjects</t>
+        </is>
+      </c>
       <c r="F73" t="inlineStr">
         <is>
           <t>2</t>
@@ -3087,7 +4057,19 @@
           <t>Diploma in Diagnostic Radiography (ddr) - Evening</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with at
+AU
+least four (4) passes in non-religious subjects including English and at
+AU
+least three (3) Credits in either Physics, Chemistry, Biology and
+AU
+Mathematics. Physics is a major subject.</t>
+        </is>
+      </c>
       <c r="F74" t="inlineStr">
         <is>
           <t>3</t>
@@ -3123,7 +4105,19 @@
           <t>Diploma in Diagnostic Radiography - Ddr - Regular</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with at
+AU
+least four (4) passes in non-religious subjects including English and at
+AU
+least three (3) Credits one in Physics and two (2) others from either
+AU
+Chemistry, Biology and Mathematics.</t>
+        </is>
+      </c>
       <c r="F75" t="inlineStr">
         <is>
           <t>3</t>
@@ -3156,10 +4150,22 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Diploma in Environmental Health Sciences -</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr"/>
+          <t>Diploma in Environmental Health Sciences - (DEHS) (dar Es Salaam)</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with at
+AU
+least four (4) Passes in non-religious Subjects, including English and at
+AU
+least Three (3) Credits one in Mathematics and two others from Physics,
+AU
+Chemistry or Biology.</t>
+        </is>
+      </c>
       <c r="F76" t="inlineStr">
         <is>
           <t>3</t>
@@ -3192,10 +4198,22 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Diploma in Environmental Health Sciences (DEHS)</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr"/>
+          <t>Diploma in Environmental Health Sciences (DEHS) - Mpwapwa, Evening</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with at
+AU
+least four (4) Passes in non-religious Subjects, including English and at
+AU
+least three (3) Credits one in Mathematics and two others from Physics,
+AU
+Chemistry and Biology.</t>
+        </is>
+      </c>
       <c r="F77" t="inlineStr">
         <is>
           <t>3</t>
@@ -3228,10 +4246,22 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Diploma in Environmental Health Sciences (DEHS)</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr"/>
+          <t>Diploma in Environmental Health Sciences (DEHS) - Tanga - Evening</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with at
+AU
+least four (4) Passes in non-religious subjects, including English and at
+AU
+least three (3) Credits one in Mathematics and two others from Physics,
+AU
+Chemistry and Biology .</t>
+        </is>
+      </c>
       <c r="F78" t="inlineStr">
         <is>
           <t>3</t>
@@ -3264,10 +4294,22 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Diploma in Environmental Health Sciences (DEHS)</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr"/>
+          <t>Diploma in Environmental Health Sciences (DEHS) - Tanga - Regular</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with at
+AU
+least Four (4) Passes in non-religious Subjects, including English and at
+AU
+least Three (3) Credits one in Mathematics and two others from Physics,
+AU
+Chemistry and Biology</t>
+        </is>
+      </c>
       <c r="F79" t="inlineStr">
         <is>
           <t>3</t>
@@ -3300,10 +4342,22 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Diploma in Environmental Health Sciences - DEHS</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr"/>
+          <t>Diploma in Environmental Health Sciences - DEHS - (Dar es Salaam) - Evening</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with at
+AU
+least Four (4) Passes in non-religious Subjects, including English and at
+AU
+least Three (3) Credits one in Mathematics and two others from Physics,
+AU
+Chemistry and Biology .</t>
+        </is>
+      </c>
       <c r="F80" t="inlineStr">
         <is>
           <t>3</t>
@@ -3336,10 +4390,22 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Diploma in Environmental Health Sciences - Dehs -</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr"/>
+          <t>Diploma in Environmental Health Sciences - Dehs - Mpwapwa</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with at
+AU
+least Four (4) Passes in non-religious Subjects, including English and at
+AU
+least Three (3) Credits one in Mathematics and two others from Physics,
+AU
+Chemistry and Biology.</t>
+        </is>
+      </c>
       <c r="F81" t="inlineStr">
         <is>
           <t>3</t>
@@ -3375,7 +4441,19 @@
           <t>Diploma in Medical Laboratory Sciences (DMLS)</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with at
+AU
+least Five (5) Passes in non-religious Subjects including Mathematics and
+AU
+English and at least Three (3) Credits in Biology,
+AU
+Chemistry and Physics.</t>
+        </is>
+      </c>
       <c r="F82" t="inlineStr">
         <is>
           <t>3</t>
@@ -3408,10 +4486,22 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Diploma in Medical Laboratory Sciences (dmls) -</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr"/>
+          <t>Diploma in Medical Laboratory Sciences (dmls) - Evening</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with at
+AU
+least Five (5) Passes in non-religious Subjects, including Mathematics and
+AU
+English and at least Three (3) Credits in Biology,
+AU
+Chemistry and Physics.</t>
+        </is>
+      </c>
       <c r="F83" t="inlineStr">
         <is>
           <t>3</t>
@@ -3447,7 +4537,19 @@
           <t>Diploma in Nursing (dn) - Evening</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with at
+AU
+least Five (5) Passes in non-religious Subjects including Mathematics and
+AU
+English and at least Three (3) Credits in Biology,
+AU
+Chemistry and Physics,</t>
+        </is>
+      </c>
       <c r="F84" t="inlineStr">
         <is>
           <t>3</t>
@@ -3483,7 +4585,19 @@
           <t>Diploma in Nursing - DN - Regular</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with at
+AU
+least Five (5) Passes in non-religious Subjects, including Physics,
+AU
+Mathematics and English and Credit passes in Biology and
+AU
+Chemistry.</t>
+        </is>
+      </c>
       <c r="F85" t="inlineStr">
         <is>
           <t>3</t>
@@ -3519,7 +4633,19 @@
           <t>Diploma in Orthopaedic Technology (DOT) - KCMC</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with at
+AU
+least Four (4) Passes in non-religious Subjects with at least Three (3)
+AU
+Credits from Physics, Chemistry, Biology or Mathematics. Credit pass in
+AU
+Engineering subjects is also acceptable as the third credit pass.</t>
+        </is>
+      </c>
       <c r="F86" t="inlineStr">
         <is>
           <t>3</t>
@@ -3552,10 +4678,22 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Diploma in Pharmaceutical Sciences (DPS) -</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr"/>
+          <t>Diploma in Pharmaceutical Sciences (DPS) - Evening</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with at
+AU
+least Fiver (5) Passes in non-religious subjects including Biology and
+AU
+Physics, and at least Three Credits in Mathematics,
+AU
+Chemistry and English.</t>
+        </is>
+      </c>
       <c r="F87" t="inlineStr">
         <is>
           <t>3</t>
@@ -3588,13 +4726,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Diploma in Pharmaceutical Sciences (DPS) -</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr"/>
+          <t>Diploma in Pharmaceutical Sciences (DPS) - Regular</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with at
+AU
+least Five (5) Passes in non-religious Subjects including Biology and
+AU
+Physics, and at least Three (3) Credits in Mathematics, Chemistry and
+AU
+English.</t>
+        </is>
+      </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 / Program Duration (Yrs)</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3627,7 +4777,17 @@
           <t>Diploma in Islamic Banking and Finance</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate in Islamic Banking and Finance OR Advanced
+AU
+Certificate of Secondary Education Examination (ACSEE) with at least one
+AU
+Principal pass and one Subsidiary in Principal subjects</t>
+        </is>
+      </c>
       <c r="F89" t="inlineStr">
         <is>
           <t>2</t>
@@ -3663,7 +4823,17 @@
           <t>Diploma in Law and Shariah</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate in Law and Shariah OR Advanced Certificate of
+AU
+Secondary Education Examination (ACSEE) with at least one Principal pass
+AU
+and one Subsidiary in Principal subjects</t>
+        </is>
+      </c>
       <c r="F90" t="inlineStr">
         <is>
           <t>2</t>
@@ -3696,10 +4866,22 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Diploma in Procurement and Logistics</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr"/>
+          <t>Diploma in Procurement and Logistics Management</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate in Procurement and Supply,Logistics,Purchasing
+AU
+and Inventory OR Advanced Certificate of Secondary Education
+AU
+Examination (ACSEE) with at least one Principal pass and one
+AU
+Subsidiary in Principal subjects</t>
+        </is>
+      </c>
       <c r="F91" t="inlineStr">
         <is>
           <t>2</t>
@@ -3735,10 +4917,28 @@
           <t>Ordinary Diploma in Accountancy</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr"/>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with
+AU
+at least four (4) passes in non-religious subjects including Basic
+AU
+Mathematics OR National Vocational Award (NVA) Level III with a
+AU
+Certificate of Secondary Education Examination (CSEE)
+AU
+Holders of Basic Technician Certificate (NTA Level 4) in Accountancy OR
+AU
+Advance Certificate of Secondary Education Examination with at least
+AU
+one Principal pass and one Subsidiary in Principal subjects</t>
+        </is>
+      </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 / 2</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -3771,10 +4971,32 @@
           <t>Ordinary Diploma in Business Administration</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with
+AU
+at least four (4) passes in non-religious subjects OR National
+AU
+Vocational Award (NVA)Level III with a Certificate of Secondary
+AU
+Education Examination (CSEE)
+AU
+Holders of Basic Technician Certificate (NTA Level 4) in Business
+AU
+Administration, Account, Finance and Banking, Marketing,
+AU
+Procurement and Supply OR Advanced Certificate of Secondary
+AU
+Education Examination (ACSEE) with at least one Principal pass and one
+AU
+Subsidiary in Principal subjects</t>
+        </is>
+      </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 / 2</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -3807,10 +5029,30 @@
           <t>Ordinary Diploma in Journalism</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with
+AU
+at least four (4) passes in non-religious subjects OR National
+AU
+Vocational Award (NVA) Level III with a Certificate of Secondary
+AU
+Education Examination (CSEE)
+AU
+Holders of Basic Technician Certificate (NTA Level 4) in Journalism,
+AU
+Mass Communication, TV Production, Media Production OR Advanced
+AU
+Certificate of Secondary Education Examination (ACSEE) with at least
+AU
+one Principal pass and one Subsidiary in Principal subjects</t>
+        </is>
+      </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 / 2</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -3843,7 +5085,19 @@
           <t>Ordinary Diploma in Medical Laboratory Sciences</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr"/>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with At
+AU
+Least four (4) Passes in non-religious Subjects including Chemistry,
+AU
+Biology, Physics/Engineering sciences/Basic Mathematics and English
+AU
+Language.</t>
+        </is>
+      </c>
       <c r="F95" t="inlineStr">
         <is>
           <t>3</t>
@@ -3879,10 +5133,34 @@
           <t>Ordinary Diploma in Science and Laboratory Technology</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr"/>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with
+AU
+Four (4) passes in non-religious subjects including Two (2) Passes in
+AU
+Biology, Chemistry, Physics/Engineering Sciences.
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with
+AU
+Four (4) Passes in non-religious Subjects including two (2) Passes in
+AU
+Biology, Chemistry, Physics/Engineering Sciences; and Possession of
+AU
+Basic Technician Certificate (NTA Level 4) in Science and Laboratory
+AU
+Technology; OR Advanced Certificate of Secondary Education
+AU
+Examination (ACSEE) with one (1) Principal Pass and one (1) Subsidiary
+AU
+Pass in Biology, Chemistry, Physics, Advanced Mathematics.</t>
+        </is>
+      </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 / 2</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -3915,10 +5193,28 @@
           <t>Ordinary Diploma in Accountancy</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr"/>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with
+AU
+at least four (4) passes in non-religious subjects including Basic
+AU
+Mathematics
+AU
+Holders of Basic Technician Certificate (NTA level 4) in Accountancy,
+AU
+Business Administration Banking and Finances OR Advanced Certificate
+AU
+of Secondary Education Examination (ACSEE) with at least one
+AU
+Principal pass and one Subsidiary in Principal subjects</t>
+        </is>
+      </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 / 2</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -3951,10 +5247,30 @@
           <t>Ordinary Diploma in Business Administration</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with
+AU
+at least four (4) passes in Non-Religious Subjects OR National
+AU
+Vocational Award (NVA) III with a Certificate of Secondary Education
+AU
+Examination (CSEE)
+AU
+Holders of Basic Technician Certificate (NTA level 4) in Business
+AU
+Administration OR Advanced Certificate of Secondary Education
+AU
+Examination (ACSEE) with at least one Principal pass and one
+AU
+Subsidiary Principal subjects</t>
+        </is>
+      </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 / 2</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -3987,10 +5303,32 @@
           <t>Ordinary Diploma in Computing and Information Technology</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr"/>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with
+AU
+At Least four (4) Passes in non-religious subjects including Basic
+AU
+Mathematics and English Language or National Vocational Award (NVA
+AU
+Level III) with a Certificate of Secondary Education Examination
+AU
+(CSEE)
+AU
+Holders of Basic Technician Certificate (NTA 4) in Information
+AU
+Technology, Computer Sciences OR Advanced Certificate of Secondary
+AU
+Education Examination (ACSEE) with one Principal pass and one
+AU
+Subsidiary.</t>
+        </is>
+      </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 / 2</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -4023,10 +5361,26 @@
           <t>Ordinary Diploma in Law</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of certificate of secondary education examination (CSEE) with
+AU
+at least four (4) passes in non- religious subjects including English
+AU
+Language
+AU
+Holders of Basic Technician Certificate (NTA level 4) in Law OR
+AU
+Advanced Certificate of Secondary Education Examination (ACSEE) with
+AU
+at least one Principal pass and one Subsidiary in Principal subjects</t>
+        </is>
+      </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 / 2</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -4059,10 +5413,26 @@
           <t>Ordinary Diploma in Procurement and Supply</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr"/>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination ( CSEE ) with
+AU
+at least four (4) passes in non- religious subjects
+AU
+Holders of Basic Technician Certificate (NTA Level 4) in Procurement
+AU
+and Supply, Logistics, Clearing and Forwarding OR Advanced
+AU
+Certificate of Secondary Education Examination (ACSEE) with at Least
+AU
+one Principal pass and one Subsidiary in Principal subjects</t>
+        </is>
+      </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 / 2</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -4095,10 +5465,30 @@
           <t>Ordinary Diploma in Records, Archives and Information Management</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr"/>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with
+AU
+at least four (4) passes in non religious subjects OR National
+AU
+Vocational Award (NVA) Level III with a Certificate of Secondary
+AU
+Education Examination (CSEE)
+AU
+Holders of Basic Technician Certificate (NTA Level 4) in Records
+AU
+Management, Medical Records, Library and information studies OR
+AU
+Advanced Certificate of Secondary Education Examination (ACSEE) with
+AU
+at least one Principal pass and one Subsidiary in Principal subjects</t>
+        </is>
+      </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 / 2</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -4131,10 +5521,30 @@
           <t>Ordinary Diploma in Social Work</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr"/>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with
+AU
+at least four (4) passes in non-religious subjects
+AU
+Holder of Basic Technician Certificate (NTA Level 4) in Social Work,
+AU
+Gender and Community Development OR Advanced Certificate of
+AU
+Secondary Education Examination (ACSEE) with at Least one Principal
+AU
+pass and one Subsidiary in Principal subjects
+AU
+MZUMBE UNIVERSITY (MU) - Government
+AU
+Mvomero District Council - Morogoro</t>
+        </is>
+      </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 / 2 / Program Duration (Yrs)</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -4169,7 +5579,11 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Holders of Certificate in Applied Statistics OR Advanced Certificate of</t>
+          <t>Holders of Certificate in Applied Statistics OR Advanced Certificate of
+AU
+Secondary Education with at least one Principal pass and one
+AU
+Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4209,7 +5623,13 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Holders of Certificate in Applied Statistics OR Advanced Certificate of</t>
+          <t>Holders of Certificate in Applied Statistics OR Advanced Certificate of
+AU
+Secondary Education Examination (ACSEE) with One Principal Pass in
+AU
+Either Chemistry, Biology or Advanced Mathematics and One
+AU
+Subsidiary in any Subject</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4247,10 +5667,26 @@
           <t>Diploma in Information Technology (dit)</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr"/>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate in Information Technology, Computer Engineering
+AU
+OR Advanced Certificate of Secondary Education
+AU
+Examination (ACSEE) with One Principal Pass in either Physics,
+AU
+Chemistry, Biology or Advanced Mathematics and One Subsidiary
+AU
+MZUMBE UNIVERSITY (MU), MBEYA COLLEGE (MMB) - Government
+AU
+Mbeya City Council - Mbeya</t>
+        </is>
+      </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2 / Program Duration (Yrs)</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -4283,7 +5719,17 @@
           <t>Diploma in Accountancy (da)</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr"/>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate in Accountancy, Finance and Banking OR Advanced
+AU
+Certificate of Secondary Education Examination (ACSEE) with at least one
+AU
+Principal pass and subsidiary in Principal subjects</t>
+        </is>
+      </c>
       <c r="F107" t="inlineStr">
         <is>
           <t>2</t>
@@ -4319,7 +5765,19 @@
           <t>Diploma in Business Administration</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr"/>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate in Business Management, Procurement and Supply
+AU
+Chain, Accountancy OR Advanced Certificate of Secondary Education
+AU
+Examination (ACSEE)With at Least one Principal pass and one subsidiary
+AU
+in Principal subjects.</t>
+        </is>
+      </c>
       <c r="F108" t="inlineStr">
         <is>
           <t>2</t>
@@ -4355,7 +5813,21 @@
           <t>Diploma in Human Resource Management</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr"/>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Human Resources Management, Local
+AU
+Government Administration, Social Work, Law, Business Management,
+AU
+Community development, Records and Archives Management. OR
+AU
+Advanced Certificate of Secondary Education Examination (ACSEE) with
+AU
+at Least one Principal Pass and one Subsidiary in Principal subjects</t>
+        </is>
+      </c>
       <c r="F109" t="inlineStr">
         <is>
           <t>2</t>
@@ -4391,7 +5863,17 @@
           <t>Diploma in Law</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr"/>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate in Law OR Advanced Certificate of Secondary
+AU
+Education Examination (ACSEE) with at Least one Principal Pass and one
+AU
+subsidiary in Principal subjects</t>
+        </is>
+      </c>
       <c r="F110" t="inlineStr">
         <is>
           <t>2</t>
@@ -4427,7 +5909,19 @@
           <t>Diploma in Logistics Management</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr"/>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate in Logistics Management, Business Administration,
+AU
+Accountancy, Banking OR Advanced Certificate of Secondary Education
+AU
+with at Least Principal Pass and one Subsidiary in
+AU
+Principal subjects</t>
+        </is>
+      </c>
       <c r="F111" t="inlineStr">
         <is>
           <t>2</t>
@@ -4460,13 +5954,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Diploma in Procurement and Logistics</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr"/>
+          <t>Diploma in Procurement and Logistics Management</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate in Procurement and Supply Chain Business
+AU
+Management, Public Administration, Accountancy OR Advanced
+AU
+Certificate of Secondary Education Examination (ACSEE) with at Least one
+AU
+Principal Pass and one subsidiary in Principal subjects</t>
+        </is>
+      </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2 / Program Duration (Yrs)</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -4499,7 +6005,15 @@
           <t>Basic Technician Certificate in Entrepreneurship</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr"/>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with at
+AU
+least four (4) passes in non-religious subjects</t>
+        </is>
+      </c>
       <c r="F113" t="inlineStr">
         <is>
           <t>1</t>
@@ -4535,7 +6049,15 @@
           <t>Basic Technician Certificate in Hair and Beauty</t>
         </is>
       </c>
-      <c r="E114" t="inlineStr"/>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of certificate of Secondary Education Examination (CSEE) with
+AU
+four (4) passes in non-religious subjects</t>
+        </is>
+      </c>
       <c r="F114" t="inlineStr">
         <is>
           <t>1</t>
@@ -4571,7 +6093,17 @@
           <t>Diploma in Common Wealth Youth Programme</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr"/>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Technician Certificate (NTA Level 5)in Youth work OR
+AU
+Advanced Certificate of Secondary Education Examination (ACSEE) with
+AU
+at least one Principal pass and Subsidiary in Principal subjects</t>
+        </is>
+      </c>
       <c r="F115" t="inlineStr">
         <is>
           <t>2</t>
@@ -4609,7 +6141,9 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Holders of Basic Technician Certificate (NTA Level 4) in Distance</t>
+          <t>Holders of Basic Technician Certificate (NTA Level 4) in Distance
+AU
+Education</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4647,7 +6181,19 @@
           <t>Diploma in Early Childhood Education (dece)</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr"/>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of certificate of secondary education examination (CSEE) with
+AU
+Four passes or with two passes for those who have NVA level III recognized
+AU
+by VETA and Grade III A OR Basic technician certificate in teaching with
+AU
+an average of B and above</t>
+        </is>
+      </c>
       <c r="F117" t="inlineStr">
         <is>
           <t>2</t>
@@ -4685,7 +6231,9 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Holders of Technician Certificate (NTA level 5) in Library and</t>
+          <t>Holders of Technician Certificate (NTA level 5) in Library and
+AU
+Information studies</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4723,7 +6271,15 @@
           <t>Diploma in Poultry Production and Health (odpph)</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr"/>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Technician Certificate ( NTA Level 5 ) in Animal Production,
+AU
+General Agriculture With 2.0 GPA and above.</t>
+        </is>
+      </c>
       <c r="F119" t="inlineStr">
         <is>
           <t>2</t>
@@ -4759,7 +6315,23 @@
           <t>Diploma in Primary Teacher Education (odpte)</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr"/>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holder of Certificate of Secondary Education Examination (CSEE) with
+AU
+four Passes or with two Passes for Those Who Have Nva Level III
+AU
+Recognized By Veta and Grade III A or Basic Technician Certificate in
+AU
+Teaching with An Average of B+ and above or Holder of Advinced
+AU
+Certificate of Secondary Education with one Principal Pass and one
+AU
+Subsidiary from Any two Subjects</t>
+        </is>
+      </c>
       <c r="F120" t="inlineStr">
         <is>
           <t>2</t>
@@ -4795,10 +6367,26 @@
           <t>Ordinary Diploma in Accountancy</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr"/>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with
+AU
+at least four (4) passes in non-religious subjects
+AU
+Holders of Basic Technical Certificate Certificate ( NTA Level 4) in
+AU
+Accountancy OR Advanced Certificate of Secondary Education
+AU
+Examination (ACSEE) with at least one Principal pass and one
+AU
+Subsidiary in Principal subjects</t>
+        </is>
+      </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 / 2</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -4831,10 +6419,28 @@
           <t>Ordinary Diploma in Business Administration</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr"/>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with
+AU
+at least four (4) passes in non-religious subjects
+AU
+Holders of Basic Technical Certificate Certificate (NTA Level 4) in
+AU
+Business Administration, Accountancy Marketing and Procurement and
+AU
+Supply OR Advanced Certificate of Secondary Education Examination
+AU
+(ACSEE) with at least one Principal Pass and one Subsidiary in Principal
+AU
+subjects</t>
+        </is>
+      </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 / 2</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -4867,10 +6473,26 @@
           <t>Ordinary Diploma in Computing and Information Communication Technology</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr"/>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with
+AU
+Four (4) passes in non-religious subjects.
+AU
+Holders of Basic Technician Certificate (NTA Level 4) in Information
+AU
+Communication Technology OR Advanced Certificate of Secondary
+AU
+Education Examination (ACSEE) with one Principal Pass and One
+AU
+Subsidiary Pass.</t>
+        </is>
+      </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 / 2</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -4903,10 +6525,28 @@
           <t>Ordinary Diploma in Procurement and Supply</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr"/>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with
+AU
+at least four (4) passes in non-religious subjects
+AU
+Holders of Basic Technician Certificate (NTA Level 5) in Procurement
+AU
+and Supply, Logistics, Clearing and Forwarding, Business
+AU
+Administration, Accounting OR Advanced Certificate of Secondary
+AU
+Education Examination (ACSEE) with one Principal Pass and one
+AU
+Subsidiary in principal subjects.</t>
+        </is>
+      </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 / 2</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -4939,10 +6579,20 @@
           <t>Ordinary Diploma in Social Work</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr"/>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with
+AU
+four (4) passes in non religious subjects
+AU
+Holders of Basic Technician Certificate (NTA Level 4) in Social work</t>
+        </is>
+      </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 / 2</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -4975,7 +6625,17 @@
           <t>Diploma in Business Administration</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr"/>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate in Business Administration OR Advanced Certificate
+AU
+of Secondary Education Examination (ACSEE) with at Least one Principal
+AU
+pass and Subsidiary in Principal subjects</t>
+        </is>
+      </c>
       <c r="F126" t="inlineStr">
         <is>
           <t>2</t>
@@ -5011,7 +6671,19 @@
           <t>Diploma in Computer Science</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr"/>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate in Computer Science (CS), Information
+AU
+Technology (IT), Business Information Technology (BIT); OR Advanced
+AU
+Certificate of Secondary Education Examination (ACSEE) with one
+AU
+principal pass and one subsidiary pass.</t>
+        </is>
+      </c>
       <c r="F127" t="inlineStr">
         <is>
           <t>2</t>
@@ -5049,7 +6721,11 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Holders of Certificate in Human Resource Management OR Advanced</t>
+          <t>Holders of Certificate in Human Resource Management OR Advanced
+AU
+Certificate of Secondary Education Examination with one Principal
+AU
+Pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -5087,7 +6763,17 @@
           <t>Diploma in Law</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr"/>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate in Law OR Advanced Certificate of Secondary
+AU
+Education Examination with at least one Principal pass and one
+AU
+Subsidiary in Principal subjects</t>
+        </is>
+      </c>
       <c r="F129" t="inlineStr">
         <is>
           <t>2</t>
@@ -5123,7 +6809,17 @@
           <t>Diploma in Library and Information Studies</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr"/>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate in Library and Information Studies OR Advanced
+AU
+Certificate of Secondary Education Examination with at least one
+AU
+Principal pass and one Subsidiary in Principal subjects</t>
+        </is>
+      </c>
       <c r="F130" t="inlineStr">
         <is>
           <t>2</t>
@@ -5159,7 +6855,19 @@
           <t>Ordinary Diploma in Clinical Medicine</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr"/>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with
+AU
+four (4) Passes in non-religious Subjects including Chemistry, Biology and
+AU
+Physics/Engineering Sciences. A Pass in Basic Mathematics and English
+AU
+Language Is An Added Advantage.</t>
+        </is>
+      </c>
       <c r="F131" t="inlineStr">
         <is>
           <t>3</t>
@@ -5195,7 +6903,17 @@
           <t>Ordinary Diploma in Environmental Health Sciences</t>
         </is>
       </c>
-      <c r="E132" t="inlineStr"/>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with At
+AU
+Least four (4) Passes in non-religious Subjects including
+AU
+Biology Chemistry and Physics/Engineering Sciences.</t>
+        </is>
+      </c>
       <c r="F132" t="inlineStr">
         <is>
           <t>3</t>
@@ -5231,7 +6949,19 @@
           <t>Ordinary Diploma in Medical Laboratory Sciences</t>
         </is>
       </c>
-      <c r="E133" t="inlineStr"/>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with At
+AU
+Least four (4) Passes in non-religious Subjects including Chemistry,
+AU
+Biology, Physics/Engineering sciences/Basic Mathematics and English
+AU
+Language.</t>
+        </is>
+      </c>
       <c r="F133" t="inlineStr">
         <is>
           <t>3</t>
@@ -5267,7 +6997,19 @@
           <t>Ordinary Diploma in Nursing and Midwifery</t>
         </is>
       </c>
-      <c r="E134" t="inlineStr"/>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with at
+AU
+least four (4) passes in non-religious subjects including
+AU
+Chemistry, Biology and Physics/Engineering Sciences. A pass in Basic
+AU
+Mathematics and English Language is an added advantage.</t>
+        </is>
+      </c>
       <c r="F134" t="inlineStr">
         <is>
           <t>3</t>
@@ -5303,7 +7045,19 @@
           <t>Ordinary Diploma in Pharmaceutical Sciences</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr"/>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with At
+AU
+Least four (4) Passes in non-religious Subjects including Chemistry and
+AU
+Biology. A Pass in Basic Mathematics and English
+AU
+Language Is An Added Advantage.</t>
+        </is>
+      </c>
       <c r="F135" t="inlineStr">
         <is>
           <t>3</t>
@@ -5339,7 +7093,27 @@
           <t>Diploma in Crop Production and Management</t>
         </is>
       </c>
-      <c r="E136" t="inlineStr"/>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate in Crop production,Agriculture General,
+AU
+Certificate in Agriculture and Livestock Production (CALP) OR Advanced
+AU
+Certificate of Secondary Education Examination (ACSEE) Passes in
+AU
+Chemistry, Biology/zoology, Physics, Mathematics, Geography or Science
+AU
+and Practice of Agriculture. The Candidate Must Pass Biology/zoology At
+AU
+Principal Level. Such Candidates Must also
+AU
+Passes in English and Mathematics at Certificate of Secondary
+AU
+Education Examination (CSEE)</t>
+        </is>
+      </c>
       <c r="F136" t="inlineStr">
         <is>
           <t>2</t>
@@ -5375,7 +7149,21 @@
           <t>Diploma in Information and Library Sciences(dils)</t>
         </is>
       </c>
-      <c r="E137" t="inlineStr"/>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Technical Certificate(NTA 5) in Librarianship, Records
+AU
+Management OR Advanced Certificate of Secondary Education with at
+AU
+least one Principal Pass in Mathematics, Physics, Biology, Chemistry,
+AU
+Science and Practice of Agriculture, Geography, Economics,
+AU
+Commerce, History, English, French and Kiswahili</t>
+        </is>
+      </c>
       <c r="F137" t="inlineStr">
         <is>
           <t>2</t>
@@ -5411,7 +7199,21 @@
           <t>Diploma in Information Technology</t>
         </is>
       </c>
-      <c r="E138" t="inlineStr"/>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate in Information Technology,Computer Engineering
+AU
+OR Advanced Certificate of Secondary Education with at least one
+AU
+Principal Pass in Mathematics, Physics, Biology, Chemistry,
+AU
+Science and Practice of Agriculture, Geography, Economics,
+AU
+Commerce, History, English, French and Kiswahili.</t>
+        </is>
+      </c>
       <c r="F138" t="inlineStr">
         <is>
           <t>2</t>
@@ -5447,7 +7249,21 @@
           <t>Diploma in Laboratory Technology</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr"/>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Basic Certificate in Laboratory Technology with GPA 2.0 from
+AU
+recognized institution OR Advanced Certificate of Secondary Education
+AU
+with at least one Principal Pass in Mathematics, Physics,
+AU
+Biology, Chemistry, Science and Practice of Agriculture, Geography,
+AU
+Economics, Commerce, History, English, French and Kiswahili.</t>
+        </is>
+      </c>
       <c r="F139" t="inlineStr">
         <is>
           <t>2</t>
@@ -5483,7 +7299,21 @@
           <t>Diploma in Records, Archives and Information Management (dram)</t>
         </is>
       </c>
-      <c r="E140" t="inlineStr"/>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Technical Certificate (NTA level 5) in Records Management,
+AU
+Librarianship OR Advanced Certificate of Secondary Education with at
+AU
+least one Principal pass in Mathematics, Physics, Biology, Chemistry,
+AU
+Science and Practice of Agriculture, Geography, Economics,
+AU
+Commerce, History, English, French and Kiswahili</t>
+        </is>
+      </c>
       <c r="F140" t="inlineStr">
         <is>
           <t>2</t>
@@ -5519,7 +7349,27 @@
           <t>Diploma in Tropical Animal Health and Production</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr"/>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate in Animal Health (AGRO VET), Certificate in Animal
+AU
+Health and Production (AHPC), Certificate in Agriculture and Livestock
+AU
+Production (CALP) OR Advanced Certificate of Secondary Education
+AU
+Examination (ACSEE) Passes in Chemistry, Biology/zoology, Physics,
+AU
+Mathematics, Geography or Science and Practice of Agriculture. The
+AU
+Candidate Must Pass Biology/zoology At Principal
+AU
+Level. Such Candidates Must also Passes in English and Mathematics at
+AU
+Certificate of Secondary Education Examination (CSEE)</t>
+        </is>
+      </c>
       <c r="F141" t="inlineStr">
         <is>
           <t>2</t>
@@ -5555,7 +7405,17 @@
           <t>Diploma in Banking and Finance</t>
         </is>
       </c>
-      <c r="E142" t="inlineStr"/>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate in Banking and Finance OR Advanced Certificate of
+AU
+Secondary Education Examination (ACSEE) with one Principal pass and
+AU
+one Subsidiary in Principal subjects</t>
+        </is>
+      </c>
       <c r="F142" t="inlineStr">
         <is>
           <t>2</t>
@@ -5628,7 +7488,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Diploma in Business Administration (human</t>
+          <t>Diploma in Business Administration (human Resource)</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -5671,7 +7531,17 @@
           <t>Diploma in Business Administration (marketing)</t>
         </is>
       </c>
-      <c r="E145" t="inlineStr"/>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate in Business Administration; OR Advanced
+AU
+Certificate of Secondary Education Examination (ACSEE) with at least one
+AU
+Principal pass and one Subsidiary in Principal subjects</t>
+        </is>
+      </c>
       <c r="F145" t="inlineStr">
         <is>
           <t>2</t>
@@ -5707,7 +7577,19 @@
           <t>Diploma in Business Administration (procurement)</t>
         </is>
       </c>
-      <c r="E146" t="inlineStr"/>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate in Business Administration, Procurement and
+AU
+Supply OR Advanced Certificate of Secondary Education Examination
+AU
+(ACSEE) with at least one Principal pass and one Subsidiary in Principal
+AU
+subjects</t>
+        </is>
+      </c>
       <c r="F146" t="inlineStr">
         <is>
           <t>2</t>
@@ -5743,7 +7625,17 @@
           <t>Diploma in Business Administration - Accounting</t>
         </is>
       </c>
-      <c r="E147" t="inlineStr"/>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate in Business Administration - Accounting OR
+AU
+Advanced Certificate of Secondary Education Examination (ACSEE) with
+AU
+one Principal pass and one Subsidiary pass in Principal subjects</t>
+        </is>
+      </c>
       <c r="F147" t="inlineStr">
         <is>
           <t>2</t>
@@ -5779,7 +7671,17 @@
           <t>Diploma in Business Administration - Marketing</t>
         </is>
       </c>
-      <c r="E148" t="inlineStr"/>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate in Business Administration - Marketing OR Advanced
+AU
+Certificate of Secondary Education Examination (ACSEE) with one
+AU
+Principal pass and one Subsidiary in Principal subjects</t>
+        </is>
+      </c>
       <c r="F148" t="inlineStr">
         <is>
           <t>2</t>
@@ -5815,7 +7717,17 @@
           <t>Diploma in Community Development</t>
         </is>
       </c>
-      <c r="E149" t="inlineStr"/>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate in Community Development OR Advanced
+AU
+Certificate of Secondary Education Examination (ACSEE) with one
+AU
+Principal pass and one Subsidiary in Principal subjects</t>
+        </is>
+      </c>
       <c r="F149" t="inlineStr">
         <is>
           <t>2</t>
@@ -5851,7 +7763,19 @@
           <t>Diploma in Computer System Maintanance</t>
         </is>
       </c>
-      <c r="E150" t="inlineStr"/>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Technician Certificate (NTA Level 5) in Computer
+AU
+Maintenance,Computer Engineering OR Advanced Certificate of
+AU
+Secondary Education Examination (ACSEE) with One Principal Pass and
+AU
+one Subsidiary Principal subjects</t>
+        </is>
+      </c>
       <c r="F150" t="inlineStr">
         <is>
           <t>2</t>
@@ -5887,7 +7811,17 @@
           <t>Diploma in Law</t>
         </is>
       </c>
-      <c r="E151" t="inlineStr"/>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate in Law OR Advanced Certificate of Secondary
+AU
+Education Examination (ACSEE) with at least one Principal pass and one
+AU
+Subsidiary in Principal subjects</t>
+        </is>
+      </c>
       <c r="F151" t="inlineStr">
         <is>
           <t>2</t>
@@ -5923,7 +7857,19 @@
           <t>Diploma in Project Planning and Management</t>
         </is>
       </c>
-      <c r="E152" t="inlineStr"/>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Technician Certificate (NTA LEVEL 5) in Project Planning and
+AU
+Management or Advanced Certificate of Secondary Education
+AU
+Examination (ACSEE) with at least one Principal pass and one
+AU
+Subsidiary in Principal subjects</t>
+        </is>
+      </c>
       <c r="F152" t="inlineStr">
         <is>
           <t>2</t>
@@ -5959,7 +7905,15 @@
           <t>Diploma in Theology</t>
         </is>
       </c>
-      <c r="E153" t="inlineStr"/>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with
+AU
+four (4) passes in non-religious subjects</t>
+        </is>
+      </c>
       <c r="F153" t="inlineStr">
         <is>
           <t>3</t>
@@ -5995,10 +7949,26 @@
           <t>Ordinary Diploma in Community Development</t>
         </is>
       </c>
-      <c r="E154" t="inlineStr"/>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with
+AU
+At Least four (4) Passes in non-religious Subjects
+AU
+Holders of Basic Technician Certificate (NTA Level 4) in Community
+AU
+Development, Gender, Youth Work or Advanced Certificate of Secondary
+AU
+Education (ACSEE) with one Principal Pass and one
+AU
+Subsidiary.</t>
+        </is>
+      </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 / 2</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -6031,7 +8001,19 @@
           <t>Ordinary Diploma in Medical Laboratory Sciences</t>
         </is>
       </c>
-      <c r="E155" t="inlineStr"/>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with At
+AU
+Least four (4) Passes in non-religious Subjects including Chemistry,
+AU
+Biology, Physics/Engineering sciences/Basic Mathematics and English
+AU
+Language.</t>
+        </is>
+      </c>
       <c r="F155" t="inlineStr">
         <is>
           <t>3</t>
@@ -6067,7 +8049,19 @@
           <t>Ordinary Diploma in Nursing and Midwifery</t>
         </is>
       </c>
-      <c r="E156" t="inlineStr"/>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with at
+AU
+least four (4) passes in non-religious subjects including
+AU
+Chemistry, Biology and Physics/Engineering Sciences. A pass in Basic
+AU
+Mathematics and English Language is an added advantage.</t>
+        </is>
+      </c>
       <c r="F156" t="inlineStr">
         <is>
           <t>3</t>
@@ -6103,7 +8097,19 @@
           <t>Ordinary Diploma in Pharmaceutical Sciences</t>
         </is>
       </c>
-      <c r="E157" t="inlineStr"/>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with At
+AU
+Least four (4) Passes in non-religious Subjects including Chemistry and
+AU
+Biology. A Pass in Basic Mathematics and English
+AU
+Language Is An Added Advantage.</t>
+        </is>
+      </c>
       <c r="F157" t="inlineStr">
         <is>
           <t>3</t>
@@ -6139,7 +8145,29 @@
           <t>Ordinary Diploma in Science and Laboratory Technology</t>
         </is>
       </c>
-      <c r="E158" t="inlineStr"/>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examinations (CSEE) with
+AU
+at least Four (4) passes in non - religious subjects including
+AU
+Physics/Engineering Science, Basic Mathematics, Chemistry and Biology;
+AU
+OR Holder of General Certificate in Engineering; OR Holder of
+AU
+Certificate of Secondary Education (CSEE) with a Minimum of pass in Basic
+AU
+Mathematics and National Vocational Award (NVA) Level III or Trade Test
+AU
+Certificate of Grade I in the relevant field offered by VETA
+AU
+Accredited Institution.
+AU
+Kinondoni Municipal Council - Dar es Salaam</t>
+        </is>
+      </c>
       <c r="F158" t="inlineStr">
         <is>
           <t>3</t>
@@ -6212,7 +8240,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Ordinary Diploma in Computer Science and</t>
+          <t>Ordinary Diploma in Computer Science and Engineering</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -6252,7 +8280,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Ordinary Diploma in Electrical and Electronics</t>
+          <t>Ordinary Diploma in Electrical and Electronics Engineering</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -6292,7 +8320,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Ordinary Diploma in Electronics and</t>
+          <t>Ordinary Diploma in Electronics and Communication Engineering</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -6335,7 +8363,35 @@
           <t>Ordinary Diploma in Industrial Engineering</t>
         </is>
       </c>
-      <c r="E163" t="inlineStr"/>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examinations (CSEE) with
+AU
+at least Four (4) passes in non-religious subjects including
+AU
+Physics/Engineering Science, Basic Mathematics and Chemistry; OR
+AU
+General Certificate in Engineering; or National Vocational Award (NVA)
+AU
+Level III or Trade Test Certificate Grade I in Industrial Engineering. Or
+AU
+Possession of Certificate of Secondary Education Examination (CSEE) from
+AU
+Technical Secondary Schools with at Least four (4) Passes in nonreligious
+AU
+Subjects, three of which must be Mathematics, Engineering Science,
+AU
+Chemistry and any one of the Following Subjects: Architectural
+AU
+Drafting/building Construction, Electrical Engineering
+AU
+Science/electrical Drafting, Workshop Technology/mechanical
+AU
+Drafting;</t>
+        </is>
+      </c>
       <c r="F163" t="inlineStr">
         <is>
           <t>3</t>
@@ -6371,10 +8427,24 @@
           <t>Ordinary Diploma in Information Technology</t>
         </is>
       </c>
-      <c r="E164" t="inlineStr"/>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examinations (CSEE) with
+AU
+At Least four (4) Passes in non-religious Subjects including
+AU
+Physics/Engineering Science and Basic Mathematics.
+AU
+Holders of Basic Technician Certificate( NTA Level 4) in Information
+AU
+Technology</t>
+        </is>
+      </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 / 2</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -6407,7 +8477,27 @@
           <t>Ordinary Diploma in Mechanical Engineering</t>
         </is>
       </c>
-      <c r="E165" t="inlineStr"/>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate in Secondary Education Examinations (CSEE) with
+AU
+at least four (4) Passes in non-religious Subjects including
+AU
+Physics/Engineering Science, Basic Mathematics and Chemistry; Or
+AU
+Holders of Certificate of Secondary Education (CSEE) with a Minimum of
+AU
+four (4) Passes and National Vocational Award (NVA) Level III or Trade
+AU
+Test Certificate of Grade I in relevant field Offered by VETA accredited
+AU
+Institution; or Holders of General Certificate in
+AU
+Engineering.</t>
+        </is>
+      </c>
       <c r="F165" t="inlineStr">
         <is>
           <t>3</t>
@@ -6443,7 +8533,25 @@
           <t>Ordinary Diploma in Mechatronics Engineering</t>
         </is>
       </c>
-      <c r="E166" t="inlineStr"/>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examinations (CSEE) with
+AU
+at least Four (4) passes in non-religious subjects including
+AU
+Physics/ Engineering Science, Basic Mathematics and Chemistry; OR
+AU
+General Certificate in Engineering; OR National Vocational Award
+AU
+(NVA) Level III or Trade Test Certificate Grade I in Mechatronics
+AU
+Engineering with pass in Certificate of Secondary Education
+AU
+Examination (CSEE)</t>
+        </is>
+      </c>
       <c r="F166" t="inlineStr">
         <is>
           <t>3</t>
@@ -6479,7 +8587,17 @@
           <t>Diploma in Accountancy</t>
         </is>
       </c>
-      <c r="E167" t="inlineStr"/>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate in Accountancy OR Advanced Certificate of
+AU
+Secondary Education with at least one Principal pass and one
+AU
+Subsidiary in Principal subjects</t>
+        </is>
+      </c>
       <c r="F167" t="inlineStr">
         <is>
           <t>2</t>
@@ -6515,7 +8633,17 @@
           <t>Diploma in Business Administration</t>
         </is>
       </c>
-      <c r="E168" t="inlineStr"/>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate in Business Administration OR Advanced Certificate
+AU
+of Secondary Education with at least one (1) Principal pass and one (1)
+AU
+Subsidiary in Principal subjects</t>
+        </is>
+      </c>
       <c r="F168" t="inlineStr">
         <is>
           <t>2</t>
@@ -6551,7 +8679,17 @@
           <t>Diploma in Law</t>
         </is>
       </c>
-      <c r="E169" t="inlineStr"/>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate in Law OR Holder of Advanced Certificate of
+AU
+Secondary Education with at least one Principal pass and one
+AU
+Subsidiary in Principal subjects</t>
+        </is>
+      </c>
       <c r="F169" t="inlineStr">
         <is>
           <t>2</t>
@@ -6587,7 +8725,21 @@
           <t>Technician Certificate in Computing, Information and Communication Technology</t>
         </is>
       </c>
-      <c r="E170" t="inlineStr"/>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with at
+AU
+least Four (4) passes in non-religious subjects including Basic Mathematics
+AU
+and English Language; OR National Vocational Award
+AU
+(NVA Level III) or Trade Test Grade II in ICT with a Certificate of
+AU
+Secondary Education Examination (CSEE)</t>
+        </is>
+      </c>
       <c r="F170" t="inlineStr">
         <is>
           <t>2</t>
@@ -6623,7 +8775,17 @@
           <t>Diploma in Law</t>
         </is>
       </c>
-      <c r="E171" t="inlineStr"/>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate in Law OR Advanced Certificate of Secondary
+AU
+Education Examinations (ACSEE) with one Principal pass and one
+AU
+Subsidiary in Principal subjects</t>
+        </is>
+      </c>
       <c r="F171" t="inlineStr">
         <is>
           <t>2</t>
@@ -6659,10 +8821,30 @@
           <t>Ordinary Diploma in Accountancy</t>
         </is>
       </c>
-      <c r="E172" t="inlineStr"/>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with
+AU
+at least four (4) passes in non-religious subjects including passes in
+AU
+Basic Mathematics OR National Vocational Award (NVA) Level III with a
+AU
+Certificate of Secondary Education Examination (CSEE)
+AU
+Holders of Basic Technician Certificate (NTA Level 4) in Accountancy or
+AU
+Advanced Certificate of Secondary Education Examinations
+AU
+Examination (ACSEE) with At Least one Principal Pass and one
+AU
+Subsidiary in Principal Subjects</t>
+        </is>
+      </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 / 2</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -6695,10 +8877,30 @@
           <t>Ordinary Diploma in Business Administration</t>
         </is>
       </c>
-      <c r="E173" t="inlineStr"/>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with
+AU
+at least four (4) passes in non-religious subjects OR National
+AU
+Vocational Award (NVA) Level III with a Certificate of Secondary
+AU
+Education Examination (CSEE)
+AU
+Holders of Basic Technician Certificate (NTA Level 4) in Business
+AU
+Administration, Marketing and Public Relation or Advanced Certificate
+AU
+of Secondary Education Examination (ACSEE) with one Principal Pass and
+AU
+one Subsidiary in Principal Subjects</t>
+        </is>
+      </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 / 2</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -6733,12 +8935,28 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Holders of Certificate of Secondary Education Examination (CSEE) with</t>
+          <t>Holders of Certificate of Secondary Education Examination (CSEE) with
+AU
+at least Four (4) passes in non-religious subjects including Basic
+AU
+Mathematics and English Language; OR National Vocational Award
+AU
+(NVA Level III) or Trade Test Grade II in ICT with a Certificate of
+AU
+Secondary Education Examination (CSEE)
+AU
+Holders of Basic Technician Certificate (NTA Level 4) in Computer
+AU
+Science, Information Technology, Business Information Technology or
+AU
+Advanced Certificate of Secondary Education Examination (ACSEE) with
+AU
+one Principal Pass and two Subsidiaries.</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 / 2</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -6771,10 +8989,30 @@
           <t>Ordinary Diploma in Journalism</t>
         </is>
       </c>
-      <c r="E175" t="inlineStr"/>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with
+AU
+at least four (4) passes in non-religious subjects including English
+AU
+Language OR National Vocational Award (NVA) Level III with a
+AU
+Certificate of Secondary Education Examination (CSEE)
+AU
+Holders of Basic Technician Certificate ( NTA Level 4) in Journalism,
+AU
+Mass Communication or Advanced Certificate of Secondary Education
+AU
+Examination (ACSEE) with at least one Principal Pass and one
+AU
+Subsidiary in Principal Subjects</t>
+        </is>
+      </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 / 2</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -6804,13 +9042,29 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Ordinary Diploma in Procurement and Supply</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr"/>
+          <t>Ordinary Diploma in Procurement and Supply ST. FRANCIS UNIVERSITY COLLEGE OF HEALTH AND ALLIED SCIENCES (SFUCHAS) (SF) - Private Kilombero District Council - Morogoro</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with
+AU
+at least four (4) passes in non-religious subjects
+AU
+Holders of Basic Technician Certificate (NTA Level 4) in Procurement
+AU
+and Supply, Business Administration and Logistics or Advanced
+AU
+Certificate of Secondary Education Examination (ACSEE) with one
+AU
+Principal Pass and one Subsidiary in Principal Subjects.</t>
+        </is>
+      </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 / 2</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -6843,7 +9097,19 @@
           <t>Ordinary Diploma in Medical Laboratory Sciences</t>
         </is>
       </c>
-      <c r="E177" t="inlineStr"/>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with At
+AU
+Least four (4) Passes in non-religious Subjects including Chemistry,
+AU
+Biology, Physics/Engineering sciences/Basic Mathematics and English
+AU
+Language.</t>
+        </is>
+      </c>
       <c r="F177" t="inlineStr">
         <is>
           <t>3</t>
@@ -6876,10 +9142,22 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Ordinary Diploma in Pharmaceutical Sciences</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr"/>
+          <t>Ordinary Diploma in Pharmaceutical Sciences ST. JOSEPH UNIVERSITY COLLEGE OF HEALTH SCIENCES (REG/UHAS/007) - Private Kinondoni Municipal Council - Dar es Salaam</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with At
+AU
+Least four (4) Passes in non-religious Subjects including
+AU
+Chemistry and Biology. A Pass in Basic Mathematics and English
+AU
+Language Is An Added Advantage.</t>
+        </is>
+      </c>
       <c r="F178" t="inlineStr">
         <is>
           <t>3</t>
@@ -6915,7 +9193,19 @@
           <t>Ordinary Diploma in Nursing and Midwifery</t>
         </is>
       </c>
-      <c r="E179" t="inlineStr"/>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with at
+AU
+least four (4) passes in non-religious subjects including Chemistry, Biology
+AU
+and Physics/Engineering Sciences. A pass in Basic
+AU
+Mathematics and English Language is an added advantage.</t>
+        </is>
+      </c>
       <c r="F179" t="inlineStr">
         <is>
           <t>3</t>
@@ -6948,10 +9238,22 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Ordinary Diploma in Pharmaceutical Sciences</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr"/>
+          <t>Ordinary Diploma in Pharmaceutical Sciences STELLA MARIS MTWARA UNIVERSITY COLLEGE (SAM) - Private Mtwara District Council - Mtwara</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with At
+AU
+Least four (4) Passes in non-religious Subjects including Chemistry and
+AU
+Biology. A Pass in Basic Mathematics and English
+AU
+Language Is An Added Advantage.</t>
+        </is>
+      </c>
       <c r="F180" t="inlineStr">
         <is>
           <t>3</t>
@@ -6984,12 +9286,14 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Technician Certificate in Librarianship and</t>
+          <t>Technician Certificate in Librarianship and Records Management</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Holders of Certificate of Secondary Education Examination (CSEE) with at</t>
+          <t>Holders of Certificate of Secondary Education Examination (CSEE) with at
+AU
+least four (4) passes in non-religious subjects</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -7027,7 +9331,17 @@
           <t>Diploma in Accountancy</t>
         </is>
       </c>
-      <c r="E182" t="inlineStr"/>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate in Accountancy OR Advanced Certificate of
+AU
+Secondary Education Examination (ACSEE) with at least one Principal pass
+AU
+and one subsidiary in Principal subjects</t>
+        </is>
+      </c>
       <c r="F182" t="inlineStr">
         <is>
           <t>2</t>
@@ -7063,7 +9377,17 @@
           <t>Diploma in Business Administration</t>
         </is>
       </c>
-      <c r="E183" t="inlineStr"/>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate in Business Administration OR Advanced Certificate
+AU
+of Secondary Education Examination (ACSEE) with at least one Principal
+AU
+pass and one subsidiary in Principal subjects</t>
+        </is>
+      </c>
       <c r="F183" t="inlineStr">
         <is>
           <t>2</t>
@@ -7099,7 +9423,17 @@
           <t>Diploma in Law</t>
         </is>
       </c>
-      <c r="E184" t="inlineStr"/>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate in Law OR Advanced Certificate of Secondary
+AU
+Education Examination (ACSEE) with at least one Principal pass and one
+AU
+subsidiary in Principal subjects</t>
+        </is>
+      </c>
       <c r="F184" t="inlineStr">
         <is>
           <t>2</t>
@@ -7137,7 +9471,9 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Holders of Technician Certificate (NTA Level 5) in Librarianship and</t>
+          <t>Holders of Technician Certificate (NTA Level 5) in Librarianship and
+AU
+Records Management</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -7175,10 +9511,28 @@
           <t>Ordinary Diploma in Accountancy</t>
         </is>
       </c>
-      <c r="E186" t="inlineStr"/>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with
+AU
+at least four (4) passes in non-religious subjects including Basic
+AU
+Mathematics OR National Vocational Award (NVA ) Level III with a
+AU
+Certificate of Secondary Education Examination (CSEE)
+AU
+Holders of Basic Technician Certificate (NTA Level 4) in Accountancy OR
+AU
+Advanced Certificate of Secondary Education Examination (ACSEE) with
+AU
+one Principal pass and one Subsidiary in Principal Subjects</t>
+        </is>
+      </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 / 2</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
@@ -7211,10 +9565,30 @@
           <t>Ordinary Diploma in Business Administration</t>
         </is>
       </c>
-      <c r="E187" t="inlineStr"/>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with
+AU
+at least four (4) passes in non-religious subjects OR National
+AU
+Vocational Award (NVA) Level III with a Certificate of Secondary
+AU
+Education Examination (CSEE)
+AU
+Holders of Basic Technician Certificate (NTA Level 4) in Business
+AU
+Administration, Human Resource Management, Accounting, Banking and
+AU
+Finance OR Advanced Certificate of Secondary Examination with one
+AU
+Principal pass and one Subsidiary in Principal subjects</t>
+        </is>
+      </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 / 2</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
@@ -7247,10 +9621,28 @@
           <t>Ordinary Diploma in Community Development</t>
         </is>
       </c>
-      <c r="E188" t="inlineStr"/>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with
+AU
+at least four (4) passes in non- religious subjects
+AU
+Holders of Basic Technician Certificate (NTA Level 4) in Community
+AU
+Development, Social Work, Community Health, Gender, Youth Work,
+AU
+Social Protection OR Advanced Certificate of Secondary Education
+AU
+Examination (ACSEE) with one Principal pass and one Subsidiary in
+AU
+principal subjects</t>
+        </is>
+      </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 / 2</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -7283,10 +9675,30 @@
           <t>Ordinary Diploma in Procurement and Supply</t>
         </is>
       </c>
-      <c r="E189" t="inlineStr"/>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with
+AU
+at least four (4) passes in non-religious subjects OR National
+AU
+Vocational Award (NVA) Level III with a Certificate of Secondary
+AU
+Education Examination (CSEE)
+AU
+Holders of Basic Technician Certificate (NTA Level 4) in Procurement
+AU
+and Supply, Logistics, Clearing and Forwarding, Inventory Management
+AU
+OR Advanced Certificate of Secondary Education Examination (ACSEE)
+AU
+with one Principal pass and one Subsidiary pass in Principal subjects</t>
+        </is>
+      </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 / 2</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -7319,10 +9731,26 @@
           <t>Ordinary Diploma in Accounting and Finance</t>
         </is>
       </c>
-      <c r="E190" t="inlineStr"/>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with
+AU
+at least four (4) Passes in non-religious Subjects
+AU
+Holders of Basic Technician Certificate (NTA Level 4) in Accountancy
+AU
+and Finance OR Advanced Certificate of Secondary Examination
+AU
+Education (ACSEE) with at least one Principal pass and one Subsidiary in
+AU
+Principal subjects</t>
+        </is>
+      </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 / 2</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -7355,10 +9783,26 @@
           <t>Ordinary Diploma in Business Administration</t>
         </is>
       </c>
-      <c r="E191" t="inlineStr"/>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with
+AU
+at least four (4) passes in non-religious subjects
+AU
+Holder of Basic Technician Certificate (NTA Level 4) in Business
+AU
+Administration OR Advanced Certificate of Secondary Education
+AU
+Examination (ACSEE) with at least one Principal pass and one subsidiary
+AU
+in Principal subjects</t>
+        </is>
+      </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 / 2</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
@@ -7391,7 +9835,19 @@
           <t>Ordinary Diploma in Clinical Medicine</t>
         </is>
       </c>
-      <c r="E192" t="inlineStr"/>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with
+AU
+four (4) passes in non-religious subjects including Chemistry, Biology and
+AU
+Physics/Engineering Sciences. A pass in Basic Mathematics and English
+AU
+Language is an added advantage</t>
+        </is>
+      </c>
       <c r="F192" t="inlineStr">
         <is>
           <t>3</t>
@@ -7424,13 +9880,29 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Ordinary Diploma in Community Development and</t>
-        </is>
-      </c>
-      <c r="E193" t="inlineStr"/>
+          <t>Ordinary Diploma in Community Development and Social Work</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with
+AU
+at least four (4) passes in non-religious subjects
+AU
+Holders of Basic Technician Certificate (NTA Level 4) in Social Work,
+AU
+Gender and Community Development OR Advanced Certificate of
+AU
+Secondary Education Examination (ACSEE) with at least one principal
+AU
+pass and one Subsidiary in Principal subjects</t>
+        </is>
+      </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 / 2</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
@@ -7463,10 +9935,26 @@
           <t>Ordinary Diploma in Human Resource Management</t>
         </is>
       </c>
-      <c r="E194" t="inlineStr"/>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with
+AU
+at least four (4) passes in non-religious subjects
+AU
+Holders of Basic Technician Certificate (NTA Level 4) in Human
+AU
+Resource Management OR Advanced Certificate of Secondary
+AU
+Examination (ACSEE) with at least one principal pass and one subsidiary
+AU
+in Principal subjects</t>
+        </is>
+      </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 / 2</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
@@ -7501,12 +9989,26 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Holders of Certificate of Secondary Education Examination (CSEE) with</t>
+          <t>Holders of Certificate of Secondary Education Examination (CSEE) with
+AU
+Four (4) passes in non-religious subjects including Basic
+AU
+Mathematics and English Language; OR National Vocational Award
+AU
+(NVA) Level III or Trade Test Grade I with Certificate of Secondary
+AU
+Education Examination (CSEE).
+AU
+Holders of Basic Technician Certificate (NTA Level 4) in Information
+AU
+Technology or Advanced Certificate of Secondary Education
+AU
+Examination (ACSEE) with one Principal Pass and one Subsidiary</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 / 2</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
@@ -7539,10 +10041,24 @@
           <t>Ordinary Diploma in Journalism</t>
         </is>
       </c>
-      <c r="E196" t="inlineStr"/>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with
+AU
+at least four (4) passes in non-religious subjects OR National Vocational
+AU
+Award (NVA) Level III with at least two passes in Certificate of
+AU
+Secondary Education Examination (CSEE)
+AU
+Holder of Basic Technician Certificate (NTA Level 4) in Journalism</t>
+        </is>
+      </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 / 2</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
@@ -7575,10 +10091,24 @@
           <t>Ordinary Diploma in Law</t>
         </is>
       </c>
-      <c r="E197" t="inlineStr"/>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with
+AU
+at least four (4) passes in non-religious subjects
+AU
+Holders of Basic Technician Certificate (NTA Level 4) in Law OR
+AU
+Advanced Certificate of Secondary Education Examination (ACSEE) with
+AU
+at least one principal pass and one subsidiary in Principal subjects</t>
+        </is>
+      </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 / 2</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
@@ -7611,10 +10141,26 @@
           <t>Ordinary Diploma in Library, Records and Information Science</t>
         </is>
       </c>
-      <c r="E198" t="inlineStr"/>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with
+AU
+at least four (4) passes in non-religious subjects
+AU
+Holders Basic Technician Certificate (NTA Level 4) in Records
+AU
+Management and Library and Information Science OR Advanced
+AU
+Certificate of Secondary Examination (ACSEE) one principal pass and one
+AU
+Subsidiary in Principal subjects</t>
+        </is>
+      </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 / 2</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
@@ -7647,7 +10193,19 @@
           <t>Ordinary Diploma in Nursing and Midwifery</t>
         </is>
       </c>
-      <c r="E199" t="inlineStr"/>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with at
+AU
+least four (4) passes in non-religious subjects including Chemistry, Biology
+AU
+and Physics/Engineering Sciences. A pass in Basic
+AU
+Mathematics and English Language is an added advantage.</t>
+        </is>
+      </c>
       <c r="F199" t="inlineStr">
         <is>
           <t>3</t>
@@ -7683,7 +10241,19 @@
           <t>Ordinary Diploma in Pharmaceutical Sciences</t>
         </is>
       </c>
-      <c r="E200" t="inlineStr"/>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with At
+AU
+Least four (4) Passes in non-religious Subjects including Chemistry and
+AU
+Biology. A Pass in Basic Mathematics and English
+AU
+Language Is An Added Advantage.</t>
+        </is>
+      </c>
       <c r="F200" t="inlineStr">
         <is>
           <t>3</t>
@@ -7719,10 +10289,26 @@
           <t>Ordinary Diploma in Procurement and Supplies Management</t>
         </is>
       </c>
-      <c r="E201" t="inlineStr"/>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with
+AU
+at least four (4) passes in non-religious subjects
+AU
+Holder of Basic Technician Certificate (NTA Level 4) in Procurement and
+AU
+Supply OR Advanced Certificate of Secondary Education
+AU
+Examination (ACSEE) with at least one principal pass and one
+AU
+Subsidiary in Principal subjects</t>
+        </is>
+      </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 / 2</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
@@ -7755,7 +10341,15 @@
           <t>Basic Technician Certificate in Hotel Operations</t>
         </is>
       </c>
-      <c r="E202" t="inlineStr"/>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with at
+AU
+least four (4) passes in non-religious subjects</t>
+        </is>
+      </c>
       <c r="F202" t="inlineStr">
         <is>
           <t>1</t>
@@ -7793,7 +10387,9 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Holders of Certificate of Secondary Education Examination (CSEE) with at</t>
+          <t>Holders of Certificate of Secondary Education Examination (CSEE) with at
+AU
+least four (4) passes in non-religious subjects</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -7831,7 +10427,15 @@
           <t>Basic Technician in Hospitality Operation</t>
         </is>
       </c>
-      <c r="E204" t="inlineStr"/>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with at
+AU
+least four (4) passes in non-religious subjects</t>
+        </is>
+      </c>
       <c r="F204" t="inlineStr">
         <is>
           <t>1</t>
@@ -7867,7 +10471,15 @@
           <t>Technician Certificate in Front Office Operations</t>
         </is>
       </c>
-      <c r="E205" t="inlineStr"/>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with at
+AU
+least four (4) passes in non-religious subjects</t>
+        </is>
+      </c>
       <c r="F205" t="inlineStr">
         <is>
           <t>2</t>
@@ -7903,7 +10515,17 @@
           <t>Technician Certificate in Travel and Tourism Operations</t>
         </is>
       </c>
-      <c r="E206" t="inlineStr"/>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examinations (CSEE) with
+AU
+at least four (4) passes in non-religious subject. English Language is an
+AU
+added advantage</t>
+        </is>
+      </c>
       <c r="F206" t="inlineStr">
         <is>
           <t>2</t>
@@ -7939,7 +10561,21 @@
           <t>Diploma in Agriculture Production</t>
         </is>
       </c>
-      <c r="E207" t="inlineStr"/>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Advanced Certificate of Secondary Education Examination
+AU
+(ACSEE) with at least one (1) principle pass in Biology and one (1)
+AU
+subsidiary pass in Chemistry, Physics, Advanced Mathematics, Agriculture
+AU
+Science and Geography. or Possession of (NTA Level 4)
+AU
+Certificate Award in Crop production.</t>
+        </is>
+      </c>
       <c r="F207" t="inlineStr">
         <is>
           <t>2</t>
@@ -7975,7 +10611,23 @@
           <t>Diploma in Animal Health and Production</t>
         </is>
       </c>
-      <c r="E208" t="inlineStr"/>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Certificate of Secondary Education Examination (CSEE) with four (4 Ds)
+AU
+Passes in non-religious Subjects including three (3 Ds) Passes in
+AU
+Biology, Chemistry, Physics/Engineering Sciences, Basic Mathematics,
+AU
+Agriculture Science and Geography; or Possession of National Vocation
+AU
+Award (NVA) Level III or Trade Test Grade I in Animal Husbandry and
+AU
+Possession of Certificate of Secondary Education Examination (CSEE).</t>
+        </is>
+      </c>
       <c r="F208" t="inlineStr">
         <is>
           <t>2</t>
@@ -8013,7 +10665,15 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Holders of Advanced Certificate of Secondary Education Examination</t>
+          <t>Holders of Advanced Certificate of Secondary Education Examination
+AU
+(ACSEE) with at least (1.5); one (1) principle pass in Biology and one
+AU
+(1) subsidiary pass in Chemistry, Physics, Advanced Mathematics,
+AU
+Agriculture Science and Geography. or Possession of (NTA Level 4)
+AU
+Certificate Award in Crop production.</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -8051,7 +10711,19 @@
           <t>Diploma in Financial Administration</t>
         </is>
       </c>
-      <c r="E210" t="inlineStr"/>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Technician Certificate (NTA Level 4) in Financial
+AU
+Administration, Accountancy, Banking and Finance OR Advanced
+AU
+Certificate of Secondary Education Examination (ACSEE) with one
+AU
+Principal pass and two Subsidiary in principal subjects</t>
+        </is>
+      </c>
       <c r="F210" t="inlineStr">
         <is>
           <t>2</t>
@@ -8087,7 +10759,15 @@
           <t>Diploma in Heritage Management and Tourism</t>
         </is>
       </c>
-      <c r="E211" t="inlineStr"/>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with at
+AU
+least four (4) passes in non-religious subjects</t>
+        </is>
+      </c>
       <c r="F211" t="inlineStr">
         <is>
           <t>3</t>
@@ -8123,7 +10803,17 @@
           <t>Diploma in Hospitality and Tourism Management</t>
         </is>
       </c>
-      <c r="E212" t="inlineStr"/>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Technician Certificate (NTA Level 5) in Hospitality and Tourism
+AU
+Management, Hotel Management, Museum, Tour Guiding,
+AU
+Archeology, Food preparation, Food Beverage and Front Office</t>
+        </is>
+      </c>
       <c r="F212" t="inlineStr">
         <is>
           <t>2</t>
@@ -8159,7 +10849,19 @@
           <t>Diploma in Inclusive and Special Needs Education (Direct Form Four)</t>
         </is>
       </c>
-      <c r="E213" t="inlineStr"/>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with at
+AU
+least four (4) passes in non-religious subjects OR Advanced Certificate of
+AU
+Secondary Education Examination (ACSEE) with at least one Principal pass
+AU
+and one subsidiary pass in Principal subjects</t>
+        </is>
+      </c>
       <c r="F213" t="inlineStr">
         <is>
           <t>3</t>
@@ -8195,7 +10897,19 @@
           <t>Diploma in Information Communication Technology with Accounting</t>
         </is>
       </c>
-      <c r="E214" t="inlineStr"/>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Basic Certificate in Computer Science, and Information
+AU
+Technology OR Advanced Certificate of Secondary Education Examination
+AU
+(ACSEE) with at least one Principal pass and one
+AU
+Subsidiary in principal subjects</t>
+        </is>
+      </c>
       <c r="F214" t="inlineStr">
         <is>
           <t>2</t>
@@ -8231,7 +10945,27 @@
           <t>Diploma in Information Technology</t>
         </is>
       </c>
-      <c r="E215" t="inlineStr"/>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holder of Advanced Certificate of Secondary Education Examination
+AU
+(ACSEE) with at least one Principal and one subsidiary in science subjects.
+AU
+A Pass in Mathematics for Computer Science is compulsory while English
+AU
+is compulsory for IT applicants (at least in O-level). OR A holder of
+AU
+Certificate in Computing discipline with Programming and Mathematics
+AU
+recognized by NACTE, NECTA or any higher learning Institution with a GPA
+AU
+of at least 3.0, also the candidate should have
+AU
+Four passes at O level one of which be in Mathematics or English.</t>
+        </is>
+      </c>
       <c r="F215" t="inlineStr">
         <is>
           <t>2</t>
@@ -8267,7 +11001,19 @@
           <t>Diploma in Language with Education</t>
         </is>
       </c>
-      <c r="E216" t="inlineStr"/>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Grade III A Certificate or any recognized Certificate in
+AU
+Education OR Advanced Certificate of Secondary Education Examination
+AU
+(ACSEE) with at least one Principal pass and one
+AU
+subsidiary in principal subjects .</t>
+        </is>
+      </c>
       <c r="F216" t="inlineStr">
         <is>
           <t>2</t>
@@ -8303,7 +11049,19 @@
           <t>Diploma in Librarian and Information Studies</t>
         </is>
       </c>
-      <c r="E217" t="inlineStr"/>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate in Librarianship, information sciences, Records
+AU
+Management OR Advanced Certificate of Secondary Education
+AU
+Examination (ACSEE) with at least one Principal pass and one
+AU
+subsidiary pass in Principal subjects</t>
+        </is>
+      </c>
       <c r="F217" t="inlineStr">
         <is>
           <t>2</t>
@@ -8339,7 +11097,17 @@
           <t>Diploma in Physical Education and Sports Sciences</t>
         </is>
       </c>
-      <c r="E218" t="inlineStr"/>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of a Certificate in Physical Education (PE) or Sports OR Advanced
+AU
+Certificate of Secondary Education Examination (ACSEE) with at least one
+AU
+Principal pass and one subsidiary pass in Principal subjects.</t>
+        </is>
+      </c>
       <c r="F218" t="inlineStr">
         <is>
           <t>2</t>
@@ -8375,7 +11143,15 @@
           <t>Diploma in Physical Education and Sports Sciences</t>
         </is>
       </c>
-      <c r="E219" t="inlineStr"/>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with at
+AU
+least four passes (4) in non religious subjects</t>
+        </is>
+      </c>
       <c r="F219" t="inlineStr">
         <is>
           <t>3</t>
@@ -8411,7 +11187,19 @@
           <t>Diploma in Procurement and Supply Management</t>
         </is>
       </c>
-      <c r="E220" t="inlineStr"/>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders Certificate in Accountancy, Banking and Finance, Marketing,
+AU
+Clearing and Forwarding ,Projects Planning ,Procurement and Supply,
+AU
+Taxation and Economics OR Advanced Certificate of Secondary
+AU
+Examination one Principal pass and one Subsidiary in principal subjects</t>
+        </is>
+      </c>
       <c r="F220" t="inlineStr">
         <is>
           <t>2</t>
@@ -8447,7 +11235,19 @@
           <t>Diploma in Social Work</t>
         </is>
       </c>
-      <c r="E221" t="inlineStr"/>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate in Social Work, Social Welfare, Teaching, Youth
+AU
+Work, Rural Development, Nursing, Community Development OR
+AU
+Advanced Certificate of Secondary Education Examination (ACSEE) with
+AU
+at least one Principal pass and one Subsidiary in Principal subjects</t>
+        </is>
+      </c>
       <c r="F221" t="inlineStr">
         <is>
           <t>2</t>
@@ -8483,7 +11283,15 @@
           <t>Diploma in Social Work</t>
         </is>
       </c>
-      <c r="E222" t="inlineStr"/>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with at
+AU
+least four (4) passes in non-religious subjects</t>
+        </is>
+      </c>
       <c r="F222" t="inlineStr">
         <is>
           <t>3</t>
@@ -8519,7 +11327,17 @@
           <t>Ordinary Diploma in Clinical Dentistry</t>
         </is>
       </c>
-      <c r="E223" t="inlineStr"/>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with at
+AU
+least four (4) passes in non-religious subjects including
+AU
+Chemistry, Biology and Physics/Engineering Sciences</t>
+        </is>
+      </c>
       <c r="F223" t="inlineStr">
         <is>
           <t>3</t>
@@ -8555,7 +11373,19 @@
           <t>Ordinary Diploma in Clinical Medicine</t>
         </is>
       </c>
-      <c r="E224" t="inlineStr"/>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with
+AU
+four (4) passes in non-religious subjects including Chemistry, Biology and
+AU
+Physics/Engineering Sciences. A pass in Basic Mathematics and English
+AU
+Language is an added advantage.</t>
+        </is>
+      </c>
       <c r="F224" t="inlineStr">
         <is>
           <t>3</t>
@@ -8593,7 +11423,9 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Holders of Technician Certificate (NTA Level 5) in Environmental</t>
+          <t>Holders of Technician Certificate (NTA Level 5) in Environmental
+AU
+Health Sciences</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -8633,7 +11465,9 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Holders of Technician Certificate (NTA Level 5) in Hospitality</t>
+          <t>Holders of Technician Certificate (NTA Level 5) in Hospitality
+AU
+Management</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -8671,7 +11505,19 @@
           <t>Ordinary Diploma in Medical Laboratory Sciences</t>
         </is>
       </c>
-      <c r="E227" t="inlineStr"/>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with At
+AU
+Least four (4) Passes in non-religious Subjects including Chemistry,
+AU
+Biology, Physics/Engineering sciences/Basic Mathematics and English
+AU
+Language.</t>
+        </is>
+      </c>
       <c r="F227" t="inlineStr">
         <is>
           <t>3</t>
@@ -8709,7 +11555,9 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Holders of Technician Certificate (NTA Level 5) in Nursing and</t>
+          <t>Holders of Technician Certificate (NTA Level 5) in Nursing and
+AU
+Midwifery</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
@@ -8747,7 +11595,19 @@
           <t>Ordinary Diploma in Pharmaceutical Sciences</t>
         </is>
       </c>
-      <c r="E229" t="inlineStr"/>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with At
+AU
+Least four (4) Passes in non-religious Subjects including Chemistry and
+AU
+Biology. A Pass in Basic Mathematics and English
+AU
+Language Is An Added Advantage.</t>
+        </is>
+      </c>
       <c r="F229" t="inlineStr">
         <is>
           <t>3</t>
@@ -8783,7 +11643,21 @@
           <t>Ordinary Diploma in Tourism Management</t>
         </is>
       </c>
-      <c r="E230" t="inlineStr"/>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Technician Certificate (NTA Level 5) in Hotel Management,
+AU
+Front Office, Food Production, Food and Beverage Services, Pastry and
+AU
+Bakery, House Keeping and Laundry
+AU
+TUMAINI UNIVERSITY DAR ES SALAAM COLLEGE (TD) - Private
+AU
+Kinondoni Municipal Council - Dar es Salaam</t>
+        </is>
+      </c>
       <c r="F230" t="inlineStr">
         <is>
           <t>1</t>
@@ -8819,7 +11693,19 @@
           <t>Diploma in Business Administration and Management</t>
         </is>
       </c>
-      <c r="E231" t="inlineStr"/>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holder of Basic Technician Certificate (NTA Level 4) in Business related
+AU
+Studies, Accounting and Banking, Marketing, Procurement and Supply OR
+AU
+Advanced Certificate of Secondary Education Examination (ACSEE) with
+AU
+one Principal pass and one Subsidiary in Principal subjects</t>
+        </is>
+      </c>
       <c r="F231" t="inlineStr">
         <is>
           <t>2</t>
@@ -8855,7 +11741,17 @@
           <t>Diploma in Law</t>
         </is>
       </c>
-      <c r="E232" t="inlineStr"/>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate in Law OR Advanced Certificate of Secondary
+AU
+Education Examination (ACSEE) with one Principal pass and a
+AU
+subsidiary pass in Principal subjects</t>
+        </is>
+      </c>
       <c r="F232" t="inlineStr">
         <is>
           <t>2</t>
@@ -8891,7 +11787,23 @@
           <t>Ordinary Diploma in Intercultural Relations</t>
         </is>
       </c>
-      <c r="E233" t="inlineStr"/>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Basic Technician Certificate (NTA Level 4) in Intercultural
+AU
+Relations, Heritage OR Advanced Certificate of Secondary Education
+AU
+Examination (ACSEE) with one Principal pass and one subsidiary in
+AU
+principal subjects
+AU
+TUMAINI UNIVERSITY MAKUMIRA (TUMA) - ARUSHA (MK) - Private
+AU
+Arumeru District Council - Arusha</t>
+        </is>
+      </c>
       <c r="F233" t="inlineStr">
         <is>
           <t>2</t>
@@ -8927,7 +11839,17 @@
           <t>Diploma in Law</t>
         </is>
       </c>
-      <c r="E234" t="inlineStr"/>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Law OR Advanced Certificate of Secondary
+AU
+Examination (ACSEE) with at least one Principal pass and one
+AU
+Subsidiary in Principal subjects</t>
+        </is>
+      </c>
       <c r="F234" t="inlineStr">
         <is>
           <t>2</t>
@@ -8963,10 +11885,30 @@
           <t>Ordinary Diploma in Accountancy</t>
         </is>
       </c>
-      <c r="E235" t="inlineStr"/>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with
+AU
+at least four (4) passes in non-religious subjects OR National
+AU
+Vocational Award (NVA ) Level III with at least two (2) passes in
+AU
+Certificate of Secondary Education Examinations (CSEE)
+AU
+Holder of Basic Technician Certificate (NTA Level 4) in Accountancy,
+AU
+Finance and Banking, Business Administration, Procurement and
+AU
+Supply OR Advanced Certificate of Secondary Education Examination
+AU
+(ACSEE) with one Principal pass and one Subsidiary in Principal subjects</t>
+        </is>
+      </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 / 2</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
@@ -8999,10 +11941,32 @@
           <t>Ordinary Diploma in Business Administration</t>
         </is>
       </c>
-      <c r="E236" t="inlineStr"/>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with
+AU
+at least four (4) passes in non-religious subjects OR National
+AU
+Vocational Award (NVA ) Level III with at least two (2) passes in
+AU
+Certificate of Secondary Education Examinations (CSEE)
+AU
+Holders of Basic Technician Certificate (NTA Level 4) in Business
+AU
+Administration, Marketing, Accountancy, Finance and Banking, Human
+AU
+Resource Management, Local Government Administration OR Advanced
+AU
+Certificate of Secondary Education Examination (ACSEE) with one
+AU
+Principal Pass and one Subsidiary in Principal Subjects.</t>
+        </is>
+      </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 / 2</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
@@ -9035,10 +11999,28 @@
           <t>Ordinary Diploma in Information Communication Technology</t>
         </is>
       </c>
-      <c r="E237" t="inlineStr"/>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with
+AU
+at least Four (4) passes in non-religious Subjects including a pass in
+AU
+Basic Mathematics and English Language
+AU
+Holders of Basic Technician Certificate (NTA level 4) in Information
+AU
+Communication Technology/Computer Engineering OR Advanced
+AU
+Certificate of Secondary Education Examination (ACSEE) with at least
+AU
+ONE Principal Pass and ONE Subsidiary pass.</t>
+        </is>
+      </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 / 2</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
@@ -9071,10 +12053,30 @@
           <t>Ordinary Diploma in Information Technology</t>
         </is>
       </c>
-      <c r="E238" t="inlineStr"/>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with
+AU
+four (4) passes in non-religious subject OR National Vocational
+AU
+Award (NVA) Level III or Trade test I with two passes in Certificate of
+AU
+Secondary Education Examination (CSEE)
+AU
+Holders of Basic Technician Certificate (NTA Level 4) in Information
+AU
+Technology (ICT) OR Advanced Certificate of Secondary Education
+AU
+Examination (ACSEE) with at least one Principal Pass and one
+AU
+Subsidiary Pass in Principal Subjects.</t>
+        </is>
+      </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 / 2</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
@@ -9107,10 +12109,30 @@
           <t>Ordinary Diploma in Music</t>
         </is>
       </c>
-      <c r="E239" t="inlineStr"/>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with
+AU
+at least four (4) passes in non-religious subjects OR National
+AU
+Vocational Award (NVA ) Level III with at least two (2) passes in
+AU
+Certificate of Secondary Education Examinations (CSEE)
+AU
+Holders of Basic Technician Certificate (NTA Level 4) in Music,
+AU
+Performing Arts, Grade IIIA Certificate, Sports OR Advanced Certificate
+AU
+of Secondary Education Examination (ACSEE) with at least one
+AU
+Principal Pass and one Subsidiary pass in Principal subjects</t>
+        </is>
+      </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 / 2</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
@@ -9143,7 +12165,19 @@
           <t>Diploma in Business Information Technology</t>
         </is>
       </c>
-      <c r="E240" t="inlineStr"/>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Technician Certificate (NTA Level 5) in Computer Science (CS),
+AU
+Information Technology (IT), Business Information Technology
+AU
+(BIT) OR Advanced Certificate of Secondary Examination One Principal
+AU
+Pass and one Subsidiary Pass in Principal Subjects.</t>
+        </is>
+      </c>
       <c r="F240" t="inlineStr">
         <is>
           <t>2</t>
@@ -9181,7 +12215,11 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Holders of Certificate in Education OR Advanced Certificate of</t>
+          <t>Holders of Certificate in Education OR Advanced Certificate of
+AU
+Secondary Education Examination With One Principal Pass and one
+AU
+Subsidiary in Principal Subjects.</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -9219,7 +12257,19 @@
           <t>Diploma in Office Administration and Human Resource Management</t>
         </is>
       </c>
-      <c r="E242" t="inlineStr"/>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate in Office Administration, Human Resource
+AU
+Management, Local Government Administration, Records Management,
+AU
+Secretarial Studies, Community Development, Business
+AU
+Administration.</t>
+        </is>
+      </c>
       <c r="F242" t="inlineStr">
         <is>
           <t>2</t>
@@ -9297,12 +12347,14 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects including Basic Mathematics OR National Vocational Award (NVA ) Level III with at least two (2) passes in Certificate of Secondary Education Examinations (CSEE)</t>
+          <t>Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects including Basic Mathematics OR National Vocational Award (NVA ) Level III with at least two (2) passes in Certificate of Secondary Education Examinations (CSEE)
+AU
+Holders of Basic Technician Certificate (NTA Level 4) in Accountancy OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal Pass and Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 / 2</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
@@ -9337,12 +12389,14 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects OR National Vocational Award (NVA ) Level III with a Certificate of Secondary Education Examinations (CSEE)</t>
+          <t>Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects OR National Vocational Award (NVA ) Level III with a Certificate of Secondary Education Examinations (CSEE)
+AU
+Holders of Basic Technician Certificate (NTA Level 4) in Business Administration, Marketing, Procurement and Supply OR Advanced Certificate of Secondary Education Examination (ACSEE) with one Principal pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 / 2</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
@@ -9372,17 +12426,23 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Ordinary Diploma in Computing and Information</t>
+          <t>Ordinary Diploma in Computing and Information Communication Technology</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Holders of Certificate of Secondary Education Examination (CSEE) with four (4) passes in non-religious subjects including passes in Basic Mathematics and English Language.</t>
+          <t>Holders of Certificate of Secondary Education Examination (CSEE) with four (4) passes in non-religious subjects including passes in Basic Mathematics and English Language.
+AU
+Holders of Basic Technician Certificate (NTA Level 4) in Computing and Information Technology OR Advanced Certificate of Secondary
+AU
+Education Examination (ACSEE) with ONE principal pass and ONE
+AU
+subsidiary pass.</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 / 2</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
@@ -9415,10 +12475,32 @@
           <t>Ordinary Diploma in Procurement and Supply</t>
         </is>
       </c>
-      <c r="E247" t="inlineStr"/>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with
+AU
+at least four (4) passes in non-religious subjects OR National
+AU
+Vocational Award (NVA ) Level III with at least two (2) passes in
+AU
+Certificate of Secondary Education Examinations (CSEE)
+AU
+Holders of Basic Technician Certificate (NTA Level 4) in Procurement and
+AU
+supply, Business Administration, Logistics, Clearing and
+AU
+Forwarding OR Advanced Certificate of Secondary Education
+AU
+Examination (ACSEE) with one Principal Pass and subsidiary in
+AU
+Principal subjects</t>
+        </is>
+      </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 / 2</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
@@ -9448,13 +12530,33 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Ordinary Diploma in Records and Archives</t>
-        </is>
-      </c>
-      <c r="E248" t="inlineStr"/>
+          <t>Ordinary Diploma in Records and Archives Management</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with
+AU
+at least Four (4) passes in Non-religious subjects
+AU
+Holders of Basic Technician Certificate (NTA Level 4) in Record
+AU
+Management, Medical Records, Library and Information Sciences OR
+AU
+Advanced Certificate of Secondary Education Examination (ACSEE) with
+AU
+one Principal pass and Subsidiary pass in Principal subjects
+AU
+UNIVERSITY OF DAR ES SALAAM (UD) - Governmen
+AU
+Kinondoni Municipal Council - Dar es Salaam</t>
+        </is>
+      </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 / 2 / t</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
@@ -9487,7 +12589,17 @@
           <t>Diploma in Chinees Language</t>
         </is>
       </c>
-      <c r="E249" t="inlineStr"/>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Advanced Certificate of Secondary Education Examination with
+AU
+Two Principal Passes in either Language Subjects or Science
+AU
+Subjects.</t>
+        </is>
+      </c>
       <c r="F249" t="inlineStr">
         <is>
           <t>2</t>
@@ -9523,7 +12635,17 @@
           <t>Diploma in Computer Science</t>
         </is>
       </c>
-      <c r="E250" t="inlineStr"/>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate in Computer Sciences, Computer Engineering OR
+AU
+Advanced Certificate of Secondary Education Examination (ACSEE) with
+AU
+One Principal Pass and One Subsidiary Pass in Principal Subjects</t>
+        </is>
+      </c>
       <c r="F250" t="inlineStr">
         <is>
           <t>2</t>
@@ -9559,7 +12681,21 @@
           <t>Diploma in Journalism</t>
         </is>
       </c>
-      <c r="E251" t="inlineStr"/>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate in Journalism, Mass Communication, Public
+AU
+Relation OR Advanced Certificate of Secondary Education Examination
+AU
+(ACSEE) with one Principal pass and one Subsidiary in Principal subjects
+AU
+UNIVERSITY OF DODOMA (DM) - Government
+AU
+Dodoma Municipal Council - Dodoma</t>
+        </is>
+      </c>
       <c r="F251" t="inlineStr">
         <is>
           <t>2</t>
@@ -9595,7 +12731,19 @@
           <t>Diploma in Accounting and Finance</t>
         </is>
       </c>
-      <c r="E252" t="inlineStr"/>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Basic Technician Certificate (NTA Level 4) in Accountancy OR
+AU
+Advanced Certificate of Secondary Education Examination (ACSEE) with
+AU
+at least one Principal pass and one Subsidiary in Principal
+AU
+Subject.</t>
+        </is>
+      </c>
       <c r="F252" t="inlineStr">
         <is>
           <t>2</t>
@@ -9633,7 +12781,15 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Holders of Basic Technician Certificate (NTA Level 4) in Business</t>
+          <t>Holders of Basic Technician Certificate (NTA Level 4) in Business
+AU
+Information Technology, Information Technology, Computer
+AU
+Sciences/Engineering OR Advanced Certificate of Secondary Education
+AU
+Examination (ACSEE) with at least one Principal Pass and one
+AU
+Subsidiary in principal subjects.</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -9673,7 +12829,13 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Holders of Basic Technician Certificate (NTA Level 4) in Computer</t>
+          <t>Holders of Basic Technician Certificate (NTA Level 4) in Computer
+AU
+Sciences/Engineering OR Advanced Certificate of Secondary Education
+AU
+Examination (ACSEE) with at least one Principal Pass and one
+AU
+Subsidiary in principal subjects.</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
@@ -9711,7 +12873,17 @@
           <t>Diploma in Education (chemistry and Biology)</t>
         </is>
       </c>
-      <c r="E255" t="inlineStr"/>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Advanced Certificate of Secondary Education Examination
+AU
+(ACSEE) with one Principal pass and Subsidiary pass in Chemistry and
+AU
+Biology.</t>
+        </is>
+      </c>
       <c r="F255" t="inlineStr">
         <is>
           <t>2</t>
@@ -9747,7 +12919,15 @@
           <t>Diploma in Education (mathematics and Ict)</t>
         </is>
       </c>
-      <c r="E256" t="inlineStr"/>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Advanced Certificate of Secondary Education Examination
+AU
+(ACSEE) with one Principal pass must be in Advanced Mathematics.</t>
+        </is>
+      </c>
       <c r="F256" t="inlineStr">
         <is>
           <t>2</t>
@@ -9783,7 +12963,17 @@
           <t>Diploma in Educational Technology</t>
         </is>
       </c>
-      <c r="E257" t="inlineStr"/>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Advanced Certificate of Secondary Education Examination
+AU
+(ACSEE) with one principal pass in science subjects and subsidiary pass in
+AU
+principal subjects.</t>
+        </is>
+      </c>
       <c r="F257" t="inlineStr">
         <is>
           <t>2</t>
@@ -9819,7 +13009,19 @@
           <t>Diploma in Film Production</t>
         </is>
       </c>
-      <c r="E258" t="inlineStr"/>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Basic Technician Certificate in Film and TV Production,
+AU
+Performing and visual Art, Education, Journalism, Music, Arts and
+AU
+Sports, Education OR Advanced Certificate of Secondary Examination
+AU
+(ACSEE) with at least one Principal pass and one Subsidiary in principal subjects.</t>
+        </is>
+      </c>
       <c r="F258" t="inlineStr">
         <is>
           <t>2</t>
@@ -9975,7 +13177,15 @@
           <t>Diploma in Information and Telecommunication Technology</t>
         </is>
       </c>
-      <c r="E262" t="inlineStr"/>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Advanced Certificate of Secondary Education Examination
+AU
+(ACSEE) with one Principal pass and Subsidiary pass in science subjects.</t>
+        </is>
+      </c>
       <c r="F262" t="inlineStr">
         <is>
           <t>2</t>
@@ -10011,7 +13221,23 @@
           <t>Diploma in Information Communication Technology</t>
         </is>
       </c>
-      <c r="E263" t="inlineStr"/>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Advanced Certificate of Secondary Education Examination (ACSEE) with
+AU
+at least one principal pass and one subsidiary in Science subjects. OR
+AU
+Certificate in Computer Science, Computing and Information
+AU
+Communication Technology, Information Technology or Business
+AU
+Information Technology with an average of ?B? grade PLUS at least four
+AU
+passes in non-religious subjects at O-Level.</t>
+        </is>
+      </c>
       <c r="F263" t="inlineStr">
         <is>
           <t>2</t>
@@ -10047,7 +13273,15 @@
           <t>Diploma in Mass Communication</t>
         </is>
       </c>
-      <c r="E264" t="inlineStr"/>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with at
+AU
+least Four (4) Passes in Non-religious subjects.</t>
+        </is>
+      </c>
       <c r="F264" t="inlineStr">
         <is>
           <t>2</t>
@@ -10085,7 +13319,9 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Holders of Technician Certificate (NTA Level 5) in Medical Laboratory</t>
+          <t>Holders of Technician Certificate (NTA Level 5) in Medical Laboratory
+AU
+Sciences</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
@@ -10123,7 +13359,17 @@
           <t>Diploma in Mineral Exploration and Mining Geology</t>
         </is>
       </c>
-      <c r="E266" t="inlineStr"/>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Advanced Certificate of Secondary Education Examination
+AU
+(CSEE) with one principal pass and one subsidiary pass in the following
+AU
+subjects Advanced Mathematics, Physics or Chemistry</t>
+        </is>
+      </c>
       <c r="F266" t="inlineStr">
         <is>
           <t>2</t>
@@ -10161,7 +13407,9 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Holders of Technician Certificate (NTA Level 5) in Nursing and</t>
+          <t>Holders of Technician Certificate (NTA Level 5) in Nursing and
+AU
+Midwifery</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
@@ -10199,7 +13447,17 @@
           <t>Diploma in Pharmacy</t>
         </is>
       </c>
-      <c r="E268" t="inlineStr"/>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with at
+AU
+four (4) passes including credit Passes in Science Subjects
+AU
+Physics or Basic Mathematics, Chemistry and Biology.</t>
+        </is>
+      </c>
       <c r="F268" t="inlineStr">
         <is>
           <t>3</t>
@@ -10235,7 +13493,21 @@
           <t>Diploma in Procurement and Logistics Management</t>
         </is>
       </c>
-      <c r="E269" t="inlineStr"/>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Basic Technician Certificate (NTA Level 4) in Procurement and
+AU
+Logistic Management, Business Administration, Logistics, Clearing and
+AU
+Forwarding OR Holders of Advanced Certificate of Secondary Education
+AU
+Examination (ACSEE) with One Principal Pass and one
+AU
+Subsidiary in principal subjects.</t>
+        </is>
+      </c>
       <c r="F269" t="inlineStr">
         <is>
           <t>2</t>
@@ -10273,7 +13545,17 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Holders of Basic Technician Certificate (NTA Level 4) in Project</t>
+          <t>Holders of Basic Technician Certificate (NTA Level 4) in Project
+AU
+Planning and Management, Procurement and Logistic Management,
+AU
+Business Administration, Logistics, Clearing and Forwarding, Public
+AU
+Administration, Local Government Administration OR Advanced
+AU
+Certificate of Secondary Education Examination (ACSEE) with One
+AU
+Principal Pass and one Subsidiary pass in principal subjects</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
@@ -10311,7 +13593,21 @@
           <t>Diploma in Public Administration and Management</t>
         </is>
       </c>
-      <c r="E271" t="inlineStr"/>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Basic Technician Certificate (NTA Level 4 ) in Public
+AU
+Administration and Management, Human Resource Management, Local
+AU
+Government Administration OR Advanced Certificate of Secondary
+AU
+Education Examination with one Principal Pass and two Subsidiary in
+AU
+principal Subjects.</t>
+        </is>
+      </c>
       <c r="F271" t="inlineStr">
         <is>
           <t>2</t>
@@ -10349,7 +13645,9 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Holders of Basic Technician Certificate (NTA Level 4) in Statistics or</t>
+          <t>Holders of Basic Technician Certificate (NTA Level 4) in Statistics or
+AU
+Economics</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
@@ -10387,7 +13685,19 @@
           <t>Ordinary Diploma in Nursing and Midwifery</t>
         </is>
       </c>
-      <c r="E273" t="inlineStr"/>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with at
+AU
+least four (4) passes in non-religious subjects including Chemistry, Biology
+AU
+and Physics/Engineering Sciences. A pass in Basic
+AU
+Mathematics and English Language is an added advantage.</t>
+        </is>
+      </c>
       <c r="F273" t="inlineStr">
         <is>
           <t>3</t>
@@ -10423,7 +13733,17 @@
           <t>Diploma in Accountancy</t>
         </is>
       </c>
-      <c r="E274" t="inlineStr"/>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holder of Certificate in Accountancy or Advanced Certificate of
+AU
+Secondary Education Examination (ACSEE) with one Principal Pass and
+AU
+one Subsidiary in Principal Subjects</t>
+        </is>
+      </c>
       <c r="F274" t="inlineStr">
         <is>
           <t>2</t>
@@ -10459,7 +13779,17 @@
           <t>Diploma in Accounting and Finance</t>
         </is>
       </c>
-      <c r="E275" t="inlineStr"/>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders Certificate in Accountancy, Business Administration OR of
+AU
+Advanced Certificate of Secondary Education Examination(ACSEE) with
+AU
+One Principal Pass and one Subsidiary in Relevant Subjects.</t>
+        </is>
+      </c>
       <c r="F275" t="inlineStr">
         <is>
           <t>2</t>
@@ -10495,7 +13825,17 @@
           <t>Diploma in Business Administration</t>
         </is>
       </c>
-      <c r="E276" t="inlineStr"/>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holder of Certificate in Business Administration, Marketing or Advanced
+AU
+Certificate of Secondary Education Examination (ACSEE) with One
+AU
+Principal Pass and one Subsidiary in Relevant Subjects.</t>
+        </is>
+      </c>
       <c r="F276" t="inlineStr">
         <is>
           <t>2</t>
@@ -10531,7 +13871,23 @@
           <t>Diploma in Community Development</t>
         </is>
       </c>
-      <c r="E277" t="inlineStr"/>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate in Community Development, Gender, Social Work,
+AU
+Youth Work, Certificate from Tanzania Police School - Moshi, Tanzania
+AU
+Police Staff College - Kidatu, zanzibar Police College Zanzibar and above
+AU
+or Advanced Certificate of Secondary Education Examination (ACSEE)
+AU
+with One Principal Pass and one Subsidiary in
+AU
+Principal Subjects.</t>
+        </is>
+      </c>
       <c r="F277" t="inlineStr">
         <is>
           <t>2</t>
@@ -10567,7 +13923,21 @@
           <t>Diploma in Counseling Psychology</t>
         </is>
       </c>
-      <c r="E278" t="inlineStr"/>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders Certificate in Community Development, Nursing, Counseling ,
+AU
+Certificate from Tanzania Police School - Moshi, Tanzania Police Staff
+AU
+College - Kidatu, Zanzibar Police College - Zanzibar or Advanced
+AU
+Certificate of Secondary Education Examination (ACSEE) with One
+AU
+Principal Pass and one Subsidiary in Principal Subjects.</t>
+        </is>
+      </c>
       <c r="F278" t="inlineStr">
         <is>
           <t>2</t>
@@ -10603,7 +13973,19 @@
           <t>Diploma in Human Resource Management</t>
         </is>
       </c>
-      <c r="E279" t="inlineStr"/>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holder of Certificate in Human Resource Management, Local
+AU
+Government Administration with OR Advanced Certificate of Secondary
+AU
+Education Examination (ACSEE) with One Principal Pass and one
+AU
+Subsidiary pass Principal Subjects.</t>
+        </is>
+      </c>
       <c r="F279" t="inlineStr">
         <is>
           <t>2</t>
@@ -10641,7 +14023,15 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Holders Certificate in Computer Science (CS), Information Technology</t>
+          <t>Holders Certificate in Computer Science (CS), Information Technology
+AU
+(IT), Business Information Technology (BIT), Records, Achieves and
+AU
+Information Management, Certificate in Education (Grade III A); OR
+AU
+Advanced Certificate of Secondary Examination (ACSEE) with One
+AU
+Principal Pass and Two Subsidiary Pass</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
@@ -10679,7 +14069,17 @@
           <t>Diploma in Journalism</t>
         </is>
       </c>
-      <c r="E281" t="inlineStr"/>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holder of Certificate in Journalism, Public Relation, Mass Communication
+AU
+or Advanced Certificate of Secondary Education Examination (ACSEE)
+AU
+with One Principal Pass and one Subsidiary pass in Principal Subjects.</t>
+        </is>
+      </c>
       <c r="F281" t="inlineStr">
         <is>
           <t>2</t>
@@ -10717,7 +14117,15 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Holder of Certificate in Law, international Relation,Certificate from</t>
+          <t>Holder of Certificate in Law, international Relation,Certificate from
+AU
+Tanzania Police School - Moshi, Tanzania Police Staff College - Kidatu,
+AU
+Zanzibar Police College - Zanzibar and above OR Holder of Advanced
+AU
+Certificate of Secondary Education Examination(ACSEE) with One
+AU
+Principal Pass and one Subsidiary in Principal Subjects.</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
@@ -10755,7 +14163,19 @@
           <t>Diploma in Leisure and Tourism Studies</t>
         </is>
       </c>
-      <c r="E283" t="inlineStr"/>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate in Leisure and Tourism Studies,Tour Guide,
+AU
+Wildlife Management ,Wildlife Tourism OR Advanced Certificate of
+AU
+Secondary Education Examination (ACSEE) with One Principal Pass and
+AU
+one Subsidiary in Principal Subjects.</t>
+        </is>
+      </c>
       <c r="F283" t="inlineStr">
         <is>
           <t>2</t>
@@ -10791,7 +14211,19 @@
           <t>Diploma in Procurement and Material Management</t>
         </is>
       </c>
-      <c r="E284" t="inlineStr"/>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders Certificate in Procurement and Supply, Logistics managements
+AU
+OR Advanced Certificate of Secondary Education Examination(ACSEE)
+AU
+with at least one Principal Pass and one Subsidiary in Principal
+AU
+Subjects</t>
+        </is>
+      </c>
       <c r="F284" t="inlineStr">
         <is>
           <t>2</t>
@@ -10827,7 +14259,15 @@
           <t>Diploma in Theology</t>
         </is>
       </c>
-      <c r="E285" t="inlineStr"/>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with At
+AU
+Least four (4) Passes including Religious Subjects.</t>
+        </is>
+      </c>
       <c r="F285" t="inlineStr">
         <is>
           <t>3</t>
@@ -10860,13 +14300,21 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>Diploma in Arts with Education</t>
-        </is>
-      </c>
-      <c r="E286" t="inlineStr"/>
+          <t>Diploma in Arts with Education Diploma in Clinical Medicine</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with at
+AU
+least four (4) passes in non-religious subjects with division three</t>
+        </is>
+      </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2 / 3</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
@@ -10933,7 +14381,15 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Holders of Basic Technician Certificate (NTA Level 4) in Community</t>
+          <t>Holders of Basic Technician Certificate (NTA Level 4) in Community
+AU
+Development, Community Health, Social Work, Gender, Youth
+AU
+Economics OR Advanced Certificate Of Secondary Education
+AU
+Examination (ACSEE) with at least one Principal pass and one
+AU
+Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
@@ -10971,7 +14427,19 @@
           <t>Diploma in Counselling and Psychology</t>
         </is>
       </c>
-      <c r="E289" t="inlineStr"/>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with at
+AU
+least four (4) passes in non-religious subjects OR National Vocational
+AU
+Award (NVA) Level III with a Certificate of Secondary
+AU
+Education Examination (CSEE)</t>
+        </is>
+      </c>
       <c r="F289" t="inlineStr">
         <is>
           <t>3</t>
@@ -11007,7 +14475,17 @@
           <t>Diploma in Law</t>
         </is>
       </c>
-      <c r="E290" t="inlineStr"/>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Basic Technician Certificate in Law; OR Advance Certificate of
+AU
+Secondary Education Examination (ACSEE) with at least one
+AU
+Principal Pass and one Subsidiary in Principal subjects</t>
+        </is>
+      </c>
       <c r="F290" t="inlineStr">
         <is>
           <t>2</t>
@@ -11045,7 +14523,11 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Holders of Certificate of Secondary Education Examination with</t>
+          <t>Holders of Certificate of Secondary Education Examination with
+AU
+Division three with at least two passes in science subjects (Physics,
+AU
+Chemistry and Biology)</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
@@ -11083,10 +14565,26 @@
           <t>Ordinary Diploma in Accountancy</t>
         </is>
       </c>
-      <c r="E292" t="inlineStr"/>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination with at least
+AU
+four (4) passes in non-religious subjects including Basic
+AU
+Mathematics
+AU
+Holders of Basic Technician Certificate (NTA Level 4) in Accountancy OR
+AU
+Advanced Certificate of Secondary Education Examination (ACSEE) with
+AU
+at least one Principal pass and one Subsidiary in Principal subjects</t>
+        </is>
+      </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 / 2</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
@@ -11119,10 +14617,26 @@
           <t>Ordinary Diploma in Business Administration</t>
         </is>
       </c>
-      <c r="E293" t="inlineStr"/>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination with at least
+AU
+four (4) passes in non-religious subjects
+AU
+Holders of Basic Technician Certificate (NTA Level 4) in Business
+AU
+Administration, Accountancy, Marketing, Procurement and Supply OR
+AU
+Advanced Certificate of Secondary Education Examination (ACSEE) with
+AU
+at least one Principal pass and one Subsidiary in Principal subjects</t>
+        </is>
+      </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 / 2</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
@@ -11155,7 +14669,19 @@
           <t>Ordinary Diploma in Clinical Medicine</t>
         </is>
       </c>
-      <c r="E294" t="inlineStr"/>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with
+AU
+four (4) passes in non-religious subjects including Chemistry, Biology and
+AU
+Physics/Engineering Sciences. A pass in Basic Mathematics and English
+AU
+Language is an added advantage.</t>
+        </is>
+      </c>
       <c r="F294" t="inlineStr">
         <is>
           <t>3</t>
@@ -11191,10 +14717,26 @@
           <t>Ordinary Diploma in Community Development</t>
         </is>
       </c>
-      <c r="E295" t="inlineStr"/>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with
+AU
+at least four (4) passes in non-religious subjects
+AU
+Holders of Basic Technician Certificate (NTA Level 4) in Community
+AU
+Development OR Advanced Certificate of Secondary Education
+AU
+Examination (ACSEE) with at least one Principal pass and one
+AU
+Subsidiary in Principal subjects</t>
+        </is>
+      </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 / 2</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
@@ -11227,10 +14769,30 @@
           <t>Ordinary Diploma in Computing and Information Technology</t>
         </is>
       </c>
-      <c r="E296" t="inlineStr"/>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with
+AU
+at least four (4) passes in non-religious Subjects Include passes in
+AU
+Basic Mathematics and English Language.
+AU
+Holders of Basic Technician Certificate (NTA Level 4) in Information and
+AU
+Communication Technology (ICT) related field or its equivalence
+AU
+recognised by NACTE OR Advanced Certificate of Secondary Education
+AU
+Examination (ACSEE) with at least ONE Principal Pass and ONE
+AU
+Subsidiary Pass in Principal Subjects.</t>
+        </is>
+      </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 / 2</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
@@ -11263,7 +14825,19 @@
           <t>Ordinary Diploma in Medical Laboratory Sciences</t>
         </is>
       </c>
-      <c r="E297" t="inlineStr"/>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with At
+AU
+Least four (4) Passes in non-religious Subjects including Chemistry,
+AU
+Biology, Physics/Engineering sciences/Basic Mathematics and English
+AU
+Language.</t>
+        </is>
+      </c>
       <c r="F297" t="inlineStr">
         <is>
           <t>3</t>
@@ -11299,7 +14873,19 @@
           <t>Ordinary Diploma in Nursing and Midwifery</t>
         </is>
       </c>
-      <c r="E298" t="inlineStr"/>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with at
+AU
+least four (4) passes in non-religious subjects including Chemistry, Biology
+AU
+and Physics/Engineering Sciences. A pass in Basic
+AU
+Mathematics and English Language is an added advantage.</t>
+        </is>
+      </c>
       <c r="F298" t="inlineStr">
         <is>
           <t>3</t>
@@ -11335,10 +14921,26 @@
           <t>Ordinary Diploma in Procurement and Supply</t>
         </is>
       </c>
-      <c r="E299" t="inlineStr"/>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AU
+Holders of Certificate of Secondary Education Examination (CSEE) with
+AU
+at least four (4) passes in non-religious subjects
+AU
+Holders of Basic Technician Certificate (NTA Level 4) in Procurement
+AU
+and Supply, Clearing and Forwarding, Logistics Management OR
+AU
+Advanced Certificate of Secondary Education Examination (ACSEE) with
+AU
+at least one Principal pass and one Subsidiary in Principal subjects</t>
+        </is>
+      </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 / 2</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">

--- a/nacte/nacte_data.xlsx
+++ b/nacte/nacte_data.xlsx
@@ -481,9 +481,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Holders of Certificate in Arts with Education or Certificate of Teachers
-AU
-Education Grade III A</t>
+          <t>Holders of Certificate in Arts with Education or Certificate of Teachers Education Grade III A</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -523,27 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with
-AU
-at least four (4) passes in non-religious subjects including Basic
-AU
-Mathematics and English Language OR National Vocational Award
-AU
-(NVA) Level III or Trade Test Grade I with a Certificate of Secondary
-AU
-Education Examination (CSEE)
-AU
-Holders of Basic Technician Certificate (NTA Level 4) in Business
-AU
-Information Technology, Information Technology, Computer
-AU
-Sciences/Engineering OR Advanced Certificate of Secondary Education
-AU
-Examination (ACSEE) with at least one Principal pass and one
-AU
-Subsidiary in Principal subjects.</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects including Basic Mathematics and English Language OR National Vocational Award (NVA) Level III or Trade Test Grade I with a Certificate of Secondary Education Examination (CSEE) Holders of Basic Technician Certificate (NTA Level 4) in Business Information Technology, Information Technology, Computer Sciences/Engineering OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal pass and one Subsidiary in Principal subjects.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -583,21 +561,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with
-AU
-at least four (4) passes in Non-religious subjects including passes in
-AU
-Basic Mathematics and English Language.
-AU
-Holders of Basic Technician Certificate (NTA Level 4) in Computing and
-AU
-Information Technology OR Advanced Certificate of Secondary
-AU
-Education (ACSEE) with at least one Principal pass and one Subsidiary in
-AU
-Principal subjects.</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in Non-religious subjects including passes in Basic Mathematics and English Language. Holders of Basic Technician Certificate (NTA Level 4) in Computing and Information Technology OR Advanced Certificate of Secondary Education (ACSEE) with at least one Principal pass and one Subsidiary in Principal subjects.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -637,21 +601,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with
-AU
-At Least four (4) Passes in non-religious subjects or National Vocational
-AU
-Award (NVA) Level III with At Least two Passes in Certificate of
-AU
-Secondary Education Examination (CSEE).
-AU
-Holders of NTA 4 in Counseling Psychology and related fields or form VI
-AU
-with at least one Principal and a subsidiary pass excluding religious
-AU
-subjects.</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with At Least four (4) Passes in non-religious subjects or National Vocational Award (NVA) Level III with At Least two Passes in Certificate of Secondary Education Examination (CSEE). Holders of NTA 4 in Counseling Psychology and related fields or form VI with at least one Principal and a subsidiary pass excluding religious subjects.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -691,21 +641,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with
-AU
-at least four (4) passes in non-religious subjects including English
-AU
-Language.
-AU
-Holders of Basic Technician Certificate (NTA Level 4) in Office
-AU
-Administration, Secretarial Studies OR Advanced Certificate of
-AU
-Secondary Education Examinations (ACSEE) with at least one Principal
-AU
-pass and one Subsidiary in Principal subjects.</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects including English Language. Holders of Basic Technician Certificate (NTA Level 4) in Office Administration, Secretarial Studies OR Advanced Certificate of Secondary Education Examinations (ACSEE) with at least one Principal pass and one Subsidiary in Principal subjects.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -745,17 +681,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with
-AU
-Minimum of Division III with at least two (2) passes in Science Subjects
-AU
-(Physics, Chemistry, Biology, Mathematics and Geography)
-AU
-CATHOLIC UNIVERSITY COLLEGE OF MBEYA (TCU/M.10/1.1) - FBO
-AU
-Mbeya City Council - Mbeya</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with Minimum of Division III with at least two (2) passes in Science Subjects (Physics, Chemistry, Biology, Mathematics and Geography) CATHOLIC UNIVERSITY COLLEGE OF MBEYA (TCU/M.10/1.1) - FBO Mbeya City Council - Mbeya</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -795,13 +721,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Holders of Basic Technician Certificate (NTA Level 4) in Accountancy,
-AU
-Finance and Banking OR Advanced Certificate of Secondary Education
-AU
-Examination (ACSEE) with at least one Principal pass and one
-AU
-Subsidiary in Principal subjects.</t>
+          <t>Holders of Basic Technician Certificate (NTA Level 4) in Accountancy, Finance and Banking OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal pass and one Subsidiary in Principal subjects.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -841,15 +761,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Basic Technician Certificate (NTA Level 4) in Business
-AU
-Administration, Finance and Banking, Marketing OR Advanced Certificate
-AU
-of Secondary Education Examination (ACSEE) with at least one Principal
-AU
-pass and one Subsidiary in Principal subjects.</t>
+          <t xml:space="preserve"> Holders of Basic Technician Certificate (NTA Level 4) in Business Administration, Finance and Banking, Marketing OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal pass and one Subsidiary in Principal subjects.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -889,15 +801,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Basic Technician Certificate (NTA Level 4 ) in Community
-AU
-Development, Social Work, Gender, Youth Work OR Advanced Certificate
-AU
-of Secondary Education Examination (ACSEE) with at least one Principal
-AU
-pass and one Subsidiary in Principal subjects.</t>
+          <t xml:space="preserve"> Holders of Basic Technician Certificate (NTA Level 4 ) in Community Development, Social Work, Gender, Youth Work OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal pass and one Subsidiary in Principal subjects.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -937,15 +841,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Basic Technician Certificate (NTA Level 4) in
-AU
-Entrepreneurship Development OR Advanced Certificate of Secondary
-AU
-Education Examination (ACSEE) with at least one Principal pass and one
-AU
-Subsidiary in Principal subjects.</t>
+          <t xml:space="preserve"> Holders of Basic Technician Certificate (NTA Level 4) in Entrepreneurship Development OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal pass and one Subsidiary in Principal subjects.</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -985,17 +881,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Basic Technician certificate (NTA Level 4) in Human
-AU
-Resource, Local Government Administration, Social work, Community
-AU
-Development, Business Management OR Advanced Certificate of
-AU
-Secondary Education Examination (ACSEE) with at least one Principal pass
-AU
-and one Subsidiary in Principal subjects.</t>
+          <t xml:space="preserve"> Holders of Basic Technician certificate (NTA Level 4) in Human Resource, Local Government Administration, Social work, Community Development, Business Management OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal pass and one Subsidiary in Principal subjects.</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1035,15 +921,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Basic Technician Certificate (NTA Level 4) in Computing and
-AU
-Information Technology OR Advanced Certificate of Secondary Education
-AU
-(ACSEE) with at least one Principal pass and one Subsidiary in Principal
-AU
-subjects</t>
+          <t xml:space="preserve"> Holders of Basic Technician Certificate (NTA Level 4) in Computing and Information Technology OR Advanced Certificate of Secondary Education (ACSEE) with at least one Principal pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1115,15 +993,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Basic Technician Certificate (NTA Level 4) in Records
-AU
-Management, Medical Records, Library and information studies OR
-AU
-Advanced Certificate of Secondary Education Examination (ACSEE) with
-AU
-at least one Principal pass and one Subsidiary in Principal subjects</t>
+          <t xml:space="preserve"> Holders of Basic Technician Certificate (NTA Level 4) in Records Management, Medical Records, Library and information studies OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1163,17 +1033,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Basic Technician Certificate (NTA Level 4) in Marketing, Public
-AU
-Relation, Business Administration, Accounting and Finance,
-AU
-Economics OR Advanced Certificate of Secondary Education Examination
-AU
-(ACSEE) with at least one Principal pass and one
-AU
-Subsidiary in Principal subjects.</t>
+          <t xml:space="preserve"> Holders of Basic Technician Certificate (NTA Level 4) in Marketing, Public Relation, Business Administration, Accounting and Finance, Economics OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal pass and one Subsidiary in Principal subjects.</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1213,21 +1073,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Basic Technician Certificate (NTA Level 4) in Procurement and
-AU
-Supply, Logistics, Clearing and Forwarding, Purchasing and Inventory OR
-AU
-Advanced Certificate of Secondary Education Examination (ACSEE) with
-AU
-at least one Principal pass and one
-AU
-Subsidiary in Principal subjects.
-AU
-CATHOLIC UNIVERSITY OF HEALTH AND ALLIED SCIENCES (CUHAS) (CU) - FBO
-AU
-Nyamagana Municipal Council - Mwanza</t>
+          <t xml:space="preserve"> Holders of Basic Technician Certificate (NTA Level 4) in Procurement and Supply, Logistics, Clearing and Forwarding, Purchasing and Inventory OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal pass and one Subsidiary in Principal subjects. CATHOLIC UNIVERSITY OF HEALTH AND ALLIED SCIENCES (CUHAS) (CU) - FBO Nyamagana Municipal Council - Mwanza</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1267,17 +1113,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate in Diagnostic Radiology with passes in science
-AU
-subjects including passes in Biology, Chemistry and Physics in
-AU
-Certificate of Secondary Education Examination (CSEE)
-AU
-DAR ES SALAAM UNIVERSITY COLLEGE OF EDUCATION (DUCE) (U/SAT/42) - Government
-AU
-Temeke Municipal Council - Dar es Salaam</t>
+          <t xml:space="preserve"> Holders of Certificate in Diagnostic Radiology with passes in science subjects including passes in Biology, Chemistry and Physics in Certificate of Secondary Education Examination (CSEE) DAR ES SALAAM UNIVERSITY COLLEGE OF EDUCATION (DUCE) (U/SAT/42) - Government Temeke Municipal Council - Dar es Salaam</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1317,25 +1153,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with
-AU
-at least four (4) passes in Non-religious subjects including two passes in
-AU
-Physics, chemistry, biology, Geography and Mathematics
-AU
-Holders of Basic Technician Certificate in Educational laboratory and
-AU
-Technology OR Advanced Certificate of Secondary Education (ACSEE)
-AU
-with one principal pass and subsidiary pass in Physics, chemistry,
-AU
-Biology, Agriculture, and Geography
-AU
-HUBERT KAIRUKI MEMORIAL UNIVERSITY (HK) - Private
-AU
-Kinondoni Municipal Council - Dar es Salaam</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in Non-religious subjects including two passes in Physics, chemistry, biology, Geography and Mathematics Holders of Basic Technician Certificate in Educational laboratory and Technology OR Advanced Certificate of Secondary Education (ACSEE) with one principal pass and subsidiary pass in Physics, chemistry, Biology, Agriculture, and Geography HUBERT KAIRUKI MEMORIAL UNIVERSITY (HK) - Private Kinondoni Municipal Council - Dar es Salaam</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1375,21 +1193,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with
-AU
-at Least four (4) Passes in non-religious Subjects
-AU
-Holders of Basic Technician Certificate (NTA Level 4) in Social Work,
-AU
-Development Planning and Community Development, Gender,
-AU
-Community Health OR Advanced Certificate of Secondary Examination
-AU
-(ACSEE) with at least one Principal Pass and one Subsidiary in Principal
-AU
-subjects</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at Least four (4) Passes in non-religious Subjects Holders of Basic Technician Certificate (NTA Level 4) in Social Work, Development Planning and Community Development, Gender, Community Health OR Advanced Certificate of Secondary Examination (ACSEE) with at least one Principal Pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1429,13 +1233,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate in Law OR Holders of Advanced Certificate of
-AU
-Secondary Education Examination (CSEE) with one Principal Pass and
-AU
-One Subsidiary in Principal subjects</t>
+          <t xml:space="preserve"> Holders of Certificate in Law OR Holders of Advanced Certificate of Secondary Education Examination (CSEE) with one Principal Pass and One Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1475,17 +1273,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with at
-AU
-least four (4) passes in non-religious subjects and Technician Certificate
-AU
-in Psychology and Counselling OR Advanced Certificate of Secondary
-AU
-Education Examination (ACSEE) with one Principal pass and one subsidiary
-AU
-in Principal subjects</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects and Technician Certificate in Psychology and Counselling OR Advanced Certificate of Secondary Education Examination (ACSEE) with one Principal pass and one subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1525,23 +1313,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with
-AU
-at least four (4) passes in non-religious subjects OR National
-AU
-Vocational Award (NVA III) with a Certificate of Secondary Education
-AU
-Examination(CSEE)
-AU
-Holders of Basic Technician Certificate (NTA level 4) in Accounts,
-AU
-Banking and Finance OR Advanced Certificate in Secondary Education
-AU
-Examination (ACSEE) with at least one Principal pass and one
-AU
-Subsidiary in Principal subjects</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects OR National Vocational Award (NVA III) with a Certificate of Secondary Education Examination(CSEE) Holders of Basic Technician Certificate (NTA level 4) in Accounts, Banking and Finance OR Advanced Certificate in Secondary Education Examination (ACSEE) with at least one Principal pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1581,23 +1353,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with
-AU
-at least four (4) passes in non-religious subjects OR National
-AU
-Vocational Award (NVA III) with two passes in Certificate of Secondary
-AU
-Education Examination(CSEE)
-AU
-Holders of Basic Technician Certificate (NTA level 4) in Business and
-AU
-Business Administration OR Advanced Certificate in Secondary Education
-AU
-Examination (ACSEE) with at least one Principal pass and one Subsidiary
-AU
-in Principal subjects</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects OR National Vocational Award (NVA III) with two passes in Certificate of Secondary Education Examination(CSEE) Holders of Basic Technician Certificate (NTA level 4) in Business and Business Administration OR Advanced Certificate in Secondary Education Examination (ACSEE) with at least one Principal pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1637,23 +1393,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with
-AU
-at least four (4) passes in non-religious subjects OR National
-AU
-Vocational Award (NVA III) with a Certificate of Secondary Education
-AU
-Examination(CSEE)
-AU
-Holders of Basic Technician Certificate (NTA level 4) in Business
-AU
-Administration and Tourism Management OR Advanced Certificate in
-AU
-Secondary Education Examination (ACSEE) with at least one Principal
-AU
-pass and one Subsidiary in Principal subjects</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects OR National Vocational Award (NVA III) with a Certificate of Secondary Education Examination(CSEE) Holders of Basic Technician Certificate (NTA level 4) in Business Administration and Tourism Management OR Advanced Certificate in Secondary Education Examination (ACSEE) with at least one Principal pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1693,27 +1433,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with
-AU
-at least four (4) passes in non-religious subjects OR National
-AU
-Vocational Award (NVA III) with a Certificate of Secondary Education
-AU
-Examination(CSEE)
-AU
-Holders of Basic Technician Certificate (NTA level 4) in Community
-AU
-Development,Business Administration,Social Protection,Social
-AU
-Work,Development Planning,Community Health,Local Goverment
-AU
-Administration,Youth Work OR Advanced Certificate in Secondary
-AU
-Education Examination (ACSEE) with at least one Principal pass and one
-AU
-Subsidiary in Principal subjects</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects OR National Vocational Award (NVA III) with a Certificate of Secondary Education Examination(CSEE) Holders of Basic Technician Certificate (NTA level 4) in Community Development,Business Administration,Social Protection,Social Work,Development Planning,Community Health,Local Goverment Administration,Youth Work OR Advanced Certificate in Secondary Education Examination (ACSEE) with at least one Principal pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1753,21 +1473,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with
-AU
-at least four (4) passes in non-religious subjects OR National
-AU
-Vocational Award (NVA) III/Trade Test II with a Certificate of
-AU
-Secondary Education Examination (CSEE).
-AU
-Holders of Basic Technician Certificate (NTA Level 4) in Computer
-AU
-Engineering OR Advanced Certificate Education Examination (ACSEE)
-AU
-with one Principal pass and one Subsidiary.</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects OR National Vocational Award (NVA) III/Trade Test II with a Certificate of Secondary Education Examination (CSEE). Holders of Basic Technician Certificate (NTA Level 4) in Computer Engineering OR Advanced Certificate Education Examination (ACSEE) with one Principal pass and one Subsidiary.</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1807,21 +1513,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Holders of Certificate of Secondary Education Examination (CSEE) with
-AU
-at least four (4) passes in non-religious subjects OR National
-AU
-Vocational Award (NVA III) with a Certificate of Secondary Education
-AU
-Examination (CSEE)
-AU
-Holders of Basic Technician Certificate (NTA level 4) in Education with
-AU
-Religious Studies, Theology OR Advanced Certificate in Secondary
-AU
-Education Examination (ACSEE) with one Principal pass and one
-AU
-Subsidiary in Principal subjects</t>
+          <t>Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects OR National Vocational Award (NVA III) with a Certificate of Secondary Education Examination (CSEE) Holders of Basic Technician Certificate (NTA level 4) in Education with Religious Studies, Theology OR Advanced Certificate in Secondary Education Examination (ACSEE) with one Principal pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1861,25 +1553,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holder of Certificate of Secondary Education Examination (CSEE) with at
-AU
-least four (4) passes in non religious subjects OR National
-AU
-Vocational Award (NVA) III/Trade Test II with a Certificate of
-AU
-Secondary Education Examination (CSEE).
-AU
-Holders of Basic Technician Certificate (NTA Level 4) in Computer
-AU
-Science, Computing Information Communication Technology, Business
-AU
-Information Technology OR Holder of Advanced Certificate of
-AU
-Secondary Education Examination (ACSEE) with one Principal pass and
-AU
-one Subsidiary pass in Principal subjects.</t>
+          <t xml:space="preserve"> Holder of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non religious subjects OR National Vocational Award (NVA) III/Trade Test II with a Certificate of Secondary Education Examination (CSEE). Holders of Basic Technician Certificate (NTA Level 4) in Computer Science, Computing Information Communication Technology, Business Information Technology OR Holder of Advanced Certificate of Secondary Education Examination (ACSEE) with one Principal pass and one Subsidiary pass in Principal subjects.</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1919,21 +1593,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with
-AU
-at least four (4) passes in non-religious subjects OR National
-AU
-Vocational Award (NVA III) with a Certificate of Secondary Education
-AU
-Examination(CSEE)
-AU
-Holders of Basic Technician Certificate (NTA level 4) in Law OR
-AU
-Advanced Certificate in Secondary Education Examination (ACSEE) with
-AU
-at least one Principal pass and one Subsidiary pass in Principal subjects</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects OR National Vocational Award (NVA III) with a Certificate of Secondary Education Examination(CSEE) Holders of Basic Technician Certificate (NTA level 4) in Law OR Advanced Certificate in Secondary Education Examination (ACSEE) with at least one Principal pass and one Subsidiary pass in Principal subjects</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1973,23 +1633,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with
-AU
-at least four (4) passes in non-religious subjects OR National
-AU
-Vocational Award (NVA III) with a Certificate of Secondary Education
-AU
-Examination(CSEE)
-AU
-Holders of Basic Technician Certificate (NTA Level 4) in Library and
-AU
-Information Studies OR Advanced Certificate in Secondary Education
-AU
-Examination (ACSEE) with at least One Principal Pass and one
-AU
-Subsidiary in Principal subjects</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects OR National Vocational Award (NVA III) with a Certificate of Secondary Education Examination(CSEE) Holders of Basic Technician Certificate (NTA Level 4) in Library and Information Studies OR Advanced Certificate in Secondary Education Examination (ACSEE) with at least One Principal Pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2029,25 +1673,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with
-AU
-at least four (4) passes in non-religious subjects OR National
-AU
-Vocational Award (NVAIII) with a Certificate of Secondary Education
-AU
-Examination(CSEE)
-AU
-Holders of Basic Technician Certificate (NTA level 4) in Procurement
-AU
-and Supply, Business Administration,logistics,Clearing and Forwarding,
-AU
-Accounts banking, Purchasing and Inventory OR Advanced Certificate in
-AU
-Secondary Education Examination (ACSEE) with one Principal pass and
-AU
-one Subsidiary in Principal subjects</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects OR National Vocational Award (NVAIII) with a Certificate of Secondary Education Examination(CSEE) Holders of Basic Technician Certificate (NTA level 4) in Procurement and Supply, Business Administration,logistics,Clearing and Forwarding, Accounts banking, Purchasing and Inventory OR Advanced Certificate in Secondary Education Examination (ACSEE) with one Principal pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2087,19 +1713,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with
-AU
-at least four (4) passes in non-religious subjects
-AU
-Holders of Basic Technician Certificate (NTA level 4) in Counselling
-AU
-Psychology, Education OR Advanced Certificate in Secondary Education
-AU
-Examination (ACSEE) with at least one Principal pass and one Subsidiary
-AU
-in Principal subjects.</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects Holders of Basic Technician Certificate (NTA level 4) in Counselling Psychology, Education OR Advanced Certificate in Secondary Education Examination (ACSEE) with at least one Principal pass and one Subsidiary in Principal subjects.</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2139,25 +1753,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with
-AU
-at least four (4) passes in non-religious subjects OR National
-AU
-Vocational Award (NVA III) with a Certificate of Secondary Education
-AU
-Examination (CSEE)
-AU
-Holders of Basic Technician Certificate (NTA level 4) in Records
-AU
-Management, Medical Records, Health in Information Science, Library
-AU
-and Information Science OR Advanced Certificate in Secondary
-AU
-Education Examination (ACSEE) with one Principal pass and one
-AU
-Subsidiary in Principal subjects</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects OR National Vocational Award (NVA III) with a Certificate of Secondary Education Examination (CSEE) Holders of Basic Technician Certificate (NTA level 4) in Records Management, Medical Records, Health in Information Science, Library and Information Science OR Advanced Certificate in Secondary Education Examination (ACSEE) with one Principal pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2197,17 +1793,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Holders of Certificate in Business Administration, Accountancy,
-AU
-Economics, Banking and Finance, Marketing, Human Resource,
-AU
-Procurement and Supplies, Law and Tax, Local Government
-AU
-Administration OR Advanced Certificate of Secondary Education
-AU
-Examination (ACSEE) with at least one Principal pass and one
-AU
-Subsidiary in Principal subjects</t>
+          <t>Holders of Certificate in Business Administration, Accountancy, Economics, Banking and Finance, Marketing, Human Resource, Procurement and Supplies, Law and Tax, Local Government Administration OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2247,15 +1833,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate in Information Technology, Computer Science
-AU
-Information Technology, Business Information Technology OR Holder of
-AU
-Advanced Certificate of Secondary Education Examination (ACSEE) with
-AU
-one Principal pass and Subsidiary pass in principal subjects</t>
+          <t xml:space="preserve"> Holders of Certificate in Information Technology, Computer Science Information Technology, Business Information Technology OR Holder of Advanced Certificate of Secondary Education Examination (ACSEE) with one Principal pass and Subsidiary pass in principal subjects</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2295,13 +1873,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate in Guidance and Counseling OR Holders of Advanced
-AU
-Certificate of Secondary Education Examination ( ACSEE) with at least
-AU
-one Principal Pass and one Subsidiary in Principal subjects</t>
+          <t xml:space="preserve"> Holders of Certificate in Guidance and Counseling OR Holders of Advanced Certificate of Secondary Education Examination ( ACSEE) with at least one Principal Pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2341,15 +1913,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate in Business Administration, Accountancy, Human
-AU
-Resource, Supplies and Procurement OR Advanced Certificate of
-AU
-Secondary Education Examination (ACSEE) with One Principal Pass and
-AU
-one Subsidiary in Principal subjects</t>
+          <t xml:space="preserve"> Holders of Certificate in Business Administration, Accountancy, Human Resource, Supplies and Procurement OR Advanced Certificate of Secondary Education Examination (ACSEE) with One Principal Pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2389,15 +1953,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate in Conflict Resolution and Peace Studies,
-AU
-Counselling Psychology OR Advanced Certificate of Secondary
-AU
-Education Examination (ACSEE) with one Principal Pass and One
-AU
-Subsidiary in Principal Subjects</t>
+          <t xml:space="preserve"> Holders of Certificate in Conflict Resolution and Peace Studies, Counselling Psychology OR Advanced Certificate of Secondary Education Examination (ACSEE) with one Principal Pass and One Subsidiary in Principal Subjects</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2437,15 +1993,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate in Law, Criminal Investigation, police science,
-AU
-Criminal Investigation, Police Science, OR Advanced Certificate of
-AU
-Secondary Education Examination (ACSEE) with one Principal Pass and
-AU
-one Subsidiary in Principal subjects</t>
+          <t xml:space="preserve"> Holders of Certificate in Law, Criminal Investigation, police science, Criminal Investigation, Police Science, OR Advanced Certificate of Secondary Education Examination (ACSEE) with one Principal Pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2485,15 +2033,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Holders of Certificate in Business Administration, Accountancy, Human
-AU
-Resource Management, Marketing Management, Marketing &amp; Public
-AU
-Relation OR Advanced Certificate of Secondary Education Examination
-AU
-(ACSEE) with at least one Principal Pass and one Subsidiary in Principal
-AU
-subjects</t>
+          <t>Holders of Certificate in Business Administration, Accountancy, Human Resource Management, Marketing Management, Marketing &amp; Public Relation OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal Pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2533,19 +2073,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate in Public Administration, Local Government
-AU
-Administration, Business Administration, Human Resource management,
-AU
-Secretarial services, Community Development,
-AU
-Community Health and Public Relation OR Advanced Certificate of
-AU
-Secondary Education Examination (ACSEE) with at least one Principal
-AU
-Pass and one Subsidiary in Principal subjects</t>
+          <t xml:space="preserve"> Holders of Certificate in Public Administration, Local Government Administration, Business Administration, Human Resource management, Secretarial services, Community Development, Community Health and Public Relation OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal Pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2585,15 +2113,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate in Social Work, Community Health, theology,
-AU
-Community Development, sociology, Social Protection OR Advanced
-AU
-Certificate of Secondary Education Examination (ACSEE) with at least one
-AU
-Principal Pass and one Subsidiary pass in Principal Subjects</t>
+          <t xml:space="preserve"> Holders of Certificate in Social Work, Community Health, theology, Community Development, sociology, Social Protection OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal Pass and one Subsidiary pass in Principal Subjects</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2633,17 +2153,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate in Procurement and Supply, Business
-AU
-Administration, Logistics, Perchance and Inventory/ clearing and
-AU
-forwarding OR Advanced Certificate of Secondary Education Examination
-AU
-(ACSEE) with at least one Principal Pass and one
-AU
-Subsidiary in Principal subjects</t>
+          <t xml:space="preserve"> Holders of Certificate in Procurement and Supply, Business Administration, Logistics, Perchance and Inventory/ clearing and forwarding OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal Pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2683,15 +2193,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with
-AU
-four (4) passes in non-religious subjects including Chemistry, Biology and
-AU
-Physics/Engineering Sciences. A pass in Basic Mathematics and English
-AU
-Language is an added advantage.</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with four (4) passes in non-religious subjects including Chemistry, Biology and Physics/Engineering Sciences. A pass in Basic Mathematics and English Language is an added advantage.</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2731,13 +2233,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with At
-AU
-Least four (4) Passes in non-religious Subjects including
-AU
-Biology Chemistry and Physics/Engineering Sciences.</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with At Least four (4) Passes in non-religious Subjects including Biology Chemistry and Physics/Engineering Sciences.</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2777,15 +2273,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with At
-AU
-Least four (4) Passes in non-religious Subjects including Chemistry,
-AU
-Biology, Physics/Engineering sciences/Basic Mathematics and English
-AU
-Language.</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with At Least four (4) Passes in non-religious Subjects including Chemistry, Biology, Physics/Engineering sciences/Basic Mathematics and English Language.</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2825,19 +2313,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with At
-AU
-Least four (4) Passes in non-religious Subjects including Chemistry and
-AU
-Biology. A Pass in Basic Mathematics and English
-AU
-Language Is An Added Advantage.
-AU
-KILIMANJARO CHRISTIAN MEDICAL UNIVERSITY COLLEGE (KCMU) (KC) - FBO
-AU
-Moshi Municipal Council - Kilimanjaro</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with At Least four (4) Passes in non-religious Subjects including Chemistry and Biology. A Pass in Basic Mathematics and English Language Is An Added Advantage. KILIMANJARO CHRISTIAN MEDICAL UNIVERSITY COLLEGE (KCMU) (KC) - FBO Moshi Municipal Council - Kilimanjaro</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2877,15 +2353,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with at
-AU
-least four (4) passes in non religious Subjects including C pass in Biology
-AU
-and any two subjects in Chemistry, Mathematics,
-AU
-Geography, Economics, Physics/Physical Sciences.</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non religious Subjects including C pass in Biology and any two subjects in Chemistry, Mathematics, Geography, Economics, Physics/Physical Sciences.</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2925,19 +2393,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with At
-AU
-Least four (4) Passes in non-religious Subjects including Chemistry,
-AU
-Biology, Physics/Engineering sciences/Basic Mathematics and English
-AU
-Language.
-AU
-MARIAN UNIVERSITY COLLEGE (MAR) - FBO
-AU
-Bagamoyo District Council - Pwani</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with At Least four (4) Passes in non-religious Subjects including Chemistry, Biology, Physics/Engineering sciences/Basic Mathematics and English Language. MARIAN UNIVERSITY COLLEGE (MAR) - FBO Bagamoyo District Council - Pwani</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2977,19 +2433,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with At
-AU
-Least four (4) Passes in non-religious Subjects including
-AU
-Chemistry and Biology. A Pass in Basic Mathematics and English
-AU
-Language Is An Added Advantage.
-AU
-MBEYA UNIVERSITY OF SCIENCE AND TECHNOLOGY (REG/EOS/003) - Government
-AU
-Mbeya City Council - Mbeya</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with At Least four (4) Passes in non-religious Subjects including Chemistry and Biology. A Pass in Basic Mathematics and English Language Is An Added Advantage. MBEYA UNIVERSITY OF SCIENCE AND TECHNOLOGY (REG/EOS/003) - Government Mbeya City Council - Mbeya</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3029,13 +2473,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with
-AU
-Four (4) Passes in non-religious Subjects, three of which must be
-AU
-Mathematics, Physics, Chemistry/Geography</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with Four (4) Passes in non-religious Subjects, three of which must be Mathematics, Physics, Chemistry/Geography</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -3075,13 +2513,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with at
-AU
-least Four (4) Passes in non-religious Subjects including
-AU
-Physics,Chemistry and Basic Mathematics.</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least Four (4) Passes in non-religious Subjects including Physics,Chemistry and Basic Mathematics.</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -3121,11 +2553,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with at
-AU
-least four (4) passes in non-religious subjects</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -3165,13 +2593,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with at
-AU
-least Four (4) passes in non-religious subjects including
-AU
-Physics, Chemistry and Basic Mathematics.</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least Four (4) passes in non-religious subjects including Physics, Chemistry and Basic Mathematics.</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3211,13 +2633,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with at
-AU
-least Four (4) passes in non-religious subjects including
-AU
-Physics, Chemistry and Basic Mathematics subjects.</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least Four (4) passes in non-religious subjects including Physics, Chemistry and Basic Mathematics subjects.</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3257,11 +2673,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with
-AU
-Four (4) passes in non-religious subjects.</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with Four (4) passes in non-religious subjects.</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -3301,13 +2713,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with at
-AU
-least Four (4) passes in non- religious subjects including a pass in Basic
-AU
-Mathematics and Physics/Engineering Sciences and Chemistry</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least Four (4) passes in non- religious subjects including a pass in Basic Mathematics and Physics/Engineering Sciences and Chemistry</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3347,13 +2753,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with at
-AU
-least Four (4) passes in non- religious subjects including a pass in Basic
-AU
-Mathematics and Physics/Engineering Sciences</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least Four (4) passes in non- religious subjects including a pass in Basic Mathematics and Physics/Engineering Sciences</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -3393,13 +2793,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with at
-AU
-least Four (4) passes in non-religious subjects including passes in Physics,
-AU
-Chemistry and Basic Mathematics.</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least Four (4) passes in non-religious subjects including passes in Physics, Chemistry and Basic Mathematics.</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -3439,35 +2833,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Certificate of Secondary Education Examination (CSEE) with at least four
-AU
-passes in non-religious subjects three of which must be in Mathematics,
-AU
-Physics/Chemistry or Biology. OR Certificate of
-AU
-Secondary Education Examination (CSEE) from Technical Secondary
-AU
-School with a pass in at least four passes in non-religious subjects
-AU
-three of which must be in Mathematics, Engineering
-AU
-Science/Chemistry and Biology and one of the following subjects:
-AU
-Architectural Drafting/Building, Construction, Electrical Engineering,
-AU
-Science/Electrical Drafting or Workshop Technology/Mechanical
-AU
-Drafting. OR Certificate of Secondary Education Examination (CSEE) with
-AU
-at least four passes in non-religious subjects two of which must be in the
-AU
-following subjects Mathematics, Physics, Chemistry or
-AU
-Biology with Trade Test Grade 1 or National Vocational Award (NVA)
-AU
-Level III issued by VETA.</t>
+          <t xml:space="preserve"> Certificate of Secondary Education Examination (CSEE) with at least four passes in non-religious subjects three of which must be in Mathematics, Physics/Chemistry or Biology. OR Certificate of Secondary Education Examination (CSEE) from Technical Secondary School with a pass in at least four passes in non-religious subjects three of which must be in Mathematics, Engineering Science/Chemistry and Biology and one of the following subjects: Architectural Drafting/Building, Construction, Electrical Engineering, Science/Electrical Drafting or Workshop Technology/Mechanical Drafting. OR Certificate of Secondary Education Examination (CSEE) with at least four passes in non-religious subjects two of which must be in the following subjects Mathematics, Physics, Chemistry or Biology with Trade Test Grade 1 or National Vocational Award (NVA) Level III issued by VETA.</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -3507,13 +2873,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with at
-AU
-least Four (4) Passes in non-religious Subjects including
-AU
-Physics, Chemistry and Basic Mathematics.</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least Four (4) Passes in non-religious Subjects including Physics, Chemistry and Basic Mathematics.</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3553,13 +2913,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holder of Certificate of Secondary Education with at least Four (4) passes
-AU
-in non-religious subject including Basic Mathematics and
-AU
-English Language.</t>
+          <t xml:space="preserve"> Holder of Certificate of Secondary Education with at least Four (4) passes in non-religious subject including Basic Mathematics and English Language.</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3599,13 +2953,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with at
-AU
-least Four (4) passes in non-religious subjects including
-AU
-Physics, Chemistry and Basic Mathematics.</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least Four (4) passes in non-religious subjects including Physics, Chemistry and Basic Mathematics.</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3645,13 +2993,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with at
-AU
-least Four (4) passes in non-religious subjects including
-AU
-Physics, Chemistry and Basic Mathematics.</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least Four (4) passes in non-religious subjects including Physics, Chemistry and Basic Mathematics.</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3691,13 +3033,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with at
-AU
-least Four (4) passes in non-religious subjects including
-AU
-Physics, Chemistry and Basic Mathematics.</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least Four (4) passes in non-religious subjects including Physics, Chemistry and Basic Mathematics.</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3737,13 +3073,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with at
-AU
-least Four (4) passes in non-religious subjects including
-AU
-Physics, Chemistry and Basic Mathematics.</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least Four (4) passes in non-religious subjects including Physics, Chemistry and Basic Mathematics.</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3783,13 +3113,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate in Business and Information Technology OR
-AU
-Advanced Certificate of Secondary Education Examination (ACSEE) with
-AU
-at least one principal pass and one subsidiary in Principal subjects</t>
+          <t xml:space="preserve"> Holders of Certificate in Business and Information Technology OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one principal pass and one subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3829,13 +3153,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate in Cooperative Management and Accounting OR
-AU
-Advanced Certificate of Secondary Education Examination (ACSEE) with
-AU
-at least one principal pass and one subsidiary in Principal subjects</t>
+          <t xml:space="preserve"> Holders of Certificate in Cooperative Management and Accounting OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one principal pass and one subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3875,13 +3193,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate in Enterprise Management OR Advanced Certificate
-AU
-of Secondary Education Examination (ACSEE) with at least one principal
-AU
-pass and one subsidiary Principal subjects</t>
+          <t xml:space="preserve"> Holders of Certificate in Enterprise Management OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one principal pass and one subsidiary Principal subjects</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3921,13 +3233,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate in Human Resource Management OR Advanced
-AU
-Certificate of Secondary Education Examination (ACSEE) with at least one
-AU
-principal pass and one subsidiary in Principal subjects</t>
+          <t xml:space="preserve"> Holders of Certificate in Human Resource Management OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one principal pass and one subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3967,13 +3273,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate in Library and Archival Studies OR Advanced
-AU
-Certificate of Secondary Education Examination (ACSEE) with at least one
-AU
-principal pass and one subsidiary Principal subjects</t>
+          <t xml:space="preserve"> Holders of Certificate in Library and Archival Studies OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one principal pass and one subsidiary Principal subjects</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -4013,13 +3313,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate in Accounting, Banking and Finance OR Advanced
-AU
-Certificate of Secondary Education Examination (ACSEE) with at least one
-AU
-principal pass and one subsidiary Principal subjects</t>
+          <t xml:space="preserve"> Holders of Certificate in Accounting, Banking and Finance OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one principal pass and one subsidiary Principal subjects</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -4059,15 +3353,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with at
-AU
-least four (4) passes in non-religious subjects including English and at
-AU
-least three (3) Credits in either Physics, Chemistry, Biology and
-AU
-Mathematics. Physics is a major subject.</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects including English and at least three (3) Credits in either Physics, Chemistry, Biology and Mathematics. Physics is a major subject.</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -4107,15 +3393,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with at
-AU
-least four (4) passes in non-religious subjects including English and at
-AU
-least three (3) Credits one in Physics and two (2) others from either
-AU
-Chemistry, Biology and Mathematics.</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects including English and at least three (3) Credits one in Physics and two (2) others from either Chemistry, Biology and Mathematics.</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -4155,15 +3433,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with at
-AU
-least four (4) Passes in non-religious Subjects, including English and at
-AU
-least Three (3) Credits one in Mathematics and two others from Physics,
-AU
-Chemistry or Biology.</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) Passes in non-religious Subjects, including English and at least Three (3) Credits one in Mathematics and two others from Physics, Chemistry or Biology.</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -4203,15 +3473,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with at
-AU
-least four (4) Passes in non-religious Subjects, including English and at
-AU
-least three (3) Credits one in Mathematics and two others from Physics,
-AU
-Chemistry and Biology.</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) Passes in non-religious Subjects, including English and at least three (3) Credits one in Mathematics and two others from Physics, Chemistry and Biology.</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -4251,15 +3513,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with at
-AU
-least four (4) Passes in non-religious subjects, including English and at
-AU
-least three (3) Credits one in Mathematics and two others from Physics,
-AU
-Chemistry and Biology .</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) Passes in non-religious subjects, including English and at least three (3) Credits one in Mathematics and two others from Physics, Chemistry and Biology .</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -4299,15 +3553,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with at
-AU
-least Four (4) Passes in non-religious Subjects, including English and at
-AU
-least Three (3) Credits one in Mathematics and two others from Physics,
-AU
-Chemistry and Biology</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least Four (4) Passes in non-religious Subjects, including English and at least Three (3) Credits one in Mathematics and two others from Physics, Chemistry and Biology</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -4347,15 +3593,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with at
-AU
-least Four (4) Passes in non-religious Subjects, including English and at
-AU
-least Three (3) Credits one in Mathematics and two others from Physics,
-AU
-Chemistry and Biology .</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least Four (4) Passes in non-religious Subjects, including English and at least Three (3) Credits one in Mathematics and two others from Physics, Chemistry and Biology .</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -4395,15 +3633,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with at
-AU
-least Four (4) Passes in non-religious Subjects, including English and at
-AU
-least Three (3) Credits one in Mathematics and two others from Physics,
-AU
-Chemistry and Biology.</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least Four (4) Passes in non-religious Subjects, including English and at least Three (3) Credits one in Mathematics and two others from Physics, Chemistry and Biology.</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -4443,15 +3673,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with at
-AU
-least Five (5) Passes in non-religious Subjects including Mathematics and
-AU
-English and at least Three (3) Credits in Biology,
-AU
-Chemistry and Physics.</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least Five (5) Passes in non-religious Subjects including Mathematics and English and at least Three (3) Credits in Biology, Chemistry and Physics.</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -4491,15 +3713,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with at
-AU
-least Five (5) Passes in non-religious Subjects, including Mathematics and
-AU
-English and at least Three (3) Credits in Biology,
-AU
-Chemistry and Physics.</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least Five (5) Passes in non-religious Subjects, including Mathematics and English and at least Three (3) Credits in Biology, Chemistry and Physics.</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -4539,15 +3753,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with at
-AU
-least Five (5) Passes in non-religious Subjects including Mathematics and
-AU
-English and at least Three (3) Credits in Biology,
-AU
-Chemistry and Physics,</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least Five (5) Passes in non-religious Subjects including Mathematics and English and at least Three (3) Credits in Biology, Chemistry and Physics,</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -4587,15 +3793,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with at
-AU
-least Five (5) Passes in non-religious Subjects, including Physics,
-AU
-Mathematics and English and Credit passes in Biology and
-AU
-Chemistry.</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least Five (5) Passes in non-religious Subjects, including Physics, Mathematics and English and Credit passes in Biology and Chemistry.</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -4635,15 +3833,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with at
-AU
-least Four (4) Passes in non-religious Subjects with at least Three (3)
-AU
-Credits from Physics, Chemistry, Biology or Mathematics. Credit pass in
-AU
-Engineering subjects is also acceptable as the third credit pass.</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least Four (4) Passes in non-religious Subjects with at least Three (3) Credits from Physics, Chemistry, Biology or Mathematics. Credit pass in Engineering subjects is also acceptable as the third credit pass.</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -4683,15 +3873,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with at
-AU
-least Fiver (5) Passes in non-religious subjects including Biology and
-AU
-Physics, and at least Three Credits in Mathematics,
-AU
-Chemistry and English.</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least Fiver (5) Passes in non-religious subjects including Biology and Physics, and at least Three Credits in Mathematics, Chemistry and English.</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -4731,15 +3913,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with at
-AU
-least Five (5) Passes in non-religious Subjects including Biology and
-AU
-Physics, and at least Three (3) Credits in Mathematics, Chemistry and
-AU
-English.</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least Five (5) Passes in non-religious Subjects including Biology and Physics, and at least Three (3) Credits in Mathematics, Chemistry and English.</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -4779,13 +3953,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate in Islamic Banking and Finance OR Advanced
-AU
-Certificate of Secondary Education Examination (ACSEE) with at least one
-AU
-Principal pass and one Subsidiary in Principal subjects</t>
+          <t xml:space="preserve"> Holders of Certificate in Islamic Banking and Finance OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -4825,13 +3993,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate in Law and Shariah OR Advanced Certificate of
-AU
-Secondary Education Examination (ACSEE) with at least one Principal pass
-AU
-and one Subsidiary in Principal subjects</t>
+          <t xml:space="preserve"> Holders of Certificate in Law and Shariah OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -4871,15 +4033,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate in Procurement and Supply,Logistics,Purchasing
-AU
-and Inventory OR Advanced Certificate of Secondary Education
-AU
-Examination (ACSEE) with at least one Principal pass and one
-AU
-Subsidiary in Principal subjects</t>
+          <t xml:space="preserve"> Holders of Certificate in Procurement and Supply,Logistics,Purchasing and Inventory OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -4919,21 +4073,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with
-AU
-at least four (4) passes in non-religious subjects including Basic
-AU
-Mathematics OR National Vocational Award (NVA) Level III with a
-AU
-Certificate of Secondary Education Examination (CSEE)
-AU
-Holders of Basic Technician Certificate (NTA Level 4) in Accountancy OR
-AU
-Advance Certificate of Secondary Education Examination with at least
-AU
-one Principal pass and one Subsidiary in Principal subjects</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects including Basic Mathematics OR National Vocational Award (NVA) Level III with a Certificate of Secondary Education Examination (CSEE) Holders of Basic Technician Certificate (NTA Level 4) in Accountancy OR Advance Certificate of Secondary Education Examination with at least one Principal pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -4973,25 +4113,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with
-AU
-at least four (4) passes in non-religious subjects OR National
-AU
-Vocational Award (NVA)Level III with a Certificate of Secondary
-AU
-Education Examination (CSEE)
-AU
-Holders of Basic Technician Certificate (NTA Level 4) in Business
-AU
-Administration, Account, Finance and Banking, Marketing,
-AU
-Procurement and Supply OR Advanced Certificate of Secondary
-AU
-Education Examination (ACSEE) with at least one Principal pass and one
-AU
-Subsidiary in Principal subjects</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects OR National Vocational Award (NVA)Level III with a Certificate of Secondary Education Examination (CSEE) Holders of Basic Technician Certificate (NTA Level 4) in Business Administration, Account, Finance and Banking, Marketing, Procurement and Supply OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -5031,23 +4153,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with
-AU
-at least four (4) passes in non-religious subjects OR National
-AU
-Vocational Award (NVA) Level III with a Certificate of Secondary
-AU
-Education Examination (CSEE)
-AU
-Holders of Basic Technician Certificate (NTA Level 4) in Journalism,
-AU
-Mass Communication, TV Production, Media Production OR Advanced
-AU
-Certificate of Secondary Education Examination (ACSEE) with at least
-AU
-one Principal pass and one Subsidiary in Principal subjects</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects OR National Vocational Award (NVA) Level III with a Certificate of Secondary Education Examination (CSEE) Holders of Basic Technician Certificate (NTA Level 4) in Journalism, Mass Communication, TV Production, Media Production OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -5087,15 +4193,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with At
-AU
-Least four (4) Passes in non-religious Subjects including Chemistry,
-AU
-Biology, Physics/Engineering sciences/Basic Mathematics and English
-AU
-Language.</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with At Least four (4) Passes in non-religious Subjects including Chemistry, Biology, Physics/Engineering sciences/Basic Mathematics and English Language.</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -5135,27 +4233,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with
-AU
-Four (4) passes in non-religious subjects including Two (2) Passes in
-AU
-Biology, Chemistry, Physics/Engineering Sciences.
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with
-AU
-Four (4) Passes in non-religious Subjects including two (2) Passes in
-AU
-Biology, Chemistry, Physics/Engineering Sciences; and Possession of
-AU
-Basic Technician Certificate (NTA Level 4) in Science and Laboratory
-AU
-Technology; OR Advanced Certificate of Secondary Education
-AU
-Examination (ACSEE) with one (1) Principal Pass and one (1) Subsidiary
-AU
-Pass in Biology, Chemistry, Physics, Advanced Mathematics.</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with Four (4) passes in non-religious subjects including Two (2) Passes in Biology, Chemistry, Physics/Engineering Sciences. Holders of Certificate of Secondary Education Examination (CSEE) with Four (4) Passes in non-religious Subjects including two (2) Passes in Biology, Chemistry, Physics/Engineering Sciences; and Possession of Basic Technician Certificate (NTA Level 4) in Science and Laboratory Technology; OR Advanced Certificate of Secondary Education Examination (ACSEE) with one (1) Principal Pass and one (1) Subsidiary Pass in Biology, Chemistry, Physics, Advanced Mathematics.</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -5195,21 +4273,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with
-AU
-at least four (4) passes in non-religious subjects including Basic
-AU
-Mathematics
-AU
-Holders of Basic Technician Certificate (NTA level 4) in Accountancy,
-AU
-Business Administration Banking and Finances OR Advanced Certificate
-AU
-of Secondary Education Examination (ACSEE) with at least one
-AU
-Principal pass and one Subsidiary in Principal subjects</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects including Basic Mathematics Holders of Basic Technician Certificate (NTA level 4) in Accountancy, Business Administration Banking and Finances OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -5249,23 +4313,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with
-AU
-at least four (4) passes in Non-Religious Subjects OR National
-AU
-Vocational Award (NVA) III with a Certificate of Secondary Education
-AU
-Examination (CSEE)
-AU
-Holders of Basic Technician Certificate (NTA level 4) in Business
-AU
-Administration OR Advanced Certificate of Secondary Education
-AU
-Examination (ACSEE) with at least one Principal pass and one
-AU
-Subsidiary Principal subjects</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in Non-Religious Subjects OR National Vocational Award (NVA) III with a Certificate of Secondary Education Examination (CSEE) Holders of Basic Technician Certificate (NTA level 4) in Business Administration OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal pass and one Subsidiary Principal subjects</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -5305,25 +4353,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with
-AU
-At Least four (4) Passes in non-religious subjects including Basic
-AU
-Mathematics and English Language or National Vocational Award (NVA
-AU
-Level III) with a Certificate of Secondary Education Examination
-AU
-(CSEE)
-AU
-Holders of Basic Technician Certificate (NTA 4) in Information
-AU
-Technology, Computer Sciences OR Advanced Certificate of Secondary
-AU
-Education Examination (ACSEE) with one Principal pass and one
-AU
-Subsidiary.</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with At Least four (4) Passes in non-religious subjects including Basic Mathematics and English Language or National Vocational Award (NVA Level III) with a Certificate of Secondary Education Examination (CSEE) Holders of Basic Technician Certificate (NTA 4) in Information Technology, Computer Sciences OR Advanced Certificate of Secondary Education Examination (ACSEE) with one Principal pass and one Subsidiary.</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -5363,19 +4393,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of certificate of secondary education examination (CSEE) with
-AU
-at least four (4) passes in non- religious subjects including English
-AU
-Language
-AU
-Holders of Basic Technician Certificate (NTA level 4) in Law OR
-AU
-Advanced Certificate of Secondary Education Examination (ACSEE) with
-AU
-at least one Principal pass and one Subsidiary in Principal subjects</t>
+          <t xml:space="preserve"> Holders of certificate of secondary education examination (CSEE) with at least four (4) passes in non- religious subjects including English Language Holders of Basic Technician Certificate (NTA level 4) in Law OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -5415,19 +4433,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination ( CSEE ) with
-AU
-at least four (4) passes in non- religious subjects
-AU
-Holders of Basic Technician Certificate (NTA Level 4) in Procurement
-AU
-and Supply, Logistics, Clearing and Forwarding OR Advanced
-AU
-Certificate of Secondary Education Examination (ACSEE) with at Least
-AU
-one Principal pass and one Subsidiary in Principal subjects</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination ( CSEE ) with at least four (4) passes in non- religious subjects Holders of Basic Technician Certificate (NTA Level 4) in Procurement and Supply, Logistics, Clearing and Forwarding OR Advanced Certificate of Secondary Education Examination (ACSEE) with at Least one Principal pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -5467,23 +4473,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with
-AU
-at least four (4) passes in non religious subjects OR National
-AU
-Vocational Award (NVA) Level III with a Certificate of Secondary
-AU
-Education Examination (CSEE)
-AU
-Holders of Basic Technician Certificate (NTA Level 4) in Records
-AU
-Management, Medical Records, Library and information studies OR
-AU
-Advanced Certificate of Secondary Education Examination (ACSEE) with
-AU
-at least one Principal pass and one Subsidiary in Principal subjects</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non religious subjects OR National Vocational Award (NVA) Level III with a Certificate of Secondary Education Examination (CSEE) Holders of Basic Technician Certificate (NTA Level 4) in Records Management, Medical Records, Library and information studies OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -5523,23 +4513,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with
-AU
-at least four (4) passes in non-religious subjects
-AU
-Holder of Basic Technician Certificate (NTA Level 4) in Social Work,
-AU
-Gender and Community Development OR Advanced Certificate of
-AU
-Secondary Education Examination (ACSEE) with at Least one Principal
-AU
-pass and one Subsidiary in Principal subjects
-AU
-MZUMBE UNIVERSITY (MU) - Government
-AU
-Mvomero District Council - Morogoro</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects Holder of Basic Technician Certificate (NTA Level 4) in Social Work, Gender and Community Development OR Advanced Certificate of Secondary Education Examination (ACSEE) with at Least one Principal pass and one Subsidiary in Principal subjects MZUMBE UNIVERSITY (MU) - Government Mvomero District Council - Morogoro</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -5579,11 +4553,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Holders of Certificate in Applied Statistics OR Advanced Certificate of
-AU
-Secondary Education with at least one Principal pass and one
-AU
-Subsidiary in Principal subjects</t>
+          <t>Holders of Certificate in Applied Statistics OR Advanced Certificate of Secondary Education with at least one Principal pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -5623,13 +4593,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Holders of Certificate in Applied Statistics OR Advanced Certificate of
-AU
-Secondary Education Examination (ACSEE) with One Principal Pass in
-AU
-Either Chemistry, Biology or Advanced Mathematics and One
-AU
-Subsidiary in any Subject</t>
+          <t>Holders of Certificate in Applied Statistics OR Advanced Certificate of Secondary Education Examination (ACSEE) with One Principal Pass in Either Chemistry, Biology or Advanced Mathematics and One Subsidiary in any Subject</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -5669,19 +4633,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate in Information Technology, Computer Engineering
-AU
-OR Advanced Certificate of Secondary Education
-AU
-Examination (ACSEE) with One Principal Pass in either Physics,
-AU
-Chemistry, Biology or Advanced Mathematics and One Subsidiary
-AU
-MZUMBE UNIVERSITY (MU), MBEYA COLLEGE (MMB) - Government
-AU
-Mbeya City Council - Mbeya</t>
+          <t xml:space="preserve"> Holders of Certificate in Information Technology, Computer Engineering OR Advanced Certificate of Secondary Education Examination (ACSEE) with One Principal Pass in either Physics, Chemistry, Biology or Advanced Mathematics and One Subsidiary MZUMBE UNIVERSITY (MU), MBEYA COLLEGE (MMB) - Government Mbeya City Council - Mbeya</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -5721,13 +4673,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate in Accountancy, Finance and Banking OR Advanced
-AU
-Certificate of Secondary Education Examination (ACSEE) with at least one
-AU
-Principal pass and subsidiary in Principal subjects</t>
+          <t xml:space="preserve"> Holders of Certificate in Accountancy, Finance and Banking OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal pass and subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -5767,15 +4713,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate in Business Management, Procurement and Supply
-AU
-Chain, Accountancy OR Advanced Certificate of Secondary Education
-AU
-Examination (ACSEE)With at Least one Principal pass and one subsidiary
-AU
-in Principal subjects.</t>
+          <t xml:space="preserve"> Holders of Certificate in Business Management, Procurement and Supply Chain, Accountancy OR Advanced Certificate of Secondary Education Examination (ACSEE)With at Least one Principal pass and one subsidiary in Principal subjects.</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -5815,17 +4753,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Human Resources Management, Local
-AU
-Government Administration, Social Work, Law, Business Management,
-AU
-Community development, Records and Archives Management. OR
-AU
-Advanced Certificate of Secondary Education Examination (ACSEE) with
-AU
-at Least one Principal Pass and one Subsidiary in Principal subjects</t>
+          <t xml:space="preserve"> Holders of Certificate of Human Resources Management, Local Government Administration, Social Work, Law, Business Management, Community development, Records and Archives Management. OR Advanced Certificate of Secondary Education Examination (ACSEE) with at Least one Principal Pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -5865,13 +4793,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate in Law OR Advanced Certificate of Secondary
-AU
-Education Examination (ACSEE) with at Least one Principal Pass and one
-AU
-subsidiary in Principal subjects</t>
+          <t xml:space="preserve"> Holders of Certificate in Law OR Advanced Certificate of Secondary Education Examination (ACSEE) with at Least one Principal Pass and one subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -5911,15 +4833,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate in Logistics Management, Business Administration,
-AU
-Accountancy, Banking OR Advanced Certificate of Secondary Education
-AU
-with at Least Principal Pass and one Subsidiary in
-AU
-Principal subjects</t>
+          <t xml:space="preserve"> Holders of Certificate in Logistics Management, Business Administration, Accountancy, Banking OR Advanced Certificate of Secondary Education with at Least Principal Pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -5959,15 +4873,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate in Procurement and Supply Chain Business
-AU
-Management, Public Administration, Accountancy OR Advanced
-AU
-Certificate of Secondary Education Examination (ACSEE) with at Least one
-AU
-Principal Pass and one subsidiary in Principal subjects</t>
+          <t xml:space="preserve"> Holders of Certificate in Procurement and Supply Chain Business Management, Public Administration, Accountancy OR Advanced Certificate of Secondary Education Examination (ACSEE) with at Least one Principal Pass and one subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -6007,11 +4913,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with at
-AU
-least four (4) passes in non-religious subjects</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -6051,11 +4953,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of certificate of Secondary Education Examination (CSEE) with
-AU
-four (4) passes in non-religious subjects</t>
+          <t xml:space="preserve"> Holders of certificate of Secondary Education Examination (CSEE) with four (4) passes in non-religious subjects</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -6095,13 +4993,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Technician Certificate (NTA Level 5)in Youth work OR
-AU
-Advanced Certificate of Secondary Education Examination (ACSEE) with
-AU
-at least one Principal pass and Subsidiary in Principal subjects</t>
+          <t xml:space="preserve"> Holders of Technician Certificate (NTA Level 5)in Youth work OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal pass and Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -6141,9 +5033,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Holders of Basic Technician Certificate (NTA Level 4) in Distance
-AU
-Education</t>
+          <t>Holders of Basic Technician Certificate (NTA Level 4) in Distance Education</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -6183,15 +5073,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of certificate of secondary education examination (CSEE) with
-AU
-Four passes or with two passes for those who have NVA level III recognized
-AU
-by VETA and Grade III A OR Basic technician certificate in teaching with
-AU
-an average of B and above</t>
+          <t xml:space="preserve"> Holders of certificate of secondary education examination (CSEE) with Four passes or with two passes for those who have NVA level III recognized by VETA and Grade III A OR Basic technician certificate in teaching with an average of B and above</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -6231,9 +5113,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Holders of Technician Certificate (NTA level 5) in Library and
-AU
-Information studies</t>
+          <t>Holders of Technician Certificate (NTA level 5) in Library and Information studies</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -6273,11 +5153,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Technician Certificate ( NTA Level 5 ) in Animal Production,
-AU
-General Agriculture With 2.0 GPA and above.</t>
+          <t xml:space="preserve"> Holders of Technician Certificate ( NTA Level 5 ) in Animal Production, General Agriculture With 2.0 GPA and above.</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -6317,19 +5193,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holder of Certificate of Secondary Education Examination (CSEE) with
-AU
-four Passes or with two Passes for Those Who Have Nva Level III
-AU
-Recognized By Veta and Grade III A or Basic Technician Certificate in
-AU
-Teaching with An Average of B+ and above or Holder of Advinced
-AU
-Certificate of Secondary Education with one Principal Pass and one
-AU
-Subsidiary from Any two Subjects</t>
+          <t xml:space="preserve"> Holder of Certificate of Secondary Education Examination (CSEE) with four Passes or with two Passes for Those Who Have Nva Level III Recognized By Veta and Grade III A or Basic Technician Certificate in Teaching with An Average of B+ and above or Holder of Advinced Certificate of Secondary Education with one Principal Pass and one Subsidiary from Any two Subjects</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -6369,19 +5233,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with
-AU
-at least four (4) passes in non-religious subjects
-AU
-Holders of Basic Technical Certificate Certificate ( NTA Level 4) in
-AU
-Accountancy OR Advanced Certificate of Secondary Education
-AU
-Examination (ACSEE) with at least one Principal pass and one
-AU
-Subsidiary in Principal subjects</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects Holders of Basic Technical Certificate Certificate ( NTA Level 4) in Accountancy OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -6421,21 +5273,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with
-AU
-at least four (4) passes in non-religious subjects
-AU
-Holders of Basic Technical Certificate Certificate (NTA Level 4) in
-AU
-Business Administration, Accountancy Marketing and Procurement and
-AU
-Supply OR Advanced Certificate of Secondary Education Examination
-AU
-(ACSEE) with at least one Principal Pass and one Subsidiary in Principal
-AU
-subjects</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects Holders of Basic Technical Certificate Certificate (NTA Level 4) in Business Administration, Accountancy Marketing and Procurement and Supply OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal Pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -6475,19 +5313,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with
-AU
-Four (4) passes in non-religious subjects.
-AU
-Holders of Basic Technician Certificate (NTA Level 4) in Information
-AU
-Communication Technology OR Advanced Certificate of Secondary
-AU
-Education Examination (ACSEE) with one Principal Pass and One
-AU
-Subsidiary Pass.</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with Four (4) passes in non-religious subjects. Holders of Basic Technician Certificate (NTA Level 4) in Information Communication Technology OR Advanced Certificate of Secondary Education Examination (ACSEE) with one Principal Pass and One Subsidiary Pass.</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -6527,21 +5353,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with
-AU
-at least four (4) passes in non-religious subjects
-AU
-Holders of Basic Technician Certificate (NTA Level 5) in Procurement
-AU
-and Supply, Logistics, Clearing and Forwarding, Business
-AU
-Administration, Accounting OR Advanced Certificate of Secondary
-AU
-Education Examination (ACSEE) with one Principal Pass and one
-AU
-Subsidiary in principal subjects.</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects Holders of Basic Technician Certificate (NTA Level 5) in Procurement and Supply, Logistics, Clearing and Forwarding, Business Administration, Accounting OR Advanced Certificate of Secondary Education Examination (ACSEE) with one Principal Pass and one Subsidiary in principal subjects.</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -6581,13 +5393,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with
-AU
-four (4) passes in non religious subjects
-AU
-Holders of Basic Technician Certificate (NTA Level 4) in Social work</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with four (4) passes in non religious subjects Holders of Basic Technician Certificate (NTA Level 4) in Social work</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -6627,13 +5433,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate in Business Administration OR Advanced Certificate
-AU
-of Secondary Education Examination (ACSEE) with at Least one Principal
-AU
-pass and Subsidiary in Principal subjects</t>
+          <t xml:space="preserve"> Holders of Certificate in Business Administration OR Advanced Certificate of Secondary Education Examination (ACSEE) with at Least one Principal pass and Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -6673,15 +5473,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate in Computer Science (CS), Information
-AU
-Technology (IT), Business Information Technology (BIT); OR Advanced
-AU
-Certificate of Secondary Education Examination (ACSEE) with one
-AU
-principal pass and one subsidiary pass.</t>
+          <t xml:space="preserve"> Holders of Certificate in Computer Science (CS), Information Technology (IT), Business Information Technology (BIT); OR Advanced Certificate of Secondary Education Examination (ACSEE) with one principal pass and one subsidiary pass.</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -6721,11 +5513,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Holders of Certificate in Human Resource Management OR Advanced
-AU
-Certificate of Secondary Education Examination with one Principal
-AU
-Pass and one Subsidiary in Principal subjects</t>
+          <t>Holders of Certificate in Human Resource Management OR Advanced Certificate of Secondary Education Examination with one Principal Pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -6765,13 +5553,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate in Law OR Advanced Certificate of Secondary
-AU
-Education Examination with at least one Principal pass and one
-AU
-Subsidiary in Principal subjects</t>
+          <t xml:space="preserve"> Holders of Certificate in Law OR Advanced Certificate of Secondary Education Examination with at least one Principal pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -6811,13 +5593,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate in Library and Information Studies OR Advanced
-AU
-Certificate of Secondary Education Examination with at least one
-AU
-Principal pass and one Subsidiary in Principal subjects</t>
+          <t xml:space="preserve"> Holders of Certificate in Library and Information Studies OR Advanced Certificate of Secondary Education Examination with at least one Principal pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -6857,15 +5633,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with
-AU
-four (4) Passes in non-religious Subjects including Chemistry, Biology and
-AU
-Physics/Engineering Sciences. A Pass in Basic Mathematics and English
-AU
-Language Is An Added Advantage.</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with four (4) Passes in non-religious Subjects including Chemistry, Biology and Physics/Engineering Sciences. A Pass in Basic Mathematics and English Language Is An Added Advantage.</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -6905,13 +5673,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with At
-AU
-Least four (4) Passes in non-religious Subjects including
-AU
-Biology Chemistry and Physics/Engineering Sciences.</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with At Least four (4) Passes in non-religious Subjects including Biology Chemistry and Physics/Engineering Sciences.</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -6951,15 +5713,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with At
-AU
-Least four (4) Passes in non-religious Subjects including Chemistry,
-AU
-Biology, Physics/Engineering sciences/Basic Mathematics and English
-AU
-Language.</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with At Least four (4) Passes in non-religious Subjects including Chemistry, Biology, Physics/Engineering sciences/Basic Mathematics and English Language.</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -6999,15 +5753,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with at
-AU
-least four (4) passes in non-religious subjects including
-AU
-Chemistry, Biology and Physics/Engineering Sciences. A pass in Basic
-AU
-Mathematics and English Language is an added advantage.</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects including Chemistry, Biology and Physics/Engineering Sciences. A pass in Basic Mathematics and English Language is an added advantage.</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -7047,15 +5793,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with At
-AU
-Least four (4) Passes in non-religious Subjects including Chemistry and
-AU
-Biology. A Pass in Basic Mathematics and English
-AU
-Language Is An Added Advantage.</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with At Least four (4) Passes in non-religious Subjects including Chemistry and Biology. A Pass in Basic Mathematics and English Language Is An Added Advantage.</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -7095,23 +5833,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate in Crop production,Agriculture General,
-AU
-Certificate in Agriculture and Livestock Production (CALP) OR Advanced
-AU
-Certificate of Secondary Education Examination (ACSEE) Passes in
-AU
-Chemistry, Biology/zoology, Physics, Mathematics, Geography or Science
-AU
-and Practice of Agriculture. The Candidate Must Pass Biology/zoology At
-AU
-Principal Level. Such Candidates Must also
-AU
-Passes in English and Mathematics at Certificate of Secondary
-AU
-Education Examination (CSEE)</t>
+          <t xml:space="preserve"> Holders of Certificate in Crop production,Agriculture General, Certificate in Agriculture and Livestock Production (CALP) OR Advanced Certificate of Secondary Education Examination (ACSEE) Passes in Chemistry, Biology/zoology, Physics, Mathematics, Geography or Science and Practice of Agriculture. The Candidate Must Pass Biology/zoology At Principal Level. Such Candidates Must also Passes in English and Mathematics at Certificate of Secondary Education Examination (CSEE)</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -7151,17 +5873,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Technical Certificate(NTA 5) in Librarianship, Records
-AU
-Management OR Advanced Certificate of Secondary Education with at
-AU
-least one Principal Pass in Mathematics, Physics, Biology, Chemistry,
-AU
-Science and Practice of Agriculture, Geography, Economics,
-AU
-Commerce, History, English, French and Kiswahili</t>
+          <t xml:space="preserve"> Holders of Technical Certificate(NTA 5) in Librarianship, Records Management OR Advanced Certificate of Secondary Education with at least one Principal Pass in Mathematics, Physics, Biology, Chemistry, Science and Practice of Agriculture, Geography, Economics, Commerce, History, English, French and Kiswahili</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -7201,17 +5913,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate in Information Technology,Computer Engineering
-AU
-OR Advanced Certificate of Secondary Education with at least one
-AU
-Principal Pass in Mathematics, Physics, Biology, Chemistry,
-AU
-Science and Practice of Agriculture, Geography, Economics,
-AU
-Commerce, History, English, French and Kiswahili.</t>
+          <t xml:space="preserve"> Holders of Certificate in Information Technology,Computer Engineering OR Advanced Certificate of Secondary Education with at least one Principal Pass in Mathematics, Physics, Biology, Chemistry, Science and Practice of Agriculture, Geography, Economics, Commerce, History, English, French and Kiswahili.</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -7251,17 +5953,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Basic Certificate in Laboratory Technology with GPA 2.0 from
-AU
-recognized institution OR Advanced Certificate of Secondary Education
-AU
-with at least one Principal Pass in Mathematics, Physics,
-AU
-Biology, Chemistry, Science and Practice of Agriculture, Geography,
-AU
-Economics, Commerce, History, English, French and Kiswahili.</t>
+          <t xml:space="preserve"> Holders of Basic Certificate in Laboratory Technology with GPA 2.0 from recognized institution OR Advanced Certificate of Secondary Education with at least one Principal Pass in Mathematics, Physics, Biology, Chemistry, Science and Practice of Agriculture, Geography, Economics, Commerce, History, English, French and Kiswahili.</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -7301,17 +5993,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Technical Certificate (NTA level 5) in Records Management,
-AU
-Librarianship OR Advanced Certificate of Secondary Education with at
-AU
-least one Principal pass in Mathematics, Physics, Biology, Chemistry,
-AU
-Science and Practice of Agriculture, Geography, Economics,
-AU
-Commerce, History, English, French and Kiswahili</t>
+          <t xml:space="preserve"> Holders of Technical Certificate (NTA level 5) in Records Management, Librarianship OR Advanced Certificate of Secondary Education with at least one Principal pass in Mathematics, Physics, Biology, Chemistry, Science and Practice of Agriculture, Geography, Economics, Commerce, History, English, French and Kiswahili</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -7351,23 +6033,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate in Animal Health (AGRO VET), Certificate in Animal
-AU
-Health and Production (AHPC), Certificate in Agriculture and Livestock
-AU
-Production (CALP) OR Advanced Certificate of Secondary Education
-AU
-Examination (ACSEE) Passes in Chemistry, Biology/zoology, Physics,
-AU
-Mathematics, Geography or Science and Practice of Agriculture. The
-AU
-Candidate Must Pass Biology/zoology At Principal
-AU
-Level. Such Candidates Must also Passes in English and Mathematics at
-AU
-Certificate of Secondary Education Examination (CSEE)</t>
+          <t xml:space="preserve"> Holders of Certificate in Animal Health (AGRO VET), Certificate in Animal Health and Production (AHPC), Certificate in Agriculture and Livestock Production (CALP) OR Advanced Certificate of Secondary Education Examination (ACSEE) Passes in Chemistry, Biology/zoology, Physics, Mathematics, Geography or Science and Practice of Agriculture. The Candidate Must Pass Biology/zoology At Principal Level. Such Candidates Must also Passes in English and Mathematics at Certificate of Secondary Education Examination (CSEE)</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -7407,13 +6073,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate in Banking and Finance OR Advanced Certificate of
-AU
-Secondary Education Examination (ACSEE) with one Principal pass and
-AU
-one Subsidiary in Principal subjects</t>
+          <t xml:space="preserve"> Holders of Certificate in Banking and Finance OR Advanced Certificate of Secondary Education Examination (ACSEE) with one Principal pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -7533,13 +6193,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate in Business Administration; OR Advanced
-AU
-Certificate of Secondary Education Examination (ACSEE) with at least one
-AU
-Principal pass and one Subsidiary in Principal subjects</t>
+          <t xml:space="preserve"> Holders of Certificate in Business Administration; OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -7579,15 +6233,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate in Business Administration, Procurement and
-AU
-Supply OR Advanced Certificate of Secondary Education Examination
-AU
-(ACSEE) with at least one Principal pass and one Subsidiary in Principal
-AU
-subjects</t>
+          <t xml:space="preserve"> Holders of Certificate in Business Administration, Procurement and Supply OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -7627,13 +6273,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate in Business Administration - Accounting OR
-AU
-Advanced Certificate of Secondary Education Examination (ACSEE) with
-AU
-one Principal pass and one Subsidiary pass in Principal subjects</t>
+          <t xml:space="preserve"> Holders of Certificate in Business Administration - Accounting OR Advanced Certificate of Secondary Education Examination (ACSEE) with one Principal pass and one Subsidiary pass in Principal subjects</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -7673,13 +6313,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate in Business Administration - Marketing OR Advanced
-AU
-Certificate of Secondary Education Examination (ACSEE) with one
-AU
-Principal pass and one Subsidiary in Principal subjects</t>
+          <t xml:space="preserve"> Holders of Certificate in Business Administration - Marketing OR Advanced Certificate of Secondary Education Examination (ACSEE) with one Principal pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -7719,13 +6353,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate in Community Development OR Advanced
-AU
-Certificate of Secondary Education Examination (ACSEE) with one
-AU
-Principal pass and one Subsidiary in Principal subjects</t>
+          <t xml:space="preserve"> Holders of Certificate in Community Development OR Advanced Certificate of Secondary Education Examination (ACSEE) with one Principal pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -7765,15 +6393,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Technician Certificate (NTA Level 5) in Computer
-AU
-Maintenance,Computer Engineering OR Advanced Certificate of
-AU
-Secondary Education Examination (ACSEE) with One Principal Pass and
-AU
-one Subsidiary Principal subjects</t>
+          <t xml:space="preserve"> Holders of Technician Certificate (NTA Level 5) in Computer Maintenance,Computer Engineering OR Advanced Certificate of Secondary Education Examination (ACSEE) with One Principal Pass and one Subsidiary Principal subjects</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -7813,13 +6433,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate in Law OR Advanced Certificate of Secondary
-AU
-Education Examination (ACSEE) with at least one Principal pass and one
-AU
-Subsidiary in Principal subjects</t>
+          <t xml:space="preserve"> Holders of Certificate in Law OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -7859,15 +6473,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Technician Certificate (NTA LEVEL 5) in Project Planning and
-AU
-Management or Advanced Certificate of Secondary Education
-AU
-Examination (ACSEE) with at least one Principal pass and one
-AU
-Subsidiary in Principal subjects</t>
+          <t xml:space="preserve"> Holders of Technician Certificate (NTA LEVEL 5) in Project Planning and Management or Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -7907,11 +6513,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with
-AU
-four (4) passes in non-religious subjects</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with four (4) passes in non-religious subjects</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -7951,19 +6553,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with
-AU
-At Least four (4) Passes in non-religious Subjects
-AU
-Holders of Basic Technician Certificate (NTA Level 4) in Community
-AU
-Development, Gender, Youth Work or Advanced Certificate of Secondary
-AU
-Education (ACSEE) with one Principal Pass and one
-AU
-Subsidiary.</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with At Least four (4) Passes in non-religious Subjects Holders of Basic Technician Certificate (NTA Level 4) in Community Development, Gender, Youth Work or Advanced Certificate of Secondary Education (ACSEE) with one Principal Pass and one Subsidiary.</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -8003,15 +6593,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with At
-AU
-Least four (4) Passes in non-religious Subjects including Chemistry,
-AU
-Biology, Physics/Engineering sciences/Basic Mathematics and English
-AU
-Language.</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with At Least four (4) Passes in non-religious Subjects including Chemistry, Biology, Physics/Engineering sciences/Basic Mathematics and English Language.</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -8051,15 +6633,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with at
-AU
-least four (4) passes in non-religious subjects including
-AU
-Chemistry, Biology and Physics/Engineering Sciences. A pass in Basic
-AU
-Mathematics and English Language is an added advantage.</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects including Chemistry, Biology and Physics/Engineering Sciences. A pass in Basic Mathematics and English Language is an added advantage.</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -8099,15 +6673,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with At
-AU
-Least four (4) Passes in non-religious Subjects including Chemistry and
-AU
-Biology. A Pass in Basic Mathematics and English
-AU
-Language Is An Added Advantage.</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with At Least four (4) Passes in non-religious Subjects including Chemistry and Biology. A Pass in Basic Mathematics and English Language Is An Added Advantage.</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -8147,25 +6713,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examinations (CSEE) with
-AU
-at least Four (4) passes in non - religious subjects including
-AU
-Physics/Engineering Science, Basic Mathematics, Chemistry and Biology;
-AU
-OR Holder of General Certificate in Engineering; OR Holder of
-AU
-Certificate of Secondary Education (CSEE) with a Minimum of pass in Basic
-AU
-Mathematics and National Vocational Award (NVA) Level III or Trade Test
-AU
-Certificate of Grade I in the relevant field offered by VETA
-AU
-Accredited Institution.
-AU
-Kinondoni Municipal Council - Dar es Salaam</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examinations (CSEE) with at least Four (4) passes in non - religious subjects including Physics/Engineering Science, Basic Mathematics, Chemistry and Biology; OR Holder of General Certificate in Engineering; OR Holder of Certificate of Secondary Education (CSEE) with a Minimum of pass in Basic Mathematics and National Vocational Award (NVA) Level III or Trade Test Certificate of Grade I in the relevant field offered by VETA Accredited Institution. Kinondoni Municipal Council - Dar es Salaam</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -8365,31 +6913,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examinations (CSEE) with
-AU
-at least Four (4) passes in non-religious subjects including
-AU
-Physics/Engineering Science, Basic Mathematics and Chemistry; OR
-AU
-General Certificate in Engineering; or National Vocational Award (NVA)
-AU
-Level III or Trade Test Certificate Grade I in Industrial Engineering. Or
-AU
-Possession of Certificate of Secondary Education Examination (CSEE) from
-AU
-Technical Secondary Schools with at Least four (4) Passes in nonreligious
-AU
-Subjects, three of which must be Mathematics, Engineering Science,
-AU
-Chemistry and any one of the Following Subjects: Architectural
-AU
-Drafting/building Construction, Electrical Engineering
-AU
-Science/electrical Drafting, Workshop Technology/mechanical
-AU
-Drafting;</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examinations (CSEE) with at least Four (4) passes in non-religious subjects including Physics/Engineering Science, Basic Mathematics and Chemistry; OR General Certificate in Engineering; or National Vocational Award (NVA) Level III or Trade Test Certificate Grade I in Industrial Engineering. Or Possession of Certificate of Secondary Education Examination (CSEE) from Technical Secondary Schools with at Least four (4) Passes in nonreligious Subjects, three of which must be Mathematics, Engineering Science, Chemistry and any one of the Following Subjects: Architectural Drafting/building Construction, Electrical Engineering Science/electrical Drafting, Workshop Technology/mechanical Drafting;</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -8429,17 +6953,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examinations (CSEE) with
-AU
-At Least four (4) Passes in non-religious Subjects including
-AU
-Physics/Engineering Science and Basic Mathematics.
-AU
-Holders of Basic Technician Certificate( NTA Level 4) in Information
-AU
-Technology</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examinations (CSEE) with At Least four (4) Passes in non-religious Subjects including Physics/Engineering Science and Basic Mathematics. Holders of Basic Technician Certificate( NTA Level 4) in Information Technology</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -8479,23 +6993,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate in Secondary Education Examinations (CSEE) with
-AU
-at least four (4) Passes in non-religious Subjects including
-AU
-Physics/Engineering Science, Basic Mathematics and Chemistry; Or
-AU
-Holders of Certificate of Secondary Education (CSEE) with a Minimum of
-AU
-four (4) Passes and National Vocational Award (NVA) Level III or Trade
-AU
-Test Certificate of Grade I in relevant field Offered by VETA accredited
-AU
-Institution; or Holders of General Certificate in
-AU
-Engineering.</t>
+          <t xml:space="preserve"> Holders of Certificate in Secondary Education Examinations (CSEE) with at least four (4) Passes in non-religious Subjects including Physics/Engineering Science, Basic Mathematics and Chemistry; Or Holders of Certificate of Secondary Education (CSEE) with a Minimum of four (4) Passes and National Vocational Award (NVA) Level III or Trade Test Certificate of Grade I in relevant field Offered by VETA accredited Institution; or Holders of General Certificate in Engineering.</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -8535,21 +7033,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examinations (CSEE) with
-AU
-at least Four (4) passes in non-religious subjects including
-AU
-Physics/ Engineering Science, Basic Mathematics and Chemistry; OR
-AU
-General Certificate in Engineering; OR National Vocational Award
-AU
-(NVA) Level III or Trade Test Certificate Grade I in Mechatronics
-AU
-Engineering with pass in Certificate of Secondary Education
-AU
-Examination (CSEE)</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examinations (CSEE) with at least Four (4) passes in non-religious subjects including Physics/ Engineering Science, Basic Mathematics and Chemistry; OR General Certificate in Engineering; OR National Vocational Award (NVA) Level III or Trade Test Certificate Grade I in Mechatronics Engineering with pass in Certificate of Secondary Education Examination (CSEE)</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -8589,13 +7073,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate in Accountancy OR Advanced Certificate of
-AU
-Secondary Education with at least one Principal pass and one
-AU
-Subsidiary in Principal subjects</t>
+          <t xml:space="preserve"> Holders of Certificate in Accountancy OR Advanced Certificate of Secondary Education with at least one Principal pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -8635,13 +7113,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate in Business Administration OR Advanced Certificate
-AU
-of Secondary Education with at least one (1) Principal pass and one (1)
-AU
-Subsidiary in Principal subjects</t>
+          <t xml:space="preserve"> Holders of Certificate in Business Administration OR Advanced Certificate of Secondary Education with at least one (1) Principal pass and one (1) Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -8681,13 +7153,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate in Law OR Holder of Advanced Certificate of
-AU
-Secondary Education with at least one Principal pass and one
-AU
-Subsidiary in Principal subjects</t>
+          <t xml:space="preserve"> Holders of Certificate in Law OR Holder of Advanced Certificate of Secondary Education with at least one Principal pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -8727,17 +7193,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with at
-AU
-least Four (4) passes in non-religious subjects including Basic Mathematics
-AU
-and English Language; OR National Vocational Award
-AU
-(NVA Level III) or Trade Test Grade II in ICT with a Certificate of
-AU
-Secondary Education Examination (CSEE)</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least Four (4) passes in non-religious subjects including Basic Mathematics and English Language; OR National Vocational Award (NVA Level III) or Trade Test Grade II in ICT with a Certificate of Secondary Education Examination (CSEE)</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -8777,13 +7233,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate in Law OR Advanced Certificate of Secondary
-AU
-Education Examinations (ACSEE) with one Principal pass and one
-AU
-Subsidiary in Principal subjects</t>
+          <t xml:space="preserve"> Holders of Certificate in Law OR Advanced Certificate of Secondary Education Examinations (ACSEE) with one Principal pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -8823,23 +7273,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with
-AU
-at least four (4) passes in non-religious subjects including passes in
-AU
-Basic Mathematics OR National Vocational Award (NVA) Level III with a
-AU
-Certificate of Secondary Education Examination (CSEE)
-AU
-Holders of Basic Technician Certificate (NTA Level 4) in Accountancy or
-AU
-Advanced Certificate of Secondary Education Examinations
-AU
-Examination (ACSEE) with At Least one Principal Pass and one
-AU
-Subsidiary in Principal Subjects</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects including passes in Basic Mathematics OR National Vocational Award (NVA) Level III with a Certificate of Secondary Education Examination (CSEE) Holders of Basic Technician Certificate (NTA Level 4) in Accountancy or Advanced Certificate of Secondary Education Examinations Examination (ACSEE) with At Least one Principal Pass and one Subsidiary in Principal Subjects</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -8879,23 +7313,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with
-AU
-at least four (4) passes in non-religious subjects OR National
-AU
-Vocational Award (NVA) Level III with a Certificate of Secondary
-AU
-Education Examination (CSEE)
-AU
-Holders of Basic Technician Certificate (NTA Level 4) in Business
-AU
-Administration, Marketing and Public Relation or Advanced Certificate
-AU
-of Secondary Education Examination (ACSEE) with one Principal Pass and
-AU
-one Subsidiary in Principal Subjects</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects OR National Vocational Award (NVA) Level III with a Certificate of Secondary Education Examination (CSEE) Holders of Basic Technician Certificate (NTA Level 4) in Business Administration, Marketing and Public Relation or Advanced Certificate of Secondary Education Examination (ACSEE) with one Principal Pass and one Subsidiary in Principal Subjects</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -8935,23 +7353,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Holders of Certificate of Secondary Education Examination (CSEE) with
-AU
-at least Four (4) passes in non-religious subjects including Basic
-AU
-Mathematics and English Language; OR National Vocational Award
-AU
-(NVA Level III) or Trade Test Grade II in ICT with a Certificate of
-AU
-Secondary Education Examination (CSEE)
-AU
-Holders of Basic Technician Certificate (NTA Level 4) in Computer
-AU
-Science, Information Technology, Business Information Technology or
-AU
-Advanced Certificate of Secondary Education Examination (ACSEE) with
-AU
-one Principal Pass and two Subsidiaries.</t>
+          <t>Holders of Certificate of Secondary Education Examination (CSEE) with at least Four (4) passes in non-religious subjects including Basic Mathematics and English Language; OR National Vocational Award (NVA Level III) or Trade Test Grade II in ICT with a Certificate of Secondary Education Examination (CSEE) Holders of Basic Technician Certificate (NTA Level 4) in Computer Science, Information Technology, Business Information Technology or Advanced Certificate of Secondary Education Examination (ACSEE) with one Principal Pass and two Subsidiaries.</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -8991,23 +7393,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with
-AU
-at least four (4) passes in non-religious subjects including English
-AU
-Language OR National Vocational Award (NVA) Level III with a
-AU
-Certificate of Secondary Education Examination (CSEE)
-AU
-Holders of Basic Technician Certificate ( NTA Level 4) in Journalism,
-AU
-Mass Communication or Advanced Certificate of Secondary Education
-AU
-Examination (ACSEE) with at least one Principal Pass and one
-AU
-Subsidiary in Principal Subjects</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects including English Language OR National Vocational Award (NVA) Level III with a Certificate of Secondary Education Examination (CSEE) Holders of Basic Technician Certificate ( NTA Level 4) in Journalism, Mass Communication or Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal Pass and one Subsidiary in Principal Subjects</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -9047,19 +7433,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with
-AU
-at least four (4) passes in non-religious subjects
-AU
-Holders of Basic Technician Certificate (NTA Level 4) in Procurement
-AU
-and Supply, Business Administration and Logistics or Advanced
-AU
-Certificate of Secondary Education Examination (ACSEE) with one
-AU
-Principal Pass and one Subsidiary in Principal Subjects.</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects Holders of Basic Technician Certificate (NTA Level 4) in Procurement and Supply, Business Administration and Logistics or Advanced Certificate of Secondary Education Examination (ACSEE) with one Principal Pass and one Subsidiary in Principal Subjects.</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -9099,15 +7473,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with At
-AU
-Least four (4) Passes in non-religious Subjects including Chemistry,
-AU
-Biology, Physics/Engineering sciences/Basic Mathematics and English
-AU
-Language.</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with At Least four (4) Passes in non-religious Subjects including Chemistry, Biology, Physics/Engineering sciences/Basic Mathematics and English Language.</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -9147,15 +7513,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with At
-AU
-Least four (4) Passes in non-religious Subjects including
-AU
-Chemistry and Biology. A Pass in Basic Mathematics and English
-AU
-Language Is An Added Advantage.</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with At Least four (4) Passes in non-religious Subjects including Chemistry and Biology. A Pass in Basic Mathematics and English Language Is An Added Advantage.</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -9195,15 +7553,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with at
-AU
-least four (4) passes in non-religious subjects including Chemistry, Biology
-AU
-and Physics/Engineering Sciences. A pass in Basic
-AU
-Mathematics and English Language is an added advantage.</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects including Chemistry, Biology and Physics/Engineering Sciences. A pass in Basic Mathematics and English Language is an added advantage.</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -9243,15 +7593,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with At
-AU
-Least four (4) Passes in non-religious Subjects including Chemistry and
-AU
-Biology. A Pass in Basic Mathematics and English
-AU
-Language Is An Added Advantage.</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with At Least four (4) Passes in non-religious Subjects including Chemistry and Biology. A Pass in Basic Mathematics and English Language Is An Added Advantage.</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -9291,9 +7633,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Holders of Certificate of Secondary Education Examination (CSEE) with at
-AU
-least four (4) passes in non-religious subjects</t>
+          <t>Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -9333,13 +7673,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate in Accountancy OR Advanced Certificate of
-AU
-Secondary Education Examination (ACSEE) with at least one Principal pass
-AU
-and one subsidiary in Principal subjects</t>
+          <t xml:space="preserve"> Holders of Certificate in Accountancy OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal pass and one subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -9379,13 +7713,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate in Business Administration OR Advanced Certificate
-AU
-of Secondary Education Examination (ACSEE) with at least one Principal
-AU
-pass and one subsidiary in Principal subjects</t>
+          <t xml:space="preserve"> Holders of Certificate in Business Administration OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal pass and one subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -9425,13 +7753,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate in Law OR Advanced Certificate of Secondary
-AU
-Education Examination (ACSEE) with at least one Principal pass and one
-AU
-subsidiary in Principal subjects</t>
+          <t xml:space="preserve"> Holders of Certificate in Law OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal pass and one subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -9471,9 +7793,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Holders of Technician Certificate (NTA Level 5) in Librarianship and
-AU
-Records Management</t>
+          <t>Holders of Technician Certificate (NTA Level 5) in Librarianship and Records Management</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -9513,21 +7833,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with
-AU
-at least four (4) passes in non-religious subjects including Basic
-AU
-Mathematics OR National Vocational Award (NVA ) Level III with a
-AU
-Certificate of Secondary Education Examination (CSEE)
-AU
-Holders of Basic Technician Certificate (NTA Level 4) in Accountancy OR
-AU
-Advanced Certificate of Secondary Education Examination (ACSEE) with
-AU
-one Principal pass and one Subsidiary in Principal Subjects</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects including Basic Mathematics OR National Vocational Award (NVA ) Level III with a Certificate of Secondary Education Examination (CSEE) Holders of Basic Technician Certificate (NTA Level 4) in Accountancy OR Advanced Certificate of Secondary Education Examination (ACSEE) with one Principal pass and one Subsidiary in Principal Subjects</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -9567,23 +7873,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with
-AU
-at least four (4) passes in non-religious subjects OR National
-AU
-Vocational Award (NVA) Level III with a Certificate of Secondary
-AU
-Education Examination (CSEE)
-AU
-Holders of Basic Technician Certificate (NTA Level 4) in Business
-AU
-Administration, Human Resource Management, Accounting, Banking and
-AU
-Finance OR Advanced Certificate of Secondary Examination with one
-AU
-Principal pass and one Subsidiary in Principal subjects</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects OR National Vocational Award (NVA) Level III with a Certificate of Secondary Education Examination (CSEE) Holders of Basic Technician Certificate (NTA Level 4) in Business Administration, Human Resource Management, Accounting, Banking and Finance OR Advanced Certificate of Secondary Examination with one Principal pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -9623,21 +7913,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with
-AU
-at least four (4) passes in non- religious subjects
-AU
-Holders of Basic Technician Certificate (NTA Level 4) in Community
-AU
-Development, Social Work, Community Health, Gender, Youth Work,
-AU
-Social Protection OR Advanced Certificate of Secondary Education
-AU
-Examination (ACSEE) with one Principal pass and one Subsidiary in
-AU
-principal subjects</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non- religious subjects Holders of Basic Technician Certificate (NTA Level 4) in Community Development, Social Work, Community Health, Gender, Youth Work, Social Protection OR Advanced Certificate of Secondary Education Examination (ACSEE) with one Principal pass and one Subsidiary in principal subjects</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -9677,23 +7953,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with
-AU
-at least four (4) passes in non-religious subjects OR National
-AU
-Vocational Award (NVA) Level III with a Certificate of Secondary
-AU
-Education Examination (CSEE)
-AU
-Holders of Basic Technician Certificate (NTA Level 4) in Procurement
-AU
-and Supply, Logistics, Clearing and Forwarding, Inventory Management
-AU
-OR Advanced Certificate of Secondary Education Examination (ACSEE)
-AU
-with one Principal pass and one Subsidiary pass in Principal subjects</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects OR National Vocational Award (NVA) Level III with a Certificate of Secondary Education Examination (CSEE) Holders of Basic Technician Certificate (NTA Level 4) in Procurement and Supply, Logistics, Clearing and Forwarding, Inventory Management OR Advanced Certificate of Secondary Education Examination (ACSEE) with one Principal pass and one Subsidiary pass in Principal subjects</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -9733,19 +7993,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with
-AU
-at least four (4) Passes in non-religious Subjects
-AU
-Holders of Basic Technician Certificate (NTA Level 4) in Accountancy
-AU
-and Finance OR Advanced Certificate of Secondary Examination
-AU
-Education (ACSEE) with at least one Principal pass and one Subsidiary in
-AU
-Principal subjects</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) Passes in non-religious Subjects Holders of Basic Technician Certificate (NTA Level 4) in Accountancy and Finance OR Advanced Certificate of Secondary Examination Education (ACSEE) with at least one Principal pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -9785,19 +8033,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with
-AU
-at least four (4) passes in non-religious subjects
-AU
-Holder of Basic Technician Certificate (NTA Level 4) in Business
-AU
-Administration OR Advanced Certificate of Secondary Education
-AU
-Examination (ACSEE) with at least one Principal pass and one subsidiary
-AU
-in Principal subjects</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects Holder of Basic Technician Certificate (NTA Level 4) in Business Administration OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal pass and one subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -9837,15 +8073,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with
-AU
-four (4) passes in non-religious subjects including Chemistry, Biology and
-AU
-Physics/Engineering Sciences. A pass in Basic Mathematics and English
-AU
-Language is an added advantage</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with four (4) passes in non-religious subjects including Chemistry, Biology and Physics/Engineering Sciences. A pass in Basic Mathematics and English Language is an added advantage</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -9885,19 +8113,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with
-AU
-at least four (4) passes in non-religious subjects
-AU
-Holders of Basic Technician Certificate (NTA Level 4) in Social Work,
-AU
-Gender and Community Development OR Advanced Certificate of
-AU
-Secondary Education Examination (ACSEE) with at least one principal
-AU
-pass and one Subsidiary in Principal subjects</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects Holders of Basic Technician Certificate (NTA Level 4) in Social Work, Gender and Community Development OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one principal pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -9937,19 +8153,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with
-AU
-at least four (4) passes in non-religious subjects
-AU
-Holders of Basic Technician Certificate (NTA Level 4) in Human
-AU
-Resource Management OR Advanced Certificate of Secondary
-AU
-Examination (ACSEE) with at least one principal pass and one subsidiary
-AU
-in Principal subjects</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects Holders of Basic Technician Certificate (NTA Level 4) in Human Resource Management OR Advanced Certificate of Secondary Examination (ACSEE) with at least one principal pass and one subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -9989,21 +8193,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Holders of Certificate of Secondary Education Examination (CSEE) with
-AU
-Four (4) passes in non-religious subjects including Basic
-AU
-Mathematics and English Language; OR National Vocational Award
-AU
-(NVA) Level III or Trade Test Grade I with Certificate of Secondary
-AU
-Education Examination (CSEE).
-AU
-Holders of Basic Technician Certificate (NTA Level 4) in Information
-AU
-Technology or Advanced Certificate of Secondary Education
-AU
-Examination (ACSEE) with one Principal Pass and one Subsidiary</t>
+          <t>Holders of Certificate of Secondary Education Examination (CSEE) with Four (4) passes in non-religious subjects including Basic Mathematics and English Language; OR National Vocational Award (NVA) Level III or Trade Test Grade I with Certificate of Secondary Education Examination (CSEE). Holders of Basic Technician Certificate (NTA Level 4) in Information Technology or Advanced Certificate of Secondary Education Examination (ACSEE) with one Principal Pass and one Subsidiary</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -10043,17 +8233,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with
-AU
-at least four (4) passes in non-religious subjects OR National Vocational
-AU
-Award (NVA) Level III with at least two passes in Certificate of
-AU
-Secondary Education Examination (CSEE)
-AU
-Holder of Basic Technician Certificate (NTA Level 4) in Journalism</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects OR National Vocational Award (NVA) Level III with at least two passes in Certificate of Secondary Education Examination (CSEE) Holder of Basic Technician Certificate (NTA Level 4) in Journalism</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -10093,17 +8273,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with
-AU
-at least four (4) passes in non-religious subjects
-AU
-Holders of Basic Technician Certificate (NTA Level 4) in Law OR
-AU
-Advanced Certificate of Secondary Education Examination (ACSEE) with
-AU
-at least one principal pass and one subsidiary in Principal subjects</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects Holders of Basic Technician Certificate (NTA Level 4) in Law OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one principal pass and one subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -10143,19 +8313,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with
-AU
-at least four (4) passes in non-religious subjects
-AU
-Holders Basic Technician Certificate (NTA Level 4) in Records
-AU
-Management and Library and Information Science OR Advanced
-AU
-Certificate of Secondary Examination (ACSEE) one principal pass and one
-AU
-Subsidiary in Principal subjects</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects Holders Basic Technician Certificate (NTA Level 4) in Records Management and Library and Information Science OR Advanced Certificate of Secondary Examination (ACSEE) one principal pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -10195,15 +8353,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with at
-AU
-least four (4) passes in non-religious subjects including Chemistry, Biology
-AU
-and Physics/Engineering Sciences. A pass in Basic
-AU
-Mathematics and English Language is an added advantage.</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects including Chemistry, Biology and Physics/Engineering Sciences. A pass in Basic Mathematics and English Language is an added advantage.</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -10243,15 +8393,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with At
-AU
-Least four (4) Passes in non-religious Subjects including Chemistry and
-AU
-Biology. A Pass in Basic Mathematics and English
-AU
-Language Is An Added Advantage.</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with At Least four (4) Passes in non-religious Subjects including Chemistry and Biology. A Pass in Basic Mathematics and English Language Is An Added Advantage.</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -10291,19 +8433,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with
-AU
-at least four (4) passes in non-religious subjects
-AU
-Holder of Basic Technician Certificate (NTA Level 4) in Procurement and
-AU
-Supply OR Advanced Certificate of Secondary Education
-AU
-Examination (ACSEE) with at least one principal pass and one
-AU
-Subsidiary in Principal subjects</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects Holder of Basic Technician Certificate (NTA Level 4) in Procurement and Supply OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one principal pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -10343,11 +8473,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with at
-AU
-least four (4) passes in non-religious subjects</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -10387,9 +8513,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Holders of Certificate of Secondary Education Examination (CSEE) with at
-AU
-least four (4) passes in non-religious subjects</t>
+          <t>Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -10429,11 +8553,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with at
-AU
-least four (4) passes in non-religious subjects</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -10473,11 +8593,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with at
-AU
-least four (4) passes in non-religious subjects</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -10517,13 +8633,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examinations (CSEE) with
-AU
-at least four (4) passes in non-religious subject. English Language is an
-AU
-added advantage</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examinations (CSEE) with at least four (4) passes in non-religious subject. English Language is an added advantage</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -10563,17 +8673,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Advanced Certificate of Secondary Education Examination
-AU
-(ACSEE) with at least one (1) principle pass in Biology and one (1)
-AU
-subsidiary pass in Chemistry, Physics, Advanced Mathematics, Agriculture
-AU
-Science and Geography. or Possession of (NTA Level 4)
-AU
-Certificate Award in Crop production.</t>
+          <t xml:space="preserve"> Holders of Advanced Certificate of Secondary Education Examination (ACSEE) with at least one (1) principle pass in Biology and one (1) subsidiary pass in Chemistry, Physics, Advanced Mathematics, Agriculture Science and Geography. or Possession of (NTA Level 4) Certificate Award in Crop production.</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -10613,19 +8713,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Certificate of Secondary Education Examination (CSEE) with four (4 Ds)
-AU
-Passes in non-religious Subjects including three (3 Ds) Passes in
-AU
-Biology, Chemistry, Physics/Engineering Sciences, Basic Mathematics,
-AU
-Agriculture Science and Geography; or Possession of National Vocation
-AU
-Award (NVA) Level III or Trade Test Grade I in Animal Husbandry and
-AU
-Possession of Certificate of Secondary Education Examination (CSEE).</t>
+          <t xml:space="preserve"> Certificate of Secondary Education Examination (CSEE) with four (4 Ds) Passes in non-religious Subjects including three (3 Ds) Passes in Biology, Chemistry, Physics/Engineering Sciences, Basic Mathematics, Agriculture Science and Geography; or Possession of National Vocation Award (NVA) Level III or Trade Test Grade I in Animal Husbandry and Possession of Certificate of Secondary Education Examination (CSEE).</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -10665,15 +8753,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Holders of Advanced Certificate of Secondary Education Examination
-AU
-(ACSEE) with at least (1.5); one (1) principle pass in Biology and one
-AU
-(1) subsidiary pass in Chemistry, Physics, Advanced Mathematics,
-AU
-Agriculture Science and Geography. or Possession of (NTA Level 4)
-AU
-Certificate Award in Crop production.</t>
+          <t>Holders of Advanced Certificate of Secondary Education Examination (ACSEE) with at least (1.5); one (1) principle pass in Biology and one (1) subsidiary pass in Chemistry, Physics, Advanced Mathematics, Agriculture Science and Geography. or Possession of (NTA Level 4) Certificate Award in Crop production.</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -10713,15 +8793,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Technician Certificate (NTA Level 4) in Financial
-AU
-Administration, Accountancy, Banking and Finance OR Advanced
-AU
-Certificate of Secondary Education Examination (ACSEE) with one
-AU
-Principal pass and two Subsidiary in principal subjects</t>
+          <t xml:space="preserve"> Holders of Technician Certificate (NTA Level 4) in Financial Administration, Accountancy, Banking and Finance OR Advanced Certificate of Secondary Education Examination (ACSEE) with one Principal pass and two Subsidiary in principal subjects</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -10761,11 +8833,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with at
-AU
-least four (4) passes in non-religious subjects</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
@@ -10805,13 +8873,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Technician Certificate (NTA Level 5) in Hospitality and Tourism
-AU
-Management, Hotel Management, Museum, Tour Guiding,
-AU
-Archeology, Food preparation, Food Beverage and Front Office</t>
+          <t xml:space="preserve"> Holders of Technician Certificate (NTA Level 5) in Hospitality and Tourism Management, Hotel Management, Museum, Tour Guiding, Archeology, Food preparation, Food Beverage and Front Office</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -10851,15 +8913,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with at
-AU
-least four (4) passes in non-religious subjects OR Advanced Certificate of
-AU
-Secondary Education Examination (ACSEE) with at least one Principal pass
-AU
-and one subsidiary pass in Principal subjects</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal pass and one subsidiary pass in Principal subjects</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -10899,15 +8953,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Basic Certificate in Computer Science, and Information
-AU
-Technology OR Advanced Certificate of Secondary Education Examination
-AU
-(ACSEE) with at least one Principal pass and one
-AU
-Subsidiary in principal subjects</t>
+          <t xml:space="preserve"> Holders of Basic Certificate in Computer Science, and Information Technology OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal pass and one Subsidiary in principal subjects</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -10947,23 +8993,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holder of Advanced Certificate of Secondary Education Examination
-AU
-(ACSEE) with at least one Principal and one subsidiary in science subjects.
-AU
-A Pass in Mathematics for Computer Science is compulsory while English
-AU
-is compulsory for IT applicants (at least in O-level). OR A holder of
-AU
-Certificate in Computing discipline with Programming and Mathematics
-AU
-recognized by NACTE, NECTA or any higher learning Institution with a GPA
-AU
-of at least 3.0, also the candidate should have
-AU
-Four passes at O level one of which be in Mathematics or English.</t>
+          <t xml:space="preserve"> Holder of Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal and one subsidiary in science subjects. A Pass in Mathematics for Computer Science is compulsory while English is compulsory for IT applicants (at least in O-level). OR A holder of Certificate in Computing discipline with Programming and Mathematics recognized by NACTE, NECTA or any higher learning Institution with a GPA of at least 3.0, also the candidate should have Four passes at O level one of which be in Mathematics or English.</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -11003,15 +9033,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Grade III A Certificate or any recognized Certificate in
-AU
-Education OR Advanced Certificate of Secondary Education Examination
-AU
-(ACSEE) with at least one Principal pass and one
-AU
-subsidiary in principal subjects .</t>
+          <t xml:space="preserve"> Holders of Grade III A Certificate or any recognized Certificate in Education OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal pass and one subsidiary in principal subjects .</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -11051,15 +9073,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate in Librarianship, information sciences, Records
-AU
-Management OR Advanced Certificate of Secondary Education
-AU
-Examination (ACSEE) with at least one Principal pass and one
-AU
-subsidiary pass in Principal subjects</t>
+          <t xml:space="preserve"> Holders of Certificate in Librarianship, information sciences, Records Management OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal pass and one subsidiary pass in Principal subjects</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -11099,13 +9113,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of a Certificate in Physical Education (PE) or Sports OR Advanced
-AU
-Certificate of Secondary Education Examination (ACSEE) with at least one
-AU
-Principal pass and one subsidiary pass in Principal subjects.</t>
+          <t xml:space="preserve"> Holders of a Certificate in Physical Education (PE) or Sports OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal pass and one subsidiary pass in Principal subjects.</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -11145,11 +9153,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with at
-AU
-least four passes (4) in non religious subjects</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four passes (4) in non religious subjects</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -11189,15 +9193,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders Certificate in Accountancy, Banking and Finance, Marketing,
-AU
-Clearing and Forwarding ,Projects Planning ,Procurement and Supply,
-AU
-Taxation and Economics OR Advanced Certificate of Secondary
-AU
-Examination one Principal pass and one Subsidiary in principal subjects</t>
+          <t xml:space="preserve"> Holders Certificate in Accountancy, Banking and Finance, Marketing, Clearing and Forwarding ,Projects Planning ,Procurement and Supply, Taxation and Economics OR Advanced Certificate of Secondary Examination one Principal pass and one Subsidiary in principal subjects</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -11237,15 +9233,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate in Social Work, Social Welfare, Teaching, Youth
-AU
-Work, Rural Development, Nursing, Community Development OR
-AU
-Advanced Certificate of Secondary Education Examination (ACSEE) with
-AU
-at least one Principal pass and one Subsidiary in Principal subjects</t>
+          <t xml:space="preserve"> Holders of Certificate in Social Work, Social Welfare, Teaching, Youth Work, Rural Development, Nursing, Community Development OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -11285,11 +9273,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with at
-AU
-least four (4) passes in non-religious subjects</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -11329,13 +9313,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with at
-AU
-least four (4) passes in non-religious subjects including
-AU
-Chemistry, Biology and Physics/Engineering Sciences</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects including Chemistry, Biology and Physics/Engineering Sciences</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -11375,15 +9353,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with
-AU
-four (4) passes in non-religious subjects including Chemistry, Biology and
-AU
-Physics/Engineering Sciences. A pass in Basic Mathematics and English
-AU
-Language is an added advantage.</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with four (4) passes in non-religious subjects including Chemistry, Biology and Physics/Engineering Sciences. A pass in Basic Mathematics and English Language is an added advantage.</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -11423,9 +9393,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Holders of Technician Certificate (NTA Level 5) in Environmental
-AU
-Health Sciences</t>
+          <t>Holders of Technician Certificate (NTA Level 5) in Environmental Health Sciences</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -11465,9 +9433,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Holders of Technician Certificate (NTA Level 5) in Hospitality
-AU
-Management</t>
+          <t>Holders of Technician Certificate (NTA Level 5) in Hospitality Management</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -11507,15 +9473,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with At
-AU
-Least four (4) Passes in non-religious Subjects including Chemistry,
-AU
-Biology, Physics/Engineering sciences/Basic Mathematics and English
-AU
-Language.</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with At Least four (4) Passes in non-religious Subjects including Chemistry, Biology, Physics/Engineering sciences/Basic Mathematics and English Language.</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -11555,9 +9513,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Holders of Technician Certificate (NTA Level 5) in Nursing and
-AU
-Midwifery</t>
+          <t>Holders of Technician Certificate (NTA Level 5) in Nursing and Midwifery</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
@@ -11597,15 +9553,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with At
-AU
-Least four (4) Passes in non-religious Subjects including Chemistry and
-AU
-Biology. A Pass in Basic Mathematics and English
-AU
-Language Is An Added Advantage.</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with At Least four (4) Passes in non-religious Subjects including Chemistry and Biology. A Pass in Basic Mathematics and English Language Is An Added Advantage.</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -11645,17 +9593,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Technician Certificate (NTA Level 5) in Hotel Management,
-AU
-Front Office, Food Production, Food and Beverage Services, Pastry and
-AU
-Bakery, House Keeping and Laundry
-AU
-TUMAINI UNIVERSITY DAR ES SALAAM COLLEGE (TD) - Private
-AU
-Kinondoni Municipal Council - Dar es Salaam</t>
+          <t xml:space="preserve"> Holders of Technician Certificate (NTA Level 5) in Hotel Management, Front Office, Food Production, Food and Beverage Services, Pastry and Bakery, House Keeping and Laundry TUMAINI UNIVERSITY DAR ES SALAAM COLLEGE (TD) - Private Kinondoni Municipal Council - Dar es Salaam</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -11695,15 +9633,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holder of Basic Technician Certificate (NTA Level 4) in Business related
-AU
-Studies, Accounting and Banking, Marketing, Procurement and Supply OR
-AU
-Advanced Certificate of Secondary Education Examination (ACSEE) with
-AU
-one Principal pass and one Subsidiary in Principal subjects</t>
+          <t xml:space="preserve"> Holder of Basic Technician Certificate (NTA Level 4) in Business related Studies, Accounting and Banking, Marketing, Procurement and Supply OR Advanced Certificate of Secondary Education Examination (ACSEE) with one Principal pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -11743,13 +9673,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate in Law OR Advanced Certificate of Secondary
-AU
-Education Examination (ACSEE) with one Principal pass and a
-AU
-subsidiary pass in Principal subjects</t>
+          <t xml:space="preserve"> Holders of Certificate in Law OR Advanced Certificate of Secondary Education Examination (ACSEE) with one Principal pass and a subsidiary pass in Principal subjects</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -11789,19 +9713,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Basic Technician Certificate (NTA Level 4) in Intercultural
-AU
-Relations, Heritage OR Advanced Certificate of Secondary Education
-AU
-Examination (ACSEE) with one Principal pass and one subsidiary in
-AU
-principal subjects
-AU
-TUMAINI UNIVERSITY MAKUMIRA (TUMA) - ARUSHA (MK) - Private
-AU
-Arumeru District Council - Arusha</t>
+          <t xml:space="preserve"> Holders of Basic Technician Certificate (NTA Level 4) in Intercultural Relations, Heritage OR Advanced Certificate of Secondary Education Examination (ACSEE) with one Principal pass and one subsidiary in principal subjects TUMAINI UNIVERSITY MAKUMIRA (TUMA) - ARUSHA (MK) - Private Arumeru District Council - Arusha</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -11841,13 +9753,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Law OR Advanced Certificate of Secondary
-AU
-Examination (ACSEE) with at least one Principal pass and one
-AU
-Subsidiary in Principal subjects</t>
+          <t xml:space="preserve"> Holders of Certificate of Law OR Advanced Certificate of Secondary Examination (ACSEE) with at least one Principal pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -11887,23 +9793,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with
-AU
-at least four (4) passes in non-religious subjects OR National
-AU
-Vocational Award (NVA ) Level III with at least two (2) passes in
-AU
-Certificate of Secondary Education Examinations (CSEE)
-AU
-Holder of Basic Technician Certificate (NTA Level 4) in Accountancy,
-AU
-Finance and Banking, Business Administration, Procurement and
-AU
-Supply OR Advanced Certificate of Secondary Education Examination
-AU
-(ACSEE) with one Principal pass and one Subsidiary in Principal subjects</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects OR National Vocational Award (NVA ) Level III with at least two (2) passes in Certificate of Secondary Education Examinations (CSEE) Holder of Basic Technician Certificate (NTA Level 4) in Accountancy, Finance and Banking, Business Administration, Procurement and Supply OR Advanced Certificate of Secondary Education Examination (ACSEE) with one Principal pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -11943,25 +9833,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with
-AU
-at least four (4) passes in non-religious subjects OR National
-AU
-Vocational Award (NVA ) Level III with at least two (2) passes in
-AU
-Certificate of Secondary Education Examinations (CSEE)
-AU
-Holders of Basic Technician Certificate (NTA Level 4) in Business
-AU
-Administration, Marketing, Accountancy, Finance and Banking, Human
-AU
-Resource Management, Local Government Administration OR Advanced
-AU
-Certificate of Secondary Education Examination (ACSEE) with one
-AU
-Principal Pass and one Subsidiary in Principal Subjects.</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects OR National Vocational Award (NVA ) Level III with at least two (2) passes in Certificate of Secondary Education Examinations (CSEE) Holders of Basic Technician Certificate (NTA Level 4) in Business Administration, Marketing, Accountancy, Finance and Banking, Human Resource Management, Local Government Administration OR Advanced Certificate of Secondary Education Examination (ACSEE) with one Principal Pass and one Subsidiary in Principal Subjects.</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
@@ -12001,21 +9873,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with
-AU
-at least Four (4) passes in non-religious Subjects including a pass in
-AU
-Basic Mathematics and English Language
-AU
-Holders of Basic Technician Certificate (NTA level 4) in Information
-AU
-Communication Technology/Computer Engineering OR Advanced
-AU
-Certificate of Secondary Education Examination (ACSEE) with at least
-AU
-ONE Principal Pass and ONE Subsidiary pass.</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least Four (4) passes in non-religious Subjects including a pass in Basic Mathematics and English Language Holders of Basic Technician Certificate (NTA level 4) in Information Communication Technology/Computer Engineering OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least ONE Principal Pass and ONE Subsidiary pass.</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -12055,23 +9913,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with
-AU
-four (4) passes in non-religious subject OR National Vocational
-AU
-Award (NVA) Level III or Trade test I with two passes in Certificate of
-AU
-Secondary Education Examination (CSEE)
-AU
-Holders of Basic Technician Certificate (NTA Level 4) in Information
-AU
-Technology (ICT) OR Advanced Certificate of Secondary Education
-AU
-Examination (ACSEE) with at least one Principal Pass and one
-AU
-Subsidiary Pass in Principal Subjects.</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with four (4) passes in non-religious subject OR National Vocational Award (NVA) Level III or Trade test I with two passes in Certificate of Secondary Education Examination (CSEE) Holders of Basic Technician Certificate (NTA Level 4) in Information Technology (ICT) OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal Pass and one Subsidiary Pass in Principal Subjects.</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -12111,23 +9953,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with
-AU
-at least four (4) passes in non-religious subjects OR National
-AU
-Vocational Award (NVA ) Level III with at least two (2) passes in
-AU
-Certificate of Secondary Education Examinations (CSEE)
-AU
-Holders of Basic Technician Certificate (NTA Level 4) in Music,
-AU
-Performing Arts, Grade IIIA Certificate, Sports OR Advanced Certificate
-AU
-of Secondary Education Examination (ACSEE) with at least one
-AU
-Principal Pass and one Subsidiary pass in Principal subjects</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects OR National Vocational Award (NVA ) Level III with at least two (2) passes in Certificate of Secondary Education Examinations (CSEE) Holders of Basic Technician Certificate (NTA Level 4) in Music, Performing Arts, Grade IIIA Certificate, Sports OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal Pass and one Subsidiary pass in Principal subjects</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
@@ -12167,15 +9993,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Technician Certificate (NTA Level 5) in Computer Science (CS),
-AU
-Information Technology (IT), Business Information Technology
-AU
-(BIT) OR Advanced Certificate of Secondary Examination One Principal
-AU
-Pass and one Subsidiary Pass in Principal Subjects.</t>
+          <t xml:space="preserve"> Holders of Technician Certificate (NTA Level 5) in Computer Science (CS), Information Technology (IT), Business Information Technology (BIT) OR Advanced Certificate of Secondary Examination One Principal Pass and one Subsidiary Pass in Principal Subjects.</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
@@ -12215,11 +10033,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Holders of Certificate in Education OR Advanced Certificate of
-AU
-Secondary Education Examination With One Principal Pass and one
-AU
-Subsidiary in Principal Subjects.</t>
+          <t>Holders of Certificate in Education OR Advanced Certificate of Secondary Education Examination With One Principal Pass and one Subsidiary in Principal Subjects.</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -12259,15 +10073,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate in Office Administration, Human Resource
-AU
-Management, Local Government Administration, Records Management,
-AU
-Secretarial Studies, Community Development, Business
-AU
-Administration.</t>
+          <t xml:space="preserve"> Holders of Certificate in Office Administration, Human Resource Management, Local Government Administration, Records Management, Secretarial Studies, Community Development, Business Administration.</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
@@ -12347,9 +10153,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects including Basic Mathematics OR National Vocational Award (NVA ) Level III with at least two (2) passes in Certificate of Secondary Education Examinations (CSEE)
-AU
-Holders of Basic Technician Certificate (NTA Level 4) in Accountancy OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal Pass and Subsidiary in Principal subjects</t>
+          <t>Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects including Basic Mathematics OR National Vocational Award (NVA ) Level III with at least two (2) passes in Certificate of Secondary Education Examinations (CSEE) Holders of Basic Technician Certificate (NTA Level 4) in Accountancy OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal Pass and Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
@@ -12389,9 +10193,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects OR National Vocational Award (NVA ) Level III with a Certificate of Secondary Education Examinations (CSEE)
-AU
-Holders of Basic Technician Certificate (NTA Level 4) in Business Administration, Marketing, Procurement and Supply OR Advanced Certificate of Secondary Education Examination (ACSEE) with one Principal pass and one Subsidiary in Principal subjects</t>
+          <t>Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects OR National Vocational Award (NVA ) Level III with a Certificate of Secondary Education Examinations (CSEE) Holders of Basic Technician Certificate (NTA Level 4) in Business Administration, Marketing, Procurement and Supply OR Advanced Certificate of Secondary Education Examination (ACSEE) with one Principal pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -12431,13 +10233,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Holders of Certificate of Secondary Education Examination (CSEE) with four (4) passes in non-religious subjects including passes in Basic Mathematics and English Language.
-AU
-Holders of Basic Technician Certificate (NTA Level 4) in Computing and Information Technology OR Advanced Certificate of Secondary
-AU
-Education Examination (ACSEE) with ONE principal pass and ONE
-AU
-subsidiary pass.</t>
+          <t>Holders of Certificate of Secondary Education Examination (CSEE) with four (4) passes in non-religious subjects including passes in Basic Mathematics and English Language. Holders of Basic Technician Certificate (NTA Level 4) in Computing and Information Technology OR Advanced Certificate of Secondary Education Examination (ACSEE) with ONE principal pass and ONE subsidiary pass.</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
@@ -12477,25 +10273,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with
-AU
-at least four (4) passes in non-religious subjects OR National
-AU
-Vocational Award (NVA ) Level III with at least two (2) passes in
-AU
-Certificate of Secondary Education Examinations (CSEE)
-AU
-Holders of Basic Technician Certificate (NTA Level 4) in Procurement and
-AU
-supply, Business Administration, Logistics, Clearing and
-AU
-Forwarding OR Advanced Certificate of Secondary Education
-AU
-Examination (ACSEE) with one Principal Pass and subsidiary in
-AU
-Principal subjects</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects OR National Vocational Award (NVA ) Level III with at least two (2) passes in Certificate of Secondary Education Examinations (CSEE) Holders of Basic Technician Certificate (NTA Level 4) in Procurement and supply, Business Administration, Logistics, Clearing and Forwarding OR Advanced Certificate of Secondary Education Examination (ACSEE) with one Principal Pass and subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
@@ -12535,23 +10313,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with
-AU
-at least Four (4) passes in Non-religious subjects
-AU
-Holders of Basic Technician Certificate (NTA Level 4) in Record
-AU
-Management, Medical Records, Library and Information Sciences OR
-AU
-Advanced Certificate of Secondary Education Examination (ACSEE) with
-AU
-one Principal pass and Subsidiary pass in Principal subjects
-AU
-UNIVERSITY OF DAR ES SALAAM (UD) - Governmen
-AU
-Kinondoni Municipal Council - Dar es Salaam</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least Four (4) passes in Non-religious subjects Holders of Basic Technician Certificate (NTA Level 4) in Record Management, Medical Records, Library and Information Sciences OR Advanced Certificate of Secondary Education Examination (ACSEE) with one Principal pass and Subsidiary pass in Principal subjects UNIVERSITY OF DAR ES SALAAM (UD) - Governmen Kinondoni Municipal Council - Dar es Salaam</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
@@ -12591,13 +10353,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Advanced Certificate of Secondary Education Examination with
-AU
-Two Principal Passes in either Language Subjects or Science
-AU
-Subjects.</t>
+          <t xml:space="preserve"> Holders of Advanced Certificate of Secondary Education Examination with Two Principal Passes in either Language Subjects or Science Subjects.</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -12637,13 +10393,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate in Computer Sciences, Computer Engineering OR
-AU
-Advanced Certificate of Secondary Education Examination (ACSEE) with
-AU
-One Principal Pass and One Subsidiary Pass in Principal Subjects</t>
+          <t xml:space="preserve"> Holders of Certificate in Computer Sciences, Computer Engineering OR Advanced Certificate of Secondary Education Examination (ACSEE) with One Principal Pass and One Subsidiary Pass in Principal Subjects</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
@@ -12683,17 +10433,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate in Journalism, Mass Communication, Public
-AU
-Relation OR Advanced Certificate of Secondary Education Examination
-AU
-(ACSEE) with one Principal pass and one Subsidiary in Principal subjects
-AU
-UNIVERSITY OF DODOMA (DM) - Government
-AU
-Dodoma Municipal Council - Dodoma</t>
+          <t xml:space="preserve"> Holders of Certificate in Journalism, Mass Communication, Public Relation OR Advanced Certificate of Secondary Education Examination (ACSEE) with one Principal pass and one Subsidiary in Principal subjects UNIVERSITY OF DODOMA (DM) - Government Dodoma Municipal Council - Dodoma</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
@@ -12733,15 +10473,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Basic Technician Certificate (NTA Level 4) in Accountancy OR
-AU
-Advanced Certificate of Secondary Education Examination (ACSEE) with
-AU
-at least one Principal pass and one Subsidiary in Principal
-AU
-Subject.</t>
+          <t xml:space="preserve"> Holders of Basic Technician Certificate (NTA Level 4) in Accountancy OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal pass and one Subsidiary in Principal Subject.</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
@@ -12781,15 +10513,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Holders of Basic Technician Certificate (NTA Level 4) in Business
-AU
-Information Technology, Information Technology, Computer
-AU
-Sciences/Engineering OR Advanced Certificate of Secondary Education
-AU
-Examination (ACSEE) with at least one Principal Pass and one
-AU
-Subsidiary in principal subjects.</t>
+          <t>Holders of Basic Technician Certificate (NTA Level 4) in Business Information Technology, Information Technology, Computer Sciences/Engineering OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal Pass and one Subsidiary in principal subjects.</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -12829,13 +10553,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Holders of Basic Technician Certificate (NTA Level 4) in Computer
-AU
-Sciences/Engineering OR Advanced Certificate of Secondary Education
-AU
-Examination (ACSEE) with at least one Principal Pass and one
-AU
-Subsidiary in principal subjects.</t>
+          <t>Holders of Basic Technician Certificate (NTA Level 4) in Computer Sciences/Engineering OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal Pass and one Subsidiary in principal subjects.</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
@@ -12875,13 +10593,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Advanced Certificate of Secondary Education Examination
-AU
-(ACSEE) with one Principal pass and Subsidiary pass in Chemistry and
-AU
-Biology.</t>
+          <t xml:space="preserve"> Holders of Advanced Certificate of Secondary Education Examination (ACSEE) with one Principal pass and Subsidiary pass in Chemistry and Biology.</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
@@ -12921,11 +10633,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Advanced Certificate of Secondary Education Examination
-AU
-(ACSEE) with one Principal pass must be in Advanced Mathematics.</t>
+          <t xml:space="preserve"> Holders of Advanced Certificate of Secondary Education Examination (ACSEE) with one Principal pass must be in Advanced Mathematics.</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
@@ -12965,13 +10673,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Advanced Certificate of Secondary Education Examination
-AU
-(ACSEE) with one principal pass in science subjects and subsidiary pass in
-AU
-principal subjects.</t>
+          <t xml:space="preserve"> Holders of Advanced Certificate of Secondary Education Examination (ACSEE) with one principal pass in science subjects and subsidiary pass in principal subjects.</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
@@ -13011,15 +10713,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Basic Technician Certificate in Film and TV Production,
-AU
-Performing and visual Art, Education, Journalism, Music, Arts and
-AU
-Sports, Education OR Advanced Certificate of Secondary Examination
-AU
-(ACSEE) with at least one Principal pass and one Subsidiary in principal subjects.</t>
+          <t xml:space="preserve"> Holders of Basic Technician Certificate in Film and TV Production, Performing and visual Art, Education, Journalism, Music, Arts and Sports, Education OR Advanced Certificate of Secondary Examination (ACSEE) with at least one Principal pass and one Subsidiary in principal subjects.</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
@@ -13179,11 +10873,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Advanced Certificate of Secondary Education Examination
-AU
-(ACSEE) with one Principal pass and Subsidiary pass in science subjects.</t>
+          <t xml:space="preserve"> Holders of Advanced Certificate of Secondary Education Examination (ACSEE) with one Principal pass and Subsidiary pass in science subjects.</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
@@ -13223,19 +10913,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Advanced Certificate of Secondary Education Examination (ACSEE) with
-AU
-at least one principal pass and one subsidiary in Science subjects. OR
-AU
-Certificate in Computer Science, Computing and Information
-AU
-Communication Technology, Information Technology or Business
-AU
-Information Technology with an average of ?B? grade PLUS at least four
-AU
-passes in non-religious subjects at O-Level.</t>
+          <t xml:space="preserve"> Advanced Certificate of Secondary Education Examination (ACSEE) with at least one principal pass and one subsidiary in Science subjects. OR Certificate in Computer Science, Computing and Information Communication Technology, Information Technology or Business Information Technology with an average of ?B? grade PLUS at least four passes in non-religious subjects at O-Level.</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
@@ -13275,11 +10953,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with at
-AU
-least Four (4) Passes in Non-religious subjects.</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least Four (4) Passes in Non-religious subjects.</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
@@ -13319,9 +10993,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Holders of Technician Certificate (NTA Level 5) in Medical Laboratory
-AU
-Sciences</t>
+          <t>Holders of Technician Certificate (NTA Level 5) in Medical Laboratory Sciences</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
@@ -13361,13 +11033,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Advanced Certificate of Secondary Education Examination
-AU
-(CSEE) with one principal pass and one subsidiary pass in the following
-AU
-subjects Advanced Mathematics, Physics or Chemistry</t>
+          <t xml:space="preserve"> Holders of Advanced Certificate of Secondary Education Examination (CSEE) with one principal pass and one subsidiary pass in the following subjects Advanced Mathematics, Physics or Chemistry</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
@@ -13407,9 +11073,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Holders of Technician Certificate (NTA Level 5) in Nursing and
-AU
-Midwifery</t>
+          <t>Holders of Technician Certificate (NTA Level 5) in Nursing and Midwifery</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
@@ -13449,13 +11113,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with at
-AU
-four (4) passes including credit Passes in Science Subjects
-AU
-Physics or Basic Mathematics, Chemistry and Biology.</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at four (4) passes including credit Passes in Science Subjects Physics or Basic Mathematics, Chemistry and Biology.</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
@@ -13495,17 +11153,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Basic Technician Certificate (NTA Level 4) in Procurement and
-AU
-Logistic Management, Business Administration, Logistics, Clearing and
-AU
-Forwarding OR Holders of Advanced Certificate of Secondary Education
-AU
-Examination (ACSEE) with One Principal Pass and one
-AU
-Subsidiary in principal subjects.</t>
+          <t xml:space="preserve"> Holders of Basic Technician Certificate (NTA Level 4) in Procurement and Logistic Management, Business Administration, Logistics, Clearing and Forwarding OR Holders of Advanced Certificate of Secondary Education Examination (ACSEE) with One Principal Pass and one Subsidiary in principal subjects.</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
@@ -13545,17 +11193,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Holders of Basic Technician Certificate (NTA Level 4) in Project
-AU
-Planning and Management, Procurement and Logistic Management,
-AU
-Business Administration, Logistics, Clearing and Forwarding, Public
-AU
-Administration, Local Government Administration OR Advanced
-AU
-Certificate of Secondary Education Examination (ACSEE) with One
-AU
-Principal Pass and one Subsidiary pass in principal subjects</t>
+          <t>Holders of Basic Technician Certificate (NTA Level 4) in Project Planning and Management, Procurement and Logistic Management, Business Administration, Logistics, Clearing and Forwarding, Public Administration, Local Government Administration OR Advanced Certificate of Secondary Education Examination (ACSEE) with One Principal Pass and one Subsidiary pass in principal subjects</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
@@ -13595,17 +11233,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Basic Technician Certificate (NTA Level 4 ) in Public
-AU
-Administration and Management, Human Resource Management, Local
-AU
-Government Administration OR Advanced Certificate of Secondary
-AU
-Education Examination with one Principal Pass and two Subsidiary in
-AU
-principal Subjects.</t>
+          <t xml:space="preserve"> Holders of Basic Technician Certificate (NTA Level 4 ) in Public Administration and Management, Human Resource Management, Local Government Administration OR Advanced Certificate of Secondary Education Examination with one Principal Pass and two Subsidiary in principal Subjects.</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
@@ -13645,9 +11273,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Holders of Basic Technician Certificate (NTA Level 4) in Statistics or
-AU
-Economics</t>
+          <t>Holders of Basic Technician Certificate (NTA Level 4) in Statistics or Economics</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
@@ -13687,15 +11313,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with at
-AU
-least four (4) passes in non-religious subjects including Chemistry, Biology
-AU
-and Physics/Engineering Sciences. A pass in Basic
-AU
-Mathematics and English Language is an added advantage.</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects including Chemistry, Biology and Physics/Engineering Sciences. A pass in Basic Mathematics and English Language is an added advantage.</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
@@ -13735,13 +11353,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holder of Certificate in Accountancy or Advanced Certificate of
-AU
-Secondary Education Examination (ACSEE) with one Principal Pass and
-AU
-one Subsidiary in Principal Subjects</t>
+          <t xml:space="preserve"> Holder of Certificate in Accountancy or Advanced Certificate of Secondary Education Examination (ACSEE) with one Principal Pass and one Subsidiary in Principal Subjects</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
@@ -13781,13 +11393,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders Certificate in Accountancy, Business Administration OR of
-AU
-Advanced Certificate of Secondary Education Examination(ACSEE) with
-AU
-One Principal Pass and one Subsidiary in Relevant Subjects.</t>
+          <t xml:space="preserve"> Holders Certificate in Accountancy, Business Administration OR of Advanced Certificate of Secondary Education Examination(ACSEE) with One Principal Pass and one Subsidiary in Relevant Subjects.</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
@@ -13827,13 +11433,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holder of Certificate in Business Administration, Marketing or Advanced
-AU
-Certificate of Secondary Education Examination (ACSEE) with One
-AU
-Principal Pass and one Subsidiary in Relevant Subjects.</t>
+          <t xml:space="preserve"> Holder of Certificate in Business Administration, Marketing or Advanced Certificate of Secondary Education Examination (ACSEE) with One Principal Pass and one Subsidiary in Relevant Subjects.</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
@@ -13873,19 +11473,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate in Community Development, Gender, Social Work,
-AU
-Youth Work, Certificate from Tanzania Police School - Moshi, Tanzania
-AU
-Police Staff College - Kidatu, zanzibar Police College Zanzibar and above
-AU
-or Advanced Certificate of Secondary Education Examination (ACSEE)
-AU
-with One Principal Pass and one Subsidiary in
-AU
-Principal Subjects.</t>
+          <t xml:space="preserve"> Holders of Certificate in Community Development, Gender, Social Work, Youth Work, Certificate from Tanzania Police School - Moshi, Tanzania Police Staff College - Kidatu, zanzibar Police College Zanzibar and above or Advanced Certificate of Secondary Education Examination (ACSEE) with One Principal Pass and one Subsidiary in Principal Subjects.</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
@@ -13925,17 +11513,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders Certificate in Community Development, Nursing, Counseling ,
-AU
-Certificate from Tanzania Police School - Moshi, Tanzania Police Staff
-AU
-College - Kidatu, Zanzibar Police College - Zanzibar or Advanced
-AU
-Certificate of Secondary Education Examination (ACSEE) with One
-AU
-Principal Pass and one Subsidiary in Principal Subjects.</t>
+          <t xml:space="preserve"> Holders Certificate in Community Development, Nursing, Counseling , Certificate from Tanzania Police School - Moshi, Tanzania Police Staff College - Kidatu, Zanzibar Police College - Zanzibar or Advanced Certificate of Secondary Education Examination (ACSEE) with One Principal Pass and one Subsidiary in Principal Subjects.</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
@@ -13975,15 +11553,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holder of Certificate in Human Resource Management, Local
-AU
-Government Administration with OR Advanced Certificate of Secondary
-AU
-Education Examination (ACSEE) with One Principal Pass and one
-AU
-Subsidiary pass Principal Subjects.</t>
+          <t xml:space="preserve"> Holder of Certificate in Human Resource Management, Local Government Administration with OR Advanced Certificate of Secondary Education Examination (ACSEE) with One Principal Pass and one Subsidiary pass Principal Subjects.</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
@@ -14023,15 +11593,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Holders Certificate in Computer Science (CS), Information Technology
-AU
-(IT), Business Information Technology (BIT), Records, Achieves and
-AU
-Information Management, Certificate in Education (Grade III A); OR
-AU
-Advanced Certificate of Secondary Examination (ACSEE) with One
-AU
-Principal Pass and Two Subsidiary Pass</t>
+          <t>Holders Certificate in Computer Science (CS), Information Technology (IT), Business Information Technology (BIT), Records, Achieves and Information Management, Certificate in Education (Grade III A); OR Advanced Certificate of Secondary Examination (ACSEE) with One Principal Pass and Two Subsidiary Pass</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
@@ -14071,13 +11633,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holder of Certificate in Journalism, Public Relation, Mass Communication
-AU
-or Advanced Certificate of Secondary Education Examination (ACSEE)
-AU
-with One Principal Pass and one Subsidiary pass in Principal Subjects.</t>
+          <t xml:space="preserve"> Holder of Certificate in Journalism, Public Relation, Mass Communication or Advanced Certificate of Secondary Education Examination (ACSEE) with One Principal Pass and one Subsidiary pass in Principal Subjects.</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
@@ -14117,15 +11673,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Holder of Certificate in Law, international Relation,Certificate from
-AU
-Tanzania Police School - Moshi, Tanzania Police Staff College - Kidatu,
-AU
-Zanzibar Police College - Zanzibar and above OR Holder of Advanced
-AU
-Certificate of Secondary Education Examination(ACSEE) with One
-AU
-Principal Pass and one Subsidiary in Principal Subjects.</t>
+          <t>Holder of Certificate in Law, international Relation,Certificate from Tanzania Police School - Moshi, Tanzania Police Staff College - Kidatu, Zanzibar Police College - Zanzibar and above OR Holder of Advanced Certificate of Secondary Education Examination(ACSEE) with One Principal Pass and one Subsidiary in Principal Subjects.</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
@@ -14165,15 +11713,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate in Leisure and Tourism Studies,Tour Guide,
-AU
-Wildlife Management ,Wildlife Tourism OR Advanced Certificate of
-AU
-Secondary Education Examination (ACSEE) with One Principal Pass and
-AU
-one Subsidiary in Principal Subjects.</t>
+          <t xml:space="preserve"> Holders of Certificate in Leisure and Tourism Studies,Tour Guide, Wildlife Management ,Wildlife Tourism OR Advanced Certificate of Secondary Education Examination (ACSEE) with One Principal Pass and one Subsidiary in Principal Subjects.</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
@@ -14213,15 +11753,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders Certificate in Procurement and Supply, Logistics managements
-AU
-OR Advanced Certificate of Secondary Education Examination(ACSEE)
-AU
-with at least one Principal Pass and one Subsidiary in Principal
-AU
-Subjects</t>
+          <t xml:space="preserve"> Holders Certificate in Procurement and Supply, Logistics managements OR Advanced Certificate of Secondary Education Examination(ACSEE) with at least one Principal Pass and one Subsidiary in Principal Subjects</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
@@ -14261,11 +11793,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with At
-AU
-Least four (4) Passes including Religious Subjects.</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with At Least four (4) Passes including Religious Subjects.</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
@@ -14305,11 +11833,7 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with at
-AU
-least four (4) passes in non-religious subjects with division three</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects with division three</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
@@ -14381,15 +11905,7 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Holders of Basic Technician Certificate (NTA Level 4) in Community
-AU
-Development, Community Health, Social Work, Gender, Youth
-AU
-Economics OR Advanced Certificate Of Secondary Education
-AU
-Examination (ACSEE) with at least one Principal pass and one
-AU
-Subsidiary in Principal subjects</t>
+          <t>Holders of Basic Technician Certificate (NTA Level 4) in Community Development, Community Health, Social Work, Gender, Youth Economics OR Advanced Certificate Of Secondary Education Examination (ACSEE) with at least one Principal pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
@@ -14429,15 +11945,7 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with at
-AU
-least four (4) passes in non-religious subjects OR National Vocational
-AU
-Award (NVA) Level III with a Certificate of Secondary
-AU
-Education Examination (CSEE)</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects OR National Vocational Award (NVA) Level III with a Certificate of Secondary Education Examination (CSEE)</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
@@ -14477,13 +11985,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Basic Technician Certificate in Law; OR Advance Certificate of
-AU
-Secondary Education Examination (ACSEE) with at least one
-AU
-Principal Pass and one Subsidiary in Principal subjects</t>
+          <t xml:space="preserve"> Holders of Basic Technician Certificate in Law; OR Advance Certificate of Secondary Education Examination (ACSEE) with at least one Principal Pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
@@ -14523,11 +12025,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Holders of Certificate of Secondary Education Examination with
-AU
-Division three with at least two passes in science subjects (Physics,
-AU
-Chemistry and Biology)</t>
+          <t>Holders of Certificate of Secondary Education Examination with Division three with at least two passes in science subjects (Physics, Chemistry and Biology)</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
@@ -14567,19 +12065,7 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination with at least
-AU
-four (4) passes in non-religious subjects including Basic
-AU
-Mathematics
-AU
-Holders of Basic Technician Certificate (NTA Level 4) in Accountancy OR
-AU
-Advanced Certificate of Secondary Education Examination (ACSEE) with
-AU
-at least one Principal pass and one Subsidiary in Principal subjects</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination with at least four (4) passes in non-religious subjects including Basic Mathematics Holders of Basic Technician Certificate (NTA Level 4) in Accountancy OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
@@ -14619,19 +12105,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination with at least
-AU
-four (4) passes in non-religious subjects
-AU
-Holders of Basic Technician Certificate (NTA Level 4) in Business
-AU
-Administration, Accountancy, Marketing, Procurement and Supply OR
-AU
-Advanced Certificate of Secondary Education Examination (ACSEE) with
-AU
-at least one Principal pass and one Subsidiary in Principal subjects</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination with at least four (4) passes in non-religious subjects Holders of Basic Technician Certificate (NTA Level 4) in Business Administration, Accountancy, Marketing, Procurement and Supply OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
@@ -14671,15 +12145,7 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with
-AU
-four (4) passes in non-religious subjects including Chemistry, Biology and
-AU
-Physics/Engineering Sciences. A pass in Basic Mathematics and English
-AU
-Language is an added advantage.</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with four (4) passes in non-religious subjects including Chemistry, Biology and Physics/Engineering Sciences. A pass in Basic Mathematics and English Language is an added advantage.</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
@@ -14719,19 +12185,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with
-AU
-at least four (4) passes in non-religious subjects
-AU
-Holders of Basic Technician Certificate (NTA Level 4) in Community
-AU
-Development OR Advanced Certificate of Secondary Education
-AU
-Examination (ACSEE) with at least one Principal pass and one
-AU
-Subsidiary in Principal subjects</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects Holders of Basic Technician Certificate (NTA Level 4) in Community Development OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
@@ -14771,23 +12225,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with
-AU
-at least four (4) passes in non-religious Subjects Include passes in
-AU
-Basic Mathematics and English Language.
-AU
-Holders of Basic Technician Certificate (NTA Level 4) in Information and
-AU
-Communication Technology (ICT) related field or its equivalence
-AU
-recognised by NACTE OR Advanced Certificate of Secondary Education
-AU
-Examination (ACSEE) with at least ONE Principal Pass and ONE
-AU
-Subsidiary Pass in Principal Subjects.</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious Subjects Include passes in Basic Mathematics and English Language. Holders of Basic Technician Certificate (NTA Level 4) in Information and Communication Technology (ICT) related field or its equivalence recognised by NACTE OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least ONE Principal Pass and ONE Subsidiary Pass in Principal Subjects.</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
@@ -14827,15 +12265,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with At
-AU
-Least four (4) Passes in non-religious Subjects including Chemistry,
-AU
-Biology, Physics/Engineering sciences/Basic Mathematics and English
-AU
-Language.</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with At Least four (4) Passes in non-religious Subjects including Chemistry, Biology, Physics/Engineering sciences/Basic Mathematics and English Language.</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
@@ -14875,15 +12305,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with at
-AU
-least four (4) passes in non-religious subjects including Chemistry, Biology
-AU
-and Physics/Engineering Sciences. A pass in Basic
-AU
-Mathematics and English Language is an added advantage.</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects including Chemistry, Biology and Physics/Engineering Sciences. A pass in Basic Mathematics and English Language is an added advantage.</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
@@ -14923,19 +12345,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-AU
-Holders of Certificate of Secondary Education Examination (CSEE) with
-AU
-at least four (4) passes in non-religious subjects
-AU
-Holders of Basic Technician Certificate (NTA Level 4) in Procurement
-AU
-and Supply, Clearing and Forwarding, Logistics Management OR
-AU
-Advanced Certificate of Secondary Education Examination (ACSEE) with
-AU
-at least one Principal pass and one Subsidiary in Principal subjects</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects Holders of Basic Technician Certificate (NTA Level 4) in Procurement and Supply, Clearing and Forwarding, Logistics Management OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">

--- a/nacte/nacte_data.xlsx
+++ b/nacte/nacte_data.xlsx
@@ -461,12 +461,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Unknown University</t>
+          <t>Program Duration (Yrs)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Unknown Region</t>
+          <t>Zanzibar Urban/West</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -481,7 +481,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Holders of Certificate in Arts with Education or Certificate of Teachers Education Grade III A</t>
+          <t>Holders of Certificate in Arts with Education or Certificate of Teachers</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -501,12 +501,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Unknown University</t>
+          <t>Education Grade III A</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Unknown Region</t>
+          <t>Zanzibar Urban/West</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -516,12 +516,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Ordinary Diploma in Business Information Technology</t>
+          <t>Ordinary Diploma in Business Information</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects including Basic Mathematics and English Language OR National Vocational Award (NVA) Level III or Trade Test Grade I with a Certificate of Secondary Education Examination (CSEE) Holders of Basic Technician Certificate (NTA Level 4) in Business Information Technology, Information Technology, Computer Sciences/Engineering OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal pass and one Subsidiary in Principal subjects.</t>
+          <t xml:space="preserve"> Holders of Basic Technician Certificate (NTA Level 4) in Business</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -541,12 +541,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Unknown University</t>
+          <t>Subsidiary in Principal subjects.</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Unknown Region</t>
+          <t>Zanzibar Urban/West</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -561,7 +561,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in Non-religious subjects including passes in Basic Mathematics and English Language. Holders of Basic Technician Certificate (NTA Level 4) in Computing and Information Technology OR Advanced Certificate of Secondary Education (ACSEE) with at least one Principal pass and one Subsidiary in Principal subjects.</t>
+          <t xml:space="preserve"> at least four (4) passes in Non-religious subjects including passes in Holders of Basic Technician Certificate (NTA Level 4) in Computing and</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -581,12 +581,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Unknown University</t>
+          <t>Principal subjects.</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Unknown Region</t>
+          <t>Zanzibar Urban/West</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -599,11 +599,7 @@
           <t>Ordinary Diploma in Counselling and Psychology</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with At Least four (4) Passes in non-religious subjects or National Vocational Award (NVA) Level III with At Least two Passes in Certificate of Secondary Education Examination (CSEE). Holders of NTA 4 in Counseling Psychology and related fields or form VI with at least one Principal and a subsidiary pass excluding religious subjects.</t>
-        </is>
-      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>3 / 2</t>
@@ -621,12 +617,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Unknown University</t>
+          <t>subjects.</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Unknown Region</t>
+          <t>Zanzibar Urban/West</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -639,11 +635,7 @@
           <t>Ordinary Diploma in Office Administration</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects including English Language. Holders of Basic Technician Certificate (NTA Level 4) in Office Administration, Secretarial Studies OR Advanced Certificate of Secondary Education Examinations (ACSEE) with at least one Principal pass and one Subsidiary in Principal subjects.</t>
-        </is>
-      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>3 / 2</t>
@@ -661,12 +653,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Unknown University</t>
+          <t>pass and one Subsidiary in Principal subjects.</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Unknown Region</t>
+          <t>Zanzibar Urban/West</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -679,14 +671,10 @@
           <t>Ordinary Diploma in Science with Education</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with Minimum of Division III with at least two (2) passes in Science Subjects (Physics, Chemistry, Biology, Mathematics and Geography) CATHOLIC UNIVERSITY COLLEGE OF MBEYA (TCU/M.10/1.1) - FBO Mbeya City Council - Mbeya</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2 / Program Duration (Yrs)</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -701,12 +689,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Unknown University</t>
+          <t>Program Duration (Yrs)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Unknown Region</t>
+          <t>Mbeya</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -721,7 +709,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Holders of Basic Technician Certificate (NTA Level 4) in Accountancy, Finance and Banking OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal pass and one Subsidiary in Principal subjects.</t>
+          <t>Holders of Basic Technician Certificate (NTA Level 4) in Accountancy,</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -741,12 +729,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Unknown University</t>
+          <t>Subsidiary in Principal subjects.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Unknown Region</t>
+          <t>Mbeya</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -759,11 +747,7 @@
           <t>Diploma in Business Administration</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Basic Technician Certificate (NTA Level 4) in Business Administration, Finance and Banking, Marketing OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal pass and one Subsidiary in Principal subjects.</t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>2</t>
@@ -781,12 +765,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Unknown University</t>
+          <t>pass and one Subsidiary in Principal subjects.</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Unknown Region</t>
+          <t>Mbeya</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -799,11 +783,7 @@
           <t>Diploma in Community Development</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Basic Technician Certificate (NTA Level 4 ) in Community Development, Social Work, Gender, Youth Work OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal pass and one Subsidiary in Principal subjects.</t>
-        </is>
-      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>2</t>
@@ -821,12 +801,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Unknown University</t>
+          <t>pass and one Subsidiary in Principal subjects.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Unknown Region</t>
+          <t>Mbeya</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -839,11 +819,7 @@
           <t>Diploma in Entrepreneurship Development</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Basic Technician Certificate (NTA Level 4) in Entrepreneurship Development OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal pass and one Subsidiary in Principal subjects.</t>
-        </is>
-      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>2</t>
@@ -861,12 +837,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Unknown University</t>
+          <t>Subsidiary in Principal subjects.</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Unknown Region</t>
+          <t>Mbeya</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -879,11 +855,7 @@
           <t>Diploma in Human Resources Management</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Basic Technician certificate (NTA Level 4) in Human Resource, Local Government Administration, Social work, Community Development, Business Management OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal pass and one Subsidiary in Principal subjects.</t>
-        </is>
-      </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>2</t>
@@ -901,12 +873,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Unknown University</t>
+          <t>and one Subsidiary in Principal subjects.</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Unknown Region</t>
+          <t>Mbeya</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -916,14 +888,10 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Diploma in Information Communication Technology Diploma in Law</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Basic Technician Certificate (NTA Level 4) in Computing and Information Technology OR Advanced Certificate of Secondary Education (ACSEE) with at least one Principal pass and one Subsidiary in Principal subjects</t>
-        </is>
-      </c>
+          <t>Diploma in Information Communication Technology</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>2</t>
@@ -941,12 +909,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Unknown University</t>
+          <t>Diploma in Law</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Unknown Region</t>
+          <t>Mbeya</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -973,12 +941,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Unknown University</t>
+          <t>Diploma in Law</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Unknown Region</t>
+          <t>Mbeya</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -991,11 +959,7 @@
           <t>Diploma in Library Studies, Records Management with Ict</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Basic Technician Certificate (NTA Level 4) in Records Management, Medical Records, Library and information studies OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal pass and one Subsidiary in Principal subjects</t>
-        </is>
-      </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>2</t>
@@ -1013,12 +977,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Unknown University</t>
+          <t>at least one Principal pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Unknown Region</t>
+          <t>Mbeya</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1031,11 +995,7 @@
           <t>Diploma in Marketing Management</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Basic Technician Certificate (NTA Level 4) in Marketing, Public Relation, Business Administration, Accounting and Finance, Economics OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal pass and one Subsidiary in Principal subjects.</t>
-        </is>
-      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>2</t>
@@ -1053,12 +1013,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Unknown University</t>
+          <t>Subsidiary in Principal subjects.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Unknown Region</t>
+          <t>Mbeya</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1073,7 +1033,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Holders of Basic Technician Certificate (NTA Level 4) in Procurement and Supply, Logistics, Clearing and Forwarding, Purchasing and Inventory OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal pass and one Subsidiary in Principal subjects. CATHOLIC UNIVERSITY OF HEALTH AND ALLIED SCIENCES (CUHAS) (CU) - FBO Nyamagana Municipal Council - Mwanza</t>
+          <t xml:space="preserve"> Admission Requirements</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1093,12 +1053,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Unknown University</t>
+          <t>CATHOLIC UNIVERSITY OF HEALTH AND ALLIED SCIENCES (CUHAS) (CU)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Unknown Region</t>
+          <t>Mwanza</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1113,7 +1073,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Holders of Certificate in Diagnostic Radiology with passes in science subjects including passes in Biology, Chemistry and Physics in Certificate of Secondary Education Examination (CSEE) DAR ES SALAAM UNIVERSITY COLLEGE OF EDUCATION (DUCE) (U/SAT/42) - Government Temeke Municipal Council - Dar es Salaam</t>
+          <t xml:space="preserve"> Admission Requirements</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1133,12 +1093,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Unknown University</t>
+          <t>DAR ES SALAAM UNIVERSITY COLLEGE OF EDUCATION (DUCE) (U/SAT/42)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Unknown Region</t>
+          <t>Dar es Salaam</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1153,7 +1113,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in Non-religious subjects including two passes in Physics, chemistry, biology, Geography and Mathematics Holders of Basic Technician Certificate in Educational laboratory and Technology OR Advanced Certificate of Secondary Education (ACSEE) with one principal pass and subsidiary pass in Physics, chemistry, Biology, Agriculture, and Geography HUBERT KAIRUKI MEMORIAL UNIVERSITY (HK) - Private Kinondoni Municipal Council - Dar es Salaam</t>
+          <t xml:space="preserve"> Admission Requirements</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1173,12 +1133,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Unknown University</t>
+          <t>HUBERT KAIRUKI MEMORIAL UNIVERSITY (HK)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Unknown Region</t>
+          <t>Dar es Salaam</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1193,7 +1153,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at Least four (4) Passes in non-religious Subjects Holders of Basic Technician Certificate (NTA Level 4) in Social Work, Development Planning and Community Development, Gender, Community Health OR Advanced Certificate of Secondary Examination (ACSEE) with at least one Principal Pass and one Subsidiary in Principal subjects</t>
+          <t xml:space="preserve"> Admission Requirements</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1223,7 +1183,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1231,11 +1191,7 @@
           <t>Diploma in Law</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate in Law OR Holders of Advanced Certificate of Secondary Education Examination (CSEE) with one Principal Pass and One Subsidiary in Principal subjects</t>
-        </is>
-      </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>2</t>
@@ -1253,7 +1209,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>JORDAN UNIVERSITY COLLEGE (JUCO) (JC)</t>
+          <t>One Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1263,7 +1219,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1271,11 +1227,7 @@
           <t>Diploma in Psychology and Counseling</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects and Technician Certificate in Psychology and Counselling OR Advanced Certificate of Secondary Education Examination (ACSEE) with one Principal pass and one subsidiary in Principal subjects</t>
-        </is>
-      </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>2</t>
@@ -1293,7 +1245,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>JORDAN UNIVERSITY COLLEGE (JUCO) (JC)</t>
+          <t>in Principal subjects</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1303,7 +1255,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1313,7 +1265,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects OR National Vocational Award (NVA III) with a Certificate of Secondary Education Examination(CSEE) Holders of Basic Technician Certificate (NTA level 4) in Accounts, Banking and Finance OR Advanced Certificate in Secondary Education Examination (ACSEE) with at least one Principal pass and one Subsidiary in Principal subjects</t>
+          <t xml:space="preserve"> Holders of Basic Technician Certificate (NTA level 4) in Accounts,</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1333,7 +1285,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>JORDAN UNIVERSITY COLLEGE (JUCO) (JC)</t>
+          <t>Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1343,7 +1295,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1351,11 +1303,7 @@
           <t>Ordinary Diploma in Business Administration</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects OR National Vocational Award (NVA III) with two passes in Certificate of Secondary Education Examination(CSEE) Holders of Basic Technician Certificate (NTA level 4) in Business and Business Administration OR Advanced Certificate in Secondary Education Examination (ACSEE) with at least one Principal pass and one Subsidiary in Principal subjects</t>
-        </is>
-      </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>3 / 2</t>
@@ -1373,7 +1321,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>JORDAN UNIVERSITY COLLEGE (JUCO) (JC)</t>
+          <t>in Principal subjects</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1383,7 +1331,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1391,11 +1339,7 @@
           <t>Ordinary Diploma in Business Administration and Tourism Management</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects OR National Vocational Award (NVA III) with a Certificate of Secondary Education Examination(CSEE) Holders of Basic Technician Certificate (NTA level 4) in Business Administration and Tourism Management OR Advanced Certificate in Secondary Education Examination (ACSEE) with at least one Principal pass and one Subsidiary in Principal subjects</t>
-        </is>
-      </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>3 / 2</t>
@@ -1413,7 +1357,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>JORDAN UNIVERSITY COLLEGE (JUCO) (JC)</t>
+          <t>pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1423,7 +1367,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1433,7 +1377,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects OR National Vocational Award (NVA III) with a Certificate of Secondary Education Examination(CSEE) Holders of Basic Technician Certificate (NTA level 4) in Community Development,Business Administration,Social Protection,Social Work,Development Planning,Community Health,Local Goverment Administration,Youth Work OR Advanced Certificate in Secondary Education Examination (ACSEE) with at least one Principal pass and one Subsidiary in Principal subjects</t>
+          <t xml:space="preserve"> Holders of Basic Technician Certificate (NTA level 4) in Community</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1453,7 +1397,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>JORDAN UNIVERSITY COLLEGE (JUCO) (JC)</t>
+          <t>Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1463,7 +1407,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1471,11 +1415,7 @@
           <t>Ordinary Diploma in Computer Science</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects OR National Vocational Award (NVA) III/Trade Test II with a Certificate of Secondary Education Examination (CSEE). Holders of Basic Technician Certificate (NTA Level 4) in Computer Engineering OR Advanced Certificate Education Examination (ACSEE) with one Principal pass and one Subsidiary.</t>
-        </is>
-      </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
           <t>3 / 2</t>
@@ -1493,7 +1433,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>JORDAN UNIVERSITY COLLEGE (JUCO) (JC)</t>
+          <t>with one Principal pass and one Subsidiary.</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1503,7 +1443,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1513,7 +1453,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects OR National Vocational Award (NVA III) with a Certificate of Secondary Education Examination (CSEE) Holders of Basic Technician Certificate (NTA level 4) in Education with Religious Studies, Theology OR Advanced Certificate in Secondary Education Examination (ACSEE) with one Principal pass and one Subsidiary in Principal subjects</t>
+          <t>Holders of Certificate of Secondary Education Examination (CSEE) with Holders of Basic Technician Certificate (NTA level 4) in Education with</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1533,7 +1473,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>JORDAN UNIVERSITY COLLEGE (JUCO) (JC)</t>
+          <t>Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1543,7 +1483,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1553,7 +1493,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Holder of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non religious subjects OR National Vocational Award (NVA) III/Trade Test II with a Certificate of Secondary Education Examination (CSEE). Holders of Basic Technician Certificate (NTA Level 4) in Computer Science, Computing Information Communication Technology, Business Information Technology OR Holder of Advanced Certificate of Secondary Education Examination (ACSEE) with one Principal pass and one Subsidiary pass in Principal subjects.</t>
+          <t xml:space="preserve"> Holders of Basic Technician Certificate (NTA Level 4) in Computer</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1573,7 +1513,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>JORDAN UNIVERSITY COLLEGE (JUCO) (JC)</t>
+          <t>one Subsidiary pass in Principal subjects.</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1583,7 +1523,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1591,11 +1531,7 @@
           <t>Ordinary Diploma in Law</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects OR National Vocational Award (NVA III) with a Certificate of Secondary Education Examination(CSEE) Holders of Basic Technician Certificate (NTA level 4) in Law OR Advanced Certificate in Secondary Education Examination (ACSEE) with at least one Principal pass and one Subsidiary pass in Principal subjects</t>
-        </is>
-      </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
           <t>3 / 2</t>
@@ -1613,7 +1549,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>JORDAN UNIVERSITY COLLEGE (JUCO) (JC)</t>
+          <t>at least one Principal pass and one Subsidiary pass in Principal subjects</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1623,7 +1559,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1633,7 +1569,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects OR National Vocational Award (NVA III) with a Certificate of Secondary Education Examination(CSEE) Holders of Basic Technician Certificate (NTA Level 4) in Library and Information Studies OR Advanced Certificate in Secondary Education Examination (ACSEE) with at least One Principal Pass and one Subsidiary in Principal subjects</t>
+          <t xml:space="preserve"> Holders of Basic Technician Certificate (NTA Level 4) in Library and</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1653,7 +1589,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>JORDAN UNIVERSITY COLLEGE (JUCO) (JC)</t>
+          <t>Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1663,7 +1599,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1671,11 +1607,7 @@
           <t>Ordinary Diploma in Procurement and Supply Chain Management</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects OR National Vocational Award (NVAIII) with a Certificate of Secondary Education Examination(CSEE) Holders of Basic Technician Certificate (NTA level 4) in Procurement and Supply, Business Administration,logistics,Clearing and Forwarding, Accounts banking, Purchasing and Inventory OR Advanced Certificate in Secondary Education Examination (ACSEE) with one Principal pass and one Subsidiary in Principal subjects</t>
-        </is>
-      </c>
+      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
           <t>3 / 2</t>
@@ -1693,7 +1625,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>JORDAN UNIVERSITY COLLEGE (JUCO) (JC)</t>
+          <t>one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1703,7 +1635,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1711,11 +1643,7 @@
           <t>Ordinary Diploma in Psychology and Counselling</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects Holders of Basic Technician Certificate (NTA level 4) in Counselling Psychology, Education OR Advanced Certificate in Secondary Education Examination (ACSEE) with at least one Principal pass and one Subsidiary in Principal subjects.</t>
-        </is>
-      </c>
+      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
           <t>3 / 2</t>
@@ -1733,7 +1661,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>JORDAN UNIVERSITY COLLEGE (JUCO) (JC)</t>
+          <t>in Principal subjects.</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1743,7 +1671,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1753,7 +1681,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects OR National Vocational Award (NVA III) with a Certificate of Secondary Education Examination (CSEE) Holders of Basic Technician Certificate (NTA level 4) in Records Management, Medical Records, Health in Information Science, Library and Information Science OR Advanced Certificate in Secondary Education Examination (ACSEE) with one Principal pass and one Subsidiary in Principal subjects</t>
+          <t xml:space="preserve"> Admission Requirements</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1783,7 +1711,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1793,7 +1721,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Holders of Certificate in Business Administration, Accountancy, Economics, Banking and Finance, Marketing, Human Resource, Procurement and Supplies, Law and Tax, Local Government Administration OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal pass and one Subsidiary in Principal subjects</t>
+          <t>Holders of Certificate in Business Administration, Accountancy,</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1813,7 +1741,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>KAMPALA INTERNATIONAL UNIVERSITY IN TANZANIA (KIUT) (KUC)</t>
+          <t>Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1823,7 +1751,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1831,11 +1759,7 @@
           <t>Diploma in Computer Science</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate in Information Technology, Computer Science Information Technology, Business Information Technology OR Holder of Advanced Certificate of Secondary Education Examination (ACSEE) with one Principal pass and Subsidiary pass in principal subjects</t>
-        </is>
-      </c>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
           <t>2</t>
@@ -1853,7 +1777,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>KAMPALA INTERNATIONAL UNIVERSITY IN TANZANIA (KIUT) (KUC)</t>
+          <t>one Principal pass and Subsidiary pass in principal subjects</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1863,7 +1787,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1871,11 +1795,7 @@
           <t>Diploma in Guidance and Counseling</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate in Guidance and Counseling OR Holders of Advanced Certificate of Secondary Education Examination ( ACSEE) with at least one Principal Pass and one Subsidiary in Principal subjects</t>
-        </is>
-      </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
           <t>2</t>
@@ -1893,7 +1813,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>KAMPALA INTERNATIONAL UNIVERSITY IN TANZANIA (KIUT) (KUC)</t>
+          <t>one Principal Pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1903,7 +1823,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1911,11 +1831,7 @@
           <t>Diploma in Human Resource Management</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate in Business Administration, Accountancy, Human Resource, Supplies and Procurement OR Advanced Certificate of Secondary Education Examination (ACSEE) with One Principal Pass and one Subsidiary in Principal subjects</t>
-        </is>
-      </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
           <t>2</t>
@@ -1933,7 +1849,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>KAMPALA INTERNATIONAL UNIVERSITY IN TANZANIA (KIUT) (KUC)</t>
+          <t>one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1943,7 +1859,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1951,11 +1867,7 @@
           <t>Diploma in in Conflict Resolution and Peace Studies</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate in Conflict Resolution and Peace Studies, Counselling Psychology OR Advanced Certificate of Secondary Education Examination (ACSEE) with one Principal Pass and One Subsidiary in Principal Subjects</t>
-        </is>
-      </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
           <t>2</t>
@@ -1973,7 +1885,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>KAMPALA INTERNATIONAL UNIVERSITY IN TANZANIA (KIUT) (KUC)</t>
+          <t>Subsidiary in Principal Subjects</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1983,7 +1895,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1991,11 +1903,7 @@
           <t>Diploma in Law</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate in Law, Criminal Investigation, police science, Criminal Investigation, Police Science, OR Advanced Certificate of Secondary Education Examination (ACSEE) with one Principal Pass and one Subsidiary in Principal subjects</t>
-        </is>
-      </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
           <t>2</t>
@@ -2013,7 +1921,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>KAMPALA INTERNATIONAL UNIVERSITY IN TANZANIA (KIUT) (KUC)</t>
+          <t>one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2023,7 +1931,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2033,7 +1941,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Holders of Certificate in Business Administration, Accountancy, Human Resource Management, Marketing Management, Marketing &amp; Public Relation OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal Pass and one Subsidiary in Principal subjects</t>
+          <t>Holders of Certificate in Business Administration, Accountancy, Human</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2053,7 +1961,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>KAMPALA INTERNATIONAL UNIVERSITY IN TANZANIA (KIUT) (KUC)</t>
+          <t>subjects</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2063,7 +1971,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2071,11 +1979,7 @@
           <t>Diploma in Public Administration</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate in Public Administration, Local Government Administration, Business Administration, Human Resource management, Secretarial services, Community Development, Community Health and Public Relation OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal Pass and one Subsidiary in Principal subjects</t>
-        </is>
-      </c>
+      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
           <t>2</t>
@@ -2093,7 +1997,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>KAMPALA INTERNATIONAL UNIVERSITY IN TANZANIA (KIUT) (KUC)</t>
+          <t>Pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2103,7 +2007,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2111,11 +2015,7 @@
           <t>Diploma in Social Work</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate in Social Work, Community Health, theology, Community Development, sociology, Social Protection OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal Pass and one Subsidiary pass in Principal Subjects</t>
-        </is>
-      </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
           <t>2</t>
@@ -2133,7 +2033,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>KAMPALA INTERNATIONAL UNIVERSITY IN TANZANIA (KIUT) (KUC)</t>
+          <t>Principal Pass and one Subsidiary pass in Principal Subjects</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2143,7 +2043,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2151,11 +2051,7 @@
           <t>Diploma in Supplies and Procurement Management</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate in Procurement and Supply, Business Administration, Logistics, Perchance and Inventory/ clearing and forwarding OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal Pass and one Subsidiary in Principal subjects</t>
-        </is>
-      </c>
+      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
           <t>2</t>
@@ -2173,7 +2069,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>KAMPALA INTERNATIONAL UNIVERSITY IN TANZANIA (KIUT) (KUC)</t>
+          <t>Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2183,7 +2079,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2191,11 +2087,7 @@
           <t>Ordinary Diploma in Clinical Medicine</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with four (4) passes in non-religious subjects including Chemistry, Biology and Physics/Engineering Sciences. A pass in Basic Mathematics and English Language is an added advantage.</t>
-        </is>
-      </c>
+      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
           <t>3</t>
@@ -2213,7 +2105,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>KAMPALA INTERNATIONAL UNIVERSITY IN TANZANIA (KIUT) (KUC)</t>
+          <t>Language is an added advantage.</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2223,7 +2115,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2231,11 +2123,7 @@
           <t>Ordinary Diploma in Environmental Health Sciences</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with At Least four (4) Passes in non-religious Subjects including Biology Chemistry and Physics/Engineering Sciences.</t>
-        </is>
-      </c>
+      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
           <t>3</t>
@@ -2253,7 +2141,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>KAMPALA INTERNATIONAL UNIVERSITY IN TANZANIA (KIUT) (KUC)</t>
+          <t>Biology Chemistry and Physics/Engineering Sciences.</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2263,7 +2151,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2271,11 +2159,7 @@
           <t>Ordinary Diploma in Medical Laboratory Sciences</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with At Least four (4) Passes in non-religious Subjects including Chemistry, Biology, Physics/Engineering sciences/Basic Mathematics and English Language.</t>
-        </is>
-      </c>
+      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
           <t>3</t>
@@ -2293,7 +2177,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>KAMPALA INTERNATIONAL UNIVERSITY IN TANZANIA (KIUT) (KUC)</t>
+          <t>Language.</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2303,7 +2187,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2311,14 +2195,10 @@
           <t>Ordinary Diploma in Pharmaceutical Sciences</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with At Least four (4) Passes in non-religious Subjects including Chemistry and Biology. A Pass in Basic Mathematics and English Language Is An Added Advantage. KILIMANJARO CHRISTIAN MEDICAL UNIVERSITY COLLEGE (KCMU) (KC) - FBO Moshi Municipal Council - Kilimanjaro</t>
-        </is>
-      </c>
+      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>3 / Program Duration (Yrs)</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2333,17 +2213,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>KAMPALA INTERNATIONAL UNIVERSITY IN TANZANIA (KIUT) (KUC)</t>
+          <t>Program Duration (Yrs)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Dar es Salaam</t>
+          <t>Kilimanjaro</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2351,11 +2231,7 @@
           <t>Diploma in Occupational Therapy</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non religious Subjects including C pass in Biology and any two subjects in Chemistry, Mathematics, Geography, Economics, Physics/Physical Sciences.</t>
-        </is>
-      </c>
+      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
           <t>3</t>
@@ -2373,17 +2249,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>KAMPALA INTERNATIONAL UNIVERSITY IN TANZANIA (KIUT) (KUC)</t>
+          <t>Geography, Economics, Physics/Physical Sciences.</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Dar es Salaam</t>
+          <t>Kilimanjaro</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2391,14 +2267,10 @@
           <t>Ordinary Diploma in Medical Laboratory Sciences</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with At Least four (4) Passes in non-religious Subjects including Chemistry, Biology, Physics/Engineering sciences/Basic Mathematics and English Language. MARIAN UNIVERSITY COLLEGE (MAR) - FBO Bagamoyo District Council - Pwani</t>
-        </is>
-      </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>3 / Program Duration (Yrs)</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2413,17 +2285,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>KAMPALA INTERNATIONAL UNIVERSITY IN TANZANIA (KIUT) (KUC)</t>
+          <t>Program Duration (Yrs)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Dar es Salaam</t>
+          <t>Pwani</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2431,14 +2303,10 @@
           <t>Ordinary Diploma in Pharmaceutical Sciences</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with At Least four (4) Passes in non-religious Subjects including Chemistry and Biology. A Pass in Basic Mathematics and English Language Is An Added Advantage. MBEYA UNIVERSITY OF SCIENCE AND TECHNOLOGY (REG/EOS/003) - Government Mbeya City Council - Mbeya</t>
-        </is>
-      </c>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>3 / Program Duration (Yrs)</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2453,17 +2321,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>KAMPALA INTERNATIONAL UNIVERSITY IN TANZANIA (KIUT) (KUC)</t>
+          <t>Program Duration (Yrs)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Dar es Salaam</t>
+          <t>Mbeya</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2471,11 +2339,7 @@
           <t>Diploma in Architecture</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with Four (4) Passes in non-religious Subjects, three of which must be Mathematics, Physics, Chemistry/Geography</t>
-        </is>
-      </c>
+      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
           <t>3</t>
@@ -2493,17 +2357,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>KAMPALA INTERNATIONAL UNIVERSITY IN TANZANIA (KIUT) (KUC)</t>
+          <t>Mathematics, Physics, Chemistry/Geography</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Dar es Salaam</t>
+          <t>Mbeya</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2511,11 +2375,7 @@
           <t>Diploma in Bio Medical Equipment Engineering</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least Four (4) Passes in non-religious Subjects including Physics,Chemistry and Basic Mathematics.</t>
-        </is>
-      </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
           <t>3</t>
@@ -2533,17 +2393,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>KAMPALA INTERNATIONAL UNIVERSITY IN TANZANIA (KIUT) (KUC)</t>
+          <t>Physics,Chemistry and Basic Mathematics.</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Dar es Salaam</t>
+          <t>Mbeya</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2551,11 +2411,7 @@
           <t>Diploma in Business Administration</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects</t>
-        </is>
-      </c>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
           <t>3</t>
@@ -2573,17 +2429,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>KAMPALA INTERNATIONAL UNIVERSITY IN TANZANIA (KIUT) (KUC)</t>
+          <t>least four (4) passes in non</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Dar es Salaam</t>
+          <t>Mbeya</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2591,11 +2447,7 @@
           <t>Diploma in Civil Engineering</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least Four (4) passes in non-religious subjects including Physics, Chemistry and Basic Mathematics.</t>
-        </is>
-      </c>
+      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
           <t>3</t>
@@ -2613,17 +2465,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>KAMPALA INTERNATIONAL UNIVERSITY IN TANZANIA (KIUT) (KUC)</t>
+          <t>Physics, Chemistry and Basic Mathematics.</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Dar es Salaam</t>
+          <t>Mbeya</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2631,11 +2483,7 @@
           <t>Diploma in Computer Engineering</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least Four (4) passes in non-religious subjects including Physics, Chemistry and Basic Mathematics subjects.</t>
-        </is>
-      </c>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
           <t>3</t>
@@ -2653,17 +2501,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>KAMPALA INTERNATIONAL UNIVERSITY IN TANZANIA (KIUT) (KUC)</t>
+          <t>Physics, Chemistry and Basic Mathematics subjects.</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Dar es Salaam</t>
+          <t>Mbeya</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2671,11 +2519,7 @@
           <t>Diploma in Computer Science</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with Four (4) passes in non-religious subjects.</t>
-        </is>
-      </c>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
           <t>3</t>
@@ -2693,17 +2537,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>KAMPALA INTERNATIONAL UNIVERSITY IN TANZANIA (KIUT) (KUC)</t>
+          <t>Four (4) passes in non</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Dar es Salaam</t>
+          <t>Mbeya</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2711,11 +2555,7 @@
           <t>Diploma in Electric and Electronics Engineering</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least Four (4) passes in non- religious subjects including a pass in Basic Mathematics and Physics/Engineering Sciences and Chemistry</t>
-        </is>
-      </c>
+      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
           <t>3</t>
@@ -2733,17 +2573,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>KAMPALA INTERNATIONAL UNIVERSITY IN TANZANIA (KIUT) (KUC)</t>
+          <t>Mathematics and Physics/Engineering Sciences and Chemistry</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Dar es Salaam</t>
+          <t>Mbeya</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2751,11 +2591,7 @@
           <t>Diploma in Electrical Engineering</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least Four (4) passes in non- religious subjects including a pass in Basic Mathematics and Physics/Engineering Sciences</t>
-        </is>
-      </c>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
           <t>3</t>
@@ -2773,17 +2609,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>KAMPALA INTERNATIONAL UNIVERSITY IN TANZANIA (KIUT) (KUC)</t>
+          <t>Mathematics and Physics/Engineering Sciences</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Dar es Salaam</t>
+          <t>Mbeya</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2791,11 +2627,7 @@
           <t>Diploma in Electronics and Telecomunication Engineering</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least Four (4) passes in non-religious subjects including passes in Physics, Chemistry and Basic Mathematics.</t>
-        </is>
-      </c>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
           <t>3</t>
@@ -2813,17 +2645,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>KAMPALA INTERNATIONAL UNIVERSITY IN TANZANIA (KIUT) (KUC)</t>
+          <t>Chemistry and Basic Mathematics.</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Dar es Salaam</t>
+          <t>Mbeya</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2831,11 +2663,7 @@
           <t>Diploma in Food Science and Technology</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Certificate of Secondary Education Examination (CSEE) with at least four passes in non-religious subjects three of which must be in Mathematics, Physics/Chemistry or Biology. OR Certificate of Secondary Education Examination (CSEE) from Technical Secondary School with a pass in at least four passes in non-religious subjects three of which must be in Mathematics, Engineering Science/Chemistry and Biology and one of the following subjects: Architectural Drafting/Building, Construction, Electrical Engineering, Science/Electrical Drafting or Workshop Technology/Mechanical Drafting. OR Certificate of Secondary Education Examination (CSEE) with at least four passes in non-religious subjects two of which must be in the following subjects Mathematics, Physics, Chemistry or Biology with Trade Test Grade 1 or National Vocational Award (NVA) Level III issued by VETA.</t>
-        </is>
-      </c>
+      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
           <t>3</t>
@@ -2853,17 +2681,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>KAMPALA INTERNATIONAL UNIVERSITY IN TANZANIA (KIUT) (KUC)</t>
+          <t>Level III issued by VETA.</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Dar es Salaam</t>
+          <t>Mbeya</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2871,11 +2699,7 @@
           <t>Diploma in High Way Engineering</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least Four (4) Passes in non-religious Subjects including Physics, Chemistry and Basic Mathematics.</t>
-        </is>
-      </c>
+      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
           <t>3</t>
@@ -2893,17 +2717,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>KAMPALA INTERNATIONAL UNIVERSITY IN TANZANIA (KIUT) (KUC)</t>
+          <t>Physics, Chemistry and Basic Mathematics.</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Dar es Salaam</t>
+          <t>Mbeya</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2911,11 +2735,7 @@
           <t>Diploma in Information and Communication Technology</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holder of Certificate of Secondary Education with at least Four (4) passes in non-religious subject including Basic Mathematics and English Language.</t>
-        </is>
-      </c>
+      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
           <t>3</t>
@@ -2933,17 +2753,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>KAMPALA INTERNATIONAL UNIVERSITY IN TANZANIA (KIUT) (KUC)</t>
+          <t>English Language.</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Dar es Salaam</t>
+          <t>Mbeya</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2951,11 +2771,7 @@
           <t>Diploma in Laboratory Sciences Technology</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least Four (4) passes in non-religious subjects including Physics, Chemistry and Basic Mathematics.</t>
-        </is>
-      </c>
+      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
           <t>3</t>
@@ -2973,17 +2789,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>KAMPALA INTERNATIONAL UNIVERSITY IN TANZANIA (KIUT) (KUC)</t>
+          <t>Physics, Chemistry and Basic Mathematics.</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Dar es Salaam</t>
+          <t>Mbeya</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2991,11 +2807,7 @@
           <t>Diploma in Mechanical Engineering</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least Four (4) passes in non-religious subjects including Physics, Chemistry and Basic Mathematics.</t>
-        </is>
-      </c>
+      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
           <t>3</t>
@@ -3013,17 +2825,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>KAMPALA INTERNATIONAL UNIVERSITY IN TANZANIA (KIUT) (KUC)</t>
+          <t>Physics, Chemistry and Basic Mathematics.</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Dar es Salaam</t>
+          <t>Mbeya</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3031,11 +2843,7 @@
           <t>Diploma in Mechatronics Engineering</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least Four (4) passes in non-religious subjects including Physics, Chemistry and Basic Mathematics.</t>
-        </is>
-      </c>
+      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
           <t>3</t>
@@ -3053,27 +2861,27 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>KAMPALA INTERNATIONAL UNIVERSITY IN TANZANIA (KIUT) (KUC)</t>
+          <t>Physics, Chemistry and Basic Mathematics.</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Dar es Salaam</t>
+          <t>Mbeya</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Diploma in Mining Engineering MOSHI UNIVERSITY COLLEGE OF COOPERATIVE AND BUSINESS STUDIES (MOCU) (MC) - Government Moshi Municipal Council - Kilimanjaro</t>
+          <t>Diploma in Mining Engineering</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least Four (4) passes in non-religious subjects including Physics, Chemistry and Basic Mathematics.</t>
+          <t xml:space="preserve"> Admission Requirements</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3093,17 +2901,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>KAMPALA INTERNATIONAL UNIVERSITY IN TANZANIA (KIUT) (KUC)</t>
+          <t>MOSHI UNIVERSITY COLLEGE OF COOPERATIVE AND BUSINESS STUDIES (MOCU) (MC)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Dar es Salaam</t>
+          <t>Kilimanjaro</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3111,11 +2919,7 @@
           <t>Diploma in Business Information and Communication Technology</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate in Business and Information Technology OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one principal pass and one subsidiary in Principal subjects</t>
-        </is>
-      </c>
+      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
           <t>2</t>
@@ -3133,17 +2937,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>KAMPALA INTERNATIONAL UNIVERSITY IN TANZANIA (KIUT) (KUC)</t>
+          <t>at least one principal pass and one subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Dar es Salaam</t>
+          <t>Kilimanjaro</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3151,11 +2955,7 @@
           <t>Diploma in Co-operative Management and Accounting</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate in Cooperative Management and Accounting OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one principal pass and one subsidiary in Principal subjects</t>
-        </is>
-      </c>
+      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
           <t>2</t>
@@ -3173,17 +2973,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>KAMPALA INTERNATIONAL UNIVERSITY IN TANZANIA (KIUT) (KUC)</t>
+          <t>at least one principal pass and one subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Dar es Salaam</t>
+          <t>Kilimanjaro</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3191,11 +2991,7 @@
           <t>Diploma in Enterprise Management</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate in Enterprise Management OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one principal pass and one subsidiary Principal subjects</t>
-        </is>
-      </c>
+      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
           <t>2</t>
@@ -3213,17 +3009,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>KAMPALA INTERNATIONAL UNIVERSITY IN TANZANIA (KIUT) (KUC)</t>
+          <t>pass and one subsidiary Principal subjects</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Dar es Salaam</t>
+          <t>Kilimanjaro</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3231,11 +3027,7 @@
           <t>Diploma in Human Resource Management</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate in Human Resource Management OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one principal pass and one subsidiary in Principal subjects</t>
-        </is>
-      </c>
+      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
           <t>2</t>
@@ -3253,17 +3045,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>KAMPALA INTERNATIONAL UNIVERSITY IN TANZANIA (KIUT) (KUC)</t>
+          <t>principal pass and one subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Dar es Salaam</t>
+          <t>Kilimanjaro</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3271,11 +3063,7 @@
           <t>Diploma in Library and Archival Studies</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate in Library and Archival Studies OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one principal pass and one subsidiary Principal subjects</t>
-        </is>
-      </c>
+      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
           <t>2</t>
@@ -3293,27 +3081,27 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>KAMPALA INTERNATIONAL UNIVERSITY IN TANZANIA (KIUT) (KUC)</t>
+          <t>principal pass and one subsidiary Principal subjects</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Dar es Salaam</t>
+          <t>Kilimanjaro</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Diploma in Microfinance Management MUHIMBILI UNIVERSITY OF HEALTH AND ALLIED SCIENCES (MH) - Government Kinondoni Municipal Council - Dar es Salaam</t>
+          <t>Diploma in Microfinance Management</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Holders of Certificate in Accounting, Banking and Finance OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one principal pass and one subsidiary Principal subjects</t>
+          <t xml:space="preserve"> Admission Requirements</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3333,7 +3121,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>KAMPALA INTERNATIONAL UNIVERSITY IN TANZANIA (KIUT) (KUC)</t>
+          <t>MUHIMBILI UNIVERSITY OF HEALTH AND ALLIED SCIENCES (MH)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3343,7 +3131,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -3351,11 +3139,7 @@
           <t>Diploma in Diagnostic Radiography (ddr) - Evening</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects including English and at least three (3) Credits in either Physics, Chemistry, Biology and Mathematics. Physics is a major subject.</t>
-        </is>
-      </c>
+      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
           <t>3</t>
@@ -3373,7 +3157,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>KAMPALA INTERNATIONAL UNIVERSITY IN TANZANIA (KIUT) (KUC)</t>
+          <t>Mathematics. Physics is a major subject.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3383,7 +3167,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3391,11 +3175,7 @@
           <t>Diploma in Diagnostic Radiography - Ddr - Regular</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects including English and at least three (3) Credits one in Physics and two (2) others from either Chemistry, Biology and Mathematics.</t>
-        </is>
-      </c>
+      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
           <t>3</t>
@@ -3413,7 +3193,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>KAMPALA INTERNATIONAL UNIVERSITY IN TANZANIA (KIUT) (KUC)</t>
+          <t>Chemistry, Biology and Mathematics.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3423,19 +3203,15 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Diploma in Environmental Health Sciences - (DEHS) (dar Es Salaam)</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) Passes in non-religious Subjects, including English and at least Three (3) Credits one in Mathematics and two others from Physics, Chemistry or Biology.</t>
-        </is>
-      </c>
+          <t>Diploma in Environmental Health Sciences -</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
           <t>3</t>
@@ -3453,7 +3229,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>KAMPALA INTERNATIONAL UNIVERSITY IN TANZANIA (KIUT) (KUC)</t>
+          <t>Chemistry or Biology.</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3463,19 +3239,15 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Diploma in Environmental Health Sciences (DEHS) - Mpwapwa, Evening</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) Passes in non-religious Subjects, including English and at least three (3) Credits one in Mathematics and two others from Physics, Chemistry and Biology.</t>
-        </is>
-      </c>
+          <t>Diploma in Environmental Health Sciences (DEHS)</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
           <t>3</t>
@@ -3493,7 +3265,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>KAMPALA INTERNATIONAL UNIVERSITY IN TANZANIA (KIUT) (KUC)</t>
+          <t>Chemistry and Biology.</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3503,19 +3275,15 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Diploma in Environmental Health Sciences (DEHS) - Tanga - Evening</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) Passes in non-religious subjects, including English and at least three (3) Credits one in Mathematics and two others from Physics, Chemistry and Biology .</t>
-        </is>
-      </c>
+          <t>Diploma in Environmental Health Sciences (DEHS)</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
           <t>3</t>
@@ -3533,7 +3301,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>KAMPALA INTERNATIONAL UNIVERSITY IN TANZANIA (KIUT) (KUC)</t>
+          <t>Chemistry and Biology .</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3543,19 +3311,15 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Diploma in Environmental Health Sciences (DEHS) - Tanga - Regular</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least Four (4) Passes in non-religious Subjects, including English and at least Three (3) Credits one in Mathematics and two others from Physics, Chemistry and Biology</t>
-        </is>
-      </c>
+          <t>Diploma in Environmental Health Sciences (DEHS)</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
           <t>3</t>
@@ -3573,7 +3337,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>KAMPALA INTERNATIONAL UNIVERSITY IN TANZANIA (KIUT) (KUC)</t>
+          <t>Chemistry and Biology</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3583,19 +3347,15 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Diploma in Environmental Health Sciences - DEHS - (Dar es Salaam) - Evening</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least Four (4) Passes in non-religious Subjects, including English and at least Three (3) Credits one in Mathematics and two others from Physics, Chemistry and Biology .</t>
-        </is>
-      </c>
+          <t>Diploma in Environmental Health Sciences - DEHS</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
           <t>3</t>
@@ -3613,7 +3373,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>KAMPALA INTERNATIONAL UNIVERSITY IN TANZANIA (KIUT) (KUC)</t>
+          <t>Chemistry and Biology .</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3623,19 +3383,15 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Diploma in Environmental Health Sciences - Dehs - Mpwapwa</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least Four (4) Passes in non-religious Subjects, including English and at least Three (3) Credits one in Mathematics and two others from Physics, Chemistry and Biology.</t>
-        </is>
-      </c>
+          <t>Diploma in Environmental Health Sciences - Dehs -</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
           <t>3</t>
@@ -3653,7 +3409,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>KAMPALA INTERNATIONAL UNIVERSITY IN TANZANIA (KIUT) (KUC)</t>
+          <t>Chemistry and Biology.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3663,7 +3419,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -3671,11 +3427,7 @@
           <t>Diploma in Medical Laboratory Sciences (DMLS)</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least Five (5) Passes in non-religious Subjects including Mathematics and English and at least Three (3) Credits in Biology, Chemistry and Physics.</t>
-        </is>
-      </c>
+      <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
           <t>3</t>
@@ -3693,7 +3445,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>KAMPALA INTERNATIONAL UNIVERSITY IN TANZANIA (KIUT) (KUC)</t>
+          <t>Chemistry and Physics.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3703,19 +3455,15 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Diploma in Medical Laboratory Sciences (dmls) - Evening</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least Five (5) Passes in non-religious Subjects, including Mathematics and English and at least Three (3) Credits in Biology, Chemistry and Physics.</t>
-        </is>
-      </c>
+          <t>Diploma in Medical Laboratory Sciences (dmls) -</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
           <t>3</t>
@@ -3733,7 +3481,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>KAMPALA INTERNATIONAL UNIVERSITY IN TANZANIA (KIUT) (KUC)</t>
+          <t>Chemistry and Physics.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3743,7 +3491,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -3751,11 +3499,7 @@
           <t>Diploma in Nursing (dn) - Evening</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least Five (5) Passes in non-religious Subjects including Mathematics and English and at least Three (3) Credits in Biology, Chemistry and Physics,</t>
-        </is>
-      </c>
+      <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
           <t>3</t>
@@ -3773,7 +3517,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>KAMPALA INTERNATIONAL UNIVERSITY IN TANZANIA (KIUT) (KUC)</t>
+          <t>Chemistry and Physics,</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3783,7 +3527,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -3791,11 +3535,7 @@
           <t>Diploma in Nursing - DN - Regular</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least Five (5) Passes in non-religious Subjects, including Physics, Mathematics and English and Credit passes in Biology and Chemistry.</t>
-        </is>
-      </c>
+      <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
           <t>3</t>
@@ -3813,7 +3553,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>KAMPALA INTERNATIONAL UNIVERSITY IN TANZANIA (KIUT) (KUC)</t>
+          <t>Chemistry.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3823,7 +3563,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -3831,11 +3571,7 @@
           <t>Diploma in Orthopaedic Technology (DOT) - KCMC</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least Four (4) Passes in non-religious Subjects with at least Three (3) Credits from Physics, Chemistry, Biology or Mathematics. Credit pass in Engineering subjects is also acceptable as the third credit pass.</t>
-        </is>
-      </c>
+      <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
           <t>3</t>
@@ -3853,7 +3589,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>KAMPALA INTERNATIONAL UNIVERSITY IN TANZANIA (KIUT) (KUC)</t>
+          <t>Engineering subjects is also acceptable as the third credit pass.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3863,19 +3599,15 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Diploma in Pharmaceutical Sciences (DPS) - Evening</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least Fiver (5) Passes in non-religious subjects including Biology and Physics, and at least Three Credits in Mathematics, Chemistry and English.</t>
-        </is>
-      </c>
+          <t>Diploma in Pharmaceutical Sciences (DPS) -</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
           <t>3</t>
@@ -3893,7 +3625,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>KAMPALA INTERNATIONAL UNIVERSITY IN TANZANIA (KIUT) (KUC)</t>
+          <t>Chemistry and English.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3903,22 +3635,18 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Diploma in Pharmaceutical Sciences (DPS) - Regular</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least Five (5) Passes in non-religious Subjects including Biology and Physics, and at least Three (3) Credits in Mathematics, Chemistry and English.</t>
-        </is>
-      </c>
+          <t>Diploma in Pharmaceutical Sciences (DPS) -</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
-          <t>3 / Program Duration (Yrs)</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3933,7 +3661,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>MUSLIM UNIVERSITY OF MOROGORO (U/TLF/03)</t>
+          <t>Program Duration (Yrs)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3943,7 +3671,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -3951,11 +3679,7 @@
           <t>Diploma in Islamic Banking and Finance</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate in Islamic Banking and Finance OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal pass and one Subsidiary in Principal subjects</t>
-        </is>
-      </c>
+      <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
           <t>2</t>
@@ -3973,7 +3697,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>MUSLIM UNIVERSITY OF MOROGORO (U/TLF/03)</t>
+          <t>Principal pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3983,7 +3707,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -3991,11 +3715,7 @@
           <t>Diploma in Law and Shariah</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate in Law and Shariah OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal pass and one Subsidiary in Principal subjects</t>
-        </is>
-      </c>
+      <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
           <t>2</t>
@@ -4013,7 +3733,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>MUSLIM UNIVERSITY OF MOROGORO (U/TLF/03)</t>
+          <t>and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4023,7 +3743,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4033,7 +3753,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Holders of Certificate in Procurement and Supply,Logistics,Purchasing and Inventory OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal pass and one Subsidiary in Principal subjects</t>
+          <t xml:space="preserve"> and Inventory OR Advanced Certificate of Secondary Education</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -4053,7 +3773,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>MUSLIM UNIVERSITY OF MOROGORO (U/TLF/03)</t>
+          <t>Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4063,7 +3783,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -4071,11 +3791,7 @@
           <t>Ordinary Diploma in Accountancy</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects including Basic Mathematics OR National Vocational Award (NVA) Level III with a Certificate of Secondary Education Examination (CSEE) Holders of Basic Technician Certificate (NTA Level 4) in Accountancy OR Advance Certificate of Secondary Education Examination with at least one Principal pass and one Subsidiary in Principal subjects</t>
-        </is>
-      </c>
+      <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
           <t>3 / 2</t>
@@ -4093,7 +3809,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>MUSLIM UNIVERSITY OF MOROGORO (U/TLF/03)</t>
+          <t>one Principal pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4103,7 +3819,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -4113,7 +3829,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects OR National Vocational Award (NVA)Level III with a Certificate of Secondary Education Examination (CSEE) Holders of Basic Technician Certificate (NTA Level 4) in Business Administration, Account, Finance and Banking, Marketing, Procurement and Supply OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal pass and one Subsidiary in Principal subjects</t>
+          <t xml:space="preserve"> Holders of Basic Technician Certificate (NTA Level 4) in Business</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -4133,7 +3849,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>MUSLIM UNIVERSITY OF MOROGORO (U/TLF/03)</t>
+          <t>Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4143,7 +3859,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -4151,11 +3867,7 @@
           <t>Ordinary Diploma in Journalism</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects OR National Vocational Award (NVA) Level III with a Certificate of Secondary Education Examination (CSEE) Holders of Basic Technician Certificate (NTA Level 4) in Journalism, Mass Communication, TV Production, Media Production OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal pass and one Subsidiary in Principal subjects</t>
-        </is>
-      </c>
+      <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
           <t>3 / 2</t>
@@ -4173,7 +3885,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>MUSLIM UNIVERSITY OF MOROGORO (U/TLF/03)</t>
+          <t>one Principal pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4183,7 +3895,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -4191,11 +3903,7 @@
           <t>Ordinary Diploma in Medical Laboratory Sciences</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with At Least four (4) Passes in non-religious Subjects including Chemistry, Biology, Physics/Engineering sciences/Basic Mathematics and English Language.</t>
-        </is>
-      </c>
+      <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
           <t>3</t>
@@ -4213,7 +3921,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>MUSLIM UNIVERSITY OF MOROGORO (U/TLF/03)</t>
+          <t>Language.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4223,7 +3931,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -4233,7 +3941,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with Four (4) passes in non-religious subjects including Two (2) Passes in Biology, Chemistry, Physics/Engineering Sciences. Holders of Certificate of Secondary Education Examination (CSEE) with Four (4) Passes in non-religious Subjects including two (2) Passes in Biology, Chemistry, Physics/Engineering Sciences; and Possession of Basic Technician Certificate (NTA Level 4) in Science and Laboratory Technology; OR Advanced Certificate of Secondary Education Examination (ACSEE) with one (1) Principal Pass and one (1) Subsidiary Pass in Biology, Chemistry, Physics, Advanced Mathematics.</t>
+          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with Admission Requirements</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -4263,7 +3971,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -4271,11 +3979,7 @@
           <t>Ordinary Diploma in Accountancy</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects including Basic Mathematics Holders of Basic Technician Certificate (NTA level 4) in Accountancy, Business Administration Banking and Finances OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal pass and one Subsidiary in Principal subjects</t>
-        </is>
-      </c>
+      <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
           <t>3 / 2</t>
@@ -4293,7 +3997,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>MWENGE CATHOLIC UNIVERSITY (U/SAT/20 AND U/BTP/20)</t>
+          <t>Principal pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4303,7 +4007,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -4313,7 +4017,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in Non-Religious Subjects OR National Vocational Award (NVA) III with a Certificate of Secondary Education Examination (CSEE) Holders of Basic Technician Certificate (NTA level 4) in Business Administration OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal pass and one Subsidiary Principal subjects</t>
+          <t xml:space="preserve"> Holders of Basic Technician Certificate (NTA level 4) in Business</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -4333,7 +4037,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>MWENGE CATHOLIC UNIVERSITY (U/SAT/20 AND U/BTP/20)</t>
+          <t>Subsidiary Principal subjects</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4343,7 +4047,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -4351,11 +4055,7 @@
           <t>Ordinary Diploma in Computing and Information Technology</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with At Least four (4) Passes in non-religious subjects including Basic Mathematics and English Language or National Vocational Award (NVA Level III) with a Certificate of Secondary Education Examination (CSEE) Holders of Basic Technician Certificate (NTA 4) in Information Technology, Computer Sciences OR Advanced Certificate of Secondary Education Examination (ACSEE) with one Principal pass and one Subsidiary.</t>
-        </is>
-      </c>
+      <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
           <t>3 / 2</t>
@@ -4373,7 +4073,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>MWENGE CATHOLIC UNIVERSITY (U/SAT/20 AND U/BTP/20)</t>
+          <t>Subsidiary.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4383,7 +4083,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -4391,11 +4091,7 @@
           <t>Ordinary Diploma in Law</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of certificate of secondary education examination (CSEE) with at least four (4) passes in non- religious subjects including English Language Holders of Basic Technician Certificate (NTA level 4) in Law OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal pass and one Subsidiary in Principal subjects</t>
-        </is>
-      </c>
+      <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
           <t>3 / 2</t>
@@ -4413,7 +4109,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>MWENGE CATHOLIC UNIVERSITY (U/SAT/20 AND U/BTP/20)</t>
+          <t>at least one Principal pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4423,7 +4119,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -4431,11 +4127,7 @@
           <t>Ordinary Diploma in Procurement and Supply</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination ( CSEE ) with at least four (4) passes in non- religious subjects Holders of Basic Technician Certificate (NTA Level 4) in Procurement and Supply, Logistics, Clearing and Forwarding OR Advanced Certificate of Secondary Education Examination (ACSEE) with at Least one Principal pass and one Subsidiary in Principal subjects</t>
-        </is>
-      </c>
+      <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
           <t>3 / 2</t>
@@ -4453,7 +4145,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>MWENGE CATHOLIC UNIVERSITY (U/SAT/20 AND U/BTP/20)</t>
+          <t>one Principal pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4463,7 +4155,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -4471,11 +4163,7 @@
           <t>Ordinary Diploma in Records, Archives and Information Management</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non religious subjects OR National Vocational Award (NVA) Level III with a Certificate of Secondary Education Examination (CSEE) Holders of Basic Technician Certificate (NTA Level 4) in Records Management, Medical Records, Library and information studies OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal pass and one Subsidiary in Principal subjects</t>
-        </is>
-      </c>
+      <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
           <t>3 / 2</t>
@@ -4493,7 +4181,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>MWENGE CATHOLIC UNIVERSITY (U/SAT/20 AND U/BTP/20)</t>
+          <t>at least one Principal pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4503,7 +4191,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -4511,14 +4199,10 @@
           <t>Ordinary Diploma in Social Work</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects Holder of Basic Technician Certificate (NTA Level 4) in Social Work, Gender and Community Development OR Advanced Certificate of Secondary Education Examination (ACSEE) with at Least one Principal pass and one Subsidiary in Principal subjects MZUMBE UNIVERSITY (MU) - Government Mvomero District Council - Morogoro</t>
-        </is>
-      </c>
+      <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
-          <t>3 / 2 / Program Duration (Yrs)</t>
+          <t>3 / 2</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -4533,17 +4217,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>MWENGE CATHOLIC UNIVERSITY (U/SAT/20 AND U/BTP/20)</t>
+          <t>Program Duration (Yrs)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Kilimanjaro</t>
+          <t>Morogoro</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -4553,7 +4237,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Holders of Certificate in Applied Statistics OR Advanced Certificate of Secondary Education with at least one Principal pass and one Subsidiary in Principal subjects</t>
+          <t>Holders of Certificate in Applied Statistics OR Advanced Certificate of</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4573,17 +4257,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>MWENGE CATHOLIC UNIVERSITY (U/SAT/20 AND U/BTP/20)</t>
+          <t>Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Kilimanjaro</t>
+          <t>Morogoro</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -4593,7 +4277,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Holders of Certificate in Applied Statistics OR Advanced Certificate of Secondary Education Examination (ACSEE) with One Principal Pass in Either Chemistry, Biology or Advanced Mathematics and One Subsidiary in any Subject</t>
+          <t>Holders of Certificate in Applied Statistics OR Advanced Certificate of</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4613,17 +4297,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>MWENGE CATHOLIC UNIVERSITY (U/SAT/20 AND U/BTP/20)</t>
+          <t>Subsidiary in any Subject</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Kilimanjaro</t>
+          <t>Morogoro</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -4631,14 +4315,10 @@
           <t>Diploma in Information Technology (dit)</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate in Information Technology, Computer Engineering OR Advanced Certificate of Secondary Education Examination (ACSEE) with One Principal Pass in either Physics, Chemistry, Biology or Advanced Mathematics and One Subsidiary MZUMBE UNIVERSITY (MU), MBEYA COLLEGE (MMB) - Government Mbeya City Council - Mbeya</t>
-        </is>
-      </c>
+      <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2 / Program Duration (Yrs)</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -4653,17 +4333,17 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>MWENGE CATHOLIC UNIVERSITY (U/SAT/20 AND U/BTP/20)</t>
+          <t>Program Duration (Yrs)</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Kilimanjaro</t>
+          <t>Mbeya</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -4671,11 +4351,7 @@
           <t>Diploma in Accountancy (da)</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate in Accountancy, Finance and Banking OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal pass and subsidiary in Principal subjects</t>
-        </is>
-      </c>
+      <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
           <t>2</t>
@@ -4693,17 +4369,17 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>MWENGE CATHOLIC UNIVERSITY (U/SAT/20 AND U/BTP/20)</t>
+          <t>Principal pass and subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Kilimanjaro</t>
+          <t>Mbeya</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -4711,11 +4387,7 @@
           <t>Diploma in Business Administration</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate in Business Management, Procurement and Supply Chain, Accountancy OR Advanced Certificate of Secondary Education Examination (ACSEE)With at Least one Principal pass and one subsidiary in Principal subjects.</t>
-        </is>
-      </c>
+      <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
           <t>2</t>
@@ -4733,17 +4405,17 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>MWENGE CATHOLIC UNIVERSITY (U/SAT/20 AND U/BTP/20)</t>
+          <t>in Principal subjects.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Kilimanjaro</t>
+          <t>Mbeya</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -4751,11 +4423,7 @@
           <t>Diploma in Human Resource Management</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Human Resources Management, Local Government Administration, Social Work, Law, Business Management, Community development, Records and Archives Management. OR Advanced Certificate of Secondary Education Examination (ACSEE) with at Least one Principal Pass and one Subsidiary in Principal subjects</t>
-        </is>
-      </c>
+      <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
           <t>2</t>
@@ -4773,17 +4441,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>MWENGE CATHOLIC UNIVERSITY (U/SAT/20 AND U/BTP/20)</t>
+          <t>at Least one Principal Pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Kilimanjaro</t>
+          <t>Mbeya</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -4791,11 +4459,7 @@
           <t>Diploma in Law</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate in Law OR Advanced Certificate of Secondary Education Examination (ACSEE) with at Least one Principal Pass and one subsidiary in Principal subjects</t>
-        </is>
-      </c>
+      <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
           <t>2</t>
@@ -4813,17 +4477,17 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>MWENGE CATHOLIC UNIVERSITY (U/SAT/20 AND U/BTP/20)</t>
+          <t>subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Kilimanjaro</t>
+          <t>Mbeya</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -4831,11 +4495,7 @@
           <t>Diploma in Logistics Management</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate in Logistics Management, Business Administration, Accountancy, Banking OR Advanced Certificate of Secondary Education with at Least Principal Pass and one Subsidiary in Principal subjects</t>
-        </is>
-      </c>
+      <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
           <t>2</t>
@@ -4853,17 +4513,17 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>MWENGE CATHOLIC UNIVERSITY (U/SAT/20 AND U/BTP/20)</t>
+          <t>Principal subjects</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Kilimanjaro</t>
+          <t>Mbeya</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -4873,12 +4533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Holders of Certificate in Procurement and Supply Chain Business Management, Public Administration, Accountancy OR Advanced Certificate of Secondary Education Examination (ACSEE) with at Least one Principal Pass and one subsidiary in Principal subjects</t>
+          <t xml:space="preserve"> Management, Public Administration, Accountancy OR Advanced</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2 / Program Duration (Yrs)</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -4893,7 +4553,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>OPEN UNIVERSITY OF TANZANIA (OUT)</t>
+          <t>Program Duration (Yrs)</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4903,7 +4563,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -4911,11 +4571,7 @@
           <t>Basic Technician Certificate in Entrepreneurship</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects</t>
-        </is>
-      </c>
+      <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
           <t>1</t>
@@ -4933,7 +4589,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>OPEN UNIVERSITY OF TANZANIA (OUT)</t>
+          <t>least four (4) passes in non</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4943,7 +4599,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -4951,11 +4607,7 @@
           <t>Basic Technician Certificate in Hair and Beauty</t>
         </is>
       </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of certificate of Secondary Education Examination (CSEE) with four (4) passes in non-religious subjects</t>
-        </is>
-      </c>
+      <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
           <t>1</t>
@@ -4973,7 +4625,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>OPEN UNIVERSITY OF TANZANIA (OUT)</t>
+          <t>four (4) passes in non</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4983,7 +4635,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -4991,11 +4643,7 @@
           <t>Diploma in Common Wealth Youth Programme</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Technician Certificate (NTA Level 5)in Youth work OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal pass and Subsidiary in Principal subjects</t>
-        </is>
-      </c>
+      <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
           <t>2</t>
@@ -5013,7 +4661,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>OPEN UNIVERSITY OF TANZANIA (OUT)</t>
+          <t>at least one Principal pass and Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -5023,7 +4671,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -5033,7 +4681,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Holders of Basic Technician Certificate (NTA Level 4) in Distance Education</t>
+          <t>Holders of Basic Technician Certificate (NTA Level 4) in Distance</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -5053,7 +4701,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>OPEN UNIVERSITY OF TANZANIA (OUT)</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -5063,7 +4711,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -5071,11 +4719,7 @@
           <t>Diploma in Early Childhood Education (dece)</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of certificate of secondary education examination (CSEE) with Four passes or with two passes for those who have NVA level III recognized by VETA and Grade III A OR Basic technician certificate in teaching with an average of B and above</t>
-        </is>
-      </c>
+      <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
           <t>2</t>
@@ -5093,7 +4737,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>OPEN UNIVERSITY OF TANZANIA (OUT)</t>
+          <t>an average of B and above</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -5103,7 +4747,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -5113,7 +4757,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Holders of Technician Certificate (NTA level 5) in Library and Information studies</t>
+          <t>Holders of Technician Certificate (NTA level 5) in Library and</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -5133,7 +4777,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>OPEN UNIVERSITY OF TANZANIA (OUT)</t>
+          <t>Information studies</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -5143,7 +4787,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -5151,11 +4795,7 @@
           <t>Diploma in Poultry Production and Health (odpph)</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Technician Certificate ( NTA Level 5 ) in Animal Production, General Agriculture With 2.0 GPA and above.</t>
-        </is>
-      </c>
+      <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
           <t>2</t>
@@ -5173,7 +4813,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>OPEN UNIVERSITY OF TANZANIA (OUT)</t>
+          <t>General Agriculture With 2.0 GPA and above.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5183,7 +4823,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -5191,11 +4831,7 @@
           <t>Diploma in Primary Teacher Education (odpte)</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holder of Certificate of Secondary Education Examination (CSEE) with four Passes or with two Passes for Those Who Have Nva Level III Recognized By Veta and Grade III A or Basic Technician Certificate in Teaching with An Average of B+ and above or Holder of Advinced Certificate of Secondary Education with one Principal Pass and one Subsidiary from Any two Subjects</t>
-        </is>
-      </c>
+      <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
           <t>2</t>
@@ -5213,7 +4849,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>OPEN UNIVERSITY OF TANZANIA (OUT)</t>
+          <t>Subsidiary from Any two Subjects</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5223,7 +4859,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -5233,7 +4869,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects Holders of Basic Technical Certificate Certificate ( NTA Level 4) in Accountancy OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal pass and one Subsidiary in Principal subjects</t>
+          <t xml:space="preserve"> Holders of Basic Technical Certificate Certificate ( NTA Level 4) in</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -5253,7 +4889,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>OPEN UNIVERSITY OF TANZANIA (OUT)</t>
+          <t>Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5263,7 +4899,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -5271,11 +4907,7 @@
           <t>Ordinary Diploma in Business Administration</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects Holders of Basic Technical Certificate Certificate (NTA Level 4) in Business Administration, Accountancy Marketing and Procurement and Supply OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal Pass and one Subsidiary in Principal subjects</t>
-        </is>
-      </c>
+      <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
           <t>3 / 2</t>
@@ -5293,7 +4925,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>OPEN UNIVERSITY OF TANZANIA (OUT)</t>
+          <t>subjects</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5303,7 +4935,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -5313,7 +4945,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with Four (4) passes in non-religious subjects. Holders of Basic Technician Certificate (NTA Level 4) in Information Communication Technology OR Advanced Certificate of Secondary Education Examination (ACSEE) with one Principal Pass and One Subsidiary Pass.</t>
+          <t xml:space="preserve"> Holders of Basic Technician Certificate (NTA Level 4) in Information</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -5333,7 +4965,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>OPEN UNIVERSITY OF TANZANIA (OUT)</t>
+          <t>Subsidiary Pass.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5343,7 +4975,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -5353,7 +4985,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects Holders of Basic Technician Certificate (NTA Level 5) in Procurement and Supply, Logistics, Clearing and Forwarding, Business Administration, Accounting OR Advanced Certificate of Secondary Education Examination (ACSEE) with one Principal Pass and one Subsidiary in principal subjects.</t>
+          <t xml:space="preserve"> Holders of Basic Technician Certificate (NTA Level 5) in Procurement</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -5373,7 +5005,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>OPEN UNIVERSITY OF TANZANIA (OUT)</t>
+          <t>Subsidiary in principal subjects.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5383,7 +5015,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -5393,7 +5025,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with four (4) passes in non religious subjects Holders of Basic Technician Certificate (NTA Level 4) in Social work</t>
+          <t xml:space="preserve"> Admission Requirements</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -5423,7 +5055,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -5431,11 +5063,7 @@
           <t>Diploma in Business Administration</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate in Business Administration OR Advanced Certificate of Secondary Education Examination (ACSEE) with at Least one Principal pass and Subsidiary in Principal subjects</t>
-        </is>
-      </c>
+      <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
           <t>2</t>
@@ -5453,7 +5081,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>RUAHA CATHOLIC UNIVERSITY (RUCU) (RU)</t>
+          <t>pass and Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5463,7 +5091,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -5471,11 +5099,7 @@
           <t>Diploma in Computer Science</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate in Computer Science (CS), Information Technology (IT), Business Information Technology (BIT); OR Advanced Certificate of Secondary Education Examination (ACSEE) with one principal pass and one subsidiary pass.</t>
-        </is>
-      </c>
+      <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
           <t>2</t>
@@ -5493,7 +5117,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>RUAHA CATHOLIC UNIVERSITY (RUCU) (RU)</t>
+          <t>principal pass and one subsidiary pass.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5503,7 +5127,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -5513,7 +5137,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Holders of Certificate in Human Resource Management OR Advanced Certificate of Secondary Education Examination with one Principal Pass and one Subsidiary in Principal subjects</t>
+          <t>Holders of Certificate in Human Resource Management OR Advanced</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -5533,7 +5157,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>RUAHA CATHOLIC UNIVERSITY (RUCU) (RU)</t>
+          <t>Pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -5543,7 +5167,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -5551,11 +5175,7 @@
           <t>Diploma in Law</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate in Law OR Advanced Certificate of Secondary Education Examination with at least one Principal pass and one Subsidiary in Principal subjects</t>
-        </is>
-      </c>
+      <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
           <t>2</t>
@@ -5573,7 +5193,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>RUAHA CATHOLIC UNIVERSITY (RUCU) (RU)</t>
+          <t>Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -5583,7 +5203,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -5591,11 +5211,7 @@
           <t>Diploma in Library and Information Studies</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate in Library and Information Studies OR Advanced Certificate of Secondary Education Examination with at least one Principal pass and one Subsidiary in Principal subjects</t>
-        </is>
-      </c>
+      <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
           <t>2</t>
@@ -5613,7 +5229,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>RUAHA CATHOLIC UNIVERSITY (RUCU) (RU)</t>
+          <t>Principal pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -5623,7 +5239,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -5631,11 +5247,7 @@
           <t>Ordinary Diploma in Clinical Medicine</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with four (4) Passes in non-religious Subjects including Chemistry, Biology and Physics/Engineering Sciences. A Pass in Basic Mathematics and English Language Is An Added Advantage.</t>
-        </is>
-      </c>
+      <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
           <t>3</t>
@@ -5653,7 +5265,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>RUAHA CATHOLIC UNIVERSITY (RUCU) (RU)</t>
+          <t>Language Is An Added Advantage.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -5663,7 +5275,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -5671,11 +5283,7 @@
           <t>Ordinary Diploma in Environmental Health Sciences</t>
         </is>
       </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with At Least four (4) Passes in non-religious Subjects including Biology Chemistry and Physics/Engineering Sciences.</t>
-        </is>
-      </c>
+      <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
           <t>3</t>
@@ -5693,7 +5301,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>RUAHA CATHOLIC UNIVERSITY (RUCU) (RU)</t>
+          <t>Biology Chemistry and Physics/Engineering Sciences.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -5703,7 +5311,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -5711,11 +5319,7 @@
           <t>Ordinary Diploma in Medical Laboratory Sciences</t>
         </is>
       </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with At Least four (4) Passes in non-religious Subjects including Chemistry, Biology, Physics/Engineering sciences/Basic Mathematics and English Language.</t>
-        </is>
-      </c>
+      <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
           <t>3</t>
@@ -5733,7 +5337,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>RUAHA CATHOLIC UNIVERSITY (RUCU) (RU)</t>
+          <t>Language.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5743,7 +5347,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -5751,11 +5355,7 @@
           <t>Ordinary Diploma in Nursing and Midwifery</t>
         </is>
       </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects including Chemistry, Biology and Physics/Engineering Sciences. A pass in Basic Mathematics and English Language is an added advantage.</t>
-        </is>
-      </c>
+      <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
           <t>3</t>
@@ -5773,7 +5373,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>RUAHA CATHOLIC UNIVERSITY (RUCU) (RU)</t>
+          <t>Mathematics and English Language is an added advantage.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -5783,7 +5383,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -5793,7 +5393,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with At Least four (4) Passes in non-religious Subjects including Chemistry and Biology. A Pass in Basic Mathematics and English Language Is An Added Advantage.</t>
+          <t xml:space="preserve"> Admission Requirements</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5823,7 +5423,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -5831,11 +5431,7 @@
           <t>Diploma in Crop Production and Management</t>
         </is>
       </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate in Crop production,Agriculture General, Certificate in Agriculture and Livestock Production (CALP) OR Advanced Certificate of Secondary Education Examination (ACSEE) Passes in Chemistry, Biology/zoology, Physics, Mathematics, Geography or Science and Practice of Agriculture. The Candidate Must Pass Biology/zoology At Principal Level. Such Candidates Must also Passes in English and Mathematics at Certificate of Secondary Education Examination (CSEE)</t>
-        </is>
-      </c>
+      <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
           <t>2</t>
@@ -5853,7 +5449,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>SOKOINE UNIVERSITY OF AGRICULTURE (SU)</t>
+          <t>Education Examination (CSEE)</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -5863,7 +5459,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -5871,11 +5467,7 @@
           <t>Diploma in Information and Library Sciences(dils)</t>
         </is>
       </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Technical Certificate(NTA 5) in Librarianship, Records Management OR Advanced Certificate of Secondary Education with at least one Principal Pass in Mathematics, Physics, Biology, Chemistry, Science and Practice of Agriculture, Geography, Economics, Commerce, History, English, French and Kiswahili</t>
-        </is>
-      </c>
+      <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
           <t>2</t>
@@ -5893,7 +5485,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>SOKOINE UNIVERSITY OF AGRICULTURE (SU)</t>
+          <t>Commerce, History, English, French and Kiswahili</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -5903,7 +5495,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -5911,11 +5503,7 @@
           <t>Diploma in Information Technology</t>
         </is>
       </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate in Information Technology,Computer Engineering OR Advanced Certificate of Secondary Education with at least one Principal Pass in Mathematics, Physics, Biology, Chemistry, Science and Practice of Agriculture, Geography, Economics, Commerce, History, English, French and Kiswahili.</t>
-        </is>
-      </c>
+      <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
           <t>2</t>
@@ -5933,7 +5521,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>SOKOINE UNIVERSITY OF AGRICULTURE (SU)</t>
+          <t>Commerce, History, English, French and Kiswahili.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -5943,7 +5531,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -5951,11 +5539,7 @@
           <t>Diploma in Laboratory Technology</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Basic Certificate in Laboratory Technology with GPA 2.0 from recognized institution OR Advanced Certificate of Secondary Education with at least one Principal Pass in Mathematics, Physics, Biology, Chemistry, Science and Practice of Agriculture, Geography, Economics, Commerce, History, English, French and Kiswahili.</t>
-        </is>
-      </c>
+      <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
           <t>2</t>
@@ -5973,7 +5557,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>SOKOINE UNIVERSITY OF AGRICULTURE (SU)</t>
+          <t>Economics, Commerce, History, English, French and Kiswahili.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -5983,7 +5567,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -5991,11 +5575,7 @@
           <t>Diploma in Records, Archives and Information Management (dram)</t>
         </is>
       </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Technical Certificate (NTA level 5) in Records Management, Librarianship OR Advanced Certificate of Secondary Education with at least one Principal pass in Mathematics, Physics, Biology, Chemistry, Science and Practice of Agriculture, Geography, Economics, Commerce, History, English, French and Kiswahili</t>
-        </is>
-      </c>
+      <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
         <is>
           <t>2</t>
@@ -6013,7 +5593,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>SOKOINE UNIVERSITY OF AGRICULTURE (SU)</t>
+          <t>Commerce, History, English, French and Kiswahili</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -6023,7 +5603,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -6033,7 +5613,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Holders of Certificate in Animal Health (AGRO VET), Certificate in Animal Health and Production (AHPC), Certificate in Agriculture and Livestock Production (CALP) OR Advanced Certificate of Secondary Education Examination (ACSEE) Passes in Chemistry, Biology/zoology, Physics, Mathematics, Geography or Science and Practice of Agriculture. The Candidate Must Pass Biology/zoology At Principal Level. Such Candidates Must also Passes in English and Mathematics at Certificate of Secondary Education Examination (CSEE)</t>
+          <t xml:space="preserve"> Admission Requirements</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -6063,7 +5643,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -6071,11 +5651,7 @@
           <t>Diploma in Banking and Finance</t>
         </is>
       </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate in Banking and Finance OR Advanced Certificate of Secondary Education Examination (ACSEE) with one Principal pass and one Subsidiary in Principal subjects</t>
-        </is>
-      </c>
+      <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
           <t>2</t>
@@ -6093,7 +5669,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ST JOHN'S UNIVERSITY OF TANZANIA (SJ)</t>
+          <t>one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -6103,7 +5679,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -6133,7 +5709,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>ST JOHN'S UNIVERSITY OF TANZANIA (SJ)</t>
+          <t>one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -6143,12 +5719,12 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Diploma in Business Administration (human Resource)</t>
+          <t>Diploma in Business Administration (human</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -6173,7 +5749,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>ST JOHN'S UNIVERSITY OF TANZANIA (SJ)</t>
+          <t>Resource)</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -6183,7 +5759,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -6191,11 +5767,7 @@
           <t>Diploma in Business Administration (marketing)</t>
         </is>
       </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate in Business Administration; OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal pass and one Subsidiary in Principal subjects</t>
-        </is>
-      </c>
+      <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr">
         <is>
           <t>2</t>
@@ -6213,7 +5785,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>ST JOHN'S UNIVERSITY OF TANZANIA (SJ)</t>
+          <t>Principal pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -6223,7 +5795,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -6231,11 +5803,7 @@
           <t>Diploma in Business Administration (procurement)</t>
         </is>
       </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate in Business Administration, Procurement and Supply OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal pass and one Subsidiary in Principal subjects</t>
-        </is>
-      </c>
+      <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
           <t>2</t>
@@ -6253,7 +5821,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>ST JOHN'S UNIVERSITY OF TANZANIA (SJ)</t>
+          <t>subjects</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -6263,7 +5831,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -6271,11 +5839,7 @@
           <t>Diploma in Business Administration - Accounting</t>
         </is>
       </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate in Business Administration - Accounting OR Advanced Certificate of Secondary Education Examination (ACSEE) with one Principal pass and one Subsidiary pass in Principal subjects</t>
-        </is>
-      </c>
+      <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
         <is>
           <t>2</t>
@@ -6293,7 +5857,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>ST JOHN'S UNIVERSITY OF TANZANIA (SJ)</t>
+          <t>one Principal pass and one Subsidiary pass in Principal subjects</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -6303,7 +5867,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -6311,11 +5875,7 @@
           <t>Diploma in Business Administration - Marketing</t>
         </is>
       </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate in Business Administration - Marketing OR Advanced Certificate of Secondary Education Examination (ACSEE) with one Principal pass and one Subsidiary in Principal subjects</t>
-        </is>
-      </c>
+      <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
           <t>2</t>
@@ -6333,7 +5893,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ST JOHN'S UNIVERSITY OF TANZANIA (SJ)</t>
+          <t>Principal pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -6343,7 +5903,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -6351,11 +5911,7 @@
           <t>Diploma in Community Development</t>
         </is>
       </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate in Community Development OR Advanced Certificate of Secondary Education Examination (ACSEE) with one Principal pass and one Subsidiary in Principal subjects</t>
-        </is>
-      </c>
+      <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
         <is>
           <t>2</t>
@@ -6373,7 +5929,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>ST JOHN'S UNIVERSITY OF TANZANIA (SJ)</t>
+          <t>Principal pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -6383,7 +5939,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -6391,11 +5947,7 @@
           <t>Diploma in Computer System Maintanance</t>
         </is>
       </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Technician Certificate (NTA Level 5) in Computer Maintenance,Computer Engineering OR Advanced Certificate of Secondary Education Examination (ACSEE) with One Principal Pass and one Subsidiary Principal subjects</t>
-        </is>
-      </c>
+      <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
         <is>
           <t>2</t>
@@ -6413,7 +5965,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>ST JOHN'S UNIVERSITY OF TANZANIA (SJ)</t>
+          <t>one Subsidiary Principal subjects</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -6423,7 +5975,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -6431,11 +5983,7 @@
           <t>Diploma in Law</t>
         </is>
       </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate in Law OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal pass and one Subsidiary in Principal subjects</t>
-        </is>
-      </c>
+      <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr">
         <is>
           <t>2</t>
@@ -6453,7 +6001,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ST JOHN'S UNIVERSITY OF TANZANIA (SJ)</t>
+          <t>Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -6463,7 +6011,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -6471,11 +6019,7 @@
           <t>Diploma in Project Planning and Management</t>
         </is>
       </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Technician Certificate (NTA LEVEL 5) in Project Planning and Management or Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal pass and one Subsidiary in Principal subjects</t>
-        </is>
-      </c>
+      <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr">
         <is>
           <t>2</t>
@@ -6493,7 +6037,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>ST JOHN'S UNIVERSITY OF TANZANIA (SJ)</t>
+          <t>Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -6503,7 +6047,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -6511,11 +6055,7 @@
           <t>Diploma in Theology</t>
         </is>
       </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with four (4) passes in non-religious subjects</t>
-        </is>
-      </c>
+      <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr">
         <is>
           <t>3</t>
@@ -6533,7 +6073,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>ST JOHN'S UNIVERSITY OF TANZANIA (SJ)</t>
+          <t>four (4) passes in non</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -6543,7 +6083,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -6551,11 +6091,7 @@
           <t>Ordinary Diploma in Community Development</t>
         </is>
       </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with At Least four (4) Passes in non-religious Subjects Holders of Basic Technician Certificate (NTA Level 4) in Community Development, Gender, Youth Work or Advanced Certificate of Secondary Education (ACSEE) with one Principal Pass and one Subsidiary.</t>
-        </is>
-      </c>
+      <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr">
         <is>
           <t>3 / 2</t>
@@ -6573,7 +6109,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>ST JOHN'S UNIVERSITY OF TANZANIA (SJ)</t>
+          <t>Subsidiary.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -6583,7 +6119,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -6591,11 +6127,7 @@
           <t>Ordinary Diploma in Medical Laboratory Sciences</t>
         </is>
       </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with At Least four (4) Passes in non-religious Subjects including Chemistry, Biology, Physics/Engineering sciences/Basic Mathematics and English Language.</t>
-        </is>
-      </c>
+      <c r="E155" t="inlineStr"/>
       <c r="F155" t="inlineStr">
         <is>
           <t>3</t>
@@ -6613,7 +6145,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>ST JOHN'S UNIVERSITY OF TANZANIA (SJ)</t>
+          <t>Language.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -6623,7 +6155,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -6631,11 +6163,7 @@
           <t>Ordinary Diploma in Nursing and Midwifery</t>
         </is>
       </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects including Chemistry, Biology and Physics/Engineering Sciences. A pass in Basic Mathematics and English Language is an added advantage.</t>
-        </is>
-      </c>
+      <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr">
         <is>
           <t>3</t>
@@ -6653,7 +6181,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>ST JOHN'S UNIVERSITY OF TANZANIA (SJ)</t>
+          <t>Mathematics and English Language is an added advantage.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -6663,7 +6191,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -6671,11 +6199,7 @@
           <t>Ordinary Diploma in Pharmaceutical Sciences</t>
         </is>
       </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with At Least four (4) Passes in non-religious Subjects including Chemistry and Biology. A Pass in Basic Mathematics and English Language Is An Added Advantage.</t>
-        </is>
-      </c>
+      <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr">
         <is>
           <t>3</t>
@@ -6693,7 +6217,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>ST JOHN'S UNIVERSITY OF TANZANIA (SJ)</t>
+          <t>Language Is An Added Advantage.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -6703,7 +6227,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -6713,12 +6237,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examinations (CSEE) with at least Four (4) passes in non - religious subjects including Physics/Engineering Science, Basic Mathematics, Chemistry and Biology; OR Holder of General Certificate in Engineering; OR Holder of Certificate of Secondary Education (CSEE) with a Minimum of pass in Basic Mathematics and National Vocational Award (NVA) Level III or Trade Test Certificate of Grade I in the relevant field offered by VETA Accredited Institution. Kinondoni Municipal Council - Dar es Salaam</t>
+          <t xml:space="preserve"> Admission Requirements</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 / Program Duration (Yrs)</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -6733,17 +6257,17 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>ST JOHN'S UNIVERSITY OF TANZANIA (SJ)</t>
+          <t>S</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Dodoma</t>
+          <t>Dar es Salaam</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -6773,22 +6297,22 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>ST JOHN'S UNIVERSITY OF TANZANIA (SJ)</t>
+          <t>S</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Dodoma</t>
+          <t>Dar es Salaam</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Ordinary Diploma in Computer Science and Engineering</t>
+          <t>Ordinary Diploma in Computer Science and</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -6813,22 +6337,22 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>ST JOHN'S UNIVERSITY OF TANZANIA (SJ)</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Dodoma</t>
+          <t>Dar es Salaam</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Ordinary Diploma in Electrical and Electronics Engineering</t>
+          <t>Ordinary Diploma in Electrical and Electronics</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -6853,22 +6377,22 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>ST JOHN'S UNIVERSITY OF TANZANIA (SJ)</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Dodoma</t>
+          <t>Dar es Salaam</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Ordinary Diploma in Electronics and Communication Engineering</t>
+          <t>Ordinary Diploma in Electronics and</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -6893,17 +6417,17 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>ST JOHN'S UNIVERSITY OF TANZANIA (SJ)</t>
+          <t>Communication Engineering</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Dodoma</t>
+          <t>Dar es Salaam</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -6911,11 +6435,7 @@
           <t>Ordinary Diploma in Industrial Engineering</t>
         </is>
       </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examinations (CSEE) with at least Four (4) passes in non-religious subjects including Physics/Engineering Science, Basic Mathematics and Chemistry; OR General Certificate in Engineering; or National Vocational Award (NVA) Level III or Trade Test Certificate Grade I in Industrial Engineering. Or Possession of Certificate of Secondary Education Examination (CSEE) from Technical Secondary Schools with at Least four (4) Passes in nonreligious Subjects, three of which must be Mathematics, Engineering Science, Chemistry and any one of the Following Subjects: Architectural Drafting/building Construction, Electrical Engineering Science/electrical Drafting, Workshop Technology/mechanical Drafting;</t>
-        </is>
-      </c>
+      <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr">
         <is>
           <t>3</t>
@@ -6933,17 +6453,17 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>ST JOHN'S UNIVERSITY OF TANZANIA (SJ)</t>
+          <t>Drafting;</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Dodoma</t>
+          <t>Dar es Salaam</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -6953,7 +6473,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examinations (CSEE) with At Least four (4) Passes in non-religious Subjects including Physics/Engineering Science and Basic Mathematics. Holders of Basic Technician Certificate( NTA Level 4) in Information Technology</t>
+          <t xml:space="preserve"> Holders of Basic Technician Certificate( NTA Level 4) in Information</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -6973,17 +6493,17 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ST JOHN'S UNIVERSITY OF TANZANIA (SJ)</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Dodoma</t>
+          <t>Dar es Salaam</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -6991,11 +6511,7 @@
           <t>Ordinary Diploma in Mechanical Engineering</t>
         </is>
       </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate in Secondary Education Examinations (CSEE) with at least four (4) Passes in non-religious Subjects including Physics/Engineering Science, Basic Mathematics and Chemistry; Or Holders of Certificate of Secondary Education (CSEE) with a Minimum of four (4) Passes and National Vocational Award (NVA) Level III or Trade Test Certificate of Grade I in relevant field Offered by VETA accredited Institution; or Holders of General Certificate in Engineering.</t>
-        </is>
-      </c>
+      <c r="E165" t="inlineStr"/>
       <c r="F165" t="inlineStr">
         <is>
           <t>3</t>
@@ -7013,17 +6529,17 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>ST JOHN'S UNIVERSITY OF TANZANIA (SJ)</t>
+          <t>Engineering.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Dodoma</t>
+          <t>Dar es Salaam</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -7033,7 +6549,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examinations (CSEE) with at least Four (4) passes in non-religious subjects including Physics/ Engineering Science, Basic Mathematics and Chemistry; OR General Certificate in Engineering; OR National Vocational Award (NVA) Level III or Trade Test Certificate Grade I in Mechatronics Engineering with pass in Certificate of Secondary Education Examination (CSEE)</t>
+          <t xml:space="preserve"> Admission Requirements</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -7063,7 +6579,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -7071,11 +6587,7 @@
           <t>Diploma in Accountancy</t>
         </is>
       </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate in Accountancy OR Advanced Certificate of Secondary Education with at least one Principal pass and one Subsidiary in Principal subjects</t>
-        </is>
-      </c>
+      <c r="E167" t="inlineStr"/>
       <c r="F167" t="inlineStr">
         <is>
           <t>2</t>
@@ -7093,7 +6605,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>ST. AUGUSTINE UNIVERSITY OF TANZANIA (SAUT)</t>
+          <t>Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -7103,7 +6615,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -7111,11 +6623,7 @@
           <t>Diploma in Business Administration</t>
         </is>
       </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate in Business Administration OR Advanced Certificate of Secondary Education with at least one (1) Principal pass and one (1) Subsidiary in Principal subjects</t>
-        </is>
-      </c>
+      <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr">
         <is>
           <t>2</t>
@@ -7133,7 +6641,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>ST. AUGUSTINE UNIVERSITY OF TANZANIA (SAUT)</t>
+          <t>Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -7143,7 +6651,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -7153,7 +6661,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Holders of Certificate in Law OR Holder of Advanced Certificate of Secondary Education with at least one Principal pass and one Subsidiary in Principal subjects</t>
+          <t xml:space="preserve"> Admission Requirements</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -7183,7 +6691,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -7191,11 +6699,7 @@
           <t>Technician Certificate in Computing, Information and Communication Technology</t>
         </is>
       </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least Four (4) passes in non-religious subjects including Basic Mathematics and English Language; OR National Vocational Award (NVA Level III) or Trade Test Grade II in ICT with a Certificate of Secondary Education Examination (CSEE)</t>
-        </is>
-      </c>
+      <c r="E170" t="inlineStr"/>
       <c r="F170" t="inlineStr">
         <is>
           <t>2</t>
@@ -7213,7 +6717,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>ST. AUGUSTINE UNIVERSITY OF TANZANIA (SAUT)</t>
+          <t>Secondary Education Examination (CSEE)</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -7223,7 +6727,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -7231,11 +6735,7 @@
           <t>Diploma in Law</t>
         </is>
       </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate in Law OR Advanced Certificate of Secondary Education Examinations (ACSEE) with one Principal pass and one Subsidiary in Principal subjects</t>
-        </is>
-      </c>
+      <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr">
         <is>
           <t>2</t>
@@ -7253,7 +6753,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>ST. AUGUSTINE UNIVERSITY OF TANZANIA (SAUT)</t>
+          <t>Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -7263,7 +6763,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -7271,11 +6771,7 @@
           <t>Ordinary Diploma in Accountancy</t>
         </is>
       </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects including passes in Basic Mathematics OR National Vocational Award (NVA) Level III with a Certificate of Secondary Education Examination (CSEE) Holders of Basic Technician Certificate (NTA Level 4) in Accountancy or Advanced Certificate of Secondary Education Examinations Examination (ACSEE) with At Least one Principal Pass and one Subsidiary in Principal Subjects</t>
-        </is>
-      </c>
+      <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr">
         <is>
           <t>3 / 2</t>
@@ -7293,7 +6789,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>ST. AUGUSTINE UNIVERSITY OF TANZANIA (SAUT)</t>
+          <t>Subsidiary in Principal Subjects</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -7303,7 +6799,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -7311,11 +6807,7 @@
           <t>Ordinary Diploma in Business Administration</t>
         </is>
       </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects OR National Vocational Award (NVA) Level III with a Certificate of Secondary Education Examination (CSEE) Holders of Basic Technician Certificate (NTA Level 4) in Business Administration, Marketing and Public Relation or Advanced Certificate of Secondary Education Examination (ACSEE) with one Principal Pass and one Subsidiary in Principal Subjects</t>
-        </is>
-      </c>
+      <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr">
         <is>
           <t>3 / 2</t>
@@ -7333,7 +6825,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>ST. AUGUSTINE UNIVERSITY OF TANZANIA (SAUT)</t>
+          <t>one Subsidiary in Principal Subjects</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -7343,7 +6835,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -7353,7 +6845,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Holders of Certificate of Secondary Education Examination (CSEE) with at least Four (4) passes in non-religious subjects including Basic Mathematics and English Language; OR National Vocational Award (NVA Level III) or Trade Test Grade II in ICT with a Certificate of Secondary Education Examination (CSEE) Holders of Basic Technician Certificate (NTA Level 4) in Computer Science, Information Technology, Business Information Technology or Advanced Certificate of Secondary Education Examination (ACSEE) with one Principal Pass and two Subsidiaries.</t>
+          <t>Holders of Certificate of Secondary Education Examination (CSEE) with</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -7373,7 +6865,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>ST. AUGUSTINE UNIVERSITY OF TANZANIA (SAUT)</t>
+          <t>one Principal Pass and two Subsidiaries.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -7383,7 +6875,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -7393,7 +6885,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects including English Language OR National Vocational Award (NVA) Level III with a Certificate of Secondary Education Examination (CSEE) Holders of Basic Technician Certificate ( NTA Level 4) in Journalism, Mass Communication or Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal Pass and one Subsidiary in Principal Subjects</t>
+          <t xml:space="preserve"> Holders of Basic Technician Certificate ( NTA Level 4) in Journalism,</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -7413,7 +6905,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>ST. AUGUSTINE UNIVERSITY OF TANZANIA (SAUT)</t>
+          <t>Subsidiary in Principal Subjects</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -7423,19 +6915,15 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Ordinary Diploma in Procurement and Supply ST. FRANCIS UNIVERSITY COLLEGE OF HEALTH AND ALLIED SCIENCES (SFUCHAS) (SF) - Private Kilombero District Council - Morogoro</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects Holders of Basic Technician Certificate (NTA Level 4) in Procurement and Supply, Business Administration and Logistics or Advanced Certificate of Secondary Education Examination (ACSEE) with one Principal Pass and one Subsidiary in Principal Subjects.</t>
-        </is>
-      </c>
+          <t>Ordinary Diploma in Procurement and Supply</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr"/>
       <c r="F176" t="inlineStr">
         <is>
           <t>3 / 2</t>
@@ -7453,17 +6941,17 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>ST. AUGUSTINE UNIVERSITY OF TANZANIA (SAUT)</t>
+          <t>ST. FRANCIS UNIVERSITY COLLEGE OF HEALTH AND ALLIED SCIENCES (SFUCHAS) (SF)</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Mwanza</t>
+          <t>Morogoro</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -7471,11 +6959,7 @@
           <t>Ordinary Diploma in Medical Laboratory Sciences</t>
         </is>
       </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with At Least four (4) Passes in non-religious Subjects including Chemistry, Biology, Physics/Engineering sciences/Basic Mathematics and English Language.</t>
-        </is>
-      </c>
+      <c r="E177" t="inlineStr"/>
       <c r="F177" t="inlineStr">
         <is>
           <t>3</t>
@@ -7493,29 +6977,25 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>ST. AUGUSTINE UNIVERSITY OF TANZANIA (SAUT)</t>
+          <t>Language.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Mwanza</t>
+          <t>Morogoro</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Ordinary Diploma in Pharmaceutical Sciences ST. JOSEPH UNIVERSITY COLLEGE OF HEALTH SCIENCES (REG/UHAS/007) - Private Kinondoni Municipal Council - Dar es Salaam</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with At Least four (4) Passes in non-religious Subjects including Chemistry and Biology. A Pass in Basic Mathematics and English Language Is An Added Advantage.</t>
-        </is>
-      </c>
+          <t>Ordinary Diploma in Pharmaceutical Sciences</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr"/>
       <c r="F178" t="inlineStr">
         <is>
           <t>3</t>
@@ -7533,17 +7013,17 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>ST. AUGUSTINE UNIVERSITY OF TANZANIA (SAUT)</t>
+          <t>ST. JOSEPH UNIVERSITY COLLEGE OF HEALTH SCIENCES (REG/UHAS/007)</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Mwanza</t>
+          <t>Dar es Salaam</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -7551,11 +7031,7 @@
           <t>Ordinary Diploma in Nursing and Midwifery</t>
         </is>
       </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects including Chemistry, Biology and Physics/Engineering Sciences. A pass in Basic Mathematics and English Language is an added advantage.</t>
-        </is>
-      </c>
+      <c r="E179" t="inlineStr"/>
       <c r="F179" t="inlineStr">
         <is>
           <t>3</t>
@@ -7573,29 +7049,25 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>ST. AUGUSTINE UNIVERSITY OF TANZANIA (SAUT)</t>
+          <t>Mathematics and English Language is an added advantage.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Mwanza</t>
+          <t>Dar es Salaam</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Ordinary Diploma in Pharmaceutical Sciences STELLA MARIS MTWARA UNIVERSITY COLLEGE (SAM) - Private Mtwara District Council - Mtwara</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with At Least four (4) Passes in non-religious Subjects including Chemistry and Biology. A Pass in Basic Mathematics and English Language Is An Added Advantage.</t>
-        </is>
-      </c>
+          <t>Ordinary Diploma in Pharmaceutical Sciences</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr"/>
       <c r="F180" t="inlineStr">
         <is>
           <t>3</t>
@@ -7613,27 +7085,27 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>ST. AUGUSTINE UNIVERSITY OF TANZANIA (SAUT)</t>
+          <t>STELLA MARIS MTWARA UNIVERSITY COLLEGE (SAM)</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Mwanza</t>
+          <t>Mtwara</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Technician Certificate in Librarianship and Records Management</t>
+          <t>Technician Certificate in Librarianship and</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects</t>
+          <t>Holders of Certificate of Secondary Education Examination (CSEE) with at</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -7653,17 +7125,17 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>ST. AUGUSTINE UNIVERSITY OF TANZANIA (SAUT)</t>
+          <t>Records Management</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Mwanza</t>
+          <t>Mtwara</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -7671,11 +7143,7 @@
           <t>Diploma in Accountancy</t>
         </is>
       </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate in Accountancy OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal pass and one subsidiary in Principal subjects</t>
-        </is>
-      </c>
+      <c r="E182" t="inlineStr"/>
       <c r="F182" t="inlineStr">
         <is>
           <t>2</t>
@@ -7693,17 +7161,17 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>ST. AUGUSTINE UNIVERSITY OF TANZANIA (SAUT)</t>
+          <t>and one subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Mwanza</t>
+          <t>Mtwara</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -7711,11 +7179,7 @@
           <t>Diploma in Business Administration</t>
         </is>
       </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate in Business Administration OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal pass and one subsidiary in Principal subjects</t>
-        </is>
-      </c>
+      <c r="E183" t="inlineStr"/>
       <c r="F183" t="inlineStr">
         <is>
           <t>2</t>
@@ -7733,17 +7197,17 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>ST. AUGUSTINE UNIVERSITY OF TANZANIA (SAUT)</t>
+          <t>pass and one subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Mwanza</t>
+          <t>Mtwara</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -7751,11 +7215,7 @@
           <t>Diploma in Law</t>
         </is>
       </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate in Law OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal pass and one subsidiary in Principal subjects</t>
-        </is>
-      </c>
+      <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr">
         <is>
           <t>2</t>
@@ -7773,17 +7233,17 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>ST. AUGUSTINE UNIVERSITY OF TANZANIA (SAUT)</t>
+          <t>subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Mwanza</t>
+          <t>Mtwara</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -7793,7 +7253,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Holders of Technician Certificate (NTA Level 5) in Librarianship and Records Management</t>
+          <t>Holders of Technician Certificate (NTA Level 5) in Librarianship and</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -7813,17 +7273,17 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>ST. AUGUSTINE UNIVERSITY OF TANZANIA (SAUT)</t>
+          <t>Records Management</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Mwanza</t>
+          <t>Mtwara</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -7831,11 +7291,7 @@
           <t>Ordinary Diploma in Accountancy</t>
         </is>
       </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects including Basic Mathematics OR National Vocational Award (NVA ) Level III with a Certificate of Secondary Education Examination (CSEE) Holders of Basic Technician Certificate (NTA Level 4) in Accountancy OR Advanced Certificate of Secondary Education Examination (ACSEE) with one Principal pass and one Subsidiary in Principal Subjects</t>
-        </is>
-      </c>
+      <c r="E186" t="inlineStr"/>
       <c r="F186" t="inlineStr">
         <is>
           <t>3 / 2</t>
@@ -7853,17 +7309,17 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>ST. AUGUSTINE UNIVERSITY OF TANZANIA (SAUT)</t>
+          <t>one Principal pass and one Subsidiary in Principal Subjects</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Mwanza</t>
+          <t>Mtwara</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -7871,11 +7327,7 @@
           <t>Ordinary Diploma in Business Administration</t>
         </is>
       </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects OR National Vocational Award (NVA) Level III with a Certificate of Secondary Education Examination (CSEE) Holders of Basic Technician Certificate (NTA Level 4) in Business Administration, Human Resource Management, Accounting, Banking and Finance OR Advanced Certificate of Secondary Examination with one Principal pass and one Subsidiary in Principal subjects</t>
-        </is>
-      </c>
+      <c r="E187" t="inlineStr"/>
       <c r="F187" t="inlineStr">
         <is>
           <t>3 / 2</t>
@@ -7893,17 +7345,17 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>ST. AUGUSTINE UNIVERSITY OF TANZANIA (SAUT)</t>
+          <t>Principal pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Mwanza</t>
+          <t>Mtwara</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -7911,11 +7363,7 @@
           <t>Ordinary Diploma in Community Development</t>
         </is>
       </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non- religious subjects Holders of Basic Technician Certificate (NTA Level 4) in Community Development, Social Work, Community Health, Gender, Youth Work, Social Protection OR Advanced Certificate of Secondary Education Examination (ACSEE) with one Principal pass and one Subsidiary in principal subjects</t>
-        </is>
-      </c>
+      <c r="E188" t="inlineStr"/>
       <c r="F188" t="inlineStr">
         <is>
           <t>3 / 2</t>
@@ -7933,17 +7381,17 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>ST. AUGUSTINE UNIVERSITY OF TANZANIA (SAUT)</t>
+          <t>principal subjects</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Mwanza</t>
+          <t>Mtwara</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -7953,7 +7401,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects OR National Vocational Award (NVA) Level III with a Certificate of Secondary Education Examination (CSEE) Holders of Basic Technician Certificate (NTA Level 4) in Procurement and Supply, Logistics, Clearing and Forwarding, Inventory Management OR Advanced Certificate of Secondary Education Examination (ACSEE) with one Principal pass and one Subsidiary pass in Principal subjects</t>
+          <t xml:space="preserve"> Admission Requirements</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -7983,7 +7431,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -7991,11 +7439,7 @@
           <t>Ordinary Diploma in Accounting and Finance</t>
         </is>
       </c>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) Passes in non-religious Subjects Holders of Basic Technician Certificate (NTA Level 4) in Accountancy and Finance OR Advanced Certificate of Secondary Examination Education (ACSEE) with at least one Principal pass and one Subsidiary in Principal subjects</t>
-        </is>
-      </c>
+      <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr">
         <is>
           <t>3 / 2</t>
@@ -8013,7 +7457,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>TEOFILO KISANJI UNIVERSITY</t>
+          <t>Principal subjects</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -8023,7 +7467,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -8031,11 +7475,7 @@
           <t>Ordinary Diploma in Business Administration</t>
         </is>
       </c>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects Holder of Basic Technician Certificate (NTA Level 4) in Business Administration OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal pass and one subsidiary in Principal subjects</t>
-        </is>
-      </c>
+      <c r="E191" t="inlineStr"/>
       <c r="F191" t="inlineStr">
         <is>
           <t>3 / 2</t>
@@ -8053,7 +7493,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>TEOFILO KISANJI UNIVERSITY</t>
+          <t>in Principal subjects</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -8063,7 +7503,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -8071,11 +7511,7 @@
           <t>Ordinary Diploma in Clinical Medicine</t>
         </is>
       </c>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with four (4) passes in non-religious subjects including Chemistry, Biology and Physics/Engineering Sciences. A pass in Basic Mathematics and English Language is an added advantage</t>
-        </is>
-      </c>
+      <c r="E192" t="inlineStr"/>
       <c r="F192" t="inlineStr">
         <is>
           <t>3</t>
@@ -8093,7 +7529,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>TEOFILO KISANJI UNIVERSITY</t>
+          <t>Language is an added advantage</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -8103,19 +7539,15 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Ordinary Diploma in Community Development and Social Work</t>
-        </is>
-      </c>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects Holders of Basic Technician Certificate (NTA Level 4) in Social Work, Gender and Community Development OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one principal pass and one Subsidiary in Principal subjects</t>
-        </is>
-      </c>
+          <t>Ordinary Diploma in Community Development and</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr"/>
       <c r="F193" t="inlineStr">
         <is>
           <t>3 / 2</t>
@@ -8133,7 +7565,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>TEOFILO KISANJI UNIVERSITY</t>
+          <t>pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -8143,7 +7575,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -8151,11 +7583,7 @@
           <t>Ordinary Diploma in Human Resource Management</t>
         </is>
       </c>
-      <c r="E194" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects Holders of Basic Technician Certificate (NTA Level 4) in Human Resource Management OR Advanced Certificate of Secondary Examination (ACSEE) with at least one principal pass and one subsidiary in Principal subjects</t>
-        </is>
-      </c>
+      <c r="E194" t="inlineStr"/>
       <c r="F194" t="inlineStr">
         <is>
           <t>3 / 2</t>
@@ -8173,7 +7601,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>TEOFILO KISANJI UNIVERSITY</t>
+          <t>in Principal subjects</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -8183,7 +7611,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -8193,7 +7621,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Holders of Certificate of Secondary Education Examination (CSEE) with Four (4) passes in non-religious subjects including Basic Mathematics and English Language; OR National Vocational Award (NVA) Level III or Trade Test Grade I with Certificate of Secondary Education Examination (CSEE). Holders of Basic Technician Certificate (NTA Level 4) in Information Technology or Advanced Certificate of Secondary Education Examination (ACSEE) with one Principal Pass and one Subsidiary</t>
+          <t>Holders of Certificate of Secondary Education Examination (CSEE) with</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -8213,7 +7641,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>TEOFILO KISANJI UNIVERSITY</t>
+          <t>Examination (ACSEE) with one Principal Pass and one Subsidiary</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -8223,7 +7651,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -8231,11 +7659,7 @@
           <t>Ordinary Diploma in Journalism</t>
         </is>
       </c>
-      <c r="E196" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects OR National Vocational Award (NVA) Level III with at least two passes in Certificate of Secondary Education Examination (CSEE) Holder of Basic Technician Certificate (NTA Level 4) in Journalism</t>
-        </is>
-      </c>
+      <c r="E196" t="inlineStr"/>
       <c r="F196" t="inlineStr">
         <is>
           <t>3 / 2</t>
@@ -8253,7 +7677,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>TEOFILO KISANJI UNIVERSITY</t>
+          <t>Holder of Basic Technician Certificate (NTA Level 4) in Journalism</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -8263,7 +7687,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -8271,11 +7695,7 @@
           <t>Ordinary Diploma in Law</t>
         </is>
       </c>
-      <c r="E197" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects Holders of Basic Technician Certificate (NTA Level 4) in Law OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one principal pass and one subsidiary in Principal subjects</t>
-        </is>
-      </c>
+      <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr">
         <is>
           <t>3 / 2</t>
@@ -8293,7 +7713,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>TEOFILO KISANJI UNIVERSITY</t>
+          <t>at least one principal pass and one subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -8303,7 +7723,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -8311,11 +7731,7 @@
           <t>Ordinary Diploma in Library, Records and Information Science</t>
         </is>
       </c>
-      <c r="E198" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects Holders Basic Technician Certificate (NTA Level 4) in Records Management and Library and Information Science OR Advanced Certificate of Secondary Examination (ACSEE) one principal pass and one Subsidiary in Principal subjects</t>
-        </is>
-      </c>
+      <c r="E198" t="inlineStr"/>
       <c r="F198" t="inlineStr">
         <is>
           <t>3 / 2</t>
@@ -8333,7 +7749,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>TEOFILO KISANJI UNIVERSITY</t>
+          <t>Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -8343,7 +7759,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -8351,11 +7767,7 @@
           <t>Ordinary Diploma in Nursing and Midwifery</t>
         </is>
       </c>
-      <c r="E199" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects including Chemistry, Biology and Physics/Engineering Sciences. A pass in Basic Mathematics and English Language is an added advantage.</t>
-        </is>
-      </c>
+      <c r="E199" t="inlineStr"/>
       <c r="F199" t="inlineStr">
         <is>
           <t>3</t>
@@ -8373,7 +7785,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>TEOFILO KISANJI UNIVERSITY</t>
+          <t>Mathematics and English Language is an added advantage.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -8383,7 +7795,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -8391,11 +7803,7 @@
           <t>Ordinary Diploma in Pharmaceutical Sciences</t>
         </is>
       </c>
-      <c r="E200" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with At Least four (4) Passes in non-religious Subjects including Chemistry and Biology. A Pass in Basic Mathematics and English Language Is An Added Advantage.</t>
-        </is>
-      </c>
+      <c r="E200" t="inlineStr"/>
       <c r="F200" t="inlineStr">
         <is>
           <t>3</t>
@@ -8413,7 +7821,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>TEOFILO KISANJI UNIVERSITY</t>
+          <t>Language Is An Added Advantage.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -8423,7 +7831,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -8433,7 +7841,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects Holder of Basic Technician Certificate (NTA Level 4) in Procurement and Supply OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one principal pass and one Subsidiary in Principal subjects</t>
+          <t xml:space="preserve"> Admission Requirements</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -8463,7 +7871,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -8471,11 +7879,7 @@
           <t>Basic Technician Certificate in Hotel Operations</t>
         </is>
       </c>
-      <c r="E202" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects</t>
-        </is>
-      </c>
+      <c r="E202" t="inlineStr"/>
       <c r="F202" t="inlineStr">
         <is>
           <t>1</t>
@@ -8493,7 +7897,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>THE STATE UNIVERSITY OF ZANZIBAR (SZ)</t>
+          <t>least four (4) passes in non</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -8503,7 +7907,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -8513,7 +7917,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects</t>
+          <t>Holders of Certificate of Secondary Education Examination (CSEE) with at</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -8533,7 +7937,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>THE STATE UNIVERSITY OF ZANZIBAR (SZ)</t>
+          <t>least four (4) passes in non</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -8543,7 +7947,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -8551,11 +7955,7 @@
           <t>Basic Technician in Hospitality Operation</t>
         </is>
       </c>
-      <c r="E204" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects</t>
-        </is>
-      </c>
+      <c r="E204" t="inlineStr"/>
       <c r="F204" t="inlineStr">
         <is>
           <t>1</t>
@@ -8573,7 +7973,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>THE STATE UNIVERSITY OF ZANZIBAR (SZ)</t>
+          <t>least four (4) passes in non</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -8583,7 +7983,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -8591,11 +7991,7 @@
           <t>Technician Certificate in Front Office Operations</t>
         </is>
       </c>
-      <c r="E205" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects</t>
-        </is>
-      </c>
+      <c r="E205" t="inlineStr"/>
       <c r="F205" t="inlineStr">
         <is>
           <t>2</t>
@@ -8613,7 +8009,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>THE STATE UNIVERSITY OF ZANZIBAR (SZ)</t>
+          <t>least four (4) passes in non</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -8623,7 +8019,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -8631,11 +8027,7 @@
           <t>Technician Certificate in Travel and Tourism Operations</t>
         </is>
       </c>
-      <c r="E206" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examinations (CSEE) with at least four (4) passes in non-religious subject. English Language is an added advantage</t>
-        </is>
-      </c>
+      <c r="E206" t="inlineStr"/>
       <c r="F206" t="inlineStr">
         <is>
           <t>2</t>
@@ -8653,7 +8045,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>THE STATE UNIVERSITY OF ZANZIBAR (SZ)</t>
+          <t>added advantage</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -8663,7 +8055,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -8671,11 +8063,7 @@
           <t>Diploma in Agriculture Production</t>
         </is>
       </c>
-      <c r="E207" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Advanced Certificate of Secondary Education Examination (ACSEE) with at least one (1) principle pass in Biology and one (1) subsidiary pass in Chemistry, Physics, Advanced Mathematics, Agriculture Science and Geography. or Possession of (NTA Level 4) Certificate Award in Crop production.</t>
-        </is>
-      </c>
+      <c r="E207" t="inlineStr"/>
       <c r="F207" t="inlineStr">
         <is>
           <t>2</t>
@@ -8693,7 +8081,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>THE STATE UNIVERSITY OF ZANZIBAR (SZ)</t>
+          <t>Certificate Award in Crop production.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -8703,7 +8091,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -8711,11 +8099,7 @@
           <t>Diploma in Animal Health and Production</t>
         </is>
       </c>
-      <c r="E208" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Certificate of Secondary Education Examination (CSEE) with four (4 Ds) Passes in non-religious Subjects including three (3 Ds) Passes in Biology, Chemistry, Physics/Engineering Sciences, Basic Mathematics, Agriculture Science and Geography; or Possession of National Vocation Award (NVA) Level III or Trade Test Grade I in Animal Husbandry and Possession of Certificate of Secondary Education Examination (CSEE).</t>
-        </is>
-      </c>
+      <c r="E208" t="inlineStr"/>
       <c r="F208" t="inlineStr">
         <is>
           <t>2</t>
@@ -8733,7 +8117,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>THE STATE UNIVERSITY OF ZANZIBAR (SZ)</t>
+          <t>Possession of Certificate of Secondary Education Examination (CSEE).</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -8743,7 +8127,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -8753,7 +8137,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Holders of Advanced Certificate of Secondary Education Examination (ACSEE) with at least (1.5); one (1) principle pass in Biology and one (1) subsidiary pass in Chemistry, Physics, Advanced Mathematics, Agriculture Science and Geography. or Possession of (NTA Level 4) Certificate Award in Crop production.</t>
+          <t>Holders of Advanced Certificate of Secondary Education Examination</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -8773,7 +8157,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>THE STATE UNIVERSITY OF ZANZIBAR (SZ)</t>
+          <t>Certificate Award in Crop production.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -8783,7 +8167,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -8791,11 +8175,7 @@
           <t>Diploma in Financial Administration</t>
         </is>
       </c>
-      <c r="E210" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Technician Certificate (NTA Level 4) in Financial Administration, Accountancy, Banking and Finance OR Advanced Certificate of Secondary Education Examination (ACSEE) with one Principal pass and two Subsidiary in principal subjects</t>
-        </is>
-      </c>
+      <c r="E210" t="inlineStr"/>
       <c r="F210" t="inlineStr">
         <is>
           <t>2</t>
@@ -8813,7 +8193,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>THE STATE UNIVERSITY OF ZANZIBAR (SZ)</t>
+          <t>Principal pass and two Subsidiary in principal subjects</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -8823,7 +8203,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -8831,11 +8211,7 @@
           <t>Diploma in Heritage Management and Tourism</t>
         </is>
       </c>
-      <c r="E211" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects</t>
-        </is>
-      </c>
+      <c r="E211" t="inlineStr"/>
       <c r="F211" t="inlineStr">
         <is>
           <t>3</t>
@@ -8853,7 +8229,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>THE STATE UNIVERSITY OF ZANZIBAR (SZ)</t>
+          <t>least four (4) passes in non</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -8863,7 +8239,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -8871,11 +8247,7 @@
           <t>Diploma in Hospitality and Tourism Management</t>
         </is>
       </c>
-      <c r="E212" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Technician Certificate (NTA Level 5) in Hospitality and Tourism Management, Hotel Management, Museum, Tour Guiding, Archeology, Food preparation, Food Beverage and Front Office</t>
-        </is>
-      </c>
+      <c r="E212" t="inlineStr"/>
       <c r="F212" t="inlineStr">
         <is>
           <t>2</t>
@@ -8893,7 +8265,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>THE STATE UNIVERSITY OF ZANZIBAR (SZ)</t>
+          <t>Archeology, Food preparation, Food Beverage and Front Office</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -8903,7 +8275,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -8911,11 +8283,7 @@
           <t>Diploma in Inclusive and Special Needs Education (Direct Form Four)</t>
         </is>
       </c>
-      <c r="E213" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal pass and one subsidiary pass in Principal subjects</t>
-        </is>
-      </c>
+      <c r="E213" t="inlineStr"/>
       <c r="F213" t="inlineStr">
         <is>
           <t>3</t>
@@ -8933,7 +8301,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>THE STATE UNIVERSITY OF ZANZIBAR (SZ)</t>
+          <t>and one subsidiary pass in Principal subjects</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -8943,7 +8311,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -8951,11 +8319,7 @@
           <t>Diploma in Information Communication Technology with Accounting</t>
         </is>
       </c>
-      <c r="E214" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Basic Certificate in Computer Science, and Information Technology OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal pass and one Subsidiary in principal subjects</t>
-        </is>
-      </c>
+      <c r="E214" t="inlineStr"/>
       <c r="F214" t="inlineStr">
         <is>
           <t>2</t>
@@ -8973,7 +8337,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>THE STATE UNIVERSITY OF ZANZIBAR (SZ)</t>
+          <t>Subsidiary in principal subjects</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -8983,7 +8347,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -8991,11 +8355,7 @@
           <t>Diploma in Information Technology</t>
         </is>
       </c>
-      <c r="E215" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holder of Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal and one subsidiary in science subjects. A Pass in Mathematics for Computer Science is compulsory while English is compulsory for IT applicants (at least in O-level). OR A holder of Certificate in Computing discipline with Programming and Mathematics recognized by NACTE, NECTA or any higher learning Institution with a GPA of at least 3.0, also the candidate should have Four passes at O level one of which be in Mathematics or English.</t>
-        </is>
-      </c>
+      <c r="E215" t="inlineStr"/>
       <c r="F215" t="inlineStr">
         <is>
           <t>2</t>
@@ -9013,7 +8373,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>THE STATE UNIVERSITY OF ZANZIBAR (SZ)</t>
+          <t>Four passes at O level one of which be in Mathematics or English.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -9023,7 +8383,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -9031,11 +8391,7 @@
           <t>Diploma in Language with Education</t>
         </is>
       </c>
-      <c r="E216" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Grade III A Certificate or any recognized Certificate in Education OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal pass and one subsidiary in principal subjects .</t>
-        </is>
-      </c>
+      <c r="E216" t="inlineStr"/>
       <c r="F216" t="inlineStr">
         <is>
           <t>2</t>
@@ -9053,7 +8409,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>THE STATE UNIVERSITY OF ZANZIBAR (SZ)</t>
+          <t>subsidiary in principal subjects .</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -9063,7 +8419,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -9071,11 +8427,7 @@
           <t>Diploma in Librarian and Information Studies</t>
         </is>
       </c>
-      <c r="E217" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate in Librarianship, information sciences, Records Management OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal pass and one subsidiary pass in Principal subjects</t>
-        </is>
-      </c>
+      <c r="E217" t="inlineStr"/>
       <c r="F217" t="inlineStr">
         <is>
           <t>2</t>
@@ -9093,7 +8445,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>THE STATE UNIVERSITY OF ZANZIBAR (SZ)</t>
+          <t>subsidiary pass in Principal subjects</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -9103,7 +8455,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -9111,11 +8463,7 @@
           <t>Diploma in Physical Education and Sports Sciences</t>
         </is>
       </c>
-      <c r="E218" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of a Certificate in Physical Education (PE) or Sports OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal pass and one subsidiary pass in Principal subjects.</t>
-        </is>
-      </c>
+      <c r="E218" t="inlineStr"/>
       <c r="F218" t="inlineStr">
         <is>
           <t>2</t>
@@ -9133,7 +8481,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>THE STATE UNIVERSITY OF ZANZIBAR (SZ)</t>
+          <t>Principal pass and one subsidiary pass in Principal subjects.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -9143,7 +8491,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -9151,11 +8499,7 @@
           <t>Diploma in Physical Education and Sports Sciences</t>
         </is>
       </c>
-      <c r="E219" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four passes (4) in non religious subjects</t>
-        </is>
-      </c>
+      <c r="E219" t="inlineStr"/>
       <c r="F219" t="inlineStr">
         <is>
           <t>3</t>
@@ -9173,7 +8517,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>THE STATE UNIVERSITY OF ZANZIBAR (SZ)</t>
+          <t>least four passes (4) in non religious subjects</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -9183,7 +8527,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -9191,11 +8535,7 @@
           <t>Diploma in Procurement and Supply Management</t>
         </is>
       </c>
-      <c r="E220" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders Certificate in Accountancy, Banking and Finance, Marketing, Clearing and Forwarding ,Projects Planning ,Procurement and Supply, Taxation and Economics OR Advanced Certificate of Secondary Examination one Principal pass and one Subsidiary in principal subjects</t>
-        </is>
-      </c>
+      <c r="E220" t="inlineStr"/>
       <c r="F220" t="inlineStr">
         <is>
           <t>2</t>
@@ -9213,7 +8553,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>THE STATE UNIVERSITY OF ZANZIBAR (SZ)</t>
+          <t>Examination one Principal pass and one Subsidiary in principal subjects</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -9223,7 +8563,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -9231,11 +8571,7 @@
           <t>Diploma in Social Work</t>
         </is>
       </c>
-      <c r="E221" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate in Social Work, Social Welfare, Teaching, Youth Work, Rural Development, Nursing, Community Development OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal pass and one Subsidiary in Principal subjects</t>
-        </is>
-      </c>
+      <c r="E221" t="inlineStr"/>
       <c r="F221" t="inlineStr">
         <is>
           <t>2</t>
@@ -9253,7 +8589,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>THE STATE UNIVERSITY OF ZANZIBAR (SZ)</t>
+          <t>at least one Principal pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -9263,7 +8599,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -9271,11 +8607,7 @@
           <t>Diploma in Social Work</t>
         </is>
       </c>
-      <c r="E222" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects</t>
-        </is>
-      </c>
+      <c r="E222" t="inlineStr"/>
       <c r="F222" t="inlineStr">
         <is>
           <t>3</t>
@@ -9293,7 +8625,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>THE STATE UNIVERSITY OF ZANZIBAR (SZ)</t>
+          <t>least four (4) passes in non</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -9303,7 +8635,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -9311,11 +8643,7 @@
           <t>Ordinary Diploma in Clinical Dentistry</t>
         </is>
       </c>
-      <c r="E223" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects including Chemistry, Biology and Physics/Engineering Sciences</t>
-        </is>
-      </c>
+      <c r="E223" t="inlineStr"/>
       <c r="F223" t="inlineStr">
         <is>
           <t>3</t>
@@ -9333,7 +8661,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>THE STATE UNIVERSITY OF ZANZIBAR (SZ)</t>
+          <t>Chemistry, Biology and Physics/Engineering Sciences</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -9343,7 +8671,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -9351,11 +8679,7 @@
           <t>Ordinary Diploma in Clinical Medicine</t>
         </is>
       </c>
-      <c r="E224" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with four (4) passes in non-religious subjects including Chemistry, Biology and Physics/Engineering Sciences. A pass in Basic Mathematics and English Language is an added advantage.</t>
-        </is>
-      </c>
+      <c r="E224" t="inlineStr"/>
       <c r="F224" t="inlineStr">
         <is>
           <t>3</t>
@@ -9373,7 +8697,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>THE STATE UNIVERSITY OF ZANZIBAR (SZ)</t>
+          <t>Language is an added advantage.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -9383,7 +8707,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -9393,7 +8717,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Holders of Technician Certificate (NTA Level 5) in Environmental Health Sciences</t>
+          <t>Holders of Technician Certificate (NTA Level 5) in Environmental</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -9413,7 +8737,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>THE STATE UNIVERSITY OF ZANZIBAR (SZ)</t>
+          <t>Health Sciences</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -9423,7 +8747,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -9433,7 +8757,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Holders of Technician Certificate (NTA Level 5) in Hospitality Management</t>
+          <t>Holders of Technician Certificate (NTA Level 5) in Hospitality</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -9453,7 +8777,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>THE STATE UNIVERSITY OF ZANZIBAR (SZ)</t>
+          <t>Management</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -9463,7 +8787,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -9471,11 +8795,7 @@
           <t>Ordinary Diploma in Medical Laboratory Sciences</t>
         </is>
       </c>
-      <c r="E227" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with At Least four (4) Passes in non-religious Subjects including Chemistry, Biology, Physics/Engineering sciences/Basic Mathematics and English Language.</t>
-        </is>
-      </c>
+      <c r="E227" t="inlineStr"/>
       <c r="F227" t="inlineStr">
         <is>
           <t>3</t>
@@ -9493,7 +8813,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>THE STATE UNIVERSITY OF ZANZIBAR (SZ)</t>
+          <t>Language.</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -9503,7 +8823,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -9513,7 +8833,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Holders of Technician Certificate (NTA Level 5) in Nursing and Midwifery</t>
+          <t>Holders of Technician Certificate (NTA Level 5) in Nursing and</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
@@ -9533,7 +8853,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>THE STATE UNIVERSITY OF ZANZIBAR (SZ)</t>
+          <t>Midwifery</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -9543,7 +8863,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -9551,11 +8871,7 @@
           <t>Ordinary Diploma in Pharmaceutical Sciences</t>
         </is>
       </c>
-      <c r="E229" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with At Least four (4) Passes in non-religious Subjects including Chemistry and Biology. A Pass in Basic Mathematics and English Language Is An Added Advantage.</t>
-        </is>
-      </c>
+      <c r="E229" t="inlineStr"/>
       <c r="F229" t="inlineStr">
         <is>
           <t>3</t>
@@ -9573,7 +8889,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>THE STATE UNIVERSITY OF ZANZIBAR (SZ)</t>
+          <t>Language Is An Added Advantage.</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -9583,7 +8899,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -9593,7 +8909,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Holders of Technician Certificate (NTA Level 5) in Hotel Management, Front Office, Food Production, Food and Beverage Services, Pastry and Bakery, House Keeping and Laundry TUMAINI UNIVERSITY DAR ES SALAAM COLLEGE (TD) - Private Kinondoni Municipal Council - Dar es Salaam</t>
+          <t xml:space="preserve"> Admission Requirements</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -9613,17 +8929,17 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>THE STATE UNIVERSITY OF ZANZIBAR (SZ)</t>
+          <t>TUMAINI UNIVERSITY DAR ES SALAAM COLLEGE (TD)</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Zanzibar Urban/West</t>
+          <t>Dar es Salaam</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -9631,11 +8947,7 @@
           <t>Diploma in Business Administration and Management</t>
         </is>
       </c>
-      <c r="E231" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holder of Basic Technician Certificate (NTA Level 4) in Business related Studies, Accounting and Banking, Marketing, Procurement and Supply OR Advanced Certificate of Secondary Education Examination (ACSEE) with one Principal pass and one Subsidiary in Principal subjects</t>
-        </is>
-      </c>
+      <c r="E231" t="inlineStr"/>
       <c r="F231" t="inlineStr">
         <is>
           <t>2</t>
@@ -9653,17 +8965,17 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>THE STATE UNIVERSITY OF ZANZIBAR (SZ)</t>
+          <t>one Principal pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Zanzibar Urban/West</t>
+          <t>Dar es Salaam</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -9671,11 +8983,7 @@
           <t>Diploma in Law</t>
         </is>
       </c>
-      <c r="E232" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate in Law OR Advanced Certificate of Secondary Education Examination (ACSEE) with one Principal pass and a subsidiary pass in Principal subjects</t>
-        </is>
-      </c>
+      <c r="E232" t="inlineStr"/>
       <c r="F232" t="inlineStr">
         <is>
           <t>2</t>
@@ -9693,17 +9001,17 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>THE STATE UNIVERSITY OF ZANZIBAR (SZ)</t>
+          <t>subsidiary pass in Principal subjects</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Zanzibar Urban/West</t>
+          <t>Dar es Salaam</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -9713,7 +9021,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Holders of Basic Technician Certificate (NTA Level 4) in Intercultural Relations, Heritage OR Advanced Certificate of Secondary Education Examination (ACSEE) with one Principal pass and one subsidiary in principal subjects TUMAINI UNIVERSITY MAKUMIRA (TUMA) - ARUSHA (MK) - Private Arumeru District Council - Arusha</t>
+          <t xml:space="preserve"> Admission Requirements</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -9733,17 +9041,17 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>THE STATE UNIVERSITY OF ZANZIBAR (SZ)</t>
+          <t>TUMAINI UNIVERSITY MAKUMIRA (TUMA)</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Zanzibar Urban/West</t>
+          <t>Arusha</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -9751,11 +9059,7 @@
           <t>Diploma in Law</t>
         </is>
       </c>
-      <c r="E234" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Law OR Advanced Certificate of Secondary Examination (ACSEE) with at least one Principal pass and one Subsidiary in Principal subjects</t>
-        </is>
-      </c>
+      <c r="E234" t="inlineStr"/>
       <c r="F234" t="inlineStr">
         <is>
           <t>2</t>
@@ -9773,17 +9077,17 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>THE STATE UNIVERSITY OF ZANZIBAR (SZ)</t>
+          <t>Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Zanzibar Urban/West</t>
+          <t>Arusha</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -9791,11 +9095,7 @@
           <t>Ordinary Diploma in Accountancy</t>
         </is>
       </c>
-      <c r="E235" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects OR National Vocational Award (NVA ) Level III with at least two (2) passes in Certificate of Secondary Education Examinations (CSEE) Holder of Basic Technician Certificate (NTA Level 4) in Accountancy, Finance and Banking, Business Administration, Procurement and Supply OR Advanced Certificate of Secondary Education Examination (ACSEE) with one Principal pass and one Subsidiary in Principal subjects</t>
-        </is>
-      </c>
+      <c r="E235" t="inlineStr"/>
       <c r="F235" t="inlineStr">
         <is>
           <t>3 / 2</t>
@@ -9813,17 +9113,17 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>THE STATE UNIVERSITY OF ZANZIBAR (SZ)</t>
+          <t>(ACSEE) with one Principal pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Zanzibar Urban/West</t>
+          <t>Arusha</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -9833,7 +9133,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects OR National Vocational Award (NVA ) Level III with at least two (2) passes in Certificate of Secondary Education Examinations (CSEE) Holders of Basic Technician Certificate (NTA Level 4) in Business Administration, Marketing, Accountancy, Finance and Banking, Human Resource Management, Local Government Administration OR Advanced Certificate of Secondary Education Examination (ACSEE) with one Principal Pass and one Subsidiary in Principal Subjects.</t>
+          <t xml:space="preserve"> Holders of Basic Technician Certificate (NTA Level 4) in Business</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
@@ -9853,17 +9153,17 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>THE STATE UNIVERSITY OF ZANZIBAR (SZ)</t>
+          <t>Principal Pass and one Subsidiary in Principal Subjects.</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Zanzibar Urban/West</t>
+          <t>Arusha</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -9871,11 +9171,7 @@
           <t>Ordinary Diploma in Information Communication Technology</t>
         </is>
       </c>
-      <c r="E237" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least Four (4) passes in non-religious Subjects including a pass in Basic Mathematics and English Language Holders of Basic Technician Certificate (NTA level 4) in Information Communication Technology/Computer Engineering OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least ONE Principal Pass and ONE Subsidiary pass.</t>
-        </is>
-      </c>
+      <c r="E237" t="inlineStr"/>
       <c r="F237" t="inlineStr">
         <is>
           <t>3 / 2</t>
@@ -9893,17 +9189,17 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>THE STATE UNIVERSITY OF ZANZIBAR (SZ)</t>
+          <t>ONE Principal Pass and ONE Subsidiary pass.</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Zanzibar Urban/West</t>
+          <t>Arusha</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -9913,7 +9209,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with four (4) passes in non-religious subject OR National Vocational Award (NVA) Level III or Trade test I with two passes in Certificate of Secondary Education Examination (CSEE) Holders of Basic Technician Certificate (NTA Level 4) in Information Technology (ICT) OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal Pass and one Subsidiary Pass in Principal Subjects.</t>
+          <t xml:space="preserve"> Holders of Basic Technician Certificate (NTA Level 4) in Information</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -9933,17 +9229,17 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>THE STATE UNIVERSITY OF ZANZIBAR (SZ)</t>
+          <t>Subsidiary Pass in Principal Subjects.</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Zanzibar Urban/West</t>
+          <t>Arusha</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -9953,7 +9249,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects OR National Vocational Award (NVA ) Level III with at least two (2) passes in Certificate of Secondary Education Examinations (CSEE) Holders of Basic Technician Certificate (NTA Level 4) in Music, Performing Arts, Grade IIIA Certificate, Sports OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal Pass and one Subsidiary pass in Principal subjects</t>
+          <t xml:space="preserve"> Admission Requirements</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
@@ -9983,7 +9279,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -9991,11 +9287,7 @@
           <t>Diploma in Business Information Technology</t>
         </is>
       </c>
-      <c r="E240" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Technician Certificate (NTA Level 5) in Computer Science (CS), Information Technology (IT), Business Information Technology (BIT) OR Advanced Certificate of Secondary Examination One Principal Pass and one Subsidiary Pass in Principal Subjects.</t>
-        </is>
-      </c>
+      <c r="E240" t="inlineStr"/>
       <c r="F240" t="inlineStr">
         <is>
           <t>2</t>
@@ -10013,7 +9305,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>UNIVERSITY OF ARUSHA</t>
+          <t>Pass and one Subsidiary Pass in Principal Subjects.</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -10023,7 +9315,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -10033,7 +9325,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Holders of Certificate in Education OR Advanced Certificate of Secondary Education Examination With One Principal Pass and one Subsidiary in Principal Subjects.</t>
+          <t>Holders of Certificate in Education OR Advanced Certificate of</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -10053,7 +9345,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>UNIVERSITY OF ARUSHA</t>
+          <t>Subsidiary in Principal Subjects.</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -10063,7 +9355,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -10071,11 +9363,7 @@
           <t>Diploma in Office Administration and Human Resource Management</t>
         </is>
       </c>
-      <c r="E242" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate in Office Administration, Human Resource Management, Local Government Administration, Records Management, Secretarial Studies, Community Development, Business Administration.</t>
-        </is>
-      </c>
+      <c r="E242" t="inlineStr"/>
       <c r="F242" t="inlineStr">
         <is>
           <t>2</t>
@@ -10093,7 +9381,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>UNIVERSITY OF ARUSHA</t>
+          <t>Administration.</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -10103,7 +9391,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -10133,7 +9421,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>UNIVERSITY OF ARUSHA</t>
+          <t>Administration.</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -10143,7 +9431,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -10173,7 +9461,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>UNIVERSITY OF ARUSHA</t>
+          <t>Administration.</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -10183,7 +9471,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -10213,7 +9501,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>UNIVERSITY OF ARUSHA</t>
+          <t>Administration.</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -10223,17 +9511,17 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Ordinary Diploma in Computing and Information Communication Technology</t>
+          <t>Ordinary Diploma in Computing and Information</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Holders of Certificate of Secondary Education Examination (CSEE) with four (4) passes in non-religious subjects including passes in Basic Mathematics and English Language. Holders of Basic Technician Certificate (NTA Level 4) in Computing and Information Technology OR Advanced Certificate of Secondary Education Examination (ACSEE) with ONE principal pass and ONE subsidiary pass.</t>
+          <t>Holders of Certificate of Secondary Education Examination (CSEE) with four (4) passes in non-religious subjects including passes in Basic Mathematics and English Language. Holders of Basic Technician Certificate (NTA Level 4) in Computing and Information Technology OR Advanced Certificate of Secondary</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
@@ -10253,7 +9541,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>UNIVERSITY OF ARUSHA</t>
+          <t>subsidiary pass.</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -10263,7 +9551,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -10273,7 +9561,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects OR National Vocational Award (NVA ) Level III with at least two (2) passes in Certificate of Secondary Education Examinations (CSEE) Holders of Basic Technician Certificate (NTA Level 4) in Procurement and supply, Business Administration, Logistics, Clearing and Forwarding OR Advanced Certificate of Secondary Education Examination (ACSEE) with one Principal Pass and subsidiary in Principal subjects</t>
+          <t xml:space="preserve"> Holders of Basic Technician Certificate (NTA Level 4) in Procurement and</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
@@ -10293,7 +9581,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>UNIVERSITY OF ARUSHA</t>
+          <t>Principal subjects</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -10303,22 +9591,18 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Ordinary Diploma in Records and Archives Management</t>
-        </is>
-      </c>
-      <c r="E248" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least Four (4) passes in Non-religious subjects Holders of Basic Technician Certificate (NTA Level 4) in Record Management, Medical Records, Library and Information Sciences OR Advanced Certificate of Secondary Education Examination (ACSEE) with one Principal pass and Subsidiary pass in Principal subjects UNIVERSITY OF DAR ES SALAAM (UD) - Governmen Kinondoni Municipal Council - Dar es Salaam</t>
-        </is>
-      </c>
+          <t>Ordinary Diploma in Records and Archives</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr"/>
       <c r="F248" t="inlineStr">
         <is>
-          <t>3 / 2 / t</t>
+          <t>3 / 2</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
@@ -10333,17 +9617,17 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>UNIVERSITY OF ARUSHA</t>
+          <t>UNIVERSITY OF DAR ES SALAAM (UD)</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Arusha</t>
+          <t>Dar es Salaam</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -10351,11 +9635,7 @@
           <t>Diploma in Chinees Language</t>
         </is>
       </c>
-      <c r="E249" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Advanced Certificate of Secondary Education Examination with Two Principal Passes in either Language Subjects or Science Subjects.</t>
-        </is>
-      </c>
+      <c r="E249" t="inlineStr"/>
       <c r="F249" t="inlineStr">
         <is>
           <t>2</t>
@@ -10373,17 +9653,17 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>UNIVERSITY OF ARUSHA</t>
+          <t>Subjects.</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Arusha</t>
+          <t>Dar es Salaam</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -10391,11 +9671,7 @@
           <t>Diploma in Computer Science</t>
         </is>
       </c>
-      <c r="E250" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate in Computer Sciences, Computer Engineering OR Advanced Certificate of Secondary Education Examination (ACSEE) with One Principal Pass and One Subsidiary Pass in Principal Subjects</t>
-        </is>
-      </c>
+      <c r="E250" t="inlineStr"/>
       <c r="F250" t="inlineStr">
         <is>
           <t>2</t>
@@ -10413,17 +9689,17 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>UNIVERSITY OF ARUSHA</t>
+          <t>One Principal Pass and One Subsidiary Pass in Principal Subjects</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Arusha</t>
+          <t>Dar es Salaam</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -10431,11 +9707,7 @@
           <t>Diploma in Journalism</t>
         </is>
       </c>
-      <c r="E251" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate in Journalism, Mass Communication, Public Relation OR Advanced Certificate of Secondary Education Examination (ACSEE) with one Principal pass and one Subsidiary in Principal subjects UNIVERSITY OF DODOMA (DM) - Government Dodoma Municipal Council - Dodoma</t>
-        </is>
-      </c>
+      <c r="E251" t="inlineStr"/>
       <c r="F251" t="inlineStr">
         <is>
           <t>2</t>
@@ -10453,17 +9725,17 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>UNIVERSITY OF ARUSHA</t>
+          <t>UNIVERSITY OF DODOMA (DM)</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Arusha</t>
+          <t>Dodoma</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -10471,11 +9743,7 @@
           <t>Diploma in Accounting and Finance</t>
         </is>
       </c>
-      <c r="E252" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Basic Technician Certificate (NTA Level 4) in Accountancy OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal pass and one Subsidiary in Principal Subject.</t>
-        </is>
-      </c>
+      <c r="E252" t="inlineStr"/>
       <c r="F252" t="inlineStr">
         <is>
           <t>2</t>
@@ -10493,17 +9761,17 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>UNIVERSITY OF ARUSHA</t>
+          <t>Subject.</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Arusha</t>
+          <t>Dodoma</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -10513,7 +9781,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Holders of Basic Technician Certificate (NTA Level 4) in Business Information Technology, Information Technology, Computer Sciences/Engineering OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal Pass and one Subsidiary in principal subjects.</t>
+          <t>Holders of Basic Technician Certificate (NTA Level 4) in Business</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -10533,17 +9801,17 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>UNIVERSITY OF ARUSHA</t>
+          <t>Subsidiary in principal subjects.</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Arusha</t>
+          <t>Dodoma</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -10553,7 +9821,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Holders of Basic Technician Certificate (NTA Level 4) in Computer Sciences/Engineering OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal Pass and one Subsidiary in principal subjects.</t>
+          <t>Holders of Basic Technician Certificate (NTA Level 4) in Computer</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
@@ -10573,17 +9841,17 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>UNIVERSITY OF ARUSHA</t>
+          <t>Subsidiary in principal subjects.</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Arusha</t>
+          <t>Dodoma</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -10591,11 +9859,7 @@
           <t>Diploma in Education (chemistry and Biology)</t>
         </is>
       </c>
-      <c r="E255" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Advanced Certificate of Secondary Education Examination (ACSEE) with one Principal pass and Subsidiary pass in Chemistry and Biology.</t>
-        </is>
-      </c>
+      <c r="E255" t="inlineStr"/>
       <c r="F255" t="inlineStr">
         <is>
           <t>2</t>
@@ -10613,17 +9877,17 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>UNIVERSITY OF ARUSHA</t>
+          <t>Biology.</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Arusha</t>
+          <t>Dodoma</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -10631,11 +9895,7 @@
           <t>Diploma in Education (mathematics and Ict)</t>
         </is>
       </c>
-      <c r="E256" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Advanced Certificate of Secondary Education Examination (ACSEE) with one Principal pass must be in Advanced Mathematics.</t>
-        </is>
-      </c>
+      <c r="E256" t="inlineStr"/>
       <c r="F256" t="inlineStr">
         <is>
           <t>2</t>
@@ -10653,17 +9913,17 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>UNIVERSITY OF ARUSHA</t>
+          <t>(ACSEE) with one Principal pass must be in Advanced Mathematics.</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Arusha</t>
+          <t>Dodoma</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -10671,11 +9931,7 @@
           <t>Diploma in Educational Technology</t>
         </is>
       </c>
-      <c r="E257" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Advanced Certificate of Secondary Education Examination (ACSEE) with one principal pass in science subjects and subsidiary pass in principal subjects.</t>
-        </is>
-      </c>
+      <c r="E257" t="inlineStr"/>
       <c r="F257" t="inlineStr">
         <is>
           <t>2</t>
@@ -10693,17 +9949,17 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>UNIVERSITY OF ARUSHA</t>
+          <t>principal subjects.</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Arusha</t>
+          <t>Dodoma</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -10711,11 +9967,7 @@
           <t>Diploma in Film Production</t>
         </is>
       </c>
-      <c r="E258" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Basic Technician Certificate in Film and TV Production, Performing and visual Art, Education, Journalism, Music, Arts and Sports, Education OR Advanced Certificate of Secondary Examination (ACSEE) with at least one Principal pass and one Subsidiary in principal subjects.</t>
-        </is>
-      </c>
+      <c r="E258" t="inlineStr"/>
       <c r="F258" t="inlineStr">
         <is>
           <t>2</t>
@@ -10733,17 +9985,17 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>UNIVERSITY OF ARUSHA</t>
+          <t>(ACSEE) with at least one Principal pass and one Subsidiary in principal subjects.</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Arusha</t>
+          <t>Dodoma</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -10773,17 +10025,17 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>UNIVERSITY OF ARUSHA</t>
+          <t>(ACSEE) with at least one Principal pass and one Subsidiary in principal subjects.</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Arusha</t>
+          <t>Dodoma</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -10813,17 +10065,17 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>UNIVERSITY OF ARUSHA</t>
+          <t>(ACSEE) with at least one Principal pass and one Subsidiary in principal subjects.</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Arusha</t>
+          <t>Dodoma</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -10853,17 +10105,17 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>UNIVERSITY OF ARUSHA</t>
+          <t>(ACSEE) with at least one Principal pass and one Subsidiary in principal subjects.</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Arusha</t>
+          <t>Dodoma</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -10871,11 +10123,7 @@
           <t>Diploma in Information and Telecommunication Technology</t>
         </is>
       </c>
-      <c r="E262" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Advanced Certificate of Secondary Education Examination (ACSEE) with one Principal pass and Subsidiary pass in science subjects.</t>
-        </is>
-      </c>
+      <c r="E262" t="inlineStr"/>
       <c r="F262" t="inlineStr">
         <is>
           <t>2</t>
@@ -10893,17 +10141,17 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>UNIVERSITY OF ARUSHA</t>
+          <t>(ACSEE) with one Principal pass and Subsidiary pass in science subjects.</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Arusha</t>
+          <t>Dodoma</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -10911,11 +10159,7 @@
           <t>Diploma in Information Communication Technology</t>
         </is>
       </c>
-      <c r="E263" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Advanced Certificate of Secondary Education Examination (ACSEE) with at least one principal pass and one subsidiary in Science subjects. OR Certificate in Computer Science, Computing and Information Communication Technology, Information Technology or Business Information Technology with an average of ?B? grade PLUS at least four passes in non-religious subjects at O-Level.</t>
-        </is>
-      </c>
+      <c r="E263" t="inlineStr"/>
       <c r="F263" t="inlineStr">
         <is>
           <t>2</t>
@@ -10933,17 +10177,17 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>UNIVERSITY OF ARUSHA</t>
+          <t>passes in non</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Arusha</t>
+          <t>Dodoma</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -10951,11 +10195,7 @@
           <t>Diploma in Mass Communication</t>
         </is>
       </c>
-      <c r="E264" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least Four (4) Passes in Non-religious subjects.</t>
-        </is>
-      </c>
+      <c r="E264" t="inlineStr"/>
       <c r="F264" t="inlineStr">
         <is>
           <t>2</t>
@@ -10973,17 +10213,17 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>UNIVERSITY OF ARUSHA</t>
+          <t>least Four (4) Passes in Non</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Arusha</t>
+          <t>Dodoma</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -10993,7 +10233,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Holders of Technician Certificate (NTA Level 5) in Medical Laboratory Sciences</t>
+          <t>Holders of Technician Certificate (NTA Level 5) in Medical Laboratory</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
@@ -11013,17 +10253,17 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>UNIVERSITY OF ARUSHA</t>
+          <t>Sciences</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Arusha</t>
+          <t>Dodoma</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -11031,11 +10271,7 @@
           <t>Diploma in Mineral Exploration and Mining Geology</t>
         </is>
       </c>
-      <c r="E266" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Advanced Certificate of Secondary Education Examination (CSEE) with one principal pass and one subsidiary pass in the following subjects Advanced Mathematics, Physics or Chemistry</t>
-        </is>
-      </c>
+      <c r="E266" t="inlineStr"/>
       <c r="F266" t="inlineStr">
         <is>
           <t>2</t>
@@ -11053,17 +10289,17 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>UNIVERSITY OF ARUSHA</t>
+          <t>subjects Advanced Mathematics, Physics or Chemistry</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Arusha</t>
+          <t>Dodoma</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -11073,7 +10309,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Holders of Technician Certificate (NTA Level 5) in Nursing and Midwifery</t>
+          <t>Holders of Technician Certificate (NTA Level 5) in Nursing and</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
@@ -11093,17 +10329,17 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>UNIVERSITY OF ARUSHA</t>
+          <t>Midwifery</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Arusha</t>
+          <t>Dodoma</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -11111,11 +10347,7 @@
           <t>Diploma in Pharmacy</t>
         </is>
       </c>
-      <c r="E268" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at four (4) passes including credit Passes in Science Subjects Physics or Basic Mathematics, Chemistry and Biology.</t>
-        </is>
-      </c>
+      <c r="E268" t="inlineStr"/>
       <c r="F268" t="inlineStr">
         <is>
           <t>3</t>
@@ -11133,17 +10365,17 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>UNIVERSITY OF ARUSHA</t>
+          <t>Physics or Basic Mathematics, Chemistry and Biology.</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Arusha</t>
+          <t>Dodoma</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -11151,11 +10383,7 @@
           <t>Diploma in Procurement and Logistics Management</t>
         </is>
       </c>
-      <c r="E269" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Basic Technician Certificate (NTA Level 4) in Procurement and Logistic Management, Business Administration, Logistics, Clearing and Forwarding OR Holders of Advanced Certificate of Secondary Education Examination (ACSEE) with One Principal Pass and one Subsidiary in principal subjects.</t>
-        </is>
-      </c>
+      <c r="E269" t="inlineStr"/>
       <c r="F269" t="inlineStr">
         <is>
           <t>2</t>
@@ -11173,17 +10401,17 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>UNIVERSITY OF ARUSHA</t>
+          <t>Subsidiary in principal subjects.</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Arusha</t>
+          <t>Dodoma</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -11193,7 +10421,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Holders of Basic Technician Certificate (NTA Level 4) in Project Planning and Management, Procurement and Logistic Management, Business Administration, Logistics, Clearing and Forwarding, Public Administration, Local Government Administration OR Advanced Certificate of Secondary Education Examination (ACSEE) with One Principal Pass and one Subsidiary pass in principal subjects</t>
+          <t>Holders of Basic Technician Certificate (NTA Level 4) in Project</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
@@ -11213,17 +10441,17 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>UNIVERSITY OF ARUSHA</t>
+          <t>Principal Pass and one Subsidiary pass in principal subjects</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Arusha</t>
+          <t>Dodoma</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -11231,11 +10459,7 @@
           <t>Diploma in Public Administration and Management</t>
         </is>
       </c>
-      <c r="E271" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Basic Technician Certificate (NTA Level 4 ) in Public Administration and Management, Human Resource Management, Local Government Administration OR Advanced Certificate of Secondary Education Examination with one Principal Pass and two Subsidiary in principal Subjects.</t>
-        </is>
-      </c>
+      <c r="E271" t="inlineStr"/>
       <c r="F271" t="inlineStr">
         <is>
           <t>2</t>
@@ -11253,17 +10477,17 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>UNIVERSITY OF ARUSHA</t>
+          <t>principal Subjects.</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Arusha</t>
+          <t>Dodoma</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -11273,7 +10497,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Holders of Basic Technician Certificate (NTA Level 4) in Statistics or Economics</t>
+          <t>Holders of Basic Technician Certificate (NTA Level 4) in Statistics or</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
@@ -11293,17 +10517,17 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>UNIVERSITY OF ARUSHA</t>
+          <t>Economics</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Arusha</t>
+          <t>Dodoma</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -11313,7 +10537,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects including Chemistry, Biology and Physics/Engineering Sciences. A pass in Basic Mathematics and English Language is an added advantage.</t>
+          <t xml:space="preserve"> Admission Requirements</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
@@ -11343,7 +10567,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -11351,11 +10575,7 @@
           <t>Diploma in Accountancy</t>
         </is>
       </c>
-      <c r="E274" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holder of Certificate in Accountancy or Advanced Certificate of Secondary Education Examination (ACSEE) with one Principal Pass and one Subsidiary in Principal Subjects</t>
-        </is>
-      </c>
+      <c r="E274" t="inlineStr"/>
       <c r="F274" t="inlineStr">
         <is>
           <t>2</t>
@@ -11373,7 +10593,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>UNIVERSITY OF IRINGA (IU)</t>
+          <t>one Subsidiary in Principal Subjects</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -11383,7 +10603,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -11391,11 +10611,7 @@
           <t>Diploma in Accounting and Finance</t>
         </is>
       </c>
-      <c r="E275" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders Certificate in Accountancy, Business Administration OR of Advanced Certificate of Secondary Education Examination(ACSEE) with One Principal Pass and one Subsidiary in Relevant Subjects.</t>
-        </is>
-      </c>
+      <c r="E275" t="inlineStr"/>
       <c r="F275" t="inlineStr">
         <is>
           <t>2</t>
@@ -11413,7 +10629,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>UNIVERSITY OF IRINGA (IU)</t>
+          <t>One Principal Pass and one Subsidiary in Relevant Subjects.</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -11423,7 +10639,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -11431,11 +10647,7 @@
           <t>Diploma in Business Administration</t>
         </is>
       </c>
-      <c r="E276" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holder of Certificate in Business Administration, Marketing or Advanced Certificate of Secondary Education Examination (ACSEE) with One Principal Pass and one Subsidiary in Relevant Subjects.</t>
-        </is>
-      </c>
+      <c r="E276" t="inlineStr"/>
       <c r="F276" t="inlineStr">
         <is>
           <t>2</t>
@@ -11453,7 +10665,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>UNIVERSITY OF IRINGA (IU)</t>
+          <t>Principal Pass and one Subsidiary in Relevant Subjects.</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -11463,7 +10675,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -11471,11 +10683,7 @@
           <t>Diploma in Community Development</t>
         </is>
       </c>
-      <c r="E277" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate in Community Development, Gender, Social Work, Youth Work, Certificate from Tanzania Police School - Moshi, Tanzania Police Staff College - Kidatu, zanzibar Police College Zanzibar and above or Advanced Certificate of Secondary Education Examination (ACSEE) with One Principal Pass and one Subsidiary in Principal Subjects.</t>
-        </is>
-      </c>
+      <c r="E277" t="inlineStr"/>
       <c r="F277" t="inlineStr">
         <is>
           <t>2</t>
@@ -11493,7 +10701,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>UNIVERSITY OF IRINGA (IU)</t>
+          <t>Principal Subjects.</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -11503,7 +10711,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -11511,11 +10719,7 @@
           <t>Diploma in Counseling Psychology</t>
         </is>
       </c>
-      <c r="E278" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders Certificate in Community Development, Nursing, Counseling , Certificate from Tanzania Police School - Moshi, Tanzania Police Staff College - Kidatu, Zanzibar Police College - Zanzibar or Advanced Certificate of Secondary Education Examination (ACSEE) with One Principal Pass and one Subsidiary in Principal Subjects.</t>
-        </is>
-      </c>
+      <c r="E278" t="inlineStr"/>
       <c r="F278" t="inlineStr">
         <is>
           <t>2</t>
@@ -11533,7 +10737,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>UNIVERSITY OF IRINGA (IU)</t>
+          <t>Principal Pass and one Subsidiary in Principal Subjects.</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -11543,7 +10747,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -11551,11 +10755,7 @@
           <t>Diploma in Human Resource Management</t>
         </is>
       </c>
-      <c r="E279" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holder of Certificate in Human Resource Management, Local Government Administration with OR Advanced Certificate of Secondary Education Examination (ACSEE) with One Principal Pass and one Subsidiary pass Principal Subjects.</t>
-        </is>
-      </c>
+      <c r="E279" t="inlineStr"/>
       <c r="F279" t="inlineStr">
         <is>
           <t>2</t>
@@ -11573,7 +10773,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>UNIVERSITY OF IRINGA (IU)</t>
+          <t>Subsidiary pass Principal Subjects.</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -11583,7 +10783,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -11593,7 +10793,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Holders Certificate in Computer Science (CS), Information Technology (IT), Business Information Technology (BIT), Records, Achieves and Information Management, Certificate in Education (Grade III A); OR Advanced Certificate of Secondary Examination (ACSEE) with One Principal Pass and Two Subsidiary Pass</t>
+          <t>Holders Certificate in Computer Science (CS), Information Technology</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
@@ -11613,7 +10813,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>UNIVERSITY OF IRINGA (IU)</t>
+          <t>Principal Pass and Two Subsidiary Pass</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -11623,7 +10823,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -11631,11 +10831,7 @@
           <t>Diploma in Journalism</t>
         </is>
       </c>
-      <c r="E281" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holder of Certificate in Journalism, Public Relation, Mass Communication or Advanced Certificate of Secondary Education Examination (ACSEE) with One Principal Pass and one Subsidiary pass in Principal Subjects.</t>
-        </is>
-      </c>
+      <c r="E281" t="inlineStr"/>
       <c r="F281" t="inlineStr">
         <is>
           <t>2</t>
@@ -11653,7 +10849,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>UNIVERSITY OF IRINGA (IU)</t>
+          <t>with One Principal Pass and one Subsidiary pass in Principal Subjects.</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -11663,7 +10859,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -11673,7 +10869,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Holder of Certificate in Law, international Relation,Certificate from Tanzania Police School - Moshi, Tanzania Police Staff College - Kidatu, Zanzibar Police College - Zanzibar and above OR Holder of Advanced Certificate of Secondary Education Examination(ACSEE) with One Principal Pass and one Subsidiary in Principal Subjects.</t>
+          <t>Holder of Certificate in Law, international Relation,Certificate from</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
@@ -11693,7 +10889,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>UNIVERSITY OF IRINGA (IU)</t>
+          <t>Principal Pass and one Subsidiary in Principal Subjects.</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -11703,7 +10899,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -11711,11 +10907,7 @@
           <t>Diploma in Leisure and Tourism Studies</t>
         </is>
       </c>
-      <c r="E283" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate in Leisure and Tourism Studies,Tour Guide, Wildlife Management ,Wildlife Tourism OR Advanced Certificate of Secondary Education Examination (ACSEE) with One Principal Pass and one Subsidiary in Principal Subjects.</t>
-        </is>
-      </c>
+      <c r="E283" t="inlineStr"/>
       <c r="F283" t="inlineStr">
         <is>
           <t>2</t>
@@ -11733,7 +10925,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>UNIVERSITY OF IRINGA (IU)</t>
+          <t>one Subsidiary in Principal Subjects.</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -11743,7 +10935,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -11751,11 +10943,7 @@
           <t>Diploma in Procurement and Material Management</t>
         </is>
       </c>
-      <c r="E284" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders Certificate in Procurement and Supply, Logistics managements OR Advanced Certificate of Secondary Education Examination(ACSEE) with at least one Principal Pass and one Subsidiary in Principal Subjects</t>
-        </is>
-      </c>
+      <c r="E284" t="inlineStr"/>
       <c r="F284" t="inlineStr">
         <is>
           <t>2</t>
@@ -11773,7 +10961,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>UNIVERSITY OF IRINGA (IU)</t>
+          <t>Subjects</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -11783,7 +10971,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -11793,7 +10981,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with At Least four (4) Passes including Religious Subjects.</t>
+          <t xml:space="preserve"> Admission Requirements</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
@@ -11813,7 +11001,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>ZANZIBAR UNIVERSITY (ZU)</t>
+          <t>Distric</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -11823,22 +11011,18 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Private Kusini</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>Diploma in Arts with Education Diploma in Clinical Medicine</t>
-        </is>
-      </c>
-      <c r="E286" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects with division three</t>
-        </is>
-      </c>
+          <t>Diploma in Arts with Education</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr"/>
       <c r="F286" t="inlineStr">
         <is>
-          <t>2 / 3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
@@ -11853,7 +11037,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>ZANZIBAR UNIVERSITY (ZU)</t>
+          <t>Diploma in Clinical Medicine</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -11863,7 +11047,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Private Kusini</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D287" t="inlineStr"/>
@@ -11885,7 +11069,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>ZANZIBAR UNIVERSITY (ZU)</t>
+          <t>Diploma in Clinical Medicine</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -11895,7 +11079,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Private Kusini</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -11905,7 +11089,7 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Holders of Basic Technician Certificate (NTA Level 4) in Community Development, Community Health, Social Work, Gender, Youth Economics OR Advanced Certificate Of Secondary Education Examination (ACSEE) with at least one Principal pass and one Subsidiary in Principal subjects</t>
+          <t>Holders of Basic Technician Certificate (NTA Level 4) in Community</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
@@ -11925,7 +11109,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>ZANZIBAR UNIVERSITY (ZU)</t>
+          <t>Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -11935,7 +11119,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Private Kusini</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -11943,11 +11127,7 @@
           <t>Diploma in Counselling and Psychology</t>
         </is>
       </c>
-      <c r="E289" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects OR National Vocational Award (NVA) Level III with a Certificate of Secondary Education Examination (CSEE)</t>
-        </is>
-      </c>
+      <c r="E289" t="inlineStr"/>
       <c r="F289" t="inlineStr">
         <is>
           <t>3</t>
@@ -11965,7 +11145,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>ZANZIBAR UNIVERSITY (ZU)</t>
+          <t>Education Examination (CSEE)</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -11975,7 +11155,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Private Kusini</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -11983,11 +11163,7 @@
           <t>Diploma in Law</t>
         </is>
       </c>
-      <c r="E290" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Basic Technician Certificate in Law; OR Advance Certificate of Secondary Education Examination (ACSEE) with at least one Principal Pass and one Subsidiary in Principal subjects</t>
-        </is>
-      </c>
+      <c r="E290" t="inlineStr"/>
       <c r="F290" t="inlineStr">
         <is>
           <t>2</t>
@@ -12005,7 +11181,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>ZANZIBAR UNIVERSITY (ZU)</t>
+          <t>Principal Pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -12015,7 +11191,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Private Kusini</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -12025,7 +11201,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Holders of Certificate of Secondary Education Examination with Division three with at least two passes in science subjects (Physics, Chemistry and Biology)</t>
+          <t>Holders of Certificate of Secondary Education Examination with</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
@@ -12045,7 +11221,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>ZANZIBAR UNIVERSITY (ZU)</t>
+          <t>Chemistry and Biology)</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -12055,7 +11231,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Private Kusini</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -12063,11 +11239,7 @@
           <t>Ordinary Diploma in Accountancy</t>
         </is>
       </c>
-      <c r="E292" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination with at least four (4) passes in non-religious subjects including Basic Mathematics Holders of Basic Technician Certificate (NTA Level 4) in Accountancy OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal pass and one Subsidiary in Principal subjects</t>
-        </is>
-      </c>
+      <c r="E292" t="inlineStr"/>
       <c r="F292" t="inlineStr">
         <is>
           <t>3 / 2</t>
@@ -12085,7 +11257,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>ZANZIBAR UNIVERSITY (ZU)</t>
+          <t>at least one Principal pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -12095,7 +11267,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Private Kusini</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -12103,11 +11275,7 @@
           <t>Ordinary Diploma in Business Administration</t>
         </is>
       </c>
-      <c r="E293" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination with at least four (4) passes in non-religious subjects Holders of Basic Technician Certificate (NTA Level 4) in Business Administration, Accountancy, Marketing, Procurement and Supply OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal pass and one Subsidiary in Principal subjects</t>
-        </is>
-      </c>
+      <c r="E293" t="inlineStr"/>
       <c r="F293" t="inlineStr">
         <is>
           <t>3 / 2</t>
@@ -12125,7 +11293,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>ZANZIBAR UNIVERSITY (ZU)</t>
+          <t>at least one Principal pass and one Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -12135,7 +11303,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Private Kusini</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -12143,11 +11311,7 @@
           <t>Ordinary Diploma in Clinical Medicine</t>
         </is>
       </c>
-      <c r="E294" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with four (4) passes in non-religious subjects including Chemistry, Biology and Physics/Engineering Sciences. A pass in Basic Mathematics and English Language is an added advantage.</t>
-        </is>
-      </c>
+      <c r="E294" t="inlineStr"/>
       <c r="F294" t="inlineStr">
         <is>
           <t>3</t>
@@ -12165,7 +11329,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>ZANZIBAR UNIVERSITY (ZU)</t>
+          <t>Language is an added advantage.</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -12175,7 +11339,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Private Kusini</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -12185,7 +11349,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects Holders of Basic Technician Certificate (NTA Level 4) in Community Development OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal pass and one Subsidiary in Principal subjects</t>
+          <t xml:space="preserve"> Holders of Basic Technician Certificate (NTA Level 4) in Community</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
@@ -12205,7 +11369,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>ZANZIBAR UNIVERSITY (ZU)</t>
+          <t>Subsidiary in Principal subjects</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -12215,7 +11379,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Private Kusini</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -12223,11 +11387,7 @@
           <t>Ordinary Diploma in Computing and Information Technology</t>
         </is>
       </c>
-      <c r="E296" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious Subjects Include passes in Basic Mathematics and English Language. Holders of Basic Technician Certificate (NTA Level 4) in Information and Communication Technology (ICT) related field or its equivalence recognised by NACTE OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least ONE Principal Pass and ONE Subsidiary Pass in Principal Subjects.</t>
-        </is>
-      </c>
+      <c r="E296" t="inlineStr"/>
       <c r="F296" t="inlineStr">
         <is>
           <t>3 / 2</t>
@@ -12245,7 +11405,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>ZANZIBAR UNIVERSITY (ZU)</t>
+          <t>Subsidiary Pass in Principal Subjects.</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -12255,7 +11415,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Private Kusini</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -12263,11 +11423,7 @@
           <t>Ordinary Diploma in Medical Laboratory Sciences</t>
         </is>
       </c>
-      <c r="E297" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with At Least four (4) Passes in non-religious Subjects including Chemistry, Biology, Physics/Engineering sciences/Basic Mathematics and English Language.</t>
-        </is>
-      </c>
+      <c r="E297" t="inlineStr"/>
       <c r="F297" t="inlineStr">
         <is>
           <t>3</t>
@@ -12285,7 +11441,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>ZANZIBAR UNIVERSITY (ZU)</t>
+          <t>Copyright © 2025 NACTVET</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -12295,7 +11451,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Private Kusini</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -12303,11 +11459,7 @@
           <t>Ordinary Diploma in Nursing and Midwifery</t>
         </is>
       </c>
-      <c r="E298" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects including Chemistry, Biology and Physics/Engineering Sciences. A pass in Basic Mathematics and English Language is an added advantage.</t>
-        </is>
-      </c>
+      <c r="E298" t="inlineStr"/>
       <c r="F298" t="inlineStr">
         <is>
           <t>3</t>
@@ -12325,7 +11477,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>ZANZIBAR UNIVERSITY (ZU)</t>
+          <t>Mathematics and English Language is an added advantage.</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -12335,7 +11487,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Private Kusini</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -12343,11 +11495,7 @@
           <t>Ordinary Diploma in Procurement and Supply</t>
         </is>
       </c>
-      <c r="E299" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Holders of Certificate of Secondary Education Examination (CSEE) with at least four (4) passes in non-religious subjects Holders of Basic Technician Certificate (NTA Level 4) in Procurement and Supply, Clearing and Forwarding, Logistics Management OR Advanced Certificate of Secondary Education Examination (ACSEE) with at least one Principal pass and one Subsidiary in Principal subjects</t>
-        </is>
-      </c>
+      <c r="E299" t="inlineStr"/>
       <c r="F299" t="inlineStr">
         <is>
           <t>3 / 2</t>
